--- a/classement_whist_2023_2025.xlsx
+++ b/classement_whist_2023_2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a20b8382962b136a/Bureau/loisir/whist/projet_application_streamlit/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="616" documentId="8_{848EF4F6-53E4-4B52-9417-5BFB5A888B23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4F2FDA5E-0541-46C9-93D2-967680491CE8}"/>
+  <xr:revisionPtr revIDLastSave="646" documentId="8_{848EF4F6-53E4-4B52-9417-5BFB5A888B23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DF2FE595-AF0A-41C8-ABD6-BC9733E1F5A4}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="91">
   <si>
     <t>global</t>
   </si>
@@ -585,10 +585,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="8">
@@ -802,10 +802,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1156,7 +1152,7 @@
       </c>
       <c r="C1" s="1">
         <f t="shared" ref="C1" si="0">IF(D2&gt;19,C2/D2,"/")</f>
-        <v>5.3651960784313726</v>
+        <v>5.3470873786407767</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -1170,7 +1166,7 @@
       </c>
       <c r="G1" s="1">
         <f t="shared" ref="G1" si="2">IF(H2&gt;19,G2/H2,"/")</f>
-        <v>7.2040082219938331</v>
+        <v>7.2250755287009065</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>2</v>
@@ -1191,7 +1187,7 @@
       </c>
       <c r="M1" s="1">
         <f t="shared" ref="M1" si="5">IF(N2&gt;19,M2/N2,"/")</f>
-        <v>5.3588785046728971</v>
+        <v>5.3621621621621625</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>2</v>
@@ -1205,7 +1201,7 @@
       </c>
       <c r="Q1" s="1">
         <f t="shared" ref="Q1" si="7">IF(R2&gt;19,Q2/R2,"/")</f>
-        <v>6.0048780487804878</v>
+        <v>5.948356807511737</v>
       </c>
       <c r="R1" s="1" t="s">
         <v>2</v>
@@ -1219,7 +1215,7 @@
       </c>
       <c r="U1" s="1">
         <f t="shared" ref="U1" si="9">IF(V2&gt;19,U2/V2,"/")</f>
-        <v>3.0192307692307692</v>
+        <v>3</v>
       </c>
       <c r="V1" s="1" t="s">
         <v>2</v>
@@ -1240,7 +1236,7 @@
       </c>
       <c r="AA1" s="1">
         <f t="shared" ref="AA1" si="12">IF(AB2&gt;19,AA2/AB2,"/")</f>
-        <v>4.1205128205128201</v>
+        <v>4.2391304347826084</v>
       </c>
       <c r="AB1" s="1" t="s">
         <v>2</v>
@@ -1357,11 +1353,11 @@
       </c>
       <c r="C2" s="1">
         <f>C4+C6+C8</f>
-        <v>4378</v>
+        <v>4406</v>
       </c>
       <c r="D2" s="1">
         <f>D4+D6+D8</f>
-        <v>816</v>
+        <v>824</v>
       </c>
       <c r="E2" s="1">
         <f t="shared" ref="E2:J2" si="27">E4+E6+E8</f>
@@ -1373,11 +1369,11 @@
       </c>
       <c r="G2" s="1">
         <f t="shared" si="27"/>
-        <v>7009.5</v>
+        <v>7174.5</v>
       </c>
       <c r="H2" s="1">
         <f t="shared" si="27"/>
-        <v>973</v>
+        <v>993</v>
       </c>
       <c r="I2" s="1">
         <f t="shared" si="27"/>
@@ -1397,11 +1393,11 @@
       </c>
       <c r="M2" s="1">
         <f t="shared" si="28"/>
-        <v>2867</v>
+        <v>2976</v>
       </c>
       <c r="N2" s="1">
         <f t="shared" si="28"/>
-        <v>535</v>
+        <v>555</v>
       </c>
       <c r="O2" s="1">
         <f t="shared" si="28"/>
@@ -1413,11 +1409,11 @@
       </c>
       <c r="Q2" s="1">
         <f t="shared" si="28"/>
-        <v>1231</v>
+        <v>1267</v>
       </c>
       <c r="R2" s="1">
         <f t="shared" si="28"/>
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="S2" s="1">
         <f t="shared" si="28"/>
@@ -1429,11 +1425,11 @@
       </c>
       <c r="U2" s="1">
         <f t="shared" si="28"/>
-        <v>471</v>
+        <v>504</v>
       </c>
       <c r="V2" s="1">
         <f t="shared" si="28"/>
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="W2" s="1">
         <f t="shared" si="28"/>
@@ -1453,11 +1449,11 @@
       </c>
       <c r="AA2" s="1">
         <f t="shared" si="28"/>
-        <v>803.5</v>
+        <v>877.5</v>
       </c>
       <c r="AB2" s="1">
         <f t="shared" si="28"/>
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="AC2" s="1">
         <f t="shared" si="28"/>
@@ -2473,7 +2469,7 @@
       </c>
       <c r="C7" s="15">
         <f>C8/D8</f>
-        <v>6.282958199356913</v>
+        <v>6.2131661442006267</v>
       </c>
       <c r="D7" s="15" t="s">
         <v>2</v>
@@ -2487,7 +2483,7 @@
       </c>
       <c r="G7" s="15">
         <f t="shared" ref="G7" si="94">G8/H8</f>
-        <v>7.4921875</v>
+        <v>7.5245726495726499</v>
       </c>
       <c r="H7" s="15" t="s">
         <v>2</v>
@@ -2508,7 +2504,7 @@
       </c>
       <c r="M7" s="15">
         <f t="shared" ref="M7" si="97">M8/N8</f>
-        <v>5.9106628242074928</v>
+        <v>5.8855585831062669</v>
       </c>
       <c r="N7" s="15" t="s">
         <v>2</v>
@@ -2522,7 +2518,7 @@
       </c>
       <c r="Q7" s="15">
         <f t="shared" ref="Q7" si="99">Q8/R8</f>
-        <v>6.115384615384615</v>
+        <v>6.0217391304347823</v>
       </c>
       <c r="R7" s="15" t="s">
         <v>2</v>
@@ -2536,7 +2532,7 @@
       </c>
       <c r="U7" s="15">
         <f t="shared" ref="U7" si="101">U8/V8</f>
-        <v>3</v>
+        <v>2.9761904761904763</v>
       </c>
       <c r="V7" s="15" t="s">
         <v>2</v>
@@ -2557,7 +2553,7 @@
       </c>
       <c r="AA7" s="15">
         <f t="shared" ref="AA7" si="104">AA8/AB8</f>
-        <v>4.7276119402985071</v>
+        <v>4.845890410958904</v>
       </c>
       <c r="AB7" s="15" t="s">
         <v>2</v>
@@ -2675,11 +2671,11 @@
       </c>
       <c r="C8" s="15">
         <f>SUM(C10:C84)</f>
-        <v>1954</v>
+        <v>1982</v>
       </c>
       <c r="D8" s="15">
         <f>SUM(D10:D84)</f>
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="E8" s="15">
         <f t="shared" ref="E8:J8" si="120">SUM(E10:E84)</f>
@@ -2691,11 +2687,11 @@
       </c>
       <c r="G8" s="15">
         <f t="shared" si="120"/>
-        <v>3356.5</v>
+        <v>3521.5</v>
       </c>
       <c r="H8" s="15">
         <f t="shared" si="120"/>
-        <v>448</v>
+        <v>468</v>
       </c>
       <c r="I8" s="15">
         <f t="shared" si="120"/>
@@ -2715,11 +2711,11 @@
       </c>
       <c r="M8" s="15">
         <f t="shared" si="121"/>
-        <v>2051</v>
+        <v>2160</v>
       </c>
       <c r="N8" s="15">
         <f t="shared" si="121"/>
-        <v>347</v>
+        <v>367</v>
       </c>
       <c r="O8" s="15">
         <f t="shared" si="121"/>
@@ -2731,11 +2727,11 @@
       </c>
       <c r="Q8" s="15">
         <f t="shared" si="121"/>
-        <v>795</v>
+        <v>831</v>
       </c>
       <c r="R8" s="15">
         <f t="shared" si="121"/>
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="S8" s="15">
         <f t="shared" si="121"/>
@@ -2747,11 +2743,11 @@
       </c>
       <c r="U8" s="15">
         <f t="shared" si="121"/>
-        <v>342</v>
+        <v>375</v>
       </c>
       <c r="V8" s="15">
         <f t="shared" si="121"/>
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="W8" s="15">
         <f t="shared" si="121"/>
@@ -2771,11 +2767,11 @@
       </c>
       <c r="AA8" s="15">
         <f t="shared" si="121"/>
-        <v>633.5</v>
+        <v>707.5</v>
       </c>
       <c r="AB8" s="15">
         <f t="shared" si="121"/>
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="AC8" s="15">
         <f t="shared" si="121"/>
@@ -2899,118 +2895,118 @@
       </c>
     </row>
     <row r="9" spans="1:63" x14ac:dyDescent="0.3">
-      <c r="C9" s="26" t="s">
+      <c r="C9" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="D9" s="26"/>
-      <c r="E9" s="26" t="s">
+      <c r="D9" s="27"/>
+      <c r="E9" s="27" t="s">
         <v>71</v>
       </c>
-      <c r="F9" s="26"/>
-      <c r="G9" s="26" t="s">
+      <c r="F9" s="27"/>
+      <c r="G9" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="H9" s="26"/>
-      <c r="I9" s="26" t="s">
+      <c r="H9" s="27"/>
+      <c r="I9" s="27" t="s">
         <v>73</v>
       </c>
-      <c r="J9" s="26"/>
-      <c r="K9" s="26" t="s">
+      <c r="J9" s="27"/>
+      <c r="K9" s="27" t="s">
         <v>74</v>
       </c>
-      <c r="L9" s="26"/>
-      <c r="M9" s="26" t="s">
+      <c r="L9" s="27"/>
+      <c r="M9" s="27" t="s">
         <v>75</v>
       </c>
-      <c r="N9" s="26"/>
-      <c r="O9" s="26" t="s">
+      <c r="N9" s="27"/>
+      <c r="O9" s="27" t="s">
         <v>76</v>
       </c>
-      <c r="P9" s="26"/>
-      <c r="Q9" s="26" t="s">
+      <c r="P9" s="27"/>
+      <c r="Q9" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="R9" s="26"/>
-      <c r="S9" s="26" t="s">
+      <c r="R9" s="27"/>
+      <c r="S9" s="27" t="s">
         <v>78</v>
       </c>
-      <c r="T9" s="26"/>
-      <c r="U9" s="26" t="s">
+      <c r="T9" s="27"/>
+      <c r="U9" s="27" t="s">
         <v>79</v>
       </c>
-      <c r="V9" s="26"/>
-      <c r="W9" s="26" t="s">
+      <c r="V9" s="27"/>
+      <c r="W9" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="X9" s="26"/>
-      <c r="Y9" s="26" t="s">
+      <c r="X9" s="27"/>
+      <c r="Y9" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="Z9" s="26"/>
-      <c r="AA9" s="26" t="s">
+      <c r="Z9" s="27"/>
+      <c r="AA9" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="AB9" s="26"/>
-      <c r="AC9" s="26" t="s">
+      <c r="AB9" s="27"/>
+      <c r="AC9" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="AD9" s="26"/>
-      <c r="AE9" s="26" t="s">
+      <c r="AD9" s="27"/>
+      <c r="AE9" s="27" t="s">
         <v>83</v>
       </c>
-      <c r="AF9" s="26"/>
-      <c r="AG9" s="26" t="s">
+      <c r="AF9" s="27"/>
+      <c r="AG9" s="27" t="s">
         <v>84</v>
       </c>
-      <c r="AH9" s="26"/>
-      <c r="AI9" s="26" t="s">
+      <c r="AH9" s="27"/>
+      <c r="AI9" s="27" t="s">
         <v>85</v>
       </c>
-      <c r="AJ9" s="26"/>
-      <c r="AK9" s="26" t="s">
+      <c r="AJ9" s="27"/>
+      <c r="AK9" s="27" t="s">
         <v>86</v>
       </c>
-      <c r="AL9" s="26"/>
-      <c r="AM9" s="27" t="s">
+      <c r="AL9" s="27"/>
+      <c r="AM9" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="AN9" s="27"/>
-      <c r="AO9" s="27" t="s">
+      <c r="AN9" s="26"/>
+      <c r="AO9" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="AP9" s="27"/>
-      <c r="AQ9" s="27" t="s">
+      <c r="AP9" s="26"/>
+      <c r="AQ9" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="AR9" s="27"/>
-      <c r="AS9" s="27" t="s">
+      <c r="AR9" s="26"/>
+      <c r="AS9" s="26" t="s">
         <v>87</v>
       </c>
-      <c r="AT9" s="27"/>
-      <c r="AU9" s="27" t="s">
+      <c r="AT9" s="26"/>
+      <c r="AU9" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="AV9" s="27"/>
-      <c r="AW9" s="27" t="s">
+      <c r="AV9" s="26"/>
+      <c r="AW9" s="26" t="s">
         <v>88</v>
       </c>
-      <c r="AX9" s="27"/>
-      <c r="AY9" s="27" t="s">
+      <c r="AX9" s="26"/>
+      <c r="AY9" s="26" t="s">
         <v>89</v>
       </c>
-      <c r="AZ9" s="27"/>
-      <c r="BA9" s="26" t="s">
+      <c r="AZ9" s="26"/>
+      <c r="BA9" s="27" t="s">
         <v>90</v>
       </c>
-      <c r="BB9" s="26"/>
-      <c r="BC9" s="26" t="s">
+      <c r="BB9" s="27"/>
+      <c r="BC9" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="BD9" s="26"/>
-      <c r="BE9" s="26" t="s">
+      <c r="BD9" s="27"/>
+      <c r="BE9" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="BF9" s="26"/>
+      <c r="BF9" s="27"/>
     </row>
     <row r="10" spans="1:63" x14ac:dyDescent="0.3">
       <c r="B10" s="1">
@@ -3048,13 +3044,64 @@
       </c>
     </row>
     <row r="17" spans="1:58" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="B17" s="1">
         <v>123</v>
+      </c>
+      <c r="G17" s="1">
+        <v>119</v>
+      </c>
+      <c r="H17" s="1">
+        <v>12</v>
+      </c>
+      <c r="M17" s="1">
+        <v>68</v>
+      </c>
+      <c r="N17" s="1">
+        <v>12</v>
+      </c>
+      <c r="U17" s="1">
+        <v>33</v>
+      </c>
+      <c r="V17" s="1">
+        <v>12</v>
+      </c>
+      <c r="AA17" s="1">
+        <v>74</v>
+      </c>
+      <c r="AB17" s="1">
+        <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:58" x14ac:dyDescent="0.3">
       <c r="B18" s="1">
         <v>122</v>
+      </c>
+      <c r="C18" s="1">
+        <v>28</v>
+      </c>
+      <c r="D18" s="1">
+        <v>8</v>
+      </c>
+      <c r="G18" s="1">
+        <v>46</v>
+      </c>
+      <c r="H18" s="1">
+        <v>8</v>
+      </c>
+      <c r="M18" s="1">
+        <v>41</v>
+      </c>
+      <c r="N18" s="1">
+        <v>8</v>
+      </c>
+      <c r="Q18" s="1">
+        <v>36</v>
+      </c>
+      <c r="R18" s="1">
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:58" x14ac:dyDescent="0.3">
@@ -4780,10 +4827,10 @@
         <v>Boris</v>
       </c>
       <c r="BN63" s="1" t="str">
-        <v>7.204</v>
+        <v>7.225</v>
       </c>
       <c r="BO63" s="1">
-        <v>973</v>
+        <v>993</v>
       </c>
       <c r="BQ63" s="1">
         <v>2</v>
@@ -4801,7 +4848,7 @@
         <v>Boris</v>
       </c>
       <c r="BW63" s="1">
-        <v>7.2040082219938331</v>
+        <v>7.2250755287009065</v>
       </c>
     </row>
     <row r="64" spans="1:75" x14ac:dyDescent="0.3">
@@ -5106,10 +5153,10 @@
         <v>Célian</v>
       </c>
       <c r="BN68" s="1" t="str">
-        <v>6.005</v>
+        <v>5.948</v>
       </c>
       <c r="BO68" s="1">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="BQ68" s="1">
         <v>7</v>
@@ -5127,7 +5174,7 @@
         <v>Célian</v>
       </c>
       <c r="BW68" s="1">
-        <v>6.0048780487804878</v>
+        <v>5.948356807511737</v>
       </c>
     </row>
     <row r="69" spans="1:75" x14ac:dyDescent="0.3">
@@ -5383,19 +5430,19 @@
         <v>10</v>
       </c>
       <c r="BM71" s="1" t="str">
-        <v>Achille</v>
+        <v>Damien</v>
       </c>
       <c r="BN71" s="1" t="str">
-        <v>5.365</v>
+        <v>5.362</v>
       </c>
       <c r="BO71" s="1">
-        <v>816</v>
+        <v>555</v>
       </c>
       <c r="BV71" s="1" t="str">
-        <v>Achille</v>
+        <v>Damien</v>
       </c>
       <c r="BW71" s="1">
-        <v>5.3651960784313726</v>
+        <v>5.3621621621621625</v>
       </c>
     </row>
     <row r="72" spans="1:75" x14ac:dyDescent="0.3">
@@ -5478,19 +5525,19 @@
         <v>11</v>
       </c>
       <c r="BM72" s="1" t="str">
-        <v>Damien</v>
+        <v>Achille</v>
       </c>
       <c r="BN72" s="1" t="str">
-        <v>5.359</v>
+        <v>5.347</v>
       </c>
       <c r="BO72" s="1">
-        <v>535</v>
+        <v>824</v>
       </c>
       <c r="BV72" s="1" t="str">
-        <v>Damien</v>
+        <v>Achille</v>
       </c>
       <c r="BW72" s="1">
-        <v>5.3588785046728971</v>
+        <v>5.3470873786407767</v>
       </c>
     </row>
     <row r="73" spans="1:75" x14ac:dyDescent="0.3">
@@ -5665,7 +5712,7 @@
       </c>
       <c r="BJ74" s="1">
         <f>AVERAGE(C1:BF1)</f>
-        <v>5.0857255139381792</v>
+        <v>5.0883101385790219</v>
       </c>
       <c r="BL74" s="1">
         <v>13</v>
@@ -5860,16 +5907,16 @@
         <v>Marie</v>
       </c>
       <c r="BN76" s="1" t="str">
-        <v>4.121</v>
+        <v>4.239</v>
       </c>
       <c r="BO76" s="1">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="BV76" s="1" t="str">
         <v>Marie</v>
       </c>
       <c r="BW76" s="1">
-        <v>4.1205128205128201</v>
+        <v>4.2391304347826084</v>
       </c>
     </row>
     <row r="77" spans="1:75" x14ac:dyDescent="0.3">
@@ -5954,16 +6001,16 @@
         <v>Luca</v>
       </c>
       <c r="BN77" s="1" t="str">
-        <v>3.019</v>
+        <v>3.000</v>
       </c>
       <c r="BO77" s="1">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="BV77" s="1" t="str">
         <v>Luca</v>
       </c>
       <c r="BW77" s="1">
-        <v>3.0192307692307692</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78" spans="1:75" x14ac:dyDescent="0.3">
@@ -7455,10 +7502,10 @@
         <v>Boris</v>
       </c>
       <c r="BX95" s="1">
-        <v>7.2039999999999997</v>
+        <v>7.2249999999999996</v>
       </c>
       <c r="BY95" s="1">
-        <v>973</v>
+        <v>993</v>
       </c>
     </row>
     <row r="96" spans="1:77" x14ac:dyDescent="0.3">
@@ -7884,10 +7931,10 @@
         <v>Célian</v>
       </c>
       <c r="BX100" s="1">
-        <v>6.0049999999999999</v>
+        <v>5.9480000000000004</v>
       </c>
       <c r="BY100" s="1">
-        <v>205</v>
+        <v>213</v>
       </c>
     </row>
     <row r="101" spans="1:77" x14ac:dyDescent="0.3">
@@ -8149,13 +8196,13 @@
         <v>10</v>
       </c>
       <c r="BW103" s="1" t="str">
-        <v>Achille</v>
+        <v>Damien</v>
       </c>
       <c r="BX103" s="1">
-        <v>5.3650000000000002</v>
+        <v>5.3620000000000001</v>
       </c>
       <c r="BY103" s="1">
-        <v>816</v>
+        <v>555</v>
       </c>
     </row>
     <row r="104" spans="1:77" x14ac:dyDescent="0.3">
@@ -8234,13 +8281,13 @@
         <v>11</v>
       </c>
       <c r="BW104" s="1" t="str">
-        <v>Damien</v>
+        <v>Achille</v>
       </c>
       <c r="BX104" s="1">
-        <v>5.359</v>
+        <v>5.3470000000000004</v>
       </c>
       <c r="BY104" s="1">
-        <v>535</v>
+        <v>824</v>
       </c>
     </row>
     <row r="105" spans="1:77" x14ac:dyDescent="0.3">
@@ -8577,10 +8624,10 @@
         <v>Marie</v>
       </c>
       <c r="BX108" s="1">
-        <v>4.1210000000000004</v>
+        <v>4.2389999999999999</v>
       </c>
       <c r="BY108" s="1">
-        <v>195</v>
+        <v>207</v>
       </c>
     </row>
     <row r="109" spans="1:77" x14ac:dyDescent="0.3">
@@ -8662,10 +8709,10 @@
         <v>Luca</v>
       </c>
       <c r="BX109" s="1">
-        <v>3.0190000000000001</v>
+        <v>3</v>
       </c>
       <c r="BY109" s="1">
-        <v>156</v>
+        <v>168</v>
       </c>
     </row>
     <row r="110" spans="1:77" x14ac:dyDescent="0.3">
@@ -9623,16 +9670,16 @@
         <v>Boris</v>
       </c>
       <c r="BW121" s="1">
-        <v>7.2040082219938331</v>
+        <v>7.2250755287009065</v>
       </c>
       <c r="BX121" s="1">
-        <v>973</v>
+        <v>993</v>
       </c>
       <c r="CA121" s="1" t="str">
         <v>Boris</v>
       </c>
       <c r="CB121" s="1">
-        <v>7.2040082219938331</v>
+        <v>7.2250755287009065</v>
       </c>
     </row>
     <row r="122" spans="1:80" x14ac:dyDescent="0.3">
@@ -9975,10 +10022,10 @@
         <v>Célian</v>
       </c>
       <c r="BW125" s="1">
-        <v>6.0048780487804878</v>
+        <v>5.948356807511737</v>
       </c>
       <c r="BX125" s="1">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="CA125" s="1" t="str">
         <v>Lou</v>
@@ -10072,7 +10119,7 @@
         <v>Célian</v>
       </c>
       <c r="CB126" s="1">
-        <v>6.0048780487804878</v>
+        <v>5.948356807511737</v>
       </c>
     </row>
     <row r="127" spans="1:80" x14ac:dyDescent="0.3">
@@ -10240,13 +10287,13 @@
       <c r="AX128" s="15"/>
       <c r="AY128" s="15"/>
       <c r="BV128" s="1" t="str">
-        <v>Achille</v>
+        <v>Damien</v>
       </c>
       <c r="BW128" s="1">
-        <v>5.3651960784313726</v>
+        <v>5.3621621621621625</v>
       </c>
       <c r="BX128" s="1">
-        <v>816</v>
+        <v>555</v>
       </c>
       <c r="CA128" s="1" t="str">
         <v>Mehdi</v>
@@ -10263,19 +10310,19 @@
         <v>26</v>
       </c>
       <c r="BV129" s="1" t="str">
+        <v>Achille</v>
+      </c>
+      <c r="BW129" s="1">
+        <v>5.3470873786407767</v>
+      </c>
+      <c r="BX129" s="1">
+        <v>824</v>
+      </c>
+      <c r="CA129" s="1" t="str">
         <v>Damien</v>
       </c>
-      <c r="BW129" s="1">
-        <v>5.3588785046728971</v>
-      </c>
-      <c r="BX129" s="1">
-        <v>535</v>
-      </c>
-      <c r="CA129" s="1" t="str">
-        <v>Achille</v>
-      </c>
       <c r="CB129" s="1">
-        <v>5.3651960784313726</v>
+        <v>5.3621621621621625</v>
       </c>
     </row>
     <row r="130" spans="1:80" x14ac:dyDescent="0.3">
@@ -10319,10 +10366,10 @@
         <v>32</v>
       </c>
       <c r="CA130" s="1" t="str">
-        <v>Damien</v>
+        <v>Achille</v>
       </c>
       <c r="CB130" s="1">
-        <v>5.3588785046728971</v>
+        <v>5.3470873786407767</v>
       </c>
     </row>
     <row r="131" spans="1:80" x14ac:dyDescent="0.3">
@@ -10454,10 +10501,10 @@
         <v>Marie</v>
       </c>
       <c r="BW133" s="1">
-        <v>4.1205128205128201</v>
+        <v>4.2391304347826084</v>
       </c>
       <c r="BX133" s="1">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="CA133" s="1" t="str">
         <v>Quentin</v>
@@ -10501,16 +10548,16 @@
         <v>Luca</v>
       </c>
       <c r="BW134" s="1">
-        <v>3.0192307692307692</v>
+        <v>3</v>
       </c>
       <c r="BX134" s="1">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="CA134" s="1" t="str">
         <v>Marie</v>
       </c>
       <c r="CB134" s="1">
-        <v>4.1205128205128201</v>
+        <v>4.2391304347826084</v>
       </c>
     </row>
     <row r="135" spans="1:80" x14ac:dyDescent="0.3">
@@ -10557,7 +10604,7 @@
         <v>Luca</v>
       </c>
       <c r="CB135" s="1">
-        <v>3.0192307692307692</v>
+        <v>3</v>
       </c>
     </row>
     <row r="136" spans="1:80" x14ac:dyDescent="0.3">
@@ -10793,18 +10840,6 @@
     <sortCondition descending="1" ref="B130:B141"/>
   </sortState>
   <mergeCells count="28">
-    <mergeCell ref="AY9:AZ9"/>
-    <mergeCell ref="AA9:AB9"/>
-    <mergeCell ref="AC9:AD9"/>
-    <mergeCell ref="AE9:AF9"/>
-    <mergeCell ref="AK9:AL9"/>
-    <mergeCell ref="AI9:AJ9"/>
-    <mergeCell ref="AG9:AH9"/>
-    <mergeCell ref="AM9:AN9"/>
-    <mergeCell ref="AO9:AP9"/>
-    <mergeCell ref="AQ9:AR9"/>
-    <mergeCell ref="AS9:AT9"/>
-    <mergeCell ref="AU9:AV9"/>
     <mergeCell ref="BA9:BB9"/>
     <mergeCell ref="BC9:BD9"/>
     <mergeCell ref="BE9:BF9"/>
@@ -10821,6 +10856,18 @@
     <mergeCell ref="U9:V9"/>
     <mergeCell ref="W9:X9"/>
     <mergeCell ref="AW9:AX9"/>
+    <mergeCell ref="AY9:AZ9"/>
+    <mergeCell ref="AA9:AB9"/>
+    <mergeCell ref="AC9:AD9"/>
+    <mergeCell ref="AE9:AF9"/>
+    <mergeCell ref="AK9:AL9"/>
+    <mergeCell ref="AI9:AJ9"/>
+    <mergeCell ref="AG9:AH9"/>
+    <mergeCell ref="AM9:AN9"/>
+    <mergeCell ref="AO9:AP9"/>
+    <mergeCell ref="AQ9:AR9"/>
+    <mergeCell ref="AS9:AT9"/>
+    <mergeCell ref="AU9:AV9"/>
   </mergeCells>
   <conditionalFormatting sqref="C1 E1 G1 I1 K1 M1 O1 Q1 S1 U1 W1 Y1 AA1 AC1 AE1 AG1 AI1 AK1 AM1 AO1 AQ1 AS1 AU1 AW1 AY1 BA1 BC1 BE1 C9:AM9 AO9 AQ9 AS9 AU9 AW9 AY9 BA9 BC9 BE9">
     <cfRule type="expression" dxfId="24" priority="41" stopIfTrue="1">
@@ -10978,10 +11025,10 @@
         <v>Boris</v>
       </c>
       <c r="C3" s="25" t="str">
-        <v>7.204</v>
+        <v>7.225</v>
       </c>
       <c r="D3" s="25">
-        <v>973</v>
+        <v>993</v>
       </c>
       <c r="F3" t="str">
         <v>entre 1 et 10</v>
@@ -11099,10 +11146,10 @@
         <v>Célian</v>
       </c>
       <c r="C8" s="25" t="str">
-        <v>6.005</v>
+        <v>5.948</v>
       </c>
       <c r="D8" s="25">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="F8" t="str">
         <v>entre 250 et 500</v>
@@ -11168,13 +11215,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="25" t="str">
-        <v>Achille</v>
+        <v>Damien</v>
       </c>
       <c r="C11" s="25" t="str">
-        <v>5.365</v>
+        <v>5.362</v>
       </c>
       <c r="D11" s="25">
-        <v>816</v>
+        <v>555</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
@@ -11182,13 +11229,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="25" t="str">
-        <v>Damien</v>
+        <v>Achille</v>
       </c>
       <c r="C12" s="25" t="str">
-        <v>5.359</v>
+        <v>5.347</v>
       </c>
       <c r="D12" s="25">
-        <v>535</v>
+        <v>824</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
@@ -11241,10 +11288,10 @@
         <v>Marie</v>
       </c>
       <c r="C16" s="25" t="str">
-        <v>4.121</v>
+        <v>4.239</v>
       </c>
       <c r="D16" s="25">
-        <v>195</v>
+        <v>207</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
@@ -11255,10 +11302,10 @@
         <v>Luca</v>
       </c>
       <c r="C17" s="25" t="str">
-        <v>3.019</v>
+        <v>3.000</v>
       </c>
       <c r="D17" s="25">
-        <v>156</v>
+        <v>168</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">

--- a/classement_whist_2023_2025.xlsx
+++ b/classement_whist_2023_2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a20b8382962b136a/Bureau/loisir/whist/projet_application_streamlit/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="702" documentId="8_{848EF4F6-53E4-4B52-9417-5BFB5A888B23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DF0CC11B-6644-4681-9D08-66AC53FD3D7B}"/>
+  <xr:revisionPtr revIDLastSave="720" documentId="8_{848EF4F6-53E4-4B52-9417-5BFB5A888B23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{78453E3D-39CC-4641-9238-10D52A819D13}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -585,10 +585,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="8">
@@ -802,6 +802,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1166,7 +1170,7 @@
       </c>
       <c r="G1" s="1">
         <f t="shared" ref="G1" si="2">IF(H2&gt;19,G2/H2,"/")</f>
-        <v>7.2462981243830207</v>
+        <v>7.2625615763546794</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>2</v>
@@ -1187,7 +1191,7 @@
       </c>
       <c r="M1" s="1">
         <f t="shared" ref="M1" si="5">IF(N2&gt;19,M2/N2,"/")</f>
-        <v>5.4105621805792161</v>
+        <v>5.4097807757166949</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>2</v>
@@ -1201,7 +1205,7 @@
       </c>
       <c r="Q1" s="1">
         <f t="shared" ref="Q1" si="7">IF(R2&gt;19,Q2/R2,"/")</f>
-        <v>6.0705394190871367</v>
+        <v>6.2357723577235769</v>
       </c>
       <c r="R1" s="1" t="s">
         <v>2</v>
@@ -1236,14 +1240,14 @@
       </c>
       <c r="AA1" s="1">
         <f t="shared" ref="AA1" si="12">IF(AB2&gt;19,AA2/AB2,"/")</f>
-        <v>4.2391304347826084</v>
+        <v>4.21875</v>
       </c>
       <c r="AB1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="AC1" s="1">
         <f>IF(AD2&gt;19,AC2/AD2,"/")</f>
-        <v>4.6962962962962962</v>
+        <v>4.7410071942446042</v>
       </c>
       <c r="AD1" s="1" t="s">
         <v>2</v>
@@ -1278,7 +1282,7 @@
       </c>
       <c r="AM1" s="1">
         <f t="shared" ref="AM1" si="17">IF(AN2&gt;19,AM2/AN2,"/")</f>
-        <v>3.0344827586206895</v>
+        <v>2.9333333333333331</v>
       </c>
       <c r="AN1" s="1" t="s">
         <v>2</v>
@@ -1341,7 +1345,7 @@
       </c>
       <c r="BE1" s="1">
         <f t="shared" ref="BE1" si="26">IF(BF2&gt;19,BE2/BF2,"/")</f>
-        <v>5.916666666666667</v>
+        <v>5.5526315789473681</v>
       </c>
       <c r="BF1" s="1" t="s">
         <v>2</v>
@@ -1369,11 +1373,11 @@
       </c>
       <c r="G2" s="1">
         <f t="shared" si="27"/>
-        <v>7340.5</v>
+        <v>7371.5</v>
       </c>
       <c r="H2" s="1">
         <f t="shared" si="27"/>
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="I2" s="1">
         <f t="shared" si="27"/>
@@ -1393,11 +1397,11 @@
       </c>
       <c r="M2" s="1">
         <f t="shared" si="28"/>
-        <v>3176</v>
+        <v>3208</v>
       </c>
       <c r="N2" s="1">
         <f t="shared" si="28"/>
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="O2" s="1">
         <f t="shared" si="28"/>
@@ -1409,11 +1413,11 @@
       </c>
       <c r="Q2" s="1">
         <f t="shared" si="28"/>
-        <v>1463</v>
+        <v>1534</v>
       </c>
       <c r="R2" s="1">
         <f t="shared" si="28"/>
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="S2" s="1">
         <f t="shared" si="28"/>
@@ -1453,15 +1457,15 @@
       </c>
       <c r="AB2" s="1">
         <f t="shared" si="28"/>
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AC2" s="1">
         <f t="shared" si="28"/>
-        <v>634</v>
+        <v>659</v>
       </c>
       <c r="AD2" s="1">
         <f t="shared" si="28"/>
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="AE2" s="1">
         <f t="shared" si="28"/>
@@ -1501,7 +1505,7 @@
       </c>
       <c r="AN2" s="1">
         <f t="shared" si="28"/>
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="AO2" s="1">
         <f t="shared" si="28"/>
@@ -1569,11 +1573,11 @@
       </c>
       <c r="BE2" s="1">
         <f t="shared" ref="BE2:BF2" si="30">BE4+BE6+BE8</f>
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="BF2" s="1">
         <f t="shared" si="30"/>
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:63" x14ac:dyDescent="0.3">
@@ -2483,7 +2487,7 @@
       </c>
       <c r="G7" s="15">
         <f t="shared" ref="G7" si="94">G8/H8</f>
-        <v>7.5563524590163933</v>
+        <v>7.5887755102040817</v>
       </c>
       <c r="H7" s="15" t="s">
         <v>2</v>
@@ -2504,7 +2508,7 @@
       </c>
       <c r="M7" s="15">
         <f t="shared" ref="M7" si="97">M8/N8</f>
-        <v>5.9147869674185465</v>
+        <v>5.9061728395061728</v>
       </c>
       <c r="N7" s="15" t="s">
         <v>2</v>
@@ -2518,7 +2522,7 @@
       </c>
       <c r="Q7" s="15">
         <f t="shared" ref="Q7" si="99">Q8/R8</f>
-        <v>6.1867469879518069</v>
+        <v>6.4210526315789478</v>
       </c>
       <c r="R7" s="15" t="s">
         <v>2</v>
@@ -2553,14 +2557,14 @@
       </c>
       <c r="AA7" s="15">
         <f t="shared" ref="AA7" si="104">AA8/AB8</f>
-        <v>4.845890410958904</v>
+        <v>4.8129251700680271</v>
       </c>
       <c r="AB7" s="15" t="s">
         <v>2</v>
       </c>
       <c r="AC7" s="15">
         <f t="shared" ref="AC7" si="105">AC8/AD8</f>
-        <v>4.944</v>
+        <v>4.9844961240310077</v>
       </c>
       <c r="AD7" s="15" t="s">
         <v>2</v>
@@ -2595,7 +2599,7 @@
       </c>
       <c r="AM7" s="15">
         <f t="shared" ref="AM7" si="110">AM8/AN8</f>
-        <v>3.0344827586206895</v>
+        <v>2.9333333333333331</v>
       </c>
       <c r="AN7" s="15" t="s">
         <v>2</v>
@@ -2658,7 +2662,7 @@
       </c>
       <c r="BE7" s="15">
         <f t="shared" ref="BE7" si="119">BE8/BF8</f>
-        <v>5.916666666666667</v>
+        <v>5.5526315789473681</v>
       </c>
       <c r="BF7" s="15" t="s">
         <v>2</v>
@@ -2687,11 +2691,11 @@
       </c>
       <c r="G8" s="15">
         <f t="shared" si="120"/>
-        <v>3687.5</v>
+        <v>3718.5</v>
       </c>
       <c r="H8" s="15">
         <f t="shared" si="120"/>
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="I8" s="15">
         <f t="shared" si="120"/>
@@ -2711,11 +2715,11 @@
       </c>
       <c r="M8" s="15">
         <f t="shared" si="121"/>
-        <v>2360</v>
+        <v>2392</v>
       </c>
       <c r="N8" s="15">
         <f t="shared" si="121"/>
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="O8" s="15">
         <f t="shared" si="121"/>
@@ -2727,11 +2731,11 @@
       </c>
       <c r="Q8" s="15">
         <f t="shared" si="121"/>
-        <v>1027</v>
+        <v>1098</v>
       </c>
       <c r="R8" s="15">
         <f t="shared" si="121"/>
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="S8" s="15">
         <f t="shared" si="121"/>
@@ -2771,15 +2775,15 @@
       </c>
       <c r="AB8" s="15">
         <f t="shared" si="121"/>
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AC8" s="15">
         <f t="shared" si="121"/>
-        <v>618</v>
+        <v>643</v>
       </c>
       <c r="AD8" s="15">
         <f t="shared" si="121"/>
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="AE8" s="15">
         <f t="shared" si="121"/>
@@ -2819,7 +2823,7 @@
       </c>
       <c r="AN8" s="15">
         <f t="shared" si="121"/>
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="AO8" s="15">
         <f t="shared" si="121"/>
@@ -2887,126 +2891,126 @@
       </c>
       <c r="BE8" s="15">
         <f t="shared" ref="BE8:BF8" si="123">SUM(BE10:BE90)</f>
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="BF8" s="15">
         <f t="shared" si="123"/>
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" spans="1:63" x14ac:dyDescent="0.3">
+      <c r="C9" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="D9" s="26"/>
+      <c r="E9" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="F9" s="26"/>
+      <c r="G9" s="26" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="9" spans="1:63" x14ac:dyDescent="0.3">
-      <c r="C9" s="27" t="s">
-        <v>70</v>
-      </c>
-      <c r="D9" s="27"/>
-      <c r="E9" s="27" t="s">
-        <v>71</v>
-      </c>
-      <c r="F9" s="27"/>
-      <c r="G9" s="27" t="s">
-        <v>72</v>
-      </c>
-      <c r="H9" s="27"/>
-      <c r="I9" s="27" t="s">
+      <c r="H9" s="26"/>
+      <c r="I9" s="26" t="s">
         <v>73</v>
       </c>
-      <c r="J9" s="27"/>
-      <c r="K9" s="27" t="s">
+      <c r="J9" s="26"/>
+      <c r="K9" s="26" t="s">
         <v>74</v>
       </c>
-      <c r="L9" s="27"/>
-      <c r="M9" s="27" t="s">
+      <c r="L9" s="26"/>
+      <c r="M9" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="N9" s="27"/>
-      <c r="O9" s="27" t="s">
+      <c r="N9" s="26"/>
+      <c r="O9" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="P9" s="27"/>
-      <c r="Q9" s="27" t="s">
+      <c r="P9" s="26"/>
+      <c r="Q9" s="26" t="s">
         <v>77</v>
       </c>
-      <c r="R9" s="27"/>
-      <c r="S9" s="27" t="s">
+      <c r="R9" s="26"/>
+      <c r="S9" s="26" t="s">
         <v>78</v>
       </c>
-      <c r="T9" s="27"/>
-      <c r="U9" s="27" t="s">
+      <c r="T9" s="26"/>
+      <c r="U9" s="26" t="s">
         <v>79</v>
       </c>
-      <c r="V9" s="27"/>
-      <c r="W9" s="27" t="s">
+      <c r="V9" s="26"/>
+      <c r="W9" s="26" t="s">
         <v>80</v>
       </c>
-      <c r="X9" s="27"/>
-      <c r="Y9" s="27" t="s">
+      <c r="X9" s="26"/>
+      <c r="Y9" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="Z9" s="27"/>
-      <c r="AA9" s="27" t="s">
+      <c r="Z9" s="26"/>
+      <c r="AA9" s="26" t="s">
         <v>82</v>
       </c>
-      <c r="AB9" s="27"/>
-      <c r="AC9" s="27" t="s">
+      <c r="AB9" s="26"/>
+      <c r="AC9" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="AD9" s="27"/>
-      <c r="AE9" s="27" t="s">
+      <c r="AD9" s="26"/>
+      <c r="AE9" s="26" t="s">
         <v>83</v>
       </c>
-      <c r="AF9" s="27"/>
-      <c r="AG9" s="27" t="s">
+      <c r="AF9" s="26"/>
+      <c r="AG9" s="26" t="s">
         <v>84</v>
       </c>
-      <c r="AH9" s="27"/>
-      <c r="AI9" s="27" t="s">
+      <c r="AH9" s="26"/>
+      <c r="AI9" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="AJ9" s="27"/>
-      <c r="AK9" s="27" t="s">
+      <c r="AJ9" s="26"/>
+      <c r="AK9" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="AL9" s="27"/>
-      <c r="AM9" s="26" t="s">
+      <c r="AL9" s="26"/>
+      <c r="AM9" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="AN9" s="26"/>
-      <c r="AO9" s="26" t="s">
+      <c r="AN9" s="27"/>
+      <c r="AO9" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="AP9" s="26"/>
-      <c r="AQ9" s="26" t="s">
+      <c r="AP9" s="27"/>
+      <c r="AQ9" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="AR9" s="26"/>
-      <c r="AS9" s="26" t="s">
+      <c r="AR9" s="27"/>
+      <c r="AS9" s="27" t="s">
         <v>87</v>
       </c>
-      <c r="AT9" s="26"/>
-      <c r="AU9" s="26" t="s">
+      <c r="AT9" s="27"/>
+      <c r="AU9" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="AV9" s="26"/>
-      <c r="AW9" s="26" t="s">
+      <c r="AV9" s="27"/>
+      <c r="AW9" s="27" t="s">
         <v>88</v>
       </c>
-      <c r="AX9" s="26"/>
-      <c r="AY9" s="26" t="s">
+      <c r="AX9" s="27"/>
+      <c r="AY9" s="27" t="s">
         <v>89</v>
       </c>
-      <c r="AZ9" s="26"/>
-      <c r="BA9" s="27" t="s">
+      <c r="AZ9" s="27"/>
+      <c r="BA9" s="26" t="s">
         <v>90</v>
       </c>
-      <c r="BB9" s="27"/>
-      <c r="BC9" s="27" t="s">
+      <c r="BB9" s="26"/>
+      <c r="BC9" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="BD9" s="27"/>
-      <c r="BE9" s="27" t="s">
+      <c r="BD9" s="26"/>
+      <c r="BE9" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="BF9" s="27"/>
+      <c r="BF9" s="26"/>
     </row>
     <row r="10" spans="1:63" x14ac:dyDescent="0.3">
       <c r="B10" s="1">
@@ -3047,6 +3051,36 @@
       <c r="B17" s="1">
         <v>129</v>
       </c>
+      <c r="G17" s="1">
+        <v>31</v>
+      </c>
+      <c r="H17" s="1">
+        <v>2</v>
+      </c>
+      <c r="M17" s="1">
+        <v>20</v>
+      </c>
+      <c r="N17" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q17" s="1">
+        <v>11</v>
+      </c>
+      <c r="R17" s="1">
+        <v>1</v>
+      </c>
+      <c r="AA17" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB17" s="1">
+        <v>1</v>
+      </c>
+      <c r="AM17" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN17" s="1">
+        <v>2</v>
+      </c>
     </row>
     <row r="18" spans="1:58" x14ac:dyDescent="0.3">
       <c r="B18" s="1">
@@ -3086,6 +3120,30 @@
     <row r="19" spans="1:58" x14ac:dyDescent="0.3">
       <c r="B19" s="1">
         <v>127</v>
+      </c>
+      <c r="M19" s="1">
+        <v>12</v>
+      </c>
+      <c r="N19" s="1">
+        <v>4</v>
+      </c>
+      <c r="Q19" s="1">
+        <v>60</v>
+      </c>
+      <c r="R19" s="1">
+        <v>4</v>
+      </c>
+      <c r="AC19" s="1">
+        <v>25</v>
+      </c>
+      <c r="AD19" s="1">
+        <v>4</v>
+      </c>
+      <c r="BE19" s="1">
+        <v>-4</v>
+      </c>
+      <c r="BF19" s="1">
+        <v>4</v>
       </c>
     </row>
     <row r="20" spans="1:58" x14ac:dyDescent="0.3">
@@ -4965,10 +5023,10 @@
         <v>Boris</v>
       </c>
       <c r="BN69" s="1" t="str">
-        <v>7.246</v>
+        <v>7.263</v>
       </c>
       <c r="BO69" s="1">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="BQ69" s="1">
         <v>2</v>
@@ -4986,7 +5044,7 @@
         <v>Boris</v>
       </c>
       <c r="BW69" s="1">
-        <v>7.2462981243830207</v>
+        <v>7.2625615763546794</v>
       </c>
     </row>
     <row r="70" spans="1:75" x14ac:dyDescent="0.3">
@@ -5028,13 +5086,13 @@
         <v>3</v>
       </c>
       <c r="BM70" s="1" t="str">
-        <v>Joachim</v>
+        <v>Célian</v>
       </c>
       <c r="BN70" s="1" t="str">
-        <v>6.202</v>
+        <v>6.236</v>
       </c>
       <c r="BO70" s="1">
-        <v>104</v>
+        <v>246</v>
       </c>
       <c r="BQ70" s="1">
         <v>3</v>
@@ -5049,10 +5107,10 @@
         <v>17</v>
       </c>
       <c r="BV70" s="1" t="str">
-        <v>Joachim</v>
+        <v>Célian</v>
       </c>
       <c r="BW70" s="1">
-        <v>6.2019230769230766</v>
+        <v>6.2357723577235769</v>
       </c>
     </row>
     <row r="71" spans="1:75" x14ac:dyDescent="0.3">
@@ -5090,13 +5148,13 @@
         <v>4</v>
       </c>
       <c r="BM71" s="1" t="str">
-        <v>Tom</v>
+        <v>Joachim</v>
       </c>
       <c r="BN71" s="1" t="str">
-        <v>6.109</v>
+        <v>6.202</v>
       </c>
       <c r="BO71" s="1">
-        <v>193</v>
+        <v>104</v>
       </c>
       <c r="BQ71" s="1">
         <v>4</v>
@@ -5111,10 +5169,10 @@
         <v>5</v>
       </c>
       <c r="BV71" s="1" t="str">
-        <v>Tom</v>
+        <v>Joachim</v>
       </c>
       <c r="BW71" s="1">
-        <v>6.1088082901554408</v>
+        <v>6.2019230769230766</v>
       </c>
     </row>
     <row r="72" spans="1:75" x14ac:dyDescent="0.3">
@@ -5156,13 +5214,13 @@
         <v>5</v>
       </c>
       <c r="BM72" s="1" t="str">
-        <v>Célian</v>
+        <v>Tom</v>
       </c>
       <c r="BN72" s="1" t="str">
-        <v>6.071</v>
+        <v>6.109</v>
       </c>
       <c r="BO72" s="1">
-        <v>241</v>
+        <v>193</v>
       </c>
       <c r="BQ72" s="1">
         <v>5</v>
@@ -5177,10 +5235,10 @@
         <v>17</v>
       </c>
       <c r="BV72" s="1" t="str">
-        <v>Célian</v>
+        <v>Tom</v>
       </c>
       <c r="BW72" s="1">
-        <v>6.0705394190871367</v>
+        <v>6.1088082901554408</v>
       </c>
     </row>
     <row r="73" spans="1:75" x14ac:dyDescent="0.3">
@@ -5288,13 +5346,13 @@
         <v>7</v>
       </c>
       <c r="BM74" s="1" t="str">
-        <v>Lou</v>
+        <v>Samuel</v>
       </c>
       <c r="BN74" s="1" t="str">
-        <v>5.917</v>
+        <v>5.910</v>
       </c>
       <c r="BO74" s="1">
-        <v>72</v>
+        <v>211</v>
       </c>
       <c r="BQ74" s="1">
         <v>7</v>
@@ -5309,10 +5367,10 @@
         <v>5</v>
       </c>
       <c r="BV74" s="1" t="str">
-        <v>Lou</v>
+        <v>Samuel</v>
       </c>
       <c r="BW74" s="1">
-        <v>5.916666666666667</v>
+        <v>5.9099526066350707</v>
       </c>
     </row>
     <row r="75" spans="1:75" x14ac:dyDescent="0.3">
@@ -5350,13 +5408,13 @@
         <v>8</v>
       </c>
       <c r="BM75" s="1" t="str">
-        <v>Samuel</v>
+        <v>Mehdi</v>
       </c>
       <c r="BN75" s="1" t="str">
-        <v>5.910</v>
+        <v>5.770</v>
       </c>
       <c r="BO75" s="1">
-        <v>211</v>
+        <v>421</v>
       </c>
       <c r="BQ75" s="1">
         <v>8</v>
@@ -5371,10 +5429,10 @@
         <v>11</v>
       </c>
       <c r="BV75" s="1" t="str">
-        <v>Samuel</v>
+        <v>Mehdi</v>
       </c>
       <c r="BW75" s="1">
-        <v>5.9099526066350707</v>
+        <v>5.7695961995249405</v>
       </c>
     </row>
     <row r="76" spans="1:75" x14ac:dyDescent="0.3">
@@ -5461,13 +5519,13 @@
         <v>9</v>
       </c>
       <c r="BM76" s="1" t="str">
-        <v>Mehdi</v>
+        <v>Lou</v>
       </c>
       <c r="BN76" s="1" t="str">
-        <v>5.770</v>
+        <v>5.553</v>
       </c>
       <c r="BO76" s="1">
-        <v>421</v>
+        <v>76</v>
       </c>
       <c r="BQ76" s="1">
         <v>9</v>
@@ -5482,10 +5540,10 @@
         <v>12</v>
       </c>
       <c r="BV76" s="1" t="str">
-        <v>Mehdi</v>
+        <v>Lou</v>
       </c>
       <c r="BW76" s="1">
-        <v>5.7695961995249405</v>
+        <v>5.5526315789473681</v>
       </c>
     </row>
     <row r="77" spans="1:75" x14ac:dyDescent="0.3">
@@ -5571,16 +5629,16 @@
         <v>Damien</v>
       </c>
       <c r="BN77" s="1" t="str">
-        <v>5.411</v>
+        <v>5.410</v>
       </c>
       <c r="BO77" s="1">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="BV77" s="1" t="str">
         <v>Damien</v>
       </c>
       <c r="BW77" s="1">
-        <v>5.4105621805792161</v>
+        <v>5.4097807757166949</v>
       </c>
     </row>
     <row r="78" spans="1:75" x14ac:dyDescent="0.3">
@@ -5850,7 +5908,7 @@
       </c>
       <c r="BJ80" s="1">
         <f>AVERAGE(C1:BF1)</f>
-        <v>5.1202992528921065</v>
+        <v>5.1066077232028775</v>
       </c>
       <c r="BL80" s="1">
         <v>13</v>
@@ -5950,16 +6008,16 @@
         <v>Jules</v>
       </c>
       <c r="BN81" s="1" t="str">
-        <v>4.696</v>
+        <v>4.741</v>
       </c>
       <c r="BO81" s="1">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="BV81" s="1" t="str">
         <v>Jules</v>
       </c>
       <c r="BW81" s="1">
-        <v>4.6962962962962962</v>
+        <v>4.7410071942446042</v>
       </c>
     </row>
     <row r="82" spans="1:75" x14ac:dyDescent="0.3">
@@ -6045,16 +6103,16 @@
         <v>Marie</v>
       </c>
       <c r="BN82" s="1" t="str">
-        <v>4.239</v>
+        <v>4.219</v>
       </c>
       <c r="BO82" s="1">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="BV82" s="1" t="str">
         <v>Marie</v>
       </c>
       <c r="BW82" s="1">
-        <v>4.2391304347826084</v>
+        <v>4.21875</v>
       </c>
     </row>
     <row r="83" spans="1:75" x14ac:dyDescent="0.3">
@@ -6136,19 +6194,19 @@
         <v>16</v>
       </c>
       <c r="BM83" s="1" t="str">
-        <v>Joey</v>
+        <v>Luca</v>
       </c>
       <c r="BN83" s="1" t="str">
-        <v>3.034</v>
+        <v>3.011</v>
       </c>
       <c r="BO83" s="1">
-        <v>58</v>
+        <v>178</v>
       </c>
       <c r="BV83" s="1" t="str">
-        <v>Joey</v>
+        <v>Luca</v>
       </c>
       <c r="BW83" s="1">
-        <v>3.0344827586206895</v>
+        <v>3.0112359550561796</v>
       </c>
     </row>
     <row r="84" spans="1:75" x14ac:dyDescent="0.3">
@@ -6239,19 +6297,19 @@
         <v>17</v>
       </c>
       <c r="BM84" s="1" t="str">
-        <v>Luca</v>
+        <v>Fantinne</v>
       </c>
       <c r="BN84" s="1" t="str">
-        <v>3.011</v>
+        <v>2.961</v>
       </c>
       <c r="BO84" s="1">
-        <v>178</v>
+        <v>51</v>
       </c>
       <c r="BV84" s="1" t="str">
-        <v>Luca</v>
+        <v>Fantinne</v>
       </c>
       <c r="BW84" s="1">
-        <v>3.0112359550561796</v>
+        <v>2.9607843137254903</v>
       </c>
     </row>
     <row r="85" spans="1:75" x14ac:dyDescent="0.3">
@@ -6334,19 +6392,19 @@
         <v>18</v>
       </c>
       <c r="BM85" s="1" t="str">
-        <v>Fantinne</v>
+        <v>Joey</v>
       </c>
       <c r="BN85" s="1" t="str">
-        <v>2.961</v>
+        <v>2.933</v>
       </c>
       <c r="BO85" s="1">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="BV85" s="1" t="str">
-        <v>Fantinne</v>
+        <v>Joey</v>
       </c>
       <c r="BW85" s="1">
-        <v>2.9607843137254903</v>
+        <v>2.9333333333333331</v>
       </c>
     </row>
     <row r="86" spans="1:75" x14ac:dyDescent="0.3">
@@ -7640,10 +7698,10 @@
         <v>Boris</v>
       </c>
       <c r="BX101" s="1">
-        <v>7.2460000000000004</v>
+        <v>7.2629999999999999</v>
       </c>
       <c r="BY101" s="1">
-        <v>1013</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="102" spans="1:77" x14ac:dyDescent="0.3">
@@ -7726,13 +7784,13 @@
         <v>3</v>
       </c>
       <c r="BW102" s="1" t="str">
-        <v>Joachim</v>
+        <v>Célian</v>
       </c>
       <c r="BX102" s="1">
-        <v>6.202</v>
+        <v>6.2359999999999998</v>
       </c>
       <c r="BY102" s="1">
-        <v>104</v>
+        <v>246</v>
       </c>
     </row>
     <row r="103" spans="1:77" x14ac:dyDescent="0.3">
@@ -7811,13 +7869,13 @@
         <v>4</v>
       </c>
       <c r="BW103" s="1" t="str">
-        <v>Tom</v>
+        <v>Joachim</v>
       </c>
       <c r="BX103" s="1">
-        <v>6.109</v>
+        <v>6.202</v>
       </c>
       <c r="BY103" s="1">
-        <v>193</v>
+        <v>104</v>
       </c>
     </row>
     <row r="104" spans="1:77" x14ac:dyDescent="0.3">
@@ -7896,13 +7954,13 @@
         <v>5</v>
       </c>
       <c r="BW104" s="1" t="str">
-        <v>Célian</v>
+        <v>Tom</v>
       </c>
       <c r="BX104" s="1">
-        <v>6.0709999999999997</v>
+        <v>6.109</v>
       </c>
       <c r="BY104" s="1">
-        <v>241</v>
+        <v>193</v>
       </c>
     </row>
     <row r="105" spans="1:77" x14ac:dyDescent="0.3">
@@ -8066,13 +8124,13 @@
         <v>7</v>
       </c>
       <c r="BW106" s="1" t="str">
-        <v>Lou</v>
+        <v>Samuel</v>
       </c>
       <c r="BX106" s="1">
-        <v>5.9169999999999998</v>
+        <v>5.91</v>
       </c>
       <c r="BY106" s="1">
-        <v>72</v>
+        <v>211</v>
       </c>
     </row>
     <row r="107" spans="1:77" x14ac:dyDescent="0.3">
@@ -8156,13 +8214,13 @@
         <v>8</v>
       </c>
       <c r="BW107" s="1" t="str">
-        <v>Samuel</v>
+        <v>Mehdi</v>
       </c>
       <c r="BX107" s="1">
-        <v>5.91</v>
+        <v>5.77</v>
       </c>
       <c r="BY107" s="1">
-        <v>211</v>
+        <v>421</v>
       </c>
     </row>
     <row r="108" spans="1:77" x14ac:dyDescent="0.3">
@@ -8245,13 +8303,13 @@
         <v>9</v>
       </c>
       <c r="BW108" s="1" t="str">
-        <v>Mehdi</v>
+        <v>Lou</v>
       </c>
       <c r="BX108" s="1">
-        <v>5.77</v>
+        <v>5.5529999999999999</v>
       </c>
       <c r="BY108" s="1">
-        <v>421</v>
+        <v>76</v>
       </c>
     </row>
     <row r="109" spans="1:77" x14ac:dyDescent="0.3">
@@ -8337,10 +8395,10 @@
         <v>Damien</v>
       </c>
       <c r="BX109" s="1">
-        <v>5.4109999999999996</v>
+        <v>5.41</v>
       </c>
       <c r="BY109" s="1">
-        <v>587</v>
+        <v>593</v>
       </c>
     </row>
     <row r="110" spans="1:77" x14ac:dyDescent="0.3">
@@ -8677,10 +8735,10 @@
         <v>Jules</v>
       </c>
       <c r="BX113" s="1">
-        <v>4.6959999999999997</v>
+        <v>4.7409999999999997</v>
       </c>
       <c r="BY113" s="1">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="114" spans="1:80" x14ac:dyDescent="0.3">
@@ -8762,10 +8820,10 @@
         <v>Marie</v>
       </c>
       <c r="BX114" s="1">
-        <v>4.2389999999999999</v>
+        <v>4.2190000000000003</v>
       </c>
       <c r="BY114" s="1">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="115" spans="1:80" x14ac:dyDescent="0.3">
@@ -8844,13 +8902,13 @@
         <v>16</v>
       </c>
       <c r="BW115" s="1" t="str">
-        <v>Joey</v>
+        <v>Luca</v>
       </c>
       <c r="BX115" s="1">
-        <v>3.0339999999999998</v>
+        <v>3.0110000000000001</v>
       </c>
       <c r="BY115" s="1">
-        <v>58</v>
+        <v>178</v>
       </c>
     </row>
     <row r="116" spans="1:80" x14ac:dyDescent="0.3">
@@ -8929,13 +8987,13 @@
         <v>17</v>
       </c>
       <c r="BW116" s="1" t="str">
-        <v>Luca</v>
+        <v>Fantinne</v>
       </c>
       <c r="BX116" s="1">
-        <v>3.0110000000000001</v>
+        <v>2.9609999999999999</v>
       </c>
       <c r="BY116" s="1">
-        <v>178</v>
+        <v>51</v>
       </c>
     </row>
     <row r="117" spans="1:80" x14ac:dyDescent="0.3">
@@ -9022,13 +9080,13 @@
         <v>18</v>
       </c>
       <c r="BW117" s="1" t="str">
-        <v>Fantinne</v>
+        <v>Joey</v>
       </c>
       <c r="BX117" s="1">
-        <v>2.9609999999999999</v>
+        <v>2.9329999999999998</v>
       </c>
       <c r="BY117" s="1">
-        <v>51</v>
+        <v>60</v>
       </c>
     </row>
     <row r="118" spans="1:80" x14ac:dyDescent="0.3">
@@ -9808,16 +9866,16 @@
         <v>Boris</v>
       </c>
       <c r="BW127" s="1">
-        <v>7.2462981243830207</v>
+        <v>7.2625615763546794</v>
       </c>
       <c r="BX127" s="1">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="CA127" s="1" t="str">
         <v>Boris</v>
       </c>
       <c r="CB127" s="1">
-        <v>7.2462981243830207</v>
+        <v>7.2625615763546794</v>
       </c>
     </row>
     <row r="128" spans="1:80" x14ac:dyDescent="0.3">
@@ -9893,19 +9951,19 @@
       <c r="AX128" s="15"/>
       <c r="AY128" s="15"/>
       <c r="BV128" s="1" t="str">
-        <v>Joachim</v>
+        <v>Célian</v>
       </c>
       <c r="BW128" s="1">
-        <v>6.2019230769230766</v>
+        <v>6.2357723577235769</v>
       </c>
       <c r="BX128" s="1">
-        <v>104</v>
+        <v>246</v>
       </c>
       <c r="CA128" s="1" t="str">
-        <v>Joachim</v>
+        <v>Célian</v>
       </c>
       <c r="CB128" s="1">
-        <v>6.2019230769230766</v>
+        <v>6.2357723577235769</v>
       </c>
     </row>
     <row r="129" spans="1:80" x14ac:dyDescent="0.3">
@@ -9981,19 +10039,19 @@
       <c r="AX129" s="15"/>
       <c r="AY129" s="15"/>
       <c r="BV129" s="1" t="str">
-        <v>Tom</v>
+        <v>Joachim</v>
       </c>
       <c r="BW129" s="1">
-        <v>6.1088082901554408</v>
+        <v>6.2019230769230766</v>
       </c>
       <c r="BX129" s="1">
-        <v>193</v>
+        <v>104</v>
       </c>
       <c r="CA129" s="1" t="str">
-        <v>Tom</v>
+        <v>Joachim</v>
       </c>
       <c r="CB129" s="1">
-        <v>6.1088082901554408</v>
+        <v>6.2019230769230766</v>
       </c>
     </row>
     <row r="130" spans="1:80" x14ac:dyDescent="0.3">
@@ -10069,19 +10127,19 @@
       <c r="AX130" s="15"/>
       <c r="AY130" s="15"/>
       <c r="BV130" s="1" t="str">
-        <v>Célian</v>
+        <v>Tom</v>
       </c>
       <c r="BW130" s="1">
-        <v>6.0705394190871367</v>
+        <v>6.1088082901554408</v>
       </c>
       <c r="BX130" s="1">
-        <v>241</v>
+        <v>193</v>
       </c>
       <c r="CA130" s="1" t="str">
-        <v>Célian</v>
+        <v>Tom</v>
       </c>
       <c r="CB130" s="1">
-        <v>6.0705394190871367</v>
+        <v>6.1088082901554408</v>
       </c>
     </row>
     <row r="131" spans="1:80" x14ac:dyDescent="0.3">
@@ -10254,10 +10312,10 @@
         <v>211</v>
       </c>
       <c r="CA132" s="1" t="str">
-        <v>Lou</v>
+        <v>Samuel</v>
       </c>
       <c r="CB132" s="1">
-        <v>5.916666666666667</v>
+        <v>5.9099526066350707</v>
       </c>
     </row>
     <row r="133" spans="1:80" x14ac:dyDescent="0.3">
@@ -10346,10 +10404,10 @@
         <v>421</v>
       </c>
       <c r="CA133" s="1" t="str">
-        <v>Samuel</v>
+        <v>Mehdi</v>
       </c>
       <c r="CB133" s="1">
-        <v>5.9099526066350707</v>
+        <v>5.7695961995249405</v>
       </c>
     </row>
     <row r="134" spans="1:80" x14ac:dyDescent="0.3">
@@ -10428,16 +10486,16 @@
         <v>Damien</v>
       </c>
       <c r="BW134" s="1">
-        <v>5.4105621805792161</v>
+        <v>5.4097807757166949</v>
       </c>
       <c r="BX134" s="1">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="CA134" s="1" t="str">
-        <v>Mehdi</v>
+        <v>Lou</v>
       </c>
       <c r="CB134" s="1">
-        <v>5.7695961995249405</v>
+        <v>5.5526315789473681</v>
       </c>
     </row>
     <row r="135" spans="1:80" x14ac:dyDescent="0.3">
@@ -10460,7 +10518,7 @@
         <v>Damien</v>
       </c>
       <c r="CB135" s="1">
-        <v>5.4105621805792161</v>
+        <v>5.4097807757166949</v>
       </c>
     </row>
     <row r="136" spans="1:80" x14ac:dyDescent="0.3">
@@ -10592,10 +10650,10 @@
         <v>Jules</v>
       </c>
       <c r="BW138" s="1">
-        <v>4.6962962962962962</v>
+        <v>4.7410071942446042</v>
       </c>
       <c r="BX138" s="1">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="CA138" s="1" t="str">
         <v>Paul</v>
@@ -10639,16 +10697,16 @@
         <v>Marie</v>
       </c>
       <c r="BW139" s="1">
-        <v>4.2391304347826084</v>
+        <v>4.21875</v>
       </c>
       <c r="BX139" s="1">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="CA139" s="1" t="str">
         <v>Jules</v>
       </c>
       <c r="CB139" s="1">
-        <v>4.6962962962962962</v>
+        <v>4.7410071942446042</v>
       </c>
     </row>
     <row r="140" spans="1:80" x14ac:dyDescent="0.3">
@@ -10683,19 +10741,19 @@
         <v>12</v>
       </c>
       <c r="BV140" s="1" t="str">
-        <v>Joey</v>
+        <v>Luca</v>
       </c>
       <c r="BW140" s="1">
-        <v>3.0344827586206895</v>
+        <v>3.0112359550561796</v>
       </c>
       <c r="BX140" s="1">
-        <v>58</v>
+        <v>178</v>
       </c>
       <c r="CA140" s="1" t="str">
         <v>Marie</v>
       </c>
       <c r="CB140" s="1">
-        <v>4.2391304347826084</v>
+        <v>4.21875</v>
       </c>
     </row>
     <row r="141" spans="1:80" x14ac:dyDescent="0.3">
@@ -10730,19 +10788,19 @@
         <v>2</v>
       </c>
       <c r="BV141" s="1" t="str">
+        <v>Fantinne</v>
+      </c>
+      <c r="BW141" s="1">
+        <v>2.9607843137254903</v>
+      </c>
+      <c r="BX141" s="1">
+        <v>51</v>
+      </c>
+      <c r="CA141" s="1" t="str">
         <v>Luca</v>
       </c>
-      <c r="BW141" s="1">
+      <c r="CB141" s="1">
         <v>3.0112359550561796</v>
-      </c>
-      <c r="BX141" s="1">
-        <v>178</v>
-      </c>
-      <c r="CA141" s="1" t="str">
-        <v>Joey</v>
-      </c>
-      <c r="CB141" s="1">
-        <v>3.0344827586206895</v>
       </c>
     </row>
     <row r="142" spans="1:80" x14ac:dyDescent="0.3">
@@ -10777,19 +10835,19 @@
         <v>13</v>
       </c>
       <c r="BV142" s="1" t="str">
+        <v>Joey</v>
+      </c>
+      <c r="BW142" s="1">
+        <v>2.9333333333333331</v>
+      </c>
+      <c r="BX142" s="1">
+        <v>60</v>
+      </c>
+      <c r="CA142" s="1" t="str">
         <v>Fantinne</v>
       </c>
-      <c r="BW142" s="1">
+      <c r="CB142" s="1">
         <v>2.9607843137254903</v>
-      </c>
-      <c r="BX142" s="1">
-        <v>51</v>
-      </c>
-      <c r="CA142" s="1" t="str">
-        <v>Luca</v>
-      </c>
-      <c r="CB142" s="1">
-        <v>3.0112359550561796</v>
       </c>
     </row>
     <row r="143" spans="1:80" x14ac:dyDescent="0.3">
@@ -10833,10 +10891,10 @@
         <v>67</v>
       </c>
       <c r="CA143" s="1" t="str">
-        <v>Fantinne</v>
+        <v>Joey</v>
       </c>
       <c r="CB143" s="1">
-        <v>2.9607843137254903</v>
+        <v>2.9333333333333331</v>
       </c>
     </row>
     <row r="144" spans="1:80" x14ac:dyDescent="0.3">
@@ -10978,6 +11036,18 @@
     <sortCondition descending="1" ref="B136:B147"/>
   </sortState>
   <mergeCells count="28">
+    <mergeCell ref="AY9:AZ9"/>
+    <mergeCell ref="AA9:AB9"/>
+    <mergeCell ref="AC9:AD9"/>
+    <mergeCell ref="AE9:AF9"/>
+    <mergeCell ref="AK9:AL9"/>
+    <mergeCell ref="AI9:AJ9"/>
+    <mergeCell ref="AG9:AH9"/>
+    <mergeCell ref="AM9:AN9"/>
+    <mergeCell ref="AO9:AP9"/>
+    <mergeCell ref="AQ9:AR9"/>
+    <mergeCell ref="AS9:AT9"/>
+    <mergeCell ref="AU9:AV9"/>
     <mergeCell ref="BA9:BB9"/>
     <mergeCell ref="BC9:BD9"/>
     <mergeCell ref="BE9:BF9"/>
@@ -10994,18 +11064,6 @@
     <mergeCell ref="U9:V9"/>
     <mergeCell ref="W9:X9"/>
     <mergeCell ref="AW9:AX9"/>
-    <mergeCell ref="AY9:AZ9"/>
-    <mergeCell ref="AA9:AB9"/>
-    <mergeCell ref="AC9:AD9"/>
-    <mergeCell ref="AE9:AF9"/>
-    <mergeCell ref="AK9:AL9"/>
-    <mergeCell ref="AI9:AJ9"/>
-    <mergeCell ref="AG9:AH9"/>
-    <mergeCell ref="AM9:AN9"/>
-    <mergeCell ref="AO9:AP9"/>
-    <mergeCell ref="AQ9:AR9"/>
-    <mergeCell ref="AS9:AT9"/>
-    <mergeCell ref="AU9:AV9"/>
   </mergeCells>
   <conditionalFormatting sqref="C1 E1 G1 I1 K1 M1 O1 Q1 S1 U1 W1 Y1 AA1 AC1 AE1 AG1 AI1 AK1 AM1 AO1 AQ1 AS1 AU1 AW1 AY1 BA1 BC1 BE1 C9:AM9 AO9 AQ9 AS9 AU9 AW9 AY9 BA9 BC9 BE9">
     <cfRule type="expression" dxfId="24" priority="41" stopIfTrue="1">
@@ -11163,10 +11221,10 @@
         <v>Boris</v>
       </c>
       <c r="C3" s="25" t="str">
-        <v>7.246</v>
+        <v>7.263</v>
       </c>
       <c r="D3" s="25">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="F3" t="str">
         <v>entre 1 et 10</v>
@@ -11185,13 +11243,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="25" t="str">
-        <v>Joachim</v>
+        <v>Célian</v>
       </c>
       <c r="C4" s="25" t="str">
-        <v>6.202</v>
+        <v>6.236</v>
       </c>
       <c r="D4" s="25">
-        <v>104</v>
+        <v>246</v>
       </c>
       <c r="F4" t="str">
         <v>entre 10 et 20</v>
@@ -11209,13 +11267,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="25" t="str">
-        <v>Tom</v>
+        <v>Joachim</v>
       </c>
       <c r="C5" s="25" t="str">
-        <v>6.109</v>
+        <v>6.202</v>
       </c>
       <c r="D5" s="25">
-        <v>193</v>
+        <v>104</v>
       </c>
       <c r="F5" t="str">
         <v>entre 20 et 50</v>
@@ -11233,13 +11291,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="25" t="str">
-        <v>Célian</v>
+        <v>Tom</v>
       </c>
       <c r="C6" s="25" t="str">
-        <v>6.071</v>
+        <v>6.109</v>
       </c>
       <c r="D6" s="25">
-        <v>241</v>
+        <v>193</v>
       </c>
       <c r="F6" t="str">
         <v>entre 50 et 100</v>
@@ -11281,13 +11339,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="25" t="str">
-        <v>Lou</v>
+        <v>Samuel</v>
       </c>
       <c r="C8" s="25" t="str">
-        <v>5.917</v>
+        <v>5.910</v>
       </c>
       <c r="D8" s="25">
-        <v>72</v>
+        <v>211</v>
       </c>
       <c r="F8" t="str">
         <v>entre 250 et 500</v>
@@ -11305,13 +11363,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="25" t="str">
-        <v>Samuel</v>
+        <v>Mehdi</v>
       </c>
       <c r="C9" s="25" t="str">
-        <v>5.910</v>
+        <v>5.770</v>
       </c>
       <c r="D9" s="25">
-        <v>211</v>
+        <v>421</v>
       </c>
       <c r="F9" t="str">
         <v>entre 500 et 1000</v>
@@ -11329,13 +11387,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="25" t="str">
-        <v>Mehdi</v>
+        <v>Lou</v>
       </c>
       <c r="C10" s="25" t="str">
-        <v>5.770</v>
+        <v>5.553</v>
       </c>
       <c r="D10" s="25">
-        <v>421</v>
+        <v>76</v>
       </c>
       <c r="F10" t="str">
         <v>plus de 1000</v>
@@ -11356,10 +11414,10 @@
         <v>Damien</v>
       </c>
       <c r="C11" s="25" t="str">
-        <v>5.411</v>
+        <v>5.410</v>
       </c>
       <c r="D11" s="25">
-        <v>587</v>
+        <v>593</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
@@ -11412,10 +11470,10 @@
         <v>Jules</v>
       </c>
       <c r="C15" s="25" t="str">
-        <v>4.696</v>
+        <v>4.741</v>
       </c>
       <c r="D15" s="25">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
@@ -11426,10 +11484,10 @@
         <v>Marie</v>
       </c>
       <c r="C16" s="25" t="str">
-        <v>4.239</v>
+        <v>4.219</v>
       </c>
       <c r="D16" s="25">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
@@ -11437,13 +11495,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="25" t="str">
-        <v>Joey</v>
+        <v>Luca</v>
       </c>
       <c r="C17" s="25" t="str">
-        <v>3.034</v>
+        <v>3.011</v>
       </c>
       <c r="D17" s="25">
-        <v>58</v>
+        <v>178</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
@@ -11451,13 +11509,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="25" t="str">
-        <v>Luca</v>
+        <v>Fantinne</v>
       </c>
       <c r="C18" s="25" t="str">
-        <v>3.011</v>
+        <v>2.961</v>
       </c>
       <c r="D18" s="25">
-        <v>178</v>
+        <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
@@ -11465,13 +11523,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="25" t="str">
-        <v>Fantinne</v>
+        <v>Joey</v>
       </c>
       <c r="C19" s="25" t="str">
-        <v>2.961</v>
+        <v>2.933</v>
       </c>
       <c r="D19" s="25">
-        <v>51</v>
+        <v>60</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">

--- a/classement_whist_2023_2025.xlsx
+++ b/classement_whist_2023_2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a20b8382962b136a/Bureau/loisir/whist/projet_application_streamlit/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="731" documentId="8_{848EF4F6-53E4-4B52-9417-5BFB5A888B23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA45DFD6-B078-4097-A72F-963B71D5E789}"/>
+  <xr:revisionPtr revIDLastSave="769" documentId="8_{848EF4F6-53E4-4B52-9417-5BFB5A888B23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E3463EEB-0D8C-4D2C-A87F-BA91729B9517}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="91">
   <si>
     <t>global</t>
   </si>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="G1" s="1">
         <f t="shared" ref="G1" si="2">IF(H2&gt;19,G2/H2,"/")</f>
-        <v>7.2625615763546794</v>
+        <v>7.1964112512124148</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>2</v>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="M1" s="1">
         <f t="shared" ref="M1" si="5">IF(N2&gt;19,M2/N2,"/")</f>
-        <v>5.5986509274873528</v>
+        <v>5.4393700787401578</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>2</v>
@@ -1205,14 +1205,14 @@
       </c>
       <c r="Q1" s="1">
         <f t="shared" ref="Q1" si="7">IF(R2&gt;19,Q2/R2,"/")</f>
-        <v>6.2357723577235769</v>
+        <v>6.1106870229007635</v>
       </c>
       <c r="R1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="S1" s="1">
         <f t="shared" ref="S1" si="8">IF(T2&gt;19,S2/T2,"/")</f>
-        <v>6.1088082901554408</v>
+        <v>6.1578947368421053</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>2</v>
@@ -1240,14 +1240,14 @@
       </c>
       <c r="AA1" s="1">
         <f t="shared" ref="AA1" si="12">IF(AB2&gt;19,AA2/AB2,"/")</f>
-        <v>4.21875</v>
+        <v>4.328125</v>
       </c>
       <c r="AB1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="AC1" s="1">
         <f>IF(AD2&gt;19,AC2/AD2,"/")</f>
-        <v>4.7410071942446042</v>
+        <v>5.0709677419354842</v>
       </c>
       <c r="AD1" s="1" t="s">
         <v>2</v>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="AM1" s="1">
         <f t="shared" ref="AM1" si="17">IF(AN2&gt;19,AM2/AN2,"/")</f>
-        <v>2.9333333333333331</v>
+        <v>4.5</v>
       </c>
       <c r="AN1" s="1" t="s">
         <v>2</v>
@@ -1296,7 +1296,7 @@
       </c>
       <c r="AQ1" s="1">
         <f t="shared" ref="AQ1" si="19">IF(AR2&gt;19,AQ2/AR2,"/")</f>
-        <v>5.0149253731343286</v>
+        <v>4.096774193548387</v>
       </c>
       <c r="AR1" s="1" t="s">
         <v>2</v>
@@ -1336,9 +1336,9 @@
       <c r="BB1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="BC1" s="1" t="str">
+      <c r="BC1" s="1">
         <f t="shared" ref="BC1" si="25">IF(BD2&gt;19,BC2/BD2,"/")</f>
-        <v>/</v>
+        <v>4.4814814814814818</v>
       </c>
       <c r="BD1" s="1" t="s">
         <v>2</v>
@@ -1373,11 +1373,11 @@
       </c>
       <c r="G2" s="1">
         <f t="shared" si="27"/>
-        <v>7371.5</v>
+        <v>7419.5</v>
       </c>
       <c r="H2" s="1">
         <f t="shared" si="27"/>
-        <v>1015</v>
+        <v>1031</v>
       </c>
       <c r="I2" s="1">
         <f t="shared" si="27"/>
@@ -1397,11 +1397,11 @@
       </c>
       <c r="M2" s="1">
         <f t="shared" si="28"/>
-        <v>3320</v>
+        <v>3454</v>
       </c>
       <c r="N2" s="1">
         <f t="shared" si="28"/>
-        <v>593</v>
+        <v>635</v>
       </c>
       <c r="O2" s="1">
         <f t="shared" si="28"/>
@@ -1413,19 +1413,19 @@
       </c>
       <c r="Q2" s="1">
         <f t="shared" si="28"/>
-        <v>1534</v>
+        <v>1601</v>
       </c>
       <c r="R2" s="1">
         <f t="shared" si="28"/>
-        <v>246</v>
+        <v>262</v>
       </c>
       <c r="S2" s="1">
         <f t="shared" si="28"/>
-        <v>1179</v>
+        <v>1287</v>
       </c>
       <c r="T2" s="1">
         <f t="shared" si="28"/>
-        <v>193</v>
+        <v>209</v>
       </c>
       <c r="U2" s="1">
         <f t="shared" si="28"/>
@@ -1453,19 +1453,19 @@
       </c>
       <c r="AA2" s="1">
         <f t="shared" si="28"/>
-        <v>877.5</v>
+        <v>969.5</v>
       </c>
       <c r="AB2" s="1">
         <f t="shared" si="28"/>
-        <v>208</v>
+        <v>224</v>
       </c>
       <c r="AC2" s="1">
         <f t="shared" si="28"/>
-        <v>659</v>
+        <v>786</v>
       </c>
       <c r="AD2" s="1">
         <f t="shared" si="28"/>
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="AE2" s="1">
         <f t="shared" si="28"/>
@@ -1501,11 +1501,11 @@
       </c>
       <c r="AM2" s="1">
         <f t="shared" si="28"/>
-        <v>176</v>
+        <v>387</v>
       </c>
       <c r="AN2" s="1">
         <f t="shared" si="28"/>
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="AO2" s="1">
         <f t="shared" si="28"/>
@@ -1517,11 +1517,11 @@
       </c>
       <c r="AQ2" s="1">
         <f t="shared" si="28"/>
-        <v>336</v>
+        <v>381</v>
       </c>
       <c r="AR2" s="1">
         <f t="shared" si="28"/>
-        <v>67</v>
+        <v>93</v>
       </c>
       <c r="AS2" s="1">
         <f t="shared" si="28"/>
@@ -1565,11 +1565,11 @@
       </c>
       <c r="BC2" s="1">
         <f t="shared" si="29"/>
-        <v>64</v>
+        <v>121</v>
       </c>
       <c r="BD2" s="1">
         <f t="shared" si="29"/>
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="BE2" s="1">
         <f t="shared" ref="BE2:BF2" si="30">BE4+BE6+BE8</f>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="G7" s="15">
         <f t="shared" ref="G7" si="94">G8/H8</f>
-        <v>7.5887755102040817</v>
+        <v>7.4436758893280635</v>
       </c>
       <c r="H7" s="15" t="s">
         <v>2</v>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="M7" s="15">
         <f t="shared" ref="M7" si="97">M8/N8</f>
-        <v>6.1827160493827158</v>
+        <v>5.9015659955257274</v>
       </c>
       <c r="N7" s="15" t="s">
         <v>2</v>
@@ -2522,14 +2522,14 @@
       </c>
       <c r="Q7" s="15">
         <f t="shared" ref="Q7" si="99">Q8/R8</f>
-        <v>6.4210526315789478</v>
+        <v>6.2299465240641707</v>
       </c>
       <c r="R7" s="15" t="s">
         <v>2</v>
       </c>
       <c r="S7" s="15">
         <f t="shared" ref="S7" si="100">S8/T8</f>
-        <v>4.8965517241379306</v>
+        <v>5.1844660194174761</v>
       </c>
       <c r="T7" s="15" t="s">
         <v>2</v>
@@ -2557,14 +2557,14 @@
       </c>
       <c r="AA7" s="15">
         <f t="shared" ref="AA7" si="104">AA8/AB8</f>
-        <v>4.8129251700680271</v>
+        <v>4.904907975460123</v>
       </c>
       <c r="AB7" s="15" t="s">
         <v>2</v>
       </c>
       <c r="AC7" s="15">
         <f t="shared" ref="AC7" si="105">AC8/AD8</f>
-        <v>4.9844961240310077</v>
+        <v>5.3103448275862073</v>
       </c>
       <c r="AD7" s="15" t="s">
         <v>2</v>
@@ -2599,7 +2599,7 @@
       </c>
       <c r="AM7" s="15">
         <f t="shared" ref="AM7" si="110">AM8/AN8</f>
-        <v>2.9333333333333331</v>
+        <v>4.5</v>
       </c>
       <c r="AN7" s="15" t="s">
         <v>2</v>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="AQ7" s="15">
         <f t="shared" ref="AQ7" si="112">AQ8/AR8</f>
-        <v>5.4117647058823533</v>
+        <v>4.1688311688311686</v>
       </c>
       <c r="AR7" s="15" t="s">
         <v>2</v>
@@ -2655,7 +2655,7 @@
       </c>
       <c r="BC7" s="15">
         <f t="shared" ref="BC7" si="118">BC8/BD8</f>
-        <v>3.7647058823529411</v>
+        <v>4.4814814814814818</v>
       </c>
       <c r="BD7" s="15" t="s">
         <v>2</v>
@@ -2691,11 +2691,11 @@
       </c>
       <c r="G8" s="15">
         <f t="shared" si="120"/>
-        <v>3718.5</v>
+        <v>3766.5</v>
       </c>
       <c r="H8" s="15">
         <f t="shared" si="120"/>
-        <v>490</v>
+        <v>506</v>
       </c>
       <c r="I8" s="15">
         <f t="shared" si="120"/>
@@ -2715,11 +2715,11 @@
       </c>
       <c r="M8" s="15">
         <f t="shared" si="121"/>
-        <v>2504</v>
+        <v>2638</v>
       </c>
       <c r="N8" s="15">
         <f t="shared" si="121"/>
-        <v>405</v>
+        <v>447</v>
       </c>
       <c r="O8" s="15">
         <f t="shared" si="121"/>
@@ -2731,19 +2731,19 @@
       </c>
       <c r="Q8" s="15">
         <f t="shared" si="121"/>
-        <v>1098</v>
+        <v>1165</v>
       </c>
       <c r="R8" s="15">
         <f t="shared" si="121"/>
-        <v>171</v>
+        <v>187</v>
       </c>
       <c r="S8" s="15">
         <f t="shared" si="121"/>
-        <v>426</v>
+        <v>534</v>
       </c>
       <c r="T8" s="15">
         <f t="shared" si="121"/>
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="U8" s="15">
         <f t="shared" si="121"/>
@@ -2771,19 +2771,19 @@
       </c>
       <c r="AA8" s="15">
         <f t="shared" si="121"/>
-        <v>707.5</v>
+        <v>799.5</v>
       </c>
       <c r="AB8" s="15">
         <f t="shared" si="121"/>
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="AC8" s="15">
         <f t="shared" si="121"/>
-        <v>643</v>
+        <v>770</v>
       </c>
       <c r="AD8" s="15">
         <f t="shared" si="121"/>
-        <v>129</v>
+        <v>145</v>
       </c>
       <c r="AE8" s="15">
         <f t="shared" si="121"/>
@@ -2819,11 +2819,11 @@
       </c>
       <c r="AM8" s="15">
         <f t="shared" si="121"/>
-        <v>176</v>
+        <v>387</v>
       </c>
       <c r="AN8" s="15">
         <f t="shared" si="121"/>
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="AO8" s="15">
         <f t="shared" si="121"/>
@@ -2835,11 +2835,11 @@
       </c>
       <c r="AQ8" s="15">
         <f t="shared" si="121"/>
-        <v>276</v>
+        <v>321</v>
       </c>
       <c r="AR8" s="15">
         <f t="shared" si="121"/>
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="AS8" s="15">
         <f t="shared" si="121"/>
@@ -2883,11 +2883,11 @@
       </c>
       <c r="BC8" s="15">
         <f t="shared" si="122"/>
-        <v>64</v>
+        <v>121</v>
       </c>
       <c r="BD8" s="15">
         <f t="shared" si="122"/>
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="BE8" s="15">
         <f t="shared" ref="BE8:BF8" si="123">SUM(BE10:BE94)</f>
@@ -3053,24 +3053,111 @@
       </c>
     </row>
     <row r="18" spans="1:58" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="B18" s="1">
         <v>132</v>
       </c>
+      <c r="G18" s="1">
+        <v>48</v>
+      </c>
+      <c r="H18" s="1">
+        <v>16</v>
+      </c>
+      <c r="M18" s="1">
+        <v>86</v>
+      </c>
+      <c r="N18" s="1">
+        <v>16</v>
+      </c>
+      <c r="S18" s="1">
+        <v>108</v>
+      </c>
+      <c r="T18" s="1">
+        <v>16</v>
+      </c>
+      <c r="AA18" s="1">
+        <v>92</v>
+      </c>
+      <c r="AB18" s="1">
+        <v>16</v>
+      </c>
+      <c r="AC18" s="1">
+        <v>127</v>
+      </c>
+      <c r="AD18" s="1">
+        <v>16</v>
+      </c>
     </row>
     <row r="19" spans="1:58" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="B19" s="1">
         <v>131</v>
       </c>
+      <c r="M19" s="1">
+        <v>48</v>
+      </c>
+      <c r="N19" s="1">
+        <v>10</v>
+      </c>
+      <c r="AM19" s="1">
+        <v>54</v>
+      </c>
+      <c r="AN19" s="1">
+        <v>10</v>
+      </c>
+      <c r="AQ19" s="1">
+        <v>23</v>
+      </c>
+      <c r="AR19" s="1">
+        <v>10</v>
+      </c>
+      <c r="BC19" s="1">
+        <v>57</v>
+      </c>
+      <c r="BD19" s="1">
+        <v>10</v>
+      </c>
     </row>
     <row r="20" spans="1:58" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="B20" s="1">
         <v>130</v>
       </c>
       <c r="M20" s="1">
         <v>112</v>
       </c>
+      <c r="N20" s="1">
+        <v>16</v>
+      </c>
+      <c r="Q20" s="1">
+        <v>67</v>
+      </c>
+      <c r="R20" s="1">
+        <v>16</v>
+      </c>
+      <c r="AM20" s="1">
+        <v>157</v>
+      </c>
+      <c r="AN20" s="1">
+        <v>16</v>
+      </c>
+      <c r="AQ20" s="1">
+        <v>22</v>
+      </c>
+      <c r="AR20" s="1">
+        <v>16</v>
+      </c>
     </row>
     <row r="21" spans="1:58" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="B21" s="1">
         <v>129</v>
       </c>
@@ -3106,6 +3193,9 @@
       </c>
     </row>
     <row r="22" spans="1:58" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="B22" s="1">
         <v>128</v>
       </c>
@@ -3141,6 +3231,9 @@
       </c>
     </row>
     <row r="23" spans="1:58" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="B23" s="1">
         <v>127</v>
       </c>
@@ -3170,6 +3263,9 @@
       </c>
     </row>
     <row r="24" spans="1:58" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="B24" s="1">
         <v>126</v>
       </c>
@@ -3199,6 +3295,9 @@
       </c>
     </row>
     <row r="25" spans="1:58" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="B25" s="1">
         <v>125</v>
       </c>
@@ -3228,6 +3327,9 @@
       </c>
     </row>
     <row r="26" spans="1:58" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="B26" s="1">
         <v>124</v>
       </c>
@@ -3295,6 +3397,9 @@
       </c>
     </row>
     <row r="28" spans="1:58" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="B28" s="1">
         <v>122</v>
       </c>
@@ -3324,6 +3429,9 @@
       </c>
     </row>
     <row r="29" spans="1:58" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="B29" s="1">
         <v>121</v>
       </c>
@@ -4953,7 +5061,7 @@
         <v>30</v>
       </c>
       <c r="BL72" s="1" cm="1">
-        <f t="array" ref="BL72:BO90">_xlfn.LET(
+        <f t="array" ref="BL72:BO91">_xlfn.LET(
   _xlpm.cols_impairs, _xlfn.SEQUENCE(1,COLUMNS(C1:BF1)/2,1,2),
   _xlpm.cols_pairs,   _xlfn.SEQUENCE(1,COLUMNS(C2:BF2)/2,2,2),
   _xlpm.noms,     TRANSPOSE(INDEX(C9:BF9,,_xlpm.cols_impairs)),
@@ -4982,7 +5090,7 @@
         <v>69</v>
       </c>
       <c r="BQ72" s="1" cm="1">
-        <f t="array" ref="BQ72:BT80">_xlfn.LET(
+        <f t="array" ref="BQ72:BT79">_xlfn.LET(
   _xlpm.cols_impairs, _xlfn.SEQUENCE(1,COLUMNS(C1:BF1)/2,1,2),
   _xlpm.cols_pairs,   _xlfn.SEQUENCE(1,COLUMNS(C2:BF2)/2,2,2),
   _xlpm.noms,     TRANSPOSE(INDEX(C9:BF9,,_xlpm.cols_impairs)),
@@ -5061,10 +5169,10 @@
         <v>Boris</v>
       </c>
       <c r="BN73" s="1" t="str">
-        <v>7.263</v>
+        <v>7.196</v>
       </c>
       <c r="BO73" s="1">
-        <v>1015</v>
+        <v>1031</v>
       </c>
       <c r="BQ73" s="1">
         <v>2</v>
@@ -5082,7 +5190,7 @@
         <v>Boris</v>
       </c>
       <c r="BW73" s="1">
-        <v>7.2625615763546794</v>
+        <v>7.1964112512124148</v>
       </c>
     </row>
     <row r="74" spans="1:75" x14ac:dyDescent="0.3">
@@ -5124,13 +5232,13 @@
         <v>3</v>
       </c>
       <c r="BM74" s="1" t="str">
-        <v>Célian</v>
+        <v>Joachim</v>
       </c>
       <c r="BN74" s="1" t="str">
-        <v>6.236</v>
+        <v>6.202</v>
       </c>
       <c r="BO74" s="1">
-        <v>246</v>
+        <v>104</v>
       </c>
       <c r="BQ74" s="1">
         <v>3</v>
@@ -5145,10 +5253,10 @@
         <v>17</v>
       </c>
       <c r="BV74" s="1" t="str">
-        <v>Célian</v>
+        <v>Joachim</v>
       </c>
       <c r="BW74" s="1">
-        <v>6.2357723577235769</v>
+        <v>6.2019230769230766</v>
       </c>
     </row>
     <row r="75" spans="1:75" x14ac:dyDescent="0.3">
@@ -5186,13 +5294,13 @@
         <v>4</v>
       </c>
       <c r="BM75" s="1" t="str">
-        <v>Joachim</v>
+        <v>Tom</v>
       </c>
       <c r="BN75" s="1" t="str">
-        <v>6.202</v>
+        <v>6.158</v>
       </c>
       <c r="BO75" s="1">
-        <v>104</v>
+        <v>209</v>
       </c>
       <c r="BQ75" s="1">
         <v>4</v>
@@ -5207,10 +5315,10 @@
         <v>5</v>
       </c>
       <c r="BV75" s="1" t="str">
-        <v>Joachim</v>
+        <v>Tom</v>
       </c>
       <c r="BW75" s="1">
-        <v>6.2019230769230766</v>
+        <v>6.1578947368421053</v>
       </c>
     </row>
     <row r="76" spans="1:75" x14ac:dyDescent="0.3">
@@ -5252,31 +5360,31 @@
         <v>5</v>
       </c>
       <c r="BM76" s="1" t="str">
-        <v>Tom</v>
+        <v>Célian</v>
       </c>
       <c r="BN76" s="1" t="str">
-        <v>6.109</v>
+        <v>6.111</v>
       </c>
       <c r="BO76" s="1">
-        <v>193</v>
+        <v>262</v>
       </c>
       <c r="BQ76" s="1">
         <v>5</v>
       </c>
       <c r="BR76" s="1" t="str">
-        <v>Stanislas</v>
+        <v>Émile</v>
       </c>
       <c r="BS76" s="1" t="str">
-        <v>3.765</v>
+        <v>3.308</v>
       </c>
       <c r="BT76" s="1">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="BV76" s="1" t="str">
-        <v>Tom</v>
+        <v>Célian</v>
       </c>
       <c r="BW76" s="1">
-        <v>6.1088082901554408</v>
+        <v>6.1106870229007635</v>
       </c>
     </row>
     <row r="77" spans="1:75" x14ac:dyDescent="0.3">
@@ -5330,13 +5438,13 @@
         <v>6</v>
       </c>
       <c r="BR77" s="1" t="str">
-        <v>Émile</v>
+        <v>Aurélien</v>
       </c>
       <c r="BS77" s="1" t="str">
-        <v>3.308</v>
+        <v>2.800</v>
       </c>
       <c r="BT77" s="1">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="BV77" s="1" t="str">
         <v>William</v>
@@ -5396,13 +5504,13 @@
         <v>7</v>
       </c>
       <c r="BR78" s="1" t="str">
-        <v>Aurélien</v>
+        <v>Maxime_Go</v>
       </c>
       <c r="BS78" s="1" t="str">
-        <v>2.800</v>
+        <v>0.727</v>
       </c>
       <c r="BT78" s="1">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="BV78" s="1" t="str">
         <v>Samuel</v>
@@ -5458,13 +5566,13 @@
         <v>8</v>
       </c>
       <c r="BR79" s="1" t="str">
-        <v>Maxime_Go</v>
+        <v>Robin</v>
       </c>
       <c r="BS79" s="1" t="str">
-        <v>0.727</v>
+        <v>-0.083</v>
       </c>
       <c r="BT79" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BV79" s="1" t="str">
         <v>Mehdi</v>
@@ -5557,31 +5665,19 @@
         <v>9</v>
       </c>
       <c r="BM80" s="1" t="str">
-        <v>Damien</v>
+        <v>Lou</v>
       </c>
       <c r="BN80" s="1" t="str">
-        <v>5.599</v>
+        <v>5.553</v>
       </c>
       <c r="BO80" s="1">
-        <v>593</v>
-      </c>
-      <c r="BQ80" s="1">
-        <v>9</v>
-      </c>
-      <c r="BR80" s="1" t="str">
-        <v>Robin</v>
-      </c>
-      <c r="BS80" s="1" t="str">
-        <v>-0.083</v>
-      </c>
-      <c r="BT80" s="1">
-        <v>12</v>
+        <v>76</v>
       </c>
       <c r="BV80" s="1" t="str">
-        <v>Damien</v>
+        <v>Lou</v>
       </c>
       <c r="BW80" s="1">
-        <v>5.5986509274873528</v>
+        <v>5.5526315789473681</v>
       </c>
     </row>
     <row r="81" spans="1:75" x14ac:dyDescent="0.3">
@@ -5664,19 +5760,19 @@
         <v>10</v>
       </c>
       <c r="BM81" s="1" t="str">
-        <v>Lou</v>
+        <v>Damien</v>
       </c>
       <c r="BN81" s="1" t="str">
-        <v>5.553</v>
+        <v>5.439</v>
       </c>
       <c r="BO81" s="1">
-        <v>76</v>
+        <v>635</v>
       </c>
       <c r="BV81" s="1" t="str">
-        <v>Lou</v>
+        <v>Damien</v>
       </c>
       <c r="BW81" s="1">
-        <v>5.5526315789473681</v>
+        <v>5.4393700787401578</v>
       </c>
     </row>
     <row r="82" spans="1:75" x14ac:dyDescent="0.3">
@@ -5850,19 +5946,19 @@
         <v>12</v>
       </c>
       <c r="BM83" s="1" t="str">
-        <v>Quentin</v>
+        <v>Jules</v>
       </c>
       <c r="BN83" s="1" t="str">
-        <v>5.015</v>
+        <v>5.071</v>
       </c>
       <c r="BO83" s="1">
-        <v>67</v>
+        <v>155</v>
       </c>
       <c r="BV83" s="1" t="str">
-        <v>Quentin</v>
+        <v>Jules</v>
       </c>
       <c r="BW83" s="1">
-        <v>5.0149253731343286</v>
+        <v>5.0709677419354842</v>
       </c>
     </row>
     <row r="84" spans="1:75" x14ac:dyDescent="0.3">
@@ -5946,7 +6042,7 @@
       </c>
       <c r="BJ84" s="1">
         <f>AVERAGE(C1:BF1)</f>
-        <v>5.1165482575065964</v>
+        <v>5.1241159673426404</v>
       </c>
       <c r="BL84" s="1">
         <v>13</v>
@@ -6043,19 +6139,19 @@
         <v>14</v>
       </c>
       <c r="BM85" s="1" t="str">
-        <v>Jules</v>
+        <v>Joey</v>
       </c>
       <c r="BN85" s="1" t="str">
-        <v>4.741</v>
+        <v>4.500</v>
       </c>
       <c r="BO85" s="1">
-        <v>139</v>
+        <v>86</v>
       </c>
       <c r="BV85" s="1" t="str">
-        <v>Jules</v>
+        <v>Joey</v>
       </c>
       <c r="BW85" s="1">
-        <v>4.7410071942446042</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="86" spans="1:75" x14ac:dyDescent="0.3">
@@ -6138,19 +6234,19 @@
         <v>15</v>
       </c>
       <c r="BM86" s="1" t="str">
-        <v>Marie</v>
+        <v>Stanislas</v>
       </c>
       <c r="BN86" s="1" t="str">
-        <v>4.219</v>
+        <v>4.481</v>
       </c>
       <c r="BO86" s="1">
-        <v>208</v>
+        <v>27</v>
       </c>
       <c r="BV86" s="1" t="str">
-        <v>Marie</v>
+        <v>Stanislas</v>
       </c>
       <c r="BW86" s="1">
-        <v>4.21875</v>
+        <v>4.4814814814814818</v>
       </c>
     </row>
     <row r="87" spans="1:75" x14ac:dyDescent="0.3">
@@ -6232,19 +6328,19 @@
         <v>16</v>
       </c>
       <c r="BM87" s="1" t="str">
-        <v>Luca</v>
+        <v>Marie</v>
       </c>
       <c r="BN87" s="1" t="str">
-        <v>3.011</v>
+        <v>4.328</v>
       </c>
       <c r="BO87" s="1">
-        <v>178</v>
+        <v>224</v>
       </c>
       <c r="BV87" s="1" t="str">
-        <v>Luca</v>
+        <v>Marie</v>
       </c>
       <c r="BW87" s="1">
-        <v>3.0112359550561796</v>
+        <v>4.328125</v>
       </c>
     </row>
     <row r="88" spans="1:75" x14ac:dyDescent="0.3">
@@ -6335,19 +6431,19 @@
         <v>17</v>
       </c>
       <c r="BM88" s="1" t="str">
-        <v>Fantinne</v>
+        <v>Quentin</v>
       </c>
       <c r="BN88" s="1" t="str">
-        <v>2.961</v>
+        <v>4.097</v>
       </c>
       <c r="BO88" s="1">
-        <v>51</v>
+        <v>93</v>
       </c>
       <c r="BV88" s="1" t="str">
-        <v>Fantinne</v>
+        <v>Quentin</v>
       </c>
       <c r="BW88" s="1">
-        <v>2.9607843137254903</v>
+        <v>4.096774193548387</v>
       </c>
     </row>
     <row r="89" spans="1:75" x14ac:dyDescent="0.3">
@@ -6430,19 +6526,19 @@
         <v>18</v>
       </c>
       <c r="BM89" s="1" t="str">
-        <v>Joey</v>
+        <v>Luca</v>
       </c>
       <c r="BN89" s="1" t="str">
-        <v>2.933</v>
+        <v>3.011</v>
       </c>
       <c r="BO89" s="1">
-        <v>60</v>
+        <v>178</v>
       </c>
       <c r="BV89" s="1" t="str">
-        <v>Joey</v>
+        <v>Luca</v>
       </c>
       <c r="BW89" s="1">
-        <v>2.9333333333333331</v>
+        <v>3.0112359550561796</v>
       </c>
     </row>
     <row r="90" spans="1:75" x14ac:dyDescent="0.3">
@@ -6529,19 +6625,19 @@
         <v>19</v>
       </c>
       <c r="BM90" s="1" t="str">
-        <v>Loulou</v>
+        <v>Fantinne</v>
       </c>
       <c r="BN90" s="1" t="str">
-        <v>2.075</v>
+        <v>2.961</v>
       </c>
       <c r="BO90" s="1">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="BV90" s="1" t="str">
-        <v>Loulou</v>
+        <v>Fantinne</v>
       </c>
       <c r="BW90" s="1">
-        <v>2.0746268656716418</v>
+        <v>2.9607843137254903</v>
       </c>
     </row>
     <row r="91" spans="1:75" x14ac:dyDescent="0.3">
@@ -6620,11 +6716,23 @@
       <c r="BJ91" s="1" t="s">
         <v>16</v>
       </c>
+      <c r="BL91" s="1">
+        <v>20</v>
+      </c>
+      <c r="BM91" s="1" t="str">
+        <v>Loulou</v>
+      </c>
+      <c r="BN91" s="1" t="str">
+        <v>2.075</v>
+      </c>
+      <c r="BO91" s="1">
+        <v>67</v>
+      </c>
       <c r="BV91" s="1" t="str">
-        <v>Harrison</v>
-      </c>
-      <c r="BW91" s="1" t="str">
-        <v>/</v>
+        <v>Loulou</v>
+      </c>
+      <c r="BW91" s="1">
+        <v>2.0746268656716418</v>
       </c>
     </row>
     <row r="92" spans="1:75" x14ac:dyDescent="0.3">
@@ -6700,7 +6808,7 @@
       <c r="AX92" s="15"/>
       <c r="AY92" s="15"/>
       <c r="BV92" s="1" t="str">
-        <v>Pascale</v>
+        <v>Harrison</v>
       </c>
       <c r="BW92" s="1" t="str">
         <v>/</v>
@@ -6783,7 +6891,7 @@
       <c r="AX93" s="15"/>
       <c r="AY93" s="15"/>
       <c r="BV93" s="1" t="str">
-        <v>Robin</v>
+        <v>Pascale</v>
       </c>
       <c r="BW93" s="1" t="str">
         <v>/</v>
@@ -6866,7 +6974,7 @@
       <c r="AX94" s="15"/>
       <c r="AY94" s="15"/>
       <c r="BV94" s="1" t="str">
-        <v>Maxime_Go</v>
+        <v>Robin</v>
       </c>
       <c r="BW94" s="1" t="str">
         <v>/</v>
@@ -6929,7 +7037,7 @@
       <c r="AX95" s="15"/>
       <c r="AY95" s="15"/>
       <c r="BV95" s="1" t="str">
-        <v>Maxime_Ca</v>
+        <v>Maxime_Go</v>
       </c>
       <c r="BW95" s="1" t="str">
         <v>/</v>
@@ -7008,7 +7116,7 @@
       <c r="AX96" s="15"/>
       <c r="AY96" s="15"/>
       <c r="BV96" s="1" t="str">
-        <v>Aurélien</v>
+        <v>Maxime_Ca</v>
       </c>
       <c r="BW96" s="1" t="str">
         <v>/</v>
@@ -7091,7 +7199,7 @@
       <c r="AX97" s="15"/>
       <c r="AY97" s="15"/>
       <c r="BV97" s="1" t="str">
-        <v>Émile</v>
+        <v>Aurélien</v>
       </c>
       <c r="BW97" s="1" t="str">
         <v>/</v>
@@ -7170,7 +7278,7 @@
       <c r="AX98" s="15"/>
       <c r="AY98" s="15"/>
       <c r="BV98" s="1" t="str">
-        <v>Amélie</v>
+        <v>Émile</v>
       </c>
       <c r="BW98" s="1" t="str">
         <v>/</v>
@@ -7249,7 +7357,7 @@
       <c r="AX99" s="15"/>
       <c r="AY99" s="15"/>
       <c r="BV99" s="1" t="str">
-        <v>Stanislas</v>
+        <v>Amélie</v>
       </c>
       <c r="BW99" s="1" t="str">
         <v>/</v>
@@ -7624,7 +7732,7 @@
       <c r="AX104" s="15"/>
       <c r="AY104" s="15"/>
       <c r="BV104" s="1" cm="1">
-        <f t="array" ref="BV104:BY122">_xlfn.LET(
+        <f t="array" ref="BV104:BY123">_xlfn.LET(
   _xlpm.cols_impairs, _xlfn.SEQUENCE(1,COLUMNS(C1:BF1)/2,1,2),
   _xlpm.cols_pairs,   _xlfn.SEQUENCE(1,COLUMNS(C2:BF2)/2,2,2),
   _xlpm.noms,     TRANSPOSE(INDEX(C9:BF9,,_xlpm.cols_impairs)),
@@ -7736,10 +7844,10 @@
         <v>Boris</v>
       </c>
       <c r="BX105" s="1">
-        <v>7.2629999999999999</v>
+        <v>7.1959999999999997</v>
       </c>
       <c r="BY105" s="1">
-        <v>1015</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="106" spans="1:77" x14ac:dyDescent="0.3">
@@ -7822,13 +7930,13 @@
         <v>3</v>
       </c>
       <c r="BW106" s="1" t="str">
-        <v>Célian</v>
+        <v>Joachim</v>
       </c>
       <c r="BX106" s="1">
-        <v>6.2359999999999998</v>
+        <v>6.202</v>
       </c>
       <c r="BY106" s="1">
-        <v>246</v>
+        <v>104</v>
       </c>
     </row>
     <row r="107" spans="1:77" x14ac:dyDescent="0.3">
@@ -7907,13 +8015,13 @@
         <v>4</v>
       </c>
       <c r="BW107" s="1" t="str">
-        <v>Joachim</v>
+        <v>Tom</v>
       </c>
       <c r="BX107" s="1">
-        <v>6.202</v>
+        <v>6.1580000000000004</v>
       </c>
       <c r="BY107" s="1">
-        <v>104</v>
+        <v>209</v>
       </c>
     </row>
     <row r="108" spans="1:77" x14ac:dyDescent="0.3">
@@ -7992,13 +8100,13 @@
         <v>5</v>
       </c>
       <c r="BW108" s="1" t="str">
-        <v>Tom</v>
+        <v>Célian</v>
       </c>
       <c r="BX108" s="1">
-        <v>6.109</v>
+        <v>6.1109999999999998</v>
       </c>
       <c r="BY108" s="1">
-        <v>193</v>
+        <v>262</v>
       </c>
     </row>
     <row r="109" spans="1:77" x14ac:dyDescent="0.3">
@@ -8341,13 +8449,13 @@
         <v>9</v>
       </c>
       <c r="BW112" s="1" t="str">
-        <v>Damien</v>
+        <v>Lou</v>
       </c>
       <c r="BX112" s="1">
-        <v>5.5990000000000002</v>
+        <v>5.5529999999999999</v>
       </c>
       <c r="BY112" s="1">
-        <v>593</v>
+        <v>76</v>
       </c>
     </row>
     <row r="113" spans="1:77" x14ac:dyDescent="0.3">
@@ -8430,13 +8538,13 @@
         <v>10</v>
       </c>
       <c r="BW113" s="1" t="str">
-        <v>Lou</v>
+        <v>Damien</v>
       </c>
       <c r="BX113" s="1">
-        <v>5.5529999999999999</v>
+        <v>5.4390000000000001</v>
       </c>
       <c r="BY113" s="1">
-        <v>76</v>
+        <v>635</v>
       </c>
     </row>
     <row r="114" spans="1:77" x14ac:dyDescent="0.3">
@@ -8600,13 +8708,13 @@
         <v>12</v>
       </c>
       <c r="BW115" s="1" t="str">
-        <v>Quentin</v>
+        <v>Jules</v>
       </c>
       <c r="BX115" s="1">
-        <v>5.0149999999999997</v>
+        <v>5.0709999999999997</v>
       </c>
       <c r="BY115" s="1">
-        <v>67</v>
+        <v>155</v>
       </c>
     </row>
     <row r="116" spans="1:77" x14ac:dyDescent="0.3">
@@ -8770,13 +8878,13 @@
         <v>14</v>
       </c>
       <c r="BW117" s="1" t="str">
-        <v>Jules</v>
+        <v>Joey</v>
       </c>
       <c r="BX117" s="1">
-        <v>4.7409999999999997</v>
+        <v>4.5</v>
       </c>
       <c r="BY117" s="1">
-        <v>139</v>
+        <v>86</v>
       </c>
     </row>
     <row r="118" spans="1:77" x14ac:dyDescent="0.3">
@@ -8855,13 +8963,13 @@
         <v>15</v>
       </c>
       <c r="BW118" s="1" t="str">
-        <v>Marie</v>
+        <v>Stanislas</v>
       </c>
       <c r="BX118" s="1">
-        <v>4.2190000000000003</v>
+        <v>4.4809999999999999</v>
       </c>
       <c r="BY118" s="1">
-        <v>208</v>
+        <v>27</v>
       </c>
     </row>
     <row r="119" spans="1:77" x14ac:dyDescent="0.3">
@@ -8940,13 +9048,13 @@
         <v>16</v>
       </c>
       <c r="BW119" s="1" t="str">
-        <v>Luca</v>
+        <v>Marie</v>
       </c>
       <c r="BX119" s="1">
-        <v>3.0110000000000001</v>
+        <v>4.3280000000000003</v>
       </c>
       <c r="BY119" s="1">
-        <v>178</v>
+        <v>224</v>
       </c>
     </row>
     <row r="120" spans="1:77" x14ac:dyDescent="0.3">
@@ -9025,13 +9133,13 @@
         <v>17</v>
       </c>
       <c r="BW120" s="1" t="str">
-        <v>Fantinne</v>
+        <v>Quentin</v>
       </c>
       <c r="BX120" s="1">
-        <v>2.9609999999999999</v>
+        <v>4.0970000000000004</v>
       </c>
       <c r="BY120" s="1">
-        <v>51</v>
+        <v>93</v>
       </c>
     </row>
     <row r="121" spans="1:77" x14ac:dyDescent="0.3">
@@ -9118,13 +9226,13 @@
         <v>18</v>
       </c>
       <c r="BW121" s="1" t="str">
-        <v>Joey</v>
+        <v>Luca</v>
       </c>
       <c r="BX121" s="1">
-        <v>2.9329999999999998</v>
+        <v>3.0110000000000001</v>
       </c>
       <c r="BY121" s="1">
-        <v>60</v>
+        <v>178</v>
       </c>
     </row>
     <row r="122" spans="1:77" x14ac:dyDescent="0.3">
@@ -9203,13 +9311,13 @@
         <v>19</v>
       </c>
       <c r="BW122" s="1" t="str">
-        <v>Loulou</v>
+        <v>Fantinne</v>
       </c>
       <c r="BX122" s="1">
-        <v>2.0750000000000002</v>
+        <v>2.9609999999999999</v>
       </c>
       <c r="BY122" s="1">
-        <v>67</v>
+        <v>51</v>
       </c>
     </row>
     <row r="123" spans="1:77" x14ac:dyDescent="0.3">
@@ -9288,6 +9396,18 @@
       <c r="AW123" s="15"/>
       <c r="AX123" s="15"/>
       <c r="AY123" s="15"/>
+      <c r="BV123" s="1">
+        <v>20</v>
+      </c>
+      <c r="BW123" s="1" t="str">
+        <v>Loulou</v>
+      </c>
+      <c r="BX123" s="1">
+        <v>2.0750000000000002</v>
+      </c>
+      <c r="BY123" s="1">
+        <v>67</v>
+      </c>
     </row>
     <row r="124" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A124" s="15" t="s">
@@ -9821,7 +9941,7 @@
         <v>69</v>
       </c>
       <c r="CA130" s="1" t="str" cm="1">
-        <f t="array" ref="CA130:CB148">_xlfn.LET(  _xlpm.noms, TRANSPOSE(INDEX(C9:BF9,_xlfn.SEQUENCE(1,COLUMNS(C9:BF9)/2,1,2))),_xlpm.moy,  TRANSPOSE(INDEX(C1:BF1,,_xlfn.SEQUENCE(1,COLUMNS(C1:BF1)/2,1,2))),_xlpm.ok, ISNUMBER(_xlpm.moy),_xlfn._xlws.SORT(CHOOSE({1,2}, _xlfn._xlws.FILTER(_xlpm.noms, _xlpm.ok), _xlfn._xlws.FILTER(_xlpm.moy, _xlpm.ok)), 2, -1))</f>
+        <f t="array" ref="CA130:CB149">_xlfn.LET(  _xlpm.noms, TRANSPOSE(INDEX(C9:BF9,_xlfn.SEQUENCE(1,COLUMNS(C9:BF9)/2,1,2))),_xlpm.moy,  TRANSPOSE(INDEX(C1:BF1,,_xlfn.SEQUENCE(1,COLUMNS(C1:BF1)/2,1,2))),_xlpm.ok, ISNUMBER(_xlpm.moy),_xlfn._xlws.SORT(CHOOSE({1,2}, _xlfn._xlws.FILTER(_xlpm.noms, _xlpm.ok), _xlfn._xlws.FILTER(_xlpm.moy, _xlpm.ok)), 2, -1))</f>
         <v>Gauthier</v>
       </c>
       <c r="CB130" s="1">
@@ -9904,16 +10024,16 @@
         <v>Boris</v>
       </c>
       <c r="BW131" s="1">
-        <v>7.2625615763546794</v>
+        <v>7.1964112512124148</v>
       </c>
       <c r="BX131" s="1">
-        <v>1015</v>
+        <v>1031</v>
       </c>
       <c r="CA131" s="1" t="str">
         <v>Boris</v>
       </c>
       <c r="CB131" s="1">
-        <v>7.2625615763546794</v>
+        <v>7.1964112512124148</v>
       </c>
     </row>
     <row r="132" spans="1:80" x14ac:dyDescent="0.3">
@@ -9989,19 +10109,19 @@
       <c r="AX132" s="15"/>
       <c r="AY132" s="15"/>
       <c r="BV132" s="1" t="str">
-        <v>Célian</v>
+        <v>Joachim</v>
       </c>
       <c r="BW132" s="1">
-        <v>6.2357723577235769</v>
+        <v>6.2019230769230766</v>
       </c>
       <c r="BX132" s="1">
-        <v>246</v>
+        <v>104</v>
       </c>
       <c r="CA132" s="1" t="str">
-        <v>Célian</v>
+        <v>Joachim</v>
       </c>
       <c r="CB132" s="1">
-        <v>6.2357723577235769</v>
+        <v>6.2019230769230766</v>
       </c>
     </row>
     <row r="133" spans="1:80" x14ac:dyDescent="0.3">
@@ -10077,19 +10197,19 @@
       <c r="AX133" s="15"/>
       <c r="AY133" s="15"/>
       <c r="BV133" s="1" t="str">
-        <v>Joachim</v>
+        <v>Tom</v>
       </c>
       <c r="BW133" s="1">
-        <v>6.2019230769230766</v>
+        <v>6.1578947368421053</v>
       </c>
       <c r="BX133" s="1">
-        <v>104</v>
+        <v>209</v>
       </c>
       <c r="CA133" s="1" t="str">
-        <v>Joachim</v>
+        <v>Tom</v>
       </c>
       <c r="CB133" s="1">
-        <v>6.2019230769230766</v>
+        <v>6.1578947368421053</v>
       </c>
     </row>
     <row r="134" spans="1:80" x14ac:dyDescent="0.3">
@@ -10165,19 +10285,19 @@
       <c r="AX134" s="15"/>
       <c r="AY134" s="15"/>
       <c r="BV134" s="1" t="str">
-        <v>Tom</v>
+        <v>Célian</v>
       </c>
       <c r="BW134" s="1">
-        <v>6.1088082901554408</v>
+        <v>6.1106870229007635</v>
       </c>
       <c r="BX134" s="1">
-        <v>193</v>
+        <v>262</v>
       </c>
       <c r="CA134" s="1" t="str">
-        <v>Tom</v>
+        <v>Célian</v>
       </c>
       <c r="CB134" s="1">
-        <v>6.1088082901554408</v>
+        <v>6.1106870229007635</v>
       </c>
     </row>
     <row r="135" spans="1:80" x14ac:dyDescent="0.3">
@@ -10524,16 +10644,16 @@
         <v>Damien</v>
       </c>
       <c r="BW138" s="1">
-        <v>5.5986509274873528</v>
+        <v>5.4393700787401578</v>
       </c>
       <c r="BX138" s="1">
-        <v>593</v>
+        <v>635</v>
       </c>
       <c r="CA138" s="1" t="str">
-        <v>Damien</v>
+        <v>Lou</v>
       </c>
       <c r="CB138" s="1">
-        <v>5.5986509274873528</v>
+        <v>5.5526315789473681</v>
       </c>
     </row>
     <row r="139" spans="1:80" x14ac:dyDescent="0.3">
@@ -10553,10 +10673,10 @@
         <v>824</v>
       </c>
       <c r="CA139" s="1" t="str">
-        <v>Lou</v>
+        <v>Damien</v>
       </c>
       <c r="CB139" s="1">
-        <v>5.5526315789473681</v>
+        <v>5.4393700787401578</v>
       </c>
     </row>
     <row r="140" spans="1:80" x14ac:dyDescent="0.3">
@@ -10591,13 +10711,13 @@
         <v>11</v>
       </c>
       <c r="BV140" s="1" t="str">
-        <v>Quentin</v>
+        <v>Jules</v>
       </c>
       <c r="BW140" s="1">
-        <v>5.0149253731343286</v>
+        <v>5.0709677419354842</v>
       </c>
       <c r="BX140" s="1">
-        <v>67</v>
+        <v>155</v>
       </c>
       <c r="CA140" s="1" t="str">
         <v>Achille</v>
@@ -10647,10 +10767,10 @@
         <v>32</v>
       </c>
       <c r="CA141" s="1" t="str">
-        <v>Quentin</v>
+        <v>Jules</v>
       </c>
       <c r="CB141" s="1">
-        <v>5.0149253731343286</v>
+        <v>5.0709677419354842</v>
       </c>
     </row>
     <row r="142" spans="1:80" x14ac:dyDescent="0.3">
@@ -10685,13 +10805,13 @@
         <v>8</v>
       </c>
       <c r="BV142" s="1" t="str">
-        <v>Jules</v>
+        <v>Joey</v>
       </c>
       <c r="BW142" s="1">
-        <v>4.7410071942446042</v>
+        <v>4.5</v>
       </c>
       <c r="BX142" s="1">
-        <v>139</v>
+        <v>86</v>
       </c>
       <c r="CA142" s="1" t="str">
         <v>Paul</v>
@@ -10735,16 +10855,16 @@
         <v>Marie</v>
       </c>
       <c r="BW143" s="1">
-        <v>4.21875</v>
+        <v>4.328125</v>
       </c>
       <c r="BX143" s="1">
-        <v>208</v>
+        <v>224</v>
       </c>
       <c r="CA143" s="1" t="str">
-        <v>Jules</v>
+        <v>Joey</v>
       </c>
       <c r="CB143" s="1">
-        <v>4.7410071942446042</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="144" spans="1:80" x14ac:dyDescent="0.3">
@@ -10779,19 +10899,19 @@
         <v>12</v>
       </c>
       <c r="BV144" s="1" t="str">
-        <v>Luca</v>
+        <v>Quentin</v>
       </c>
       <c r="BW144" s="1">
-        <v>3.0112359550561796</v>
+        <v>4.096774193548387</v>
       </c>
       <c r="BX144" s="1">
-        <v>178</v>
+        <v>93</v>
       </c>
       <c r="CA144" s="1" t="str">
-        <v>Marie</v>
+        <v>Stanislas</v>
       </c>
       <c r="CB144" s="1">
-        <v>4.21875</v>
+        <v>4.4814814814814818</v>
       </c>
     </row>
     <row r="145" spans="1:80" x14ac:dyDescent="0.3">
@@ -10826,19 +10946,19 @@
         <v>2</v>
       </c>
       <c r="BV145" s="1" t="str">
-        <v>Fantinne</v>
+        <v>Luca</v>
       </c>
       <c r="BW145" s="1">
-        <v>2.9607843137254903</v>
+        <v>3.0112359550561796</v>
       </c>
       <c r="BX145" s="1">
-        <v>51</v>
+        <v>178</v>
       </c>
       <c r="CA145" s="1" t="str">
-        <v>Luca</v>
+        <v>Marie</v>
       </c>
       <c r="CB145" s="1">
-        <v>3.0112359550561796</v>
+        <v>4.328125</v>
       </c>
     </row>
     <row r="146" spans="1:80" x14ac:dyDescent="0.3">
@@ -10873,19 +10993,19 @@
         <v>13</v>
       </c>
       <c r="BV146" s="1" t="str">
-        <v>Joey</v>
+        <v>Fantinne</v>
       </c>
       <c r="BW146" s="1">
-        <v>2.9333333333333331</v>
+        <v>2.9607843137254903</v>
       </c>
       <c r="BX146" s="1">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="CA146" s="1" t="str">
-        <v>Fantinne</v>
+        <v>Quentin</v>
       </c>
       <c r="CB146" s="1">
-        <v>2.9607843137254903</v>
+        <v>4.096774193548387</v>
       </c>
     </row>
     <row r="147" spans="1:80" x14ac:dyDescent="0.3">
@@ -10929,10 +11049,10 @@
         <v>67</v>
       </c>
       <c r="CA147" s="1" t="str">
-        <v>Joey</v>
+        <v>Luca</v>
       </c>
       <c r="CB147" s="1">
-        <v>2.9333333333333331</v>
+        <v>3.0112359550561796</v>
       </c>
     </row>
     <row r="148" spans="1:80" x14ac:dyDescent="0.3">
@@ -10967,10 +11087,10 @@
         <v>11</v>
       </c>
       <c r="CA148" s="1" t="str">
-        <v>Loulou</v>
+        <v>Fantinne</v>
       </c>
       <c r="CB148" s="1">
-        <v>2.0746268656716418</v>
+        <v>2.9607843137254903</v>
       </c>
     </row>
     <row r="149" spans="1:80" x14ac:dyDescent="0.3">
@@ -11003,6 +11123,12 @@
       </c>
       <c r="N149" s="1">
         <v>13</v>
+      </c>
+      <c r="CA149" s="1" t="str">
+        <v>Loulou</v>
+      </c>
+      <c r="CB149" s="1">
+        <v>2.0746268656716418</v>
       </c>
     </row>
     <row r="150" spans="1:80" x14ac:dyDescent="0.3">
@@ -11202,7 +11328,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22D977F6-AD3F-47F0-926D-61192148887D}">
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="13.6640625" customWidth="1"/>
@@ -11235,7 +11361,7 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="25" cm="1">
-        <f t="array" ref="A2:D20">_xlfn.ANCHORARRAY('All stat'!BL72)</f>
+        <f t="array" ref="A2:D21">_xlfn.ANCHORARRAY('All stat'!BL72)</f>
         <v>1</v>
       </c>
       <c r="B2" s="25" t="str">
@@ -11259,10 +11385,10 @@
         <v>Boris</v>
       </c>
       <c r="C3" s="25" t="str">
-        <v>7.263</v>
+        <v>7.196</v>
       </c>
       <c r="D3" s="25">
-        <v>1015</v>
+        <v>1031</v>
       </c>
       <c r="F3" t="str">
         <v>entre 1 et 10</v>
@@ -11281,13 +11407,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="25" t="str">
-        <v>Célian</v>
+        <v>Joachim</v>
       </c>
       <c r="C4" s="25" t="str">
-        <v>6.236</v>
+        <v>6.202</v>
       </c>
       <c r="D4" s="25">
-        <v>246</v>
+        <v>104</v>
       </c>
       <c r="F4" t="str">
         <v>entre 10 et 20</v>
@@ -11305,13 +11431,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="25" t="str">
-        <v>Joachim</v>
+        <v>Tom</v>
       </c>
       <c r="C5" s="25" t="str">
-        <v>6.202</v>
+        <v>6.158</v>
       </c>
       <c r="D5" s="25">
-        <v>104</v>
+        <v>209</v>
       </c>
       <c r="F5" t="str">
         <v>entre 20 et 50</v>
@@ -11329,13 +11455,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="25" t="str">
-        <v>Tom</v>
+        <v>Célian</v>
       </c>
       <c r="C6" s="25" t="str">
-        <v>6.109</v>
+        <v>6.111</v>
       </c>
       <c r="D6" s="25">
-        <v>193</v>
+        <v>262</v>
       </c>
       <c r="F6" t="str">
         <v>entre 50 et 100</v>
@@ -11425,13 +11551,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="25" t="str">
-        <v>Damien</v>
+        <v>Lou</v>
       </c>
       <c r="C10" s="25" t="str">
-        <v>5.599</v>
+        <v>5.553</v>
       </c>
       <c r="D10" s="25">
-        <v>593</v>
+        <v>76</v>
       </c>
       <c r="F10" t="str">
         <v>plus de 1000</v>
@@ -11449,13 +11575,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="25" t="str">
-        <v>Lou</v>
+        <v>Damien</v>
       </c>
       <c r="C11" s="25" t="str">
-        <v>5.553</v>
+        <v>5.439</v>
       </c>
       <c r="D11" s="25">
-        <v>76</v>
+        <v>635</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
@@ -11477,13 +11603,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="25" t="str">
-        <v>Quentin</v>
+        <v>Jules</v>
       </c>
       <c r="C13" s="25" t="str">
-        <v>5.015</v>
+        <v>5.071</v>
       </c>
       <c r="D13" s="25">
-        <v>67</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
@@ -11505,13 +11631,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="25" t="str">
-        <v>Jules</v>
+        <v>Joey</v>
       </c>
       <c r="C15" s="25" t="str">
-        <v>4.741</v>
+        <v>4.500</v>
       </c>
       <c r="D15" s="25">
-        <v>139</v>
+        <v>86</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
@@ -11519,13 +11645,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="25" t="str">
-        <v>Marie</v>
+        <v>Stanislas</v>
       </c>
       <c r="C16" s="25" t="str">
-        <v>4.219</v>
+        <v>4.481</v>
       </c>
       <c r="D16" s="25">
-        <v>208</v>
+        <v>27</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
@@ -11533,13 +11659,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="25" t="str">
-        <v>Luca</v>
+        <v>Marie</v>
       </c>
       <c r="C17" s="25" t="str">
-        <v>3.011</v>
+        <v>4.328</v>
       </c>
       <c r="D17" s="25">
-        <v>178</v>
+        <v>224</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
@@ -11547,13 +11673,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="25" t="str">
-        <v>Fantinne</v>
+        <v>Quentin</v>
       </c>
       <c r="C18" s="25" t="str">
-        <v>2.961</v>
+        <v>4.097</v>
       </c>
       <c r="D18" s="25">
-        <v>51</v>
+        <v>93</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
@@ -11561,13 +11687,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="25" t="str">
-        <v>Joey</v>
+        <v>Luca</v>
       </c>
       <c r="C19" s="25" t="str">
-        <v>2.933</v>
+        <v>3.011</v>
       </c>
       <c r="D19" s="25">
-        <v>60</v>
+        <v>178</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
@@ -11575,12 +11701,26 @@
         <v>19</v>
       </c>
       <c r="B20" s="25" t="str">
+        <v>Fantinne</v>
+      </c>
+      <c r="C20" s="25" t="str">
+        <v>2.961</v>
+      </c>
+      <c r="D20" s="25">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="str">
         <v>Loulou</v>
       </c>
-      <c r="C20" s="25" t="str">
+      <c r="C21" t="str">
         <v>2.075</v>
       </c>
-      <c r="D20" s="25">
+      <c r="D21">
         <v>67</v>
       </c>
     </row>

--- a/classement_whist_2023_2025.xlsx
+++ b/classement_whist_2023_2025.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a20b8382962b136a/Bureau/loisir/whist/projet_application_streamlit/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/A20B8382962B136A/Bureau/loisir/whist/projet_application_streamlit/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="769" documentId="8_{848EF4F6-53E4-4B52-9417-5BFB5A888B23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E3463EEB-0D8C-4D2C-A87F-BA91729B9517}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="14_{D8C30FC8-DD4A-4CBA-A5BF-091BFC36F9C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{754371CA-87D8-450E-B2F8-FE4EA38100DA}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="93">
   <si>
     <t>global</t>
   </si>
@@ -329,6 +329,12 @@
   </si>
   <si>
     <t>Amélie</t>
+  </si>
+  <si>
+    <t>Hugo</t>
+  </si>
+  <si>
+    <t>?</t>
   </si>
 </sst>
 </file>
@@ -1125,29 +1131,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:CB151"/>
+  <dimension ref="A1:CH151"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.5546875" style="1" customWidth="1"/>
     <col min="2" max="2" width="16.77734375" style="1" customWidth="1"/>
-    <col min="3" max="59" width="5.77734375" style="1" customWidth="1"/>
-    <col min="60" max="60" width="11.5546875" style="1"/>
-    <col min="61" max="61" width="18.33203125" style="1" customWidth="1"/>
-    <col min="62" max="62" width="20.6640625" style="1" customWidth="1"/>
-    <col min="63" max="63" width="11.5546875" style="1"/>
-    <col min="64" max="64" width="16.88671875" style="1" customWidth="1"/>
-    <col min="65" max="66" width="11.5546875" style="1"/>
-    <col min="67" max="67" width="20.33203125" style="1" customWidth="1"/>
-    <col min="68" max="68" width="23.6640625" style="1" customWidth="1"/>
-    <col min="69" max="69" width="21.109375" style="1" customWidth="1"/>
-    <col min="70" max="70" width="20.33203125" style="1" customWidth="1"/>
-    <col min="71" max="71" width="19.21875" style="1" customWidth="1"/>
-    <col min="72" max="72" width="20.77734375" style="1" customWidth="1"/>
-    <col min="73" max="73" width="15.77734375" style="1" customWidth="1"/>
-    <col min="74" max="16384" width="11.5546875" style="1"/>
+    <col min="3" max="65" width="5.77734375" style="1" customWidth="1"/>
+    <col min="66" max="66" width="11.5546875" style="1"/>
+    <col min="67" max="68" width="20.6640625" style="1" customWidth="1"/>
+    <col min="69" max="69" width="11.5546875" style="1"/>
+    <col min="70" max="70" width="16.88671875" style="1" customWidth="1"/>
+    <col min="71" max="72" width="11.5546875" style="1"/>
+    <col min="73" max="73" width="20.33203125" style="1" customWidth="1"/>
+    <col min="74" max="74" width="23.6640625" style="1" customWidth="1"/>
+    <col min="75" max="75" width="21.109375" style="1" customWidth="1"/>
+    <col min="76" max="76" width="20.33203125" style="1" customWidth="1"/>
+    <col min="77" max="77" width="19.21875" style="1" customWidth="1"/>
+    <col min="78" max="78" width="20.77734375" style="1" customWidth="1"/>
+    <col min="79" max="79" width="15.77734375" style="1" customWidth="1"/>
+    <col min="80" max="16384" width="11.5546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1170,7 +1175,7 @@
       </c>
       <c r="G1" s="1">
         <f t="shared" ref="G1" si="2">IF(H2&gt;19,G2/H2,"/")</f>
-        <v>7.1964112512124148</v>
+        <v>7.1900866217516839</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>2</v>
@@ -1191,7 +1196,7 @@
       </c>
       <c r="M1" s="1">
         <f t="shared" ref="M1" si="5">IF(N2&gt;19,M2/N2,"/")</f>
-        <v>5.4393700787401578</v>
+        <v>5.4743390357698285</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>2</v>
@@ -1212,7 +1217,7 @@
       </c>
       <c r="S1" s="1">
         <f t="shared" ref="S1" si="8">IF(T2&gt;19,S2/T2,"/")</f>
-        <v>6.1578947368421053</v>
+        <v>6.0460829493087553</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>2</v>
@@ -1351,7 +1356,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:69" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1373,11 +1378,11 @@
       </c>
       <c r="G2" s="1">
         <f t="shared" si="27"/>
-        <v>7419.5</v>
+        <v>7470.5</v>
       </c>
       <c r="H2" s="1">
         <f t="shared" si="27"/>
-        <v>1031</v>
+        <v>1039</v>
       </c>
       <c r="I2" s="1">
         <f t="shared" si="27"/>
@@ -1397,11 +1402,11 @@
       </c>
       <c r="M2" s="1">
         <f t="shared" si="28"/>
-        <v>3454</v>
+        <v>3520</v>
       </c>
       <c r="N2" s="1">
         <f t="shared" si="28"/>
-        <v>635</v>
+        <v>643</v>
       </c>
       <c r="O2" s="1">
         <f t="shared" si="28"/>
@@ -1421,11 +1426,11 @@
       </c>
       <c r="S2" s="1">
         <f t="shared" si="28"/>
-        <v>1287</v>
+        <v>1312</v>
       </c>
       <c r="T2" s="1">
         <f t="shared" si="28"/>
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="U2" s="1">
         <f t="shared" si="28"/>
@@ -1580,7 +1585,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="3" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1783,14 +1788,14 @@
       <c r="BF3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="BI3" s="1" t="s">
+      <c r="BO3" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="BK3" s="1" t="s">
+      <c r="BQ3" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:69" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
         <v>3</v>
       </c>
@@ -2018,16 +2023,16 @@
         <f t="shared" si="61"/>
         <v>0</v>
       </c>
-      <c r="BJ4" s="1" t="b">
+      <c r="BP4" s="1" t="b">
         <f>NOT(OR("/",AVERAGE($C$1:$AL$1)&gt;AC$1,SMALL($C$1:$AL$1,1)=AC$1,SMALL($C$1:$AL$1,2)=AC$1,SMALL($C$1:$AL$1,3)=AC$1,LARGE($C$1:$AL$1,1)=AC$1,LARGE($C$1:$AL$1,2)=AC$1,LARGE($C$1:$AL$1,3)=AC$1))</f>
         <v>0</v>
       </c>
-      <c r="BK4" s="1" t="e">
+      <c r="BQ4" s="1" t="e">
         <f>$C$10:$C$151,$E$10:$E$151,$G$10:$G$151,$I$10:$I$151,$K$10:$K$151,$M$10:$M$151,$O$10:$O$151,$Q$10:$Q$151,$S$10:$S$151,$U$10:$U$151,$W$10:$W$151,$Y$10:$Y$151,$AA$10:$AA$151,$AC$10:$AC$151,$AE$10:$AE$151,$AG$10:$AG$151,$AI$10:$AI$151,$AK$10:$AK$151,$AM$10:$AM$151,$AO$10:$AO$151,$AQ$10:$AQ$151,$AS$10:$AS$151,$AU$10:$AU$151,$AW$10:$AW$151,$AY$10:$AY$151,$BA$10:$BA$151,$BC$10:$BC$151,$BE$10:$BE$151</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="5" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -2230,12 +2235,12 @@
       <c r="BF5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="BK5" s="1" t="e">
+      <c r="BQ5" s="1" t="e">
         <f>$D$10:$D$151,$F$10:$F$151,$H$10:$H$151,$J$10:$J$151,$L$10:$L$151,$N$10:$N$151,$P$10:$P$151,$R$10:$R$151,$T$10:$T$151,$V$10:$V$151,$X$10:$X$151,$Z$10:$Z$151,$AB$10:$AB$151,$AD$10:$AD$151,$AF$10:$AF$151,$AH$10:$AH$151,$AJ$10:$AJ$151,$AL$10:$AL$151,$AN$10:$AN$151,$AP$10:$AP$151,$AR$10:$AR$151,$AT$10:$AT$151,$AV$10:$AV$151,$AX$10:$AX$151,$AZ$10:$AZ$151,$BB$10:$BB$151,$BD$10:$BD$151,$BF$10:$BF$151</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="6" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:69" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
         <v>3</v>
       </c>
@@ -2464,7 +2469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
         <v>27</v>
       </c>
@@ -2487,7 +2492,7 @@
       </c>
       <c r="G7" s="15">
         <f t="shared" ref="G7" si="94">G8/H8</f>
-        <v>7.4436758893280635</v>
+        <v>7.4270428015564205</v>
       </c>
       <c r="H7" s="15" t="s">
         <v>2</v>
@@ -2508,7 +2513,7 @@
       </c>
       <c r="M7" s="15">
         <f t="shared" ref="M7" si="97">M8/N8</f>
-        <v>5.9015659955257274</v>
+        <v>5.9428571428571431</v>
       </c>
       <c r="N7" s="15" t="s">
         <v>2</v>
@@ -2529,7 +2534,7 @@
       </c>
       <c r="S7" s="15">
         <f t="shared" ref="S7" si="100">S8/T8</f>
-        <v>5.1844660194174761</v>
+        <v>5.0360360360360357</v>
       </c>
       <c r="T7" s="15" t="s">
         <v>2</v>
@@ -2668,7 +2673,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A8" s="15"/>
       <c r="B8" s="15" t="s">
         <v>3</v>
@@ -2691,11 +2696,11 @@
       </c>
       <c r="G8" s="15">
         <f t="shared" si="120"/>
-        <v>3766.5</v>
+        <v>3817.5</v>
       </c>
       <c r="H8" s="15">
         <f t="shared" si="120"/>
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="I8" s="15">
         <f t="shared" si="120"/>
@@ -2715,11 +2720,11 @@
       </c>
       <c r="M8" s="15">
         <f t="shared" si="121"/>
-        <v>2638</v>
+        <v>2704</v>
       </c>
       <c r="N8" s="15">
         <f t="shared" si="121"/>
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="O8" s="15">
         <f t="shared" si="121"/>
@@ -2739,11 +2744,11 @@
       </c>
       <c r="S8" s="15">
         <f t="shared" si="121"/>
-        <v>534</v>
+        <v>559</v>
       </c>
       <c r="T8" s="15">
         <f t="shared" si="121"/>
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="U8" s="15">
         <f t="shared" si="121"/>
@@ -2898,7 +2903,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="9" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:69" x14ac:dyDescent="0.3">
       <c r="C9" s="27" t="s">
         <v>70</v>
       </c>
@@ -3011,40 +3016,70 @@
         <v>34</v>
       </c>
       <c r="BF9" s="27"/>
-    </row>
-    <row r="10" spans="1:63" x14ac:dyDescent="0.3">
+      <c r="BG9" s="26" t="s">
+        <v>91</v>
+      </c>
+      <c r="BH9" s="26"/>
+      <c r="BI9" s="27" t="s">
+        <v>92</v>
+      </c>
+      <c r="BJ9" s="27"/>
+      <c r="BK9" s="27" t="s">
+        <v>92</v>
+      </c>
+      <c r="BL9" s="27"/>
+    </row>
+    <row r="10" spans="1:69" x14ac:dyDescent="0.3">
       <c r="B10" s="1">
         <v>140</v>
       </c>
     </row>
-    <row r="11" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:69" x14ac:dyDescent="0.3">
       <c r="B11" s="1">
         <v>139</v>
       </c>
     </row>
-    <row r="12" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:69" x14ac:dyDescent="0.3">
       <c r="B12" s="1">
         <v>138</v>
       </c>
     </row>
-    <row r="13" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:69" x14ac:dyDescent="0.3">
       <c r="B13" s="1">
         <v>137</v>
       </c>
     </row>
-    <row r="14" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:69" x14ac:dyDescent="0.3">
       <c r="B14" s="1">
         <v>136</v>
       </c>
     </row>
-    <row r="15" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:69" x14ac:dyDescent="0.3">
       <c r="B15" s="1">
         <v>135</v>
       </c>
     </row>
-    <row r="16" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:69" x14ac:dyDescent="0.3">
       <c r="B16" s="1">
         <v>134</v>
+      </c>
+      <c r="G16" s="1">
+        <v>51</v>
+      </c>
+      <c r="H16" s="1">
+        <v>8</v>
+      </c>
+      <c r="M16" s="1">
+        <v>66</v>
+      </c>
+      <c r="N16" s="1">
+        <v>8</v>
+      </c>
+      <c r="S16" s="1">
+        <v>25</v>
+      </c>
+      <c r="T16" s="1">
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:58" x14ac:dyDescent="0.3">
@@ -4116,7 +4151,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>7</v>
       </c>
@@ -4154,7 +4189,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="50" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>7</v>
       </c>
@@ -4195,7 +4230,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="51" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>7</v>
       </c>
@@ -4227,7 +4262,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="52" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>7</v>
       </c>
@@ -4259,7 +4294,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>7</v>
       </c>
@@ -4291,7 +4326,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="54" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>7</v>
       </c>
@@ -4323,7 +4358,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="55" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
         <v>7</v>
       </c>
@@ -4355,7 +4390,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="56" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>7</v>
       </c>
@@ -4387,7 +4422,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="57" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
         <v>7</v>
       </c>
@@ -4419,7 +4454,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="58" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
         <v>7</v>
       </c>
@@ -4451,7 +4486,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="59" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>7</v>
       </c>
@@ -4482,14 +4517,14 @@
       <c r="AB59" s="1">
         <v>16</v>
       </c>
-      <c r="BP59" s="1" t="s">
+      <c r="BV59" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="BR59" s="1" t="s">
+      <c r="BX59" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="60" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
         <v>7</v>
       </c>
@@ -4520,11 +4555,11 @@
       <c r="V60" s="1">
         <v>12</v>
       </c>
-      <c r="BP60" s="1" t="s">
+      <c r="BV60" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="61" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
         <v>7</v>
       </c>
@@ -4555,18 +4590,18 @@
       <c r="R61" s="1">
         <v>5</v>
       </c>
-      <c r="BP61" s="1" t="s">
+      <c r="BV61" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="BQ61" s="23"/>
-      <c r="BR61" s="1" t="s">
+      <c r="BW61" s="23"/>
+      <c r="BX61" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="BS61" s="1" t="s">
+      <c r="BY61" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="62" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
         <v>7</v>
       </c>
@@ -4597,18 +4632,18 @@
       <c r="T62" s="1">
         <v>4</v>
       </c>
-      <c r="BP62" s="1" t="s">
+      <c r="BV62" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="BQ62" s="24"/>
-      <c r="BR62" s="1" t="s">
+      <c r="BW62" s="24"/>
+      <c r="BX62" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="BS62" s="1" t="s">
+      <c r="BY62" s="1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="63" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
         <v>7</v>
       </c>
@@ -4639,18 +4674,18 @@
       <c r="N63" s="1">
         <v>3</v>
       </c>
-      <c r="BP63" s="1" t="s">
+      <c r="BV63" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="BQ63" s="17"/>
-      <c r="BR63" s="1" t="s">
+      <c r="BW63" s="17"/>
+      <c r="BX63" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="BS63" s="1" t="s">
+      <c r="BY63" s="1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="64" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
         <v>7</v>
       </c>
@@ -4681,18 +4716,18 @@
       <c r="L64" s="1">
         <v>4</v>
       </c>
-      <c r="BP64" s="1" t="s">
+      <c r="BV64" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="BQ64" s="18"/>
-      <c r="BR64" s="1" t="s">
+      <c r="BW64" s="18"/>
+      <c r="BX64" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="BS64" s="1" t="s">
+      <c r="BY64" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="65" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:81" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
         <v>7</v>
       </c>
@@ -4723,18 +4758,18 @@
       <c r="AB65" s="1">
         <v>8</v>
       </c>
-      <c r="BP65" s="1" t="s">
+      <c r="BV65" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="BQ65" s="21"/>
-      <c r="BR65" s="1" t="s">
+      <c r="BW65" s="21"/>
+      <c r="BX65" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="BS65" s="1" t="s">
+      <c r="BY65" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="66" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:81" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
         <v>7</v>
       </c>
@@ -4771,18 +4806,18 @@
       <c r="AB66" s="1">
         <v>8</v>
       </c>
-      <c r="BP66" s="1" t="s">
+      <c r="BV66" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="BQ66" s="19"/>
-      <c r="BR66" s="1" t="s">
+      <c r="BW66" s="19"/>
+      <c r="BX66" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="BS66" s="1" t="s">
+      <c r="BY66" s="1" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="67" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:81" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
         <v>7</v>
       </c>
@@ -4813,18 +4848,18 @@
       <c r="T67" s="1">
         <v>8</v>
       </c>
-      <c r="BP67" s="1" t="s">
+      <c r="BV67" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="BQ67" s="20"/>
-      <c r="BR67" s="1" t="s">
+      <c r="BW67" s="20"/>
+      <c r="BX67" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="BS67" s="1" t="s">
+      <c r="BY67" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="68" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:81" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
         <v>7</v>
       </c>
@@ -4855,18 +4890,18 @@
       <c r="AJ68" s="1">
         <v>12</v>
       </c>
-      <c r="BP68" s="1" t="s">
+      <c r="BV68" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="BQ68" s="22"/>
-      <c r="BR68" s="1" t="s">
+      <c r="BW68" s="22"/>
+      <c r="BX68" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="BS68" s="1" t="s">
+      <c r="BY68" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="69" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:81" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
         <v>7</v>
       </c>
@@ -4910,7 +4945,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="70" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:81" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
         <v>7</v>
       </c>
@@ -4947,35 +4982,35 @@
       <c r="V70" s="1">
         <v>7</v>
       </c>
-      <c r="BL70" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="BM70" s="1" t="s">
+      <c r="BR70" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="BS70" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="BN70" s="1" t="s">
+      <c r="BT70" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="BO70" s="1" t="s">
+      <c r="BU70" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="BQ70" s="1" t="s">
+      <c r="BW70" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="BR70" s="1" t="s">
+      <c r="BX70" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="BS70" s="1" t="s">
+      <c r="BY70" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="BT70" s="1" t="s">
+      <c r="BZ70" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="BV70" s="1" t="s">
+      <c r="CB70" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="71" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:81" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
         <v>7</v>
       </c>
@@ -5007,7 +5042,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="72" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:81" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
         <v>7</v>
       </c>
@@ -5056,12 +5091,12 @@
       <c r="BB72" s="1">
         <v>2</v>
       </c>
-      <c r="BI72" s="2"/>
-      <c r="BJ72" s="1" t="s">
+      <c r="BO72" s="2"/>
+      <c r="BP72" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="BL72" s="1" cm="1">
-        <f t="array" ref="BL72:BO91">_xlfn.LET(
+      <c r="BR72" s="1" cm="1">
+        <f t="array" ref="BR72:BU91">_xlfn.LET(
   _xlpm.cols_impairs, _xlfn.SEQUENCE(1,COLUMNS(C1:BF1)/2,1,2),
   _xlpm.cols_pairs,   _xlfn.SEQUENCE(1,COLUMNS(C2:BF2)/2,2,2),
   _xlpm.noms,     TRANSPOSE(INDEX(C9:BF9,,_xlpm.cols_impairs)),
@@ -5080,17 +5115,17 @@
 )</f>
         <v>1</v>
       </c>
-      <c r="BM72" s="1" t="str">
+      <c r="BS72" s="1" t="str">
         <v>Gauthier</v>
       </c>
-      <c r="BN72" s="1" t="str">
+      <c r="BT72" s="1" t="str">
         <v>7.391</v>
       </c>
-      <c r="BO72" s="1">
+      <c r="BU72" s="1">
         <v>69</v>
       </c>
-      <c r="BQ72" s="1" cm="1">
-        <f t="array" ref="BQ72:BT79">_xlfn.LET(
+      <c r="BW72" s="1" cm="1">
+        <f t="array" ref="BW72:BZ79">_xlfn.LET(
   _xlpm.cols_impairs, _xlfn.SEQUENCE(1,COLUMNS(C1:BF1)/2,1,2),
   _xlpm.cols_pairs,   _xlfn.SEQUENCE(1,COLUMNS(C2:BF2)/2,2,2),
   _xlpm.noms,     TRANSPOSE(INDEX(C9:BF9,,_xlpm.cols_impairs)),
@@ -5110,24 +5145,24 @@
 )</f>
         <v>1</v>
       </c>
-      <c r="BR72" s="1" t="str">
+      <c r="BX72" s="1" t="str">
         <v>Amélie</v>
       </c>
-      <c r="BS72" s="1" t="str">
+      <c r="BY72" s="1" t="str">
         <v>17.000</v>
       </c>
-      <c r="BT72" s="1">
-        <v>2</v>
-      </c>
-      <c r="BV72" s="1" t="str" cm="1">
-        <f t="array" ref="BV72:BW99">_xlfn.LET(  _xlpm.noms, TRANSPOSE(INDEX(C9:BF9,_xlfn.SEQUENCE(1,COLUMNS(C9:BF9)/2,1,2))),_xlpm.moy,  TRANSPOSE(INDEX(C1:BF1,,_xlfn.SEQUENCE(1,COLUMNS(C1:BF1)/2,1,2))),_xlfn.SORTBY(CHOOSE({1,2}, _xlpm.noms, _xlpm.moy), IF(ISNUMBER(_xlpm.moy), _xlpm.moy, -1E+99), -1))</f>
+      <c r="BZ72" s="1">
+        <v>2</v>
+      </c>
+      <c r="CB72" s="1" t="str" cm="1">
+        <f t="array" ref="CB72:CC99">_xlfn.LET(  _xlpm.noms, TRANSPOSE(INDEX(C9:BF9,_xlfn.SEQUENCE(1,COLUMNS(C9:BF9)/2,1,2))),_xlpm.moy,  TRANSPOSE(INDEX(C1:BF1,,_xlfn.SEQUENCE(1,COLUMNS(C1:BF1)/2,1,2))),_xlfn.SORTBY(CHOOSE({1,2}, _xlpm.noms, _xlpm.moy), IF(ISNUMBER(_xlpm.moy), _xlpm.moy, -1E+99), -1))</f>
         <v>Gauthier</v>
       </c>
-      <c r="BW72" s="1">
+      <c r="CC72" s="1">
         <v>7.3913043478260869</v>
       </c>
     </row>
-    <row r="73" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:81" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
         <v>24</v>
       </c>
@@ -5158,42 +5193,42 @@
       <c r="AB73" s="1">
         <v>8</v>
       </c>
-      <c r="BI73" s="3"/>
-      <c r="BJ73" s="1" t="s">
+      <c r="BO73" s="3"/>
+      <c r="BP73" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="BL73" s="1">
-        <v>2</v>
-      </c>
-      <c r="BM73" s="1" t="str">
+      <c r="BR73" s="1">
+        <v>2</v>
+      </c>
+      <c r="BS73" s="1" t="str">
         <v>Boris</v>
       </c>
-      <c r="BN73" s="1" t="str">
-        <v>7.196</v>
-      </c>
-      <c r="BO73" s="1">
-        <v>1031</v>
-      </c>
-      <c r="BQ73" s="1">
-        <v>2</v>
-      </c>
-      <c r="BR73" s="1" t="str">
+      <c r="BT73" s="1" t="str">
+        <v>7.190</v>
+      </c>
+      <c r="BU73" s="1">
+        <v>1039</v>
+      </c>
+      <c r="BW73" s="1">
+        <v>2</v>
+      </c>
+      <c r="BX73" s="1" t="str">
         <v>Maxime_Ca</v>
       </c>
-      <c r="BS73" s="1" t="str">
+      <c r="BY73" s="1" t="str">
         <v>8.500</v>
       </c>
-      <c r="BT73" s="1">
+      <c r="BZ73" s="1">
         <v>4</v>
       </c>
-      <c r="BV73" s="1" t="str">
+      <c r="CB73" s="1" t="str">
         <v>Boris</v>
       </c>
-      <c r="BW73" s="1">
-        <v>7.1964112512124148</v>
-      </c>
-    </row>
-    <row r="74" spans="1:75" x14ac:dyDescent="0.3">
+      <c r="CC73" s="1">
+        <v>7.1900866217516839</v>
+      </c>
+    </row>
+    <row r="74" spans="1:81" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
         <v>24</v>
       </c>
@@ -5224,42 +5259,42 @@
       <c r="AJ74" s="1">
         <v>4</v>
       </c>
-      <c r="BI74" s="4"/>
-      <c r="BJ74" s="1" t="s">
+      <c r="BO74" s="4"/>
+      <c r="BP74" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="BL74" s="1">
+      <c r="BR74" s="1">
         <v>3</v>
       </c>
-      <c r="BM74" s="1" t="str">
+      <c r="BS74" s="1" t="str">
         <v>Joachim</v>
       </c>
-      <c r="BN74" s="1" t="str">
+      <c r="BT74" s="1" t="str">
         <v>6.202</v>
       </c>
-      <c r="BO74" s="1">
+      <c r="BU74" s="1">
         <v>104</v>
       </c>
-      <c r="BQ74" s="1">
+      <c r="BW74" s="1">
         <v>3</v>
       </c>
-      <c r="BR74" s="1" t="str">
+      <c r="BX74" s="1" t="str">
         <v>Pascale</v>
       </c>
-      <c r="BS74" s="1" t="str">
+      <c r="BY74" s="1" t="str">
         <v>7.118</v>
       </c>
-      <c r="BT74" s="1">
+      <c r="BZ74" s="1">
         <v>17</v>
       </c>
-      <c r="BV74" s="1" t="str">
+      <c r="CB74" s="1" t="str">
         <v>Joachim</v>
       </c>
-      <c r="BW74" s="1">
+      <c r="CC74" s="1">
         <v>6.2019230769230766</v>
       </c>
     </row>
-    <row r="75" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:81" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
         <v>22</v>
       </c>
@@ -5290,38 +5325,38 @@
       <c r="AV75" s="1">
         <v>4</v>
       </c>
-      <c r="BL75" s="1">
+      <c r="BR75" s="1">
         <v>4</v>
       </c>
-      <c r="BM75" s="1" t="str">
-        <v>Tom</v>
-      </c>
-      <c r="BN75" s="1" t="str">
-        <v>6.158</v>
-      </c>
-      <c r="BO75" s="1">
-        <v>209</v>
-      </c>
-      <c r="BQ75" s="1">
+      <c r="BS75" s="1" t="str">
+        <v>Célian</v>
+      </c>
+      <c r="BT75" s="1" t="str">
+        <v>6.111</v>
+      </c>
+      <c r="BU75" s="1">
+        <v>262</v>
+      </c>
+      <c r="BW75" s="1">
         <v>4</v>
       </c>
-      <c r="BR75" s="1" t="str">
+      <c r="BX75" s="1" t="str">
         <v>Harrison</v>
       </c>
-      <c r="BS75" s="1" t="str">
+      <c r="BY75" s="1" t="str">
         <v>5.400</v>
       </c>
-      <c r="BT75" s="1">
+      <c r="BZ75" s="1">
         <v>5</v>
       </c>
-      <c r="BV75" s="1" t="str">
-        <v>Tom</v>
-      </c>
-      <c r="BW75" s="1">
-        <v>6.1578947368421053</v>
-      </c>
-    </row>
-    <row r="76" spans="1:75" x14ac:dyDescent="0.3">
+      <c r="CB75" s="1" t="str">
+        <v>Célian</v>
+      </c>
+      <c r="CC75" s="1">
+        <v>6.1106870229007635</v>
+      </c>
+    </row>
+    <row r="76" spans="1:81" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
         <v>7</v>
       </c>
@@ -5352,42 +5387,42 @@
       <c r="V76" s="1">
         <v>4</v>
       </c>
-      <c r="BI76" s="5"/>
-      <c r="BJ76" s="1" t="s">
+      <c r="BO76" s="5"/>
+      <c r="BP76" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="BL76" s="1">
+      <c r="BR76" s="1">
         <v>5</v>
       </c>
-      <c r="BM76" s="1" t="str">
-        <v>Célian</v>
-      </c>
-      <c r="BN76" s="1" t="str">
-        <v>6.111</v>
-      </c>
-      <c r="BO76" s="1">
-        <v>262</v>
-      </c>
-      <c r="BQ76" s="1">
+      <c r="BS76" s="1" t="str">
+        <v>William</v>
+      </c>
+      <c r="BT76" s="1" t="str">
+        <v>6.069</v>
+      </c>
+      <c r="BU76" s="1">
+        <v>29</v>
+      </c>
+      <c r="BW76" s="1">
         <v>5</v>
       </c>
-      <c r="BR76" s="1" t="str">
+      <c r="BX76" s="1" t="str">
         <v>Émile</v>
       </c>
-      <c r="BS76" s="1" t="str">
+      <c r="BY76" s="1" t="str">
         <v>3.308</v>
       </c>
-      <c r="BT76" s="1">
+      <c r="BZ76" s="1">
         <v>13</v>
       </c>
-      <c r="BV76" s="1" t="str">
-        <v>Célian</v>
-      </c>
-      <c r="BW76" s="1">
-        <v>6.1106870229007635</v>
-      </c>
-    </row>
-    <row r="77" spans="1:75" x14ac:dyDescent="0.3">
+      <c r="CB76" s="1" t="str">
+        <v>William</v>
+      </c>
+      <c r="CC76" s="1">
+        <v>6.068965517241379</v>
+      </c>
+    </row>
+    <row r="77" spans="1:81" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
         <v>7</v>
       </c>
@@ -5418,42 +5453,42 @@
       <c r="AB77" s="1">
         <v>7</v>
       </c>
-      <c r="BI77" s="10"/>
-      <c r="BJ77" s="1" t="s">
+      <c r="BO77" s="10"/>
+      <c r="BP77" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="BL77" s="1">
+      <c r="BR77" s="1">
         <v>6</v>
       </c>
-      <c r="BM77" s="1" t="str">
-        <v>William</v>
-      </c>
-      <c r="BN77" s="1" t="str">
-        <v>6.069</v>
-      </c>
-      <c r="BO77" s="1">
-        <v>29</v>
-      </c>
-      <c r="BQ77" s="1">
+      <c r="BS77" s="1" t="str">
+        <v>Tom</v>
+      </c>
+      <c r="BT77" s="1" t="str">
+        <v>6.046</v>
+      </c>
+      <c r="BU77" s="1">
+        <v>217</v>
+      </c>
+      <c r="BW77" s="1">
         <v>6</v>
       </c>
-      <c r="BR77" s="1" t="str">
+      <c r="BX77" s="1" t="str">
         <v>Aurélien</v>
       </c>
-      <c r="BS77" s="1" t="str">
+      <c r="BY77" s="1" t="str">
         <v>2.800</v>
       </c>
-      <c r="BT77" s="1">
+      <c r="BZ77" s="1">
         <v>5</v>
       </c>
-      <c r="BV77" s="1" t="str">
-        <v>William</v>
-      </c>
-      <c r="BW77" s="1">
-        <v>6.068965517241379</v>
-      </c>
-    </row>
-    <row r="78" spans="1:75" x14ac:dyDescent="0.3">
+      <c r="CB77" s="1" t="str">
+        <v>Tom</v>
+      </c>
+      <c r="CC77" s="1">
+        <v>6.0460829493087553</v>
+      </c>
+    </row>
+    <row r="78" spans="1:81" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
         <v>7</v>
       </c>
@@ -5484,42 +5519,42 @@
       <c r="V78" s="1">
         <v>1</v>
       </c>
-      <c r="BI78" s="6"/>
-      <c r="BJ78" s="1" t="s">
+      <c r="BO78" s="6"/>
+      <c r="BP78" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="BL78" s="1">
-        <v>7</v>
-      </c>
-      <c r="BM78" s="1" t="str">
+      <c r="BR78" s="1">
+        <v>7</v>
+      </c>
+      <c r="BS78" s="1" t="str">
         <v>Samuel</v>
       </c>
-      <c r="BN78" s="1" t="str">
+      <c r="BT78" s="1" t="str">
         <v>5.910</v>
       </c>
-      <c r="BO78" s="1">
+      <c r="BU78" s="1">
         <v>211</v>
       </c>
-      <c r="BQ78" s="1">
-        <v>7</v>
-      </c>
-      <c r="BR78" s="1" t="str">
+      <c r="BW78" s="1">
+        <v>7</v>
+      </c>
+      <c r="BX78" s="1" t="str">
         <v>Maxime_Go</v>
       </c>
-      <c r="BS78" s="1" t="str">
+      <c r="BY78" s="1" t="str">
         <v>0.727</v>
       </c>
-      <c r="BT78" s="1">
+      <c r="BZ78" s="1">
         <v>11</v>
       </c>
-      <c r="BV78" s="1" t="str">
+      <c r="CB78" s="1" t="str">
         <v>Samuel</v>
       </c>
-      <c r="BW78" s="1">
+      <c r="CC78" s="1">
         <v>5.9099526066350707</v>
       </c>
     </row>
-    <row r="79" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:81" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
         <v>7</v>
       </c>
@@ -5550,38 +5585,38 @@
       <c r="AX79" s="1">
         <v>5</v>
       </c>
-      <c r="BL79" s="1">
-        <v>8</v>
-      </c>
-      <c r="BM79" s="1" t="str">
+      <c r="BR79" s="1">
+        <v>8</v>
+      </c>
+      <c r="BS79" s="1" t="str">
         <v>Mehdi</v>
       </c>
-      <c r="BN79" s="1" t="str">
+      <c r="BT79" s="1" t="str">
         <v>5.770</v>
       </c>
-      <c r="BO79" s="1">
+      <c r="BU79" s="1">
         <v>421</v>
       </c>
-      <c r="BQ79" s="1">
-        <v>8</v>
-      </c>
-      <c r="BR79" s="1" t="str">
+      <c r="BW79" s="1">
+        <v>8</v>
+      </c>
+      <c r="BX79" s="1" t="str">
         <v>Robin</v>
       </c>
-      <c r="BS79" s="1" t="str">
+      <c r="BY79" s="1" t="str">
         <v>-0.083</v>
       </c>
-      <c r="BT79" s="1">
+      <c r="BZ79" s="1">
         <v>12</v>
       </c>
-      <c r="BV79" s="1" t="str">
+      <c r="CB79" s="1" t="str">
         <v>Mehdi</v>
       </c>
-      <c r="BW79" s="1">
+      <c r="CC79" s="1">
         <v>5.7695961995249405</v>
       </c>
     </row>
-    <row r="80" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:81" x14ac:dyDescent="0.3">
       <c r="A80" s="15" t="s">
         <v>7</v>
       </c>
@@ -5657,30 +5692,30 @@
       <c r="AW80" s="15"/>
       <c r="AX80" s="15"/>
       <c r="AY80" s="15"/>
-      <c r="BI80" s="7"/>
-      <c r="BJ80" s="1" t="s">
+      <c r="BO80" s="7"/>
+      <c r="BP80" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="BL80" s="1">
+      <c r="BR80" s="1">
         <v>9</v>
       </c>
-      <c r="BM80" s="1" t="str">
+      <c r="BS80" s="1" t="str">
         <v>Lou</v>
       </c>
-      <c r="BN80" s="1" t="str">
+      <c r="BT80" s="1" t="str">
         <v>5.553</v>
       </c>
-      <c r="BO80" s="1">
+      <c r="BU80" s="1">
         <v>76</v>
       </c>
-      <c r="BV80" s="1" t="str">
+      <c r="CB80" s="1" t="str">
         <v>Lou</v>
       </c>
-      <c r="BW80" s="1">
+      <c r="CC80" s="1">
         <v>5.5526315789473681</v>
       </c>
     </row>
-    <row r="81" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:81" x14ac:dyDescent="0.3">
       <c r="A81" s="15" t="s">
         <v>7</v>
       </c>
@@ -5752,30 +5787,30 @@
       <c r="AW81" s="15"/>
       <c r="AX81" s="15"/>
       <c r="AY81" s="15"/>
-      <c r="BI81" s="8"/>
-      <c r="BJ81" s="1" t="s">
+      <c r="BO81" s="8"/>
+      <c r="BP81" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="BL81" s="1">
+      <c r="BR81" s="1">
         <v>10</v>
       </c>
-      <c r="BM81" s="1" t="str">
+      <c r="BS81" s="1" t="str">
         <v>Damien</v>
       </c>
-      <c r="BN81" s="1" t="str">
-        <v>5.439</v>
-      </c>
-      <c r="BO81" s="1">
-        <v>635</v>
-      </c>
-      <c r="BV81" s="1" t="str">
+      <c r="BT81" s="1" t="str">
+        <v>5.474</v>
+      </c>
+      <c r="BU81" s="1">
+        <v>643</v>
+      </c>
+      <c r="CB81" s="1" t="str">
         <v>Damien</v>
       </c>
-      <c r="BW81" s="1">
-        <v>5.4393700787401578</v>
-      </c>
-    </row>
-    <row r="82" spans="1:75" x14ac:dyDescent="0.3">
+      <c r="CC81" s="1">
+        <v>5.4743390357698285</v>
+      </c>
+    </row>
+    <row r="82" spans="1:81" x14ac:dyDescent="0.3">
       <c r="A82" s="15" t="s">
         <v>7</v>
       </c>
@@ -5847,30 +5882,30 @@
       <c r="AW82" s="15"/>
       <c r="AX82" s="15"/>
       <c r="AY82" s="15"/>
-      <c r="BI82" s="9"/>
-      <c r="BJ82" s="1" t="s">
+      <c r="BO82" s="9"/>
+      <c r="BP82" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="BL82" s="1">
+      <c r="BR82" s="1">
         <v>11</v>
       </c>
-      <c r="BM82" s="1" t="str">
+      <c r="BS82" s="1" t="str">
         <v>Achille</v>
       </c>
-      <c r="BN82" s="1" t="str">
+      <c r="BT82" s="1" t="str">
         <v>5.347</v>
       </c>
-      <c r="BO82" s="1">
+      <c r="BU82" s="1">
         <v>824</v>
       </c>
-      <c r="BV82" s="1" t="str">
+      <c r="CB82" s="1" t="str">
         <v>Achille</v>
       </c>
-      <c r="BW82" s="1">
+      <c r="CC82" s="1">
         <v>5.3470873786407767</v>
       </c>
     </row>
-    <row r="83" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:81" x14ac:dyDescent="0.3">
       <c r="A83" s="15" t="s">
         <v>7</v>
       </c>
@@ -5942,26 +5977,26 @@
       <c r="AW83" s="15"/>
       <c r="AX83" s="15"/>
       <c r="AY83" s="15"/>
-      <c r="BL83" s="1">
+      <c r="BR83" s="1">
         <v>12</v>
       </c>
-      <c r="BM83" s="1" t="str">
+      <c r="BS83" s="1" t="str">
         <v>Jules</v>
       </c>
-      <c r="BN83" s="1" t="str">
+      <c r="BT83" s="1" t="str">
         <v>5.071</v>
       </c>
-      <c r="BO83" s="1">
+      <c r="BU83" s="1">
         <v>155</v>
       </c>
-      <c r="BV83" s="1" t="str">
+      <c r="CB83" s="1" t="str">
         <v>Jules</v>
       </c>
-      <c r="BW83" s="1">
+      <c r="CC83" s="1">
         <v>5.0709677419354842</v>
       </c>
     </row>
-    <row r="84" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:81" x14ac:dyDescent="0.3">
       <c r="A84" s="15" t="s">
         <v>7</v>
       </c>
@@ -6037,33 +6072,33 @@
       <c r="AW84" s="15"/>
       <c r="AX84" s="15"/>
       <c r="AY84" s="15"/>
-      <c r="BI84" s="1" t="s">
+      <c r="BO84" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="BJ84" s="1">
+      <c r="BP84" s="1">
         <f>AVERAGE(C1:BF1)</f>
-        <v>5.1241159673426404</v>
-      </c>
-      <c r="BL84" s="1">
+        <v>5.1199575943444193</v>
+      </c>
+      <c r="BR84" s="1">
         <v>13</v>
       </c>
-      <c r="BM84" s="1" t="str">
+      <c r="BS84" s="1" t="str">
         <v>Paul</v>
       </c>
-      <c r="BN84" s="1" t="str">
+      <c r="BT84" s="1" t="str">
         <v>4.813</v>
       </c>
-      <c r="BO84" s="1">
+      <c r="BU84" s="1">
         <v>32</v>
       </c>
-      <c r="BV84" s="1" t="str">
+      <c r="CB84" s="1" t="str">
         <v>Paul</v>
       </c>
-      <c r="BW84" s="1">
+      <c r="CC84" s="1">
         <v>4.8125</v>
       </c>
     </row>
-    <row r="85" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:81" x14ac:dyDescent="0.3">
       <c r="A85" s="15" t="s">
         <v>7</v>
       </c>
@@ -6135,26 +6170,26 @@
       <c r="AW85" s="15"/>
       <c r="AX85" s="15"/>
       <c r="AY85" s="15"/>
-      <c r="BL85" s="1">
+      <c r="BR85" s="1">
         <v>14</v>
       </c>
-      <c r="BM85" s="1" t="str">
+      <c r="BS85" s="1" t="str">
         <v>Joey</v>
       </c>
-      <c r="BN85" s="1" t="str">
+      <c r="BT85" s="1" t="str">
         <v>4.500</v>
       </c>
-      <c r="BO85" s="1">
+      <c r="BU85" s="1">
         <v>86</v>
       </c>
-      <c r="BV85" s="1" t="str">
+      <c r="CB85" s="1" t="str">
         <v>Joey</v>
       </c>
-      <c r="BW85" s="1">
+      <c r="CC85" s="1">
         <v>4.5</v>
       </c>
     </row>
-    <row r="86" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:81" x14ac:dyDescent="0.3">
       <c r="A86" s="15" t="s">
         <v>23</v>
       </c>
@@ -6230,26 +6265,26 @@
       <c r="AW86" s="15"/>
       <c r="AX86" s="15"/>
       <c r="AY86" s="15"/>
-      <c r="BL86" s="1">
+      <c r="BR86" s="1">
         <v>15</v>
       </c>
-      <c r="BM86" s="1" t="str">
+      <c r="BS86" s="1" t="str">
         <v>Stanislas</v>
       </c>
-      <c r="BN86" s="1" t="str">
+      <c r="BT86" s="1" t="str">
         <v>4.481</v>
       </c>
-      <c r="BO86" s="1">
+      <c r="BU86" s="1">
         <v>27</v>
       </c>
-      <c r="BV86" s="1" t="str">
+      <c r="CB86" s="1" t="str">
         <v>Stanislas</v>
       </c>
-      <c r="BW86" s="1">
+      <c r="CC86" s="1">
         <v>4.4814814814814818</v>
       </c>
     </row>
-    <row r="87" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:81" x14ac:dyDescent="0.3">
       <c r="A87" s="15" t="s">
         <v>23</v>
       </c>
@@ -6321,29 +6356,29 @@
       <c r="AW87" s="15"/>
       <c r="AX87" s="15"/>
       <c r="AY87" s="15"/>
-      <c r="BJ87" s="1" t="s">
+      <c r="BP87" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="BL87" s="1">
+      <c r="BR87" s="1">
         <v>16</v>
       </c>
-      <c r="BM87" s="1" t="str">
+      <c r="BS87" s="1" t="str">
         <v>Marie</v>
       </c>
-      <c r="BN87" s="1" t="str">
+      <c r="BT87" s="1" t="str">
         <v>4.328</v>
       </c>
-      <c r="BO87" s="1">
+      <c r="BU87" s="1">
         <v>224</v>
       </c>
-      <c r="BV87" s="1" t="str">
+      <c r="CB87" s="1" t="str">
         <v>Marie</v>
       </c>
-      <c r="BW87" s="1">
+      <c r="CC87" s="1">
         <v>4.328125</v>
       </c>
     </row>
-    <row r="88" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:81" x14ac:dyDescent="0.3">
       <c r="A88" s="15" t="s">
         <v>7</v>
       </c>
@@ -6423,30 +6458,30 @@
       <c r="AW88" s="15"/>
       <c r="AX88" s="15"/>
       <c r="AY88" s="15"/>
-      <c r="BI88" s="11"/>
-      <c r="BJ88" s="1" t="s">
+      <c r="BO88" s="11"/>
+      <c r="BP88" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="BL88" s="1">
+      <c r="BR88" s="1">
         <v>17</v>
       </c>
-      <c r="BM88" s="1" t="str">
+      <c r="BS88" s="1" t="str">
         <v>Quentin</v>
       </c>
-      <c r="BN88" s="1" t="str">
+      <c r="BT88" s="1" t="str">
         <v>4.097</v>
       </c>
-      <c r="BO88" s="1">
+      <c r="BU88" s="1">
         <v>93</v>
       </c>
-      <c r="BV88" s="1" t="str">
+      <c r="CB88" s="1" t="str">
         <v>Quentin</v>
       </c>
-      <c r="BW88" s="1">
+      <c r="CC88" s="1">
         <v>4.096774193548387</v>
       </c>
     </row>
-    <row r="89" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:81" x14ac:dyDescent="0.3">
       <c r="A89" s="15" t="s">
         <v>7</v>
       </c>
@@ -6518,30 +6553,30 @@
       <c r="AW89" s="15"/>
       <c r="AX89" s="15"/>
       <c r="AY89" s="15"/>
-      <c r="BI89" s="14"/>
-      <c r="BJ89" s="1" t="s">
+      <c r="BO89" s="14"/>
+      <c r="BP89" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="BL89" s="1">
+      <c r="BR89" s="1">
         <v>18</v>
       </c>
-      <c r="BM89" s="1" t="str">
+      <c r="BS89" s="1" t="str">
         <v>Luca</v>
       </c>
-      <c r="BN89" s="1" t="str">
+      <c r="BT89" s="1" t="str">
         <v>3.011</v>
       </c>
-      <c r="BO89" s="1">
+      <c r="BU89" s="1">
         <v>178</v>
       </c>
-      <c r="BV89" s="1" t="str">
+      <c r="CB89" s="1" t="str">
         <v>Luca</v>
       </c>
-      <c r="BW89" s="1">
+      <c r="CC89" s="1">
         <v>3.0112359550561796</v>
       </c>
     </row>
-    <row r="90" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:81" x14ac:dyDescent="0.3">
       <c r="A90" s="15" t="s">
         <v>7</v>
       </c>
@@ -6617,30 +6652,30 @@
       <c r="AW90" s="15"/>
       <c r="AX90" s="15"/>
       <c r="AY90" s="15"/>
-      <c r="BI90" s="13"/>
-      <c r="BJ90" s="1" t="s">
+      <c r="BO90" s="13"/>
+      <c r="BP90" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="BL90" s="1">
+      <c r="BR90" s="1">
         <v>19</v>
       </c>
-      <c r="BM90" s="1" t="str">
+      <c r="BS90" s="1" t="str">
         <v>Fantinne</v>
       </c>
-      <c r="BN90" s="1" t="str">
+      <c r="BT90" s="1" t="str">
         <v>2.961</v>
       </c>
-      <c r="BO90" s="1">
+      <c r="BU90" s="1">
         <v>51</v>
       </c>
-      <c r="BV90" s="1" t="str">
+      <c r="CB90" s="1" t="str">
         <v>Fantinne</v>
       </c>
-      <c r="BW90" s="1">
+      <c r="CC90" s="1">
         <v>2.9607843137254903</v>
       </c>
     </row>
-    <row r="91" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:81" x14ac:dyDescent="0.3">
       <c r="A91" s="15" t="s">
         <v>7</v>
       </c>
@@ -6712,30 +6747,30 @@
       <c r="AW91" s="15"/>
       <c r="AX91" s="15"/>
       <c r="AY91" s="15"/>
-      <c r="BI91" s="12"/>
-      <c r="BJ91" s="1" t="s">
+      <c r="BO91" s="12"/>
+      <c r="BP91" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="BL91" s="1">
+      <c r="BR91" s="1">
         <v>20</v>
       </c>
-      <c r="BM91" s="1" t="str">
+      <c r="BS91" s="1" t="str">
         <v>Loulou</v>
       </c>
-      <c r="BN91" s="1" t="str">
+      <c r="BT91" s="1" t="str">
         <v>2.075</v>
       </c>
-      <c r="BO91" s="1">
+      <c r="BU91" s="1">
         <v>67</v>
       </c>
-      <c r="BV91" s="1" t="str">
+      <c r="CB91" s="1" t="str">
         <v>Loulou</v>
       </c>
-      <c r="BW91" s="1">
+      <c r="CC91" s="1">
         <v>2.0746268656716418</v>
       </c>
     </row>
-    <row r="92" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:81" x14ac:dyDescent="0.3">
       <c r="A92" s="15" t="s">
         <v>7</v>
       </c>
@@ -6807,14 +6842,14 @@
       <c r="AW92" s="15"/>
       <c r="AX92" s="15"/>
       <c r="AY92" s="15"/>
-      <c r="BV92" s="1" t="str">
+      <c r="CB92" s="1" t="str">
         <v>Harrison</v>
       </c>
-      <c r="BW92" s="1" t="str">
+      <c r="CC92" s="1" t="str">
         <v>/</v>
       </c>
     </row>
-    <row r="93" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:81" x14ac:dyDescent="0.3">
       <c r="A93" s="15" t="s">
         <v>7</v>
       </c>
@@ -6890,14 +6925,14 @@
       <c r="AW93" s="15"/>
       <c r="AX93" s="15"/>
       <c r="AY93" s="15"/>
-      <c r="BV93" s="1" t="str">
+      <c r="CB93" s="1" t="str">
         <v>Pascale</v>
       </c>
-      <c r="BW93" s="1" t="str">
+      <c r="CC93" s="1" t="str">
         <v>/</v>
       </c>
     </row>
-    <row r="94" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:81" x14ac:dyDescent="0.3">
       <c r="A94" s="15" t="s">
         <v>7</v>
       </c>
@@ -6973,14 +7008,14 @@
       <c r="AW94" s="15"/>
       <c r="AX94" s="15"/>
       <c r="AY94" s="15"/>
-      <c r="BV94" s="1" t="str">
+      <c r="CB94" s="1" t="str">
         <v>Robin</v>
       </c>
-      <c r="BW94" s="1" t="str">
+      <c r="CC94" s="1" t="str">
         <v>/</v>
       </c>
     </row>
-    <row r="95" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:81" x14ac:dyDescent="0.3">
       <c r="A95" s="15" t="s">
         <v>25</v>
       </c>
@@ -7036,14 +7071,14 @@
       <c r="AW95" s="15"/>
       <c r="AX95" s="15"/>
       <c r="AY95" s="15"/>
-      <c r="BV95" s="1" t="str">
+      <c r="CB95" s="1" t="str">
         <v>Maxime_Go</v>
       </c>
-      <c r="BW95" s="1" t="str">
+      <c r="CC95" s="1" t="str">
         <v>/</v>
       </c>
     </row>
-    <row r="96" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:81" x14ac:dyDescent="0.3">
       <c r="A96" s="15" t="s">
         <v>7</v>
       </c>
@@ -7115,14 +7150,14 @@
       <c r="AW96" s="15"/>
       <c r="AX96" s="15"/>
       <c r="AY96" s="15"/>
-      <c r="BV96" s="1" t="str">
+      <c r="CB96" s="1" t="str">
         <v>Maxime_Ca</v>
       </c>
-      <c r="BW96" s="1" t="str">
+      <c r="CC96" s="1" t="str">
         <v>/</v>
       </c>
     </row>
-    <row r="97" spans="1:77" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:83" x14ac:dyDescent="0.3">
       <c r="A97" s="15" t="s">
         <v>7</v>
       </c>
@@ -7198,14 +7233,14 @@
       <c r="AW97" s="15"/>
       <c r="AX97" s="15"/>
       <c r="AY97" s="15"/>
-      <c r="BV97" s="1" t="str">
+      <c r="CB97" s="1" t="str">
         <v>Aurélien</v>
       </c>
-      <c r="BW97" s="1" t="str">
+      <c r="CC97" s="1" t="str">
         <v>/</v>
       </c>
     </row>
-    <row r="98" spans="1:77" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:83" x14ac:dyDescent="0.3">
       <c r="A98" s="15" t="s">
         <v>7</v>
       </c>
@@ -7277,14 +7312,14 @@
       <c r="AW98" s="15"/>
       <c r="AX98" s="15"/>
       <c r="AY98" s="15"/>
-      <c r="BV98" s="1" t="str">
+      <c r="CB98" s="1" t="str">
         <v>Émile</v>
       </c>
-      <c r="BW98" s="1" t="str">
+      <c r="CC98" s="1" t="str">
         <v>/</v>
       </c>
     </row>
-    <row r="99" spans="1:77" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:83" x14ac:dyDescent="0.3">
       <c r="A99" s="15" t="s">
         <v>7</v>
       </c>
@@ -7356,14 +7391,14 @@
       <c r="AW99" s="15"/>
       <c r="AX99" s="15"/>
       <c r="AY99" s="15"/>
-      <c r="BV99" s="1" t="str">
+      <c r="CB99" s="1" t="str">
         <v>Amélie</v>
       </c>
-      <c r="BW99" s="1" t="str">
+      <c r="CC99" s="1" t="str">
         <v>/</v>
       </c>
     </row>
-    <row r="100" spans="1:77" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:83" x14ac:dyDescent="0.3">
       <c r="A100" s="15" t="s">
         <v>7</v>
       </c>
@@ -7436,7 +7471,7 @@
       <c r="AX100" s="15"/>
       <c r="AY100" s="15"/>
     </row>
-    <row r="101" spans="1:77" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:83" x14ac:dyDescent="0.3">
       <c r="A101" s="15" t="s">
         <v>7</v>
       </c>
@@ -7509,7 +7544,7 @@
       <c r="AX101" s="15"/>
       <c r="AY101" s="15"/>
     </row>
-    <row r="102" spans="1:77" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:83" x14ac:dyDescent="0.3">
       <c r="A102" s="15" t="s">
         <v>7</v>
       </c>
@@ -7586,7 +7621,7 @@
       <c r="AX102" s="15"/>
       <c r="AY102" s="15"/>
     </row>
-    <row r="103" spans="1:77" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:83" x14ac:dyDescent="0.3">
       <c r="A103" s="15" t="s">
         <v>7</v>
       </c>
@@ -7659,7 +7694,7 @@
       <c r="AX103" s="15"/>
       <c r="AY103" s="15"/>
     </row>
-    <row r="104" spans="1:77" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:83" x14ac:dyDescent="0.3">
       <c r="A104" s="15" t="s">
         <v>7</v>
       </c>
@@ -7731,8 +7766,8 @@
       <c r="AW104" s="15"/>
       <c r="AX104" s="15"/>
       <c r="AY104" s="15"/>
-      <c r="BV104" s="1" cm="1">
-        <f t="array" ref="BV104:BY123">_xlfn.LET(
+      <c r="CB104" s="1" cm="1">
+        <f t="array" ref="CB104:CE123">_xlfn.LET(
   _xlpm.cols_impairs, _xlfn.SEQUENCE(1,COLUMNS(C1:BF1)/2,1,2),
   _xlpm.cols_pairs,   _xlfn.SEQUENCE(1,COLUMNS(C2:BF2)/2,2,2),
   _xlpm.noms,     TRANSPOSE(INDEX(C9:BF9,,_xlpm.cols_impairs)),
@@ -7751,17 +7786,17 @@
 )</f>
         <v>1</v>
       </c>
-      <c r="BW104" s="1" t="str">
+      <c r="CC104" s="1" t="str">
         <v>Gauthier</v>
       </c>
-      <c r="BX104" s="1">
+      <c r="CD104" s="1">
         <v>7.391</v>
       </c>
-      <c r="BY104" s="1">
+      <c r="CE104" s="1">
         <v>69</v>
       </c>
     </row>
-    <row r="105" spans="1:77" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:83" x14ac:dyDescent="0.3">
       <c r="A105" s="15" t="s">
         <v>7</v>
       </c>
@@ -7837,20 +7872,20 @@
       <c r="AW105" s="15"/>
       <c r="AX105" s="15"/>
       <c r="AY105" s="15"/>
-      <c r="BV105" s="1">
-        <v>2</v>
-      </c>
-      <c r="BW105" s="1" t="str">
+      <c r="CB105" s="1">
+        <v>2</v>
+      </c>
+      <c r="CC105" s="1" t="str">
         <v>Boris</v>
       </c>
-      <c r="BX105" s="1">
-        <v>7.1959999999999997</v>
-      </c>
-      <c r="BY105" s="1">
-        <v>1031</v>
-      </c>
-    </row>
-    <row r="106" spans="1:77" x14ac:dyDescent="0.3">
+      <c r="CD105" s="1">
+        <v>7.19</v>
+      </c>
+      <c r="CE105" s="1">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="106" spans="1:83" x14ac:dyDescent="0.3">
       <c r="A106" s="15" t="s">
         <v>7</v>
       </c>
@@ -7926,20 +7961,20 @@
       <c r="AW106" s="15"/>
       <c r="AX106" s="15"/>
       <c r="AY106" s="15"/>
-      <c r="BV106" s="1">
+      <c r="CB106" s="1">
         <v>3</v>
       </c>
-      <c r="BW106" s="1" t="str">
+      <c r="CC106" s="1" t="str">
         <v>Joachim</v>
       </c>
-      <c r="BX106" s="1">
+      <c r="CD106" s="1">
         <v>6.202</v>
       </c>
-      <c r="BY106" s="1">
+      <c r="CE106" s="1">
         <v>104</v>
       </c>
     </row>
-    <row r="107" spans="1:77" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:83" x14ac:dyDescent="0.3">
       <c r="A107" s="15" t="s">
         <v>7</v>
       </c>
@@ -8011,20 +8046,20 @@
       <c r="AW107" s="15"/>
       <c r="AX107" s="15"/>
       <c r="AY107" s="15"/>
-      <c r="BV107" s="1">
+      <c r="CB107" s="1">
         <v>4</v>
       </c>
-      <c r="BW107" s="1" t="str">
-        <v>Tom</v>
-      </c>
-      <c r="BX107" s="1">
-        <v>6.1580000000000004</v>
-      </c>
-      <c r="BY107" s="1">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="108" spans="1:77" x14ac:dyDescent="0.3">
+      <c r="CC107" s="1" t="str">
+        <v>Célian</v>
+      </c>
+      <c r="CD107" s="1">
+        <v>6.1109999999999998</v>
+      </c>
+      <c r="CE107" s="1">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="108" spans="1:83" x14ac:dyDescent="0.3">
       <c r="A108" s="15" t="s">
         <v>7</v>
       </c>
@@ -8096,20 +8131,20 @@
       <c r="AW108" s="15"/>
       <c r="AX108" s="15"/>
       <c r="AY108" s="15"/>
-      <c r="BV108" s="1">
+      <c r="CB108" s="1">
         <v>5</v>
       </c>
-      <c r="BW108" s="1" t="str">
-        <v>Célian</v>
-      </c>
-      <c r="BX108" s="1">
-        <v>6.1109999999999998</v>
-      </c>
-      <c r="BY108" s="1">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="109" spans="1:77" x14ac:dyDescent="0.3">
+      <c r="CC108" s="1" t="str">
+        <v>William</v>
+      </c>
+      <c r="CD108" s="1">
+        <v>6.069</v>
+      </c>
+      <c r="CE108" s="1">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="109" spans="1:83" x14ac:dyDescent="0.3">
       <c r="A109" s="15" t="s">
         <v>7</v>
       </c>
@@ -8181,20 +8216,20 @@
       <c r="AW109" s="15"/>
       <c r="AX109" s="15"/>
       <c r="AY109" s="15"/>
-      <c r="BV109" s="1">
+      <c r="CB109" s="1">
         <v>6</v>
       </c>
-      <c r="BW109" s="1" t="str">
-        <v>William</v>
-      </c>
-      <c r="BX109" s="1">
-        <v>6.069</v>
-      </c>
-      <c r="BY109" s="1">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="110" spans="1:77" x14ac:dyDescent="0.3">
+      <c r="CC109" s="1" t="str">
+        <v>Tom</v>
+      </c>
+      <c r="CD109" s="1">
+        <v>6.0460000000000003</v>
+      </c>
+      <c r="CE109" s="1">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="110" spans="1:83" x14ac:dyDescent="0.3">
       <c r="A110" s="15" t="s">
         <v>7</v>
       </c>
@@ -8266,20 +8301,20 @@
       <c r="AW110" s="15"/>
       <c r="AX110" s="15"/>
       <c r="AY110" s="15"/>
-      <c r="BV110" s="1">
-        <v>7</v>
-      </c>
-      <c r="BW110" s="1" t="str">
+      <c r="CB110" s="1">
+        <v>7</v>
+      </c>
+      <c r="CC110" s="1" t="str">
         <v>Samuel</v>
       </c>
-      <c r="BX110" s="1">
+      <c r="CD110" s="1">
         <v>5.91</v>
       </c>
-      <c r="BY110" s="1">
+      <c r="CE110" s="1">
         <v>211</v>
       </c>
     </row>
-    <row r="111" spans="1:77" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:83" x14ac:dyDescent="0.3">
       <c r="A111" s="15" t="s">
         <v>7</v>
       </c>
@@ -8356,20 +8391,20 @@
       <c r="AZ111" s="15">
         <v>8</v>
       </c>
-      <c r="BV111" s="1">
-        <v>8</v>
-      </c>
-      <c r="BW111" s="1" t="str">
+      <c r="CB111" s="1">
+        <v>8</v>
+      </c>
+      <c r="CC111" s="1" t="str">
         <v>Mehdi</v>
       </c>
-      <c r="BX111" s="1">
+      <c r="CD111" s="1">
         <v>5.77</v>
       </c>
-      <c r="BY111" s="1">
+      <c r="CE111" s="1">
         <v>421</v>
       </c>
     </row>
-    <row r="112" spans="1:77" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:83" x14ac:dyDescent="0.3">
       <c r="A112" s="15" t="s">
         <v>7</v>
       </c>
@@ -8445,20 +8480,20 @@
       <c r="AW112" s="15"/>
       <c r="AX112" s="15"/>
       <c r="AY112" s="15"/>
-      <c r="BV112" s="1">
+      <c r="CB112" s="1">
         <v>9</v>
       </c>
-      <c r="BW112" s="1" t="str">
+      <c r="CC112" s="1" t="str">
         <v>Lou</v>
       </c>
-      <c r="BX112" s="1">
+      <c r="CD112" s="1">
         <v>5.5529999999999999</v>
       </c>
-      <c r="BY112" s="1">
+      <c r="CE112" s="1">
         <v>76</v>
       </c>
     </row>
-    <row r="113" spans="1:77" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:83" x14ac:dyDescent="0.3">
       <c r="A113" s="15" t="s">
         <v>7</v>
       </c>
@@ -8534,20 +8569,20 @@
       <c r="AW113" s="15"/>
       <c r="AX113" s="15"/>
       <c r="AY113" s="15"/>
-      <c r="BV113" s="1">
+      <c r="CB113" s="1">
         <v>10</v>
       </c>
-      <c r="BW113" s="1" t="str">
+      <c r="CC113" s="1" t="str">
         <v>Damien</v>
       </c>
-      <c r="BX113" s="1">
-        <v>5.4390000000000001</v>
-      </c>
-      <c r="BY113" s="1">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="114" spans="1:77" x14ac:dyDescent="0.3">
+      <c r="CD113" s="1">
+        <v>5.4740000000000002</v>
+      </c>
+      <c r="CE113" s="1">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="114" spans="1:83" x14ac:dyDescent="0.3">
       <c r="A114" s="15" t="s">
         <v>7</v>
       </c>
@@ -8619,20 +8654,20 @@
       <c r="AW114" s="15"/>
       <c r="AX114" s="15"/>
       <c r="AY114" s="15"/>
-      <c r="BV114" s="1">
+      <c r="CB114" s="1">
         <v>11</v>
       </c>
-      <c r="BW114" s="1" t="str">
+      <c r="CC114" s="1" t="str">
         <v>Achille</v>
       </c>
-      <c r="BX114" s="1">
+      <c r="CD114" s="1">
         <v>5.3470000000000004</v>
       </c>
-      <c r="BY114" s="1">
+      <c r="CE114" s="1">
         <v>824</v>
       </c>
     </row>
-    <row r="115" spans="1:77" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:83" x14ac:dyDescent="0.3">
       <c r="A115" s="15" t="s">
         <v>7</v>
       </c>
@@ -8704,20 +8739,20 @@
       <c r="AW115" s="15"/>
       <c r="AX115" s="15"/>
       <c r="AY115" s="15"/>
-      <c r="BV115" s="1">
+      <c r="CB115" s="1">
         <v>12</v>
       </c>
-      <c r="BW115" s="1" t="str">
+      <c r="CC115" s="1" t="str">
         <v>Jules</v>
       </c>
-      <c r="BX115" s="1">
+      <c r="CD115" s="1">
         <v>5.0709999999999997</v>
       </c>
-      <c r="BY115" s="1">
+      <c r="CE115" s="1">
         <v>155</v>
       </c>
     </row>
-    <row r="116" spans="1:77" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:83" x14ac:dyDescent="0.3">
       <c r="A116" s="15" t="s">
         <v>7</v>
       </c>
@@ -8785,20 +8820,20 @@
       <c r="AW116" s="15"/>
       <c r="AX116" s="15"/>
       <c r="AY116" s="15"/>
-      <c r="BV116" s="1">
+      <c r="CB116" s="1">
         <v>13</v>
       </c>
-      <c r="BW116" s="1" t="str">
+      <c r="CC116" s="1" t="str">
         <v>Paul</v>
       </c>
-      <c r="BX116" s="1">
+      <c r="CD116" s="1">
         <v>4.8129999999999997</v>
       </c>
-      <c r="BY116" s="1">
+      <c r="CE116" s="1">
         <v>32</v>
       </c>
     </row>
-    <row r="117" spans="1:77" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:83" x14ac:dyDescent="0.3">
       <c r="A117" s="15" t="s">
         <v>7</v>
       </c>
@@ -8874,20 +8909,20 @@
       <c r="AW117" s="15"/>
       <c r="AX117" s="15"/>
       <c r="AY117" s="15"/>
-      <c r="BV117" s="1">
+      <c r="CB117" s="1">
         <v>14</v>
       </c>
-      <c r="BW117" s="1" t="str">
+      <c r="CC117" s="1" t="str">
         <v>Joey</v>
       </c>
-      <c r="BX117" s="1">
+      <c r="CD117" s="1">
         <v>4.5</v>
       </c>
-      <c r="BY117" s="1">
+      <c r="CE117" s="1">
         <v>86</v>
       </c>
     </row>
-    <row r="118" spans="1:77" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:83" x14ac:dyDescent="0.3">
       <c r="A118" s="15" t="s">
         <v>7</v>
       </c>
@@ -8959,20 +8994,20 @@
       <c r="AW118" s="15"/>
       <c r="AX118" s="15"/>
       <c r="AY118" s="15"/>
-      <c r="BV118" s="1">
+      <c r="CB118" s="1">
         <v>15</v>
       </c>
-      <c r="BW118" s="1" t="str">
+      <c r="CC118" s="1" t="str">
         <v>Stanislas</v>
       </c>
-      <c r="BX118" s="1">
+      <c r="CD118" s="1">
         <v>4.4809999999999999</v>
       </c>
-      <c r="BY118" s="1">
+      <c r="CE118" s="1">
         <v>27</v>
       </c>
     </row>
-    <row r="119" spans="1:77" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:83" x14ac:dyDescent="0.3">
       <c r="A119" s="15" t="s">
         <v>7</v>
       </c>
@@ -9044,20 +9079,20 @@
       <c r="AW119" s="15"/>
       <c r="AX119" s="15"/>
       <c r="AY119" s="15"/>
-      <c r="BV119" s="1">
+      <c r="CB119" s="1">
         <v>16</v>
       </c>
-      <c r="BW119" s="1" t="str">
+      <c r="CC119" s="1" t="str">
         <v>Marie</v>
       </c>
-      <c r="BX119" s="1">
+      <c r="CD119" s="1">
         <v>4.3280000000000003</v>
       </c>
-      <c r="BY119" s="1">
+      <c r="CE119" s="1">
         <v>224</v>
       </c>
     </row>
-    <row r="120" spans="1:77" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:83" x14ac:dyDescent="0.3">
       <c r="A120" s="15" t="s">
         <v>7</v>
       </c>
@@ -9129,20 +9164,20 @@
       <c r="AW120" s="15"/>
       <c r="AX120" s="15"/>
       <c r="AY120" s="15"/>
-      <c r="BV120" s="1">
+      <c r="CB120" s="1">
         <v>17</v>
       </c>
-      <c r="BW120" s="1" t="str">
+      <c r="CC120" s="1" t="str">
         <v>Quentin</v>
       </c>
-      <c r="BX120" s="1">
+      <c r="CD120" s="1">
         <v>4.0970000000000004</v>
       </c>
-      <c r="BY120" s="1">
+      <c r="CE120" s="1">
         <v>93</v>
       </c>
     </row>
-    <row r="121" spans="1:77" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:83" x14ac:dyDescent="0.3">
       <c r="A121" s="15" t="s">
         <v>7</v>
       </c>
@@ -9222,20 +9257,20 @@
       <c r="AW121" s="15"/>
       <c r="AX121" s="15"/>
       <c r="AY121" s="15"/>
-      <c r="BV121" s="1">
+      <c r="CB121" s="1">
         <v>18</v>
       </c>
-      <c r="BW121" s="1" t="str">
+      <c r="CC121" s="1" t="str">
         <v>Luca</v>
       </c>
-      <c r="BX121" s="1">
+      <c r="CD121" s="1">
         <v>3.0110000000000001</v>
       </c>
-      <c r="BY121" s="1">
+      <c r="CE121" s="1">
         <v>178</v>
       </c>
     </row>
-    <row r="122" spans="1:77" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:83" x14ac:dyDescent="0.3">
       <c r="A122" s="15" t="s">
         <v>7</v>
       </c>
@@ -9307,20 +9342,20 @@
       <c r="AW122" s="15"/>
       <c r="AX122" s="15"/>
       <c r="AY122" s="15"/>
-      <c r="BV122" s="1">
+      <c r="CB122" s="1">
         <v>19</v>
       </c>
-      <c r="BW122" s="1" t="str">
+      <c r="CC122" s="1" t="str">
         <v>Fantinne</v>
       </c>
-      <c r="BX122" s="1">
+      <c r="CD122" s="1">
         <v>2.9609999999999999</v>
       </c>
-      <c r="BY122" s="1">
+      <c r="CE122" s="1">
         <v>51</v>
       </c>
     </row>
-    <row r="123" spans="1:77" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:83" x14ac:dyDescent="0.3">
       <c r="A123" s="15" t="s">
         <v>7</v>
       </c>
@@ -9396,20 +9431,20 @@
       <c r="AW123" s="15"/>
       <c r="AX123" s="15"/>
       <c r="AY123" s="15"/>
-      <c r="BV123" s="1">
+      <c r="CB123" s="1">
         <v>20</v>
       </c>
-      <c r="BW123" s="1" t="str">
+      <c r="CC123" s="1" t="str">
         <v>Loulou</v>
       </c>
-      <c r="BX123" s="1">
+      <c r="CD123" s="1">
         <v>2.0750000000000002</v>
       </c>
-      <c r="BY123" s="1">
+      <c r="CE123" s="1">
         <v>67</v>
       </c>
     </row>
-    <row r="124" spans="1:77" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:83" x14ac:dyDescent="0.3">
       <c r="A124" s="15" t="s">
         <v>7</v>
       </c>
@@ -9482,7 +9517,7 @@
       <c r="AX124" s="15"/>
       <c r="AY124" s="15"/>
     </row>
-    <row r="125" spans="1:77" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:83" x14ac:dyDescent="0.3">
       <c r="A125" s="15" t="s">
         <v>7</v>
       </c>
@@ -9559,7 +9594,7 @@
       <c r="AX125" s="15"/>
       <c r="AY125" s="15"/>
     </row>
-    <row r="126" spans="1:77" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:83" x14ac:dyDescent="0.3">
       <c r="A126" s="15" t="s">
         <v>7</v>
       </c>
@@ -9632,7 +9667,7 @@
       <c r="AX126" s="15"/>
       <c r="AY126" s="15"/>
     </row>
-    <row r="127" spans="1:77" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:83" x14ac:dyDescent="0.3">
       <c r="A127" s="15" t="s">
         <v>7</v>
       </c>
@@ -9705,7 +9740,7 @@
       <c r="AX127" s="15"/>
       <c r="AY127" s="15"/>
     </row>
-    <row r="128" spans="1:77" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:83" x14ac:dyDescent="0.3">
       <c r="A128" s="15" t="s">
         <v>7</v>
       </c>
@@ -9778,7 +9813,7 @@
       <c r="AX128" s="15"/>
       <c r="AY128" s="15"/>
     </row>
-    <row r="129" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:86" x14ac:dyDescent="0.3">
       <c r="A129" s="15" t="s">
         <v>7</v>
       </c>
@@ -9851,7 +9886,7 @@
       <c r="AX129" s="15"/>
       <c r="AY129" s="15"/>
     </row>
-    <row r="130" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:86" x14ac:dyDescent="0.3">
       <c r="A130" s="15" t="s">
         <v>7</v>
       </c>
@@ -9923,8 +9958,8 @@
       <c r="AW130" s="15"/>
       <c r="AX130" s="15"/>
       <c r="AY130" s="15"/>
-      <c r="BV130" s="1" t="str" cm="1">
-        <f t="array" ref="BV130:BX147">_xlfn.LET(_xlpm.cols_impairs, _xlfn.SEQUENCE(1,COLUMNS(C1:AZ1)/2,1,2),
+      <c r="CB130" s="1" t="str" cm="1">
+        <f t="array" ref="CB130:CD147">_xlfn.LET(_xlpm.cols_impairs, _xlfn.SEQUENCE(1,COLUMNS(C1:AZ1)/2,1,2),
   _xlpm.cols_pairs,   _xlfn.SEQUENCE(1,COLUMNS(C2:AZ2)/2,2,2),
   _xlpm.noms,     TRANSPOSE(INDEX(C9:AZ9,,_xlpm.cols_impairs)),
   _xlpm.moy,      TRANSPOSE(INDEX(C1:AZ1,,_xlpm.cols_impairs)),
@@ -9934,21 +9969,21 @@
 )</f>
         <v>Gauthier</v>
       </c>
-      <c r="BW130" s="1">
+      <c r="CC130" s="1">
         <v>7.3913043478260869</v>
       </c>
-      <c r="BX130" s="1">
+      <c r="CD130" s="1">
         <v>69</v>
       </c>
-      <c r="CA130" s="1" t="str" cm="1">
-        <f t="array" ref="CA130:CB149">_xlfn.LET(  _xlpm.noms, TRANSPOSE(INDEX(C9:BF9,_xlfn.SEQUENCE(1,COLUMNS(C9:BF9)/2,1,2))),_xlpm.moy,  TRANSPOSE(INDEX(C1:BF1,,_xlfn.SEQUENCE(1,COLUMNS(C1:BF1)/2,1,2))),_xlpm.ok, ISNUMBER(_xlpm.moy),_xlfn._xlws.SORT(CHOOSE({1,2}, _xlfn._xlws.FILTER(_xlpm.noms, _xlpm.ok), _xlfn._xlws.FILTER(_xlpm.moy, _xlpm.ok)), 2, -1))</f>
+      <c r="CG130" s="1" t="str" cm="1">
+        <f t="array" ref="CG130:CH149">_xlfn.LET(  _xlpm.noms, TRANSPOSE(INDEX(C9:BF9,_xlfn.SEQUENCE(1,COLUMNS(C9:BF9)/2,1,2))),_xlpm.moy,  TRANSPOSE(INDEX(C1:BF1,,_xlfn.SEQUENCE(1,COLUMNS(C1:BF1)/2,1,2))),_xlpm.ok, ISNUMBER(_xlpm.moy),_xlfn._xlws.SORT(CHOOSE({1,2}, _xlfn._xlws.FILTER(_xlpm.noms, _xlpm.ok), _xlfn._xlws.FILTER(_xlpm.moy, _xlpm.ok)), 2, -1))</f>
         <v>Gauthier</v>
       </c>
-      <c r="CB130" s="1">
+      <c r="CH130" s="1">
         <v>7.3913043478260869</v>
       </c>
     </row>
-    <row r="131" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:86" x14ac:dyDescent="0.3">
       <c r="A131" s="15" t="s">
         <v>7</v>
       </c>
@@ -10020,23 +10055,23 @@
       <c r="AW131" s="15"/>
       <c r="AX131" s="15"/>
       <c r="AY131" s="15"/>
-      <c r="BV131" s="1" t="str">
+      <c r="CB131" s="1" t="str">
         <v>Boris</v>
       </c>
-      <c r="BW131" s="1">
-        <v>7.1964112512124148</v>
-      </c>
-      <c r="BX131" s="1">
-        <v>1031</v>
-      </c>
-      <c r="CA131" s="1" t="str">
+      <c r="CC131" s="1">
+        <v>7.1900866217516839</v>
+      </c>
+      <c r="CD131" s="1">
+        <v>1039</v>
+      </c>
+      <c r="CG131" s="1" t="str">
         <v>Boris</v>
       </c>
-      <c r="CB131" s="1">
-        <v>7.1964112512124148</v>
-      </c>
-    </row>
-    <row r="132" spans="1:80" x14ac:dyDescent="0.3">
+      <c r="CH131" s="1">
+        <v>7.1900866217516839</v>
+      </c>
+    </row>
+    <row r="132" spans="1:86" x14ac:dyDescent="0.3">
       <c r="A132" s="15" t="s">
         <v>7</v>
       </c>
@@ -10108,23 +10143,23 @@
       <c r="AW132" s="15"/>
       <c r="AX132" s="15"/>
       <c r="AY132" s="15"/>
-      <c r="BV132" s="1" t="str">
+      <c r="CB132" s="1" t="str">
         <v>Joachim</v>
       </c>
-      <c r="BW132" s="1">
+      <c r="CC132" s="1">
         <v>6.2019230769230766</v>
       </c>
-      <c r="BX132" s="1">
+      <c r="CD132" s="1">
         <v>104</v>
       </c>
-      <c r="CA132" s="1" t="str">
+      <c r="CG132" s="1" t="str">
         <v>Joachim</v>
       </c>
-      <c r="CB132" s="1">
+      <c r="CH132" s="1">
         <v>6.2019230769230766</v>
       </c>
     </row>
-    <row r="133" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:86" x14ac:dyDescent="0.3">
       <c r="A133" s="15" t="s">
         <v>7</v>
       </c>
@@ -10196,23 +10231,23 @@
       <c r="AW133" s="15"/>
       <c r="AX133" s="15"/>
       <c r="AY133" s="15"/>
-      <c r="BV133" s="1" t="str">
-        <v>Tom</v>
-      </c>
-      <c r="BW133" s="1">
-        <v>6.1578947368421053</v>
-      </c>
-      <c r="BX133" s="1">
-        <v>209</v>
-      </c>
-      <c r="CA133" s="1" t="str">
-        <v>Tom</v>
-      </c>
-      <c r="CB133" s="1">
-        <v>6.1578947368421053</v>
-      </c>
-    </row>
-    <row r="134" spans="1:80" x14ac:dyDescent="0.3">
+      <c r="CB133" s="1" t="str">
+        <v>Célian</v>
+      </c>
+      <c r="CC133" s="1">
+        <v>6.1106870229007635</v>
+      </c>
+      <c r="CD133" s="1">
+        <v>262</v>
+      </c>
+      <c r="CG133" s="1" t="str">
+        <v>Célian</v>
+      </c>
+      <c r="CH133" s="1">
+        <v>6.1106870229007635</v>
+      </c>
+    </row>
+    <row r="134" spans="1:86" x14ac:dyDescent="0.3">
       <c r="A134" s="15" t="s">
         <v>7</v>
       </c>
@@ -10284,23 +10319,23 @@
       <c r="AW134" s="15"/>
       <c r="AX134" s="15"/>
       <c r="AY134" s="15"/>
-      <c r="BV134" s="1" t="str">
-        <v>Célian</v>
-      </c>
-      <c r="BW134" s="1">
-        <v>6.1106870229007635</v>
-      </c>
-      <c r="BX134" s="1">
-        <v>262</v>
-      </c>
-      <c r="CA134" s="1" t="str">
-        <v>Célian</v>
-      </c>
-      <c r="CB134" s="1">
-        <v>6.1106870229007635</v>
-      </c>
-    </row>
-    <row r="135" spans="1:80" x14ac:dyDescent="0.3">
+      <c r="CB134" s="1" t="str">
+        <v>William</v>
+      </c>
+      <c r="CC134" s="1">
+        <v>6.068965517241379</v>
+      </c>
+      <c r="CD134" s="1">
+        <v>29</v>
+      </c>
+      <c r="CG134" s="1" t="str">
+        <v>William</v>
+      </c>
+      <c r="CH134" s="1">
+        <v>6.068965517241379</v>
+      </c>
+    </row>
+    <row r="135" spans="1:86" x14ac:dyDescent="0.3">
       <c r="A135" s="15" t="s">
         <v>7</v>
       </c>
@@ -10372,23 +10407,23 @@
       <c r="AW135" s="15"/>
       <c r="AX135" s="15"/>
       <c r="AY135" s="15"/>
-      <c r="BV135" s="1" t="str">
-        <v>William</v>
-      </c>
-      <c r="BW135" s="1">
-        <v>6.068965517241379</v>
-      </c>
-      <c r="BX135" s="1">
-        <v>29</v>
-      </c>
-      <c r="CA135" s="1" t="str">
-        <v>William</v>
-      </c>
-      <c r="CB135" s="1">
-        <v>6.068965517241379</v>
-      </c>
-    </row>
-    <row r="136" spans="1:80" x14ac:dyDescent="0.3">
+      <c r="CB135" s="1" t="str">
+        <v>Tom</v>
+      </c>
+      <c r="CC135" s="1">
+        <v>6.0460829493087553</v>
+      </c>
+      <c r="CD135" s="1">
+        <v>217</v>
+      </c>
+      <c r="CG135" s="1" t="str">
+        <v>Tom</v>
+      </c>
+      <c r="CH135" s="1">
+        <v>6.0460829493087553</v>
+      </c>
+    </row>
+    <row r="136" spans="1:86" x14ac:dyDescent="0.3">
       <c r="A136" s="15" t="s">
         <v>7</v>
       </c>
@@ -10460,23 +10495,23 @@
       <c r="AW136" s="15"/>
       <c r="AX136" s="15"/>
       <c r="AY136" s="15"/>
-      <c r="BV136" s="1" t="str">
+      <c r="CB136" s="1" t="str">
         <v>Samuel</v>
       </c>
-      <c r="BW136" s="1">
+      <c r="CC136" s="1">
         <v>5.9099526066350707</v>
       </c>
-      <c r="BX136" s="1">
+      <c r="CD136" s="1">
         <v>211</v>
       </c>
-      <c r="CA136" s="1" t="str">
+      <c r="CG136" s="1" t="str">
         <v>Samuel</v>
       </c>
-      <c r="CB136" s="1">
+      <c r="CH136" s="1">
         <v>5.9099526066350707</v>
       </c>
     </row>
-    <row r="137" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:86" x14ac:dyDescent="0.3">
       <c r="A137" s="15" t="s">
         <v>7</v>
       </c>
@@ -10552,23 +10587,23 @@
       <c r="AW137" s="15"/>
       <c r="AX137" s="15"/>
       <c r="AY137" s="15"/>
-      <c r="BV137" s="1" t="str">
+      <c r="CB137" s="1" t="str">
         <v>Mehdi</v>
       </c>
-      <c r="BW137" s="1">
+      <c r="CC137" s="1">
         <v>5.7695961995249405</v>
       </c>
-      <c r="BX137" s="1">
+      <c r="CD137" s="1">
         <v>421</v>
       </c>
-      <c r="CA137" s="1" t="str">
+      <c r="CG137" s="1" t="str">
         <v>Mehdi</v>
       </c>
-      <c r="CB137" s="1">
+      <c r="CH137" s="1">
         <v>5.7695961995249405</v>
       </c>
     </row>
-    <row r="138" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:86" x14ac:dyDescent="0.3">
       <c r="A138" s="15" t="s">
         <v>7</v>
       </c>
@@ -10640,46 +10675,46 @@
       <c r="AW138" s="15"/>
       <c r="AX138" s="15"/>
       <c r="AY138" s="15"/>
-      <c r="BV138" s="1" t="str">
+      <c r="CB138" s="1" t="str">
         <v>Damien</v>
       </c>
-      <c r="BW138" s="1">
-        <v>5.4393700787401578</v>
-      </c>
-      <c r="BX138" s="1">
-        <v>635</v>
-      </c>
-      <c r="CA138" s="1" t="str">
+      <c r="CC138" s="1">
+        <v>5.4743390357698285</v>
+      </c>
+      <c r="CD138" s="1">
+        <v>643</v>
+      </c>
+      <c r="CG138" s="1" t="str">
         <v>Lou</v>
       </c>
-      <c r="CB138" s="1">
+      <c r="CH138" s="1">
         <v>5.5526315789473681</v>
       </c>
     </row>
-    <row r="139" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:86" x14ac:dyDescent="0.3">
       <c r="A139" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="BV139" s="1" t="str">
+      <c r="CB139" s="1" t="str">
         <v>Achille</v>
       </c>
-      <c r="BW139" s="1">
+      <c r="CC139" s="1">
         <v>5.3470873786407767</v>
       </c>
-      <c r="BX139" s="1">
+      <c r="CD139" s="1">
         <v>824</v>
       </c>
-      <c r="CA139" s="1" t="str">
+      <c r="CG139" s="1" t="str">
         <v>Damien</v>
       </c>
-      <c r="CB139" s="1">
-        <v>5.4393700787401578</v>
-      </c>
-    </row>
-    <row r="140" spans="1:80" x14ac:dyDescent="0.3">
+      <c r="CH139" s="1">
+        <v>5.4743390357698285</v>
+      </c>
+    </row>
+    <row r="140" spans="1:86" x14ac:dyDescent="0.3">
       <c r="A140" s="1" t="s">
         <v>7</v>
       </c>
@@ -10710,23 +10745,23 @@
       <c r="Z140" s="1">
         <v>11</v>
       </c>
-      <c r="BV140" s="1" t="str">
+      <c r="CB140" s="1" t="str">
         <v>Jules</v>
       </c>
-      <c r="BW140" s="1">
+      <c r="CC140" s="1">
         <v>5.0709677419354842</v>
       </c>
-      <c r="BX140" s="1">
+      <c r="CD140" s="1">
         <v>155</v>
       </c>
-      <c r="CA140" s="1" t="str">
+      <c r="CG140" s="1" t="str">
         <v>Achille</v>
       </c>
-      <c r="CB140" s="1">
+      <c r="CH140" s="1">
         <v>5.3470873786407767</v>
       </c>
     </row>
-    <row r="141" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:86" x14ac:dyDescent="0.3">
       <c r="A141" s="1" t="s">
         <v>7</v>
       </c>
@@ -10757,23 +10792,23 @@
       <c r="N141" s="1">
         <v>20</v>
       </c>
-      <c r="BV141" s="1" t="str">
+      <c r="CB141" s="1" t="str">
         <v>Paul</v>
       </c>
-      <c r="BW141" s="1">
+      <c r="CC141" s="1">
         <v>4.8125</v>
       </c>
-      <c r="BX141" s="1">
+      <c r="CD141" s="1">
         <v>32</v>
       </c>
-      <c r="CA141" s="1" t="str">
+      <c r="CG141" s="1" t="str">
         <v>Jules</v>
       </c>
-      <c r="CB141" s="1">
+      <c r="CH141" s="1">
         <v>5.0709677419354842</v>
       </c>
     </row>
-    <row r="142" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:86" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="s">
         <v>7</v>
       </c>
@@ -10804,23 +10839,23 @@
       <c r="N142" s="1">
         <v>8</v>
       </c>
-      <c r="BV142" s="1" t="str">
+      <c r="CB142" s="1" t="str">
         <v>Joey</v>
       </c>
-      <c r="BW142" s="1">
+      <c r="CC142" s="1">
         <v>4.5</v>
       </c>
-      <c r="BX142" s="1">
+      <c r="CD142" s="1">
         <v>86</v>
       </c>
-      <c r="CA142" s="1" t="str">
+      <c r="CG142" s="1" t="str">
         <v>Paul</v>
       </c>
-      <c r="CB142" s="1">
+      <c r="CH142" s="1">
         <v>4.8125</v>
       </c>
     </row>
-    <row r="143" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:86" x14ac:dyDescent="0.3">
       <c r="A143" s="1" t="s">
         <v>7</v>
       </c>
@@ -10851,23 +10886,23 @@
       <c r="AB143" s="1">
         <v>9</v>
       </c>
-      <c r="BV143" s="1" t="str">
+      <c r="CB143" s="1" t="str">
         <v>Marie</v>
       </c>
-      <c r="BW143" s="1">
+      <c r="CC143" s="1">
         <v>4.328125</v>
       </c>
-      <c r="BX143" s="1">
+      <c r="CD143" s="1">
         <v>224</v>
       </c>
-      <c r="CA143" s="1" t="str">
+      <c r="CG143" s="1" t="str">
         <v>Joey</v>
       </c>
-      <c r="CB143" s="1">
+      <c r="CH143" s="1">
         <v>4.5</v>
       </c>
     </row>
-    <row r="144" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:86" x14ac:dyDescent="0.3">
       <c r="A144" s="1" t="s">
         <v>7</v>
       </c>
@@ -10898,23 +10933,23 @@
       <c r="AB144" s="1">
         <v>12</v>
       </c>
-      <c r="BV144" s="1" t="str">
+      <c r="CB144" s="1" t="str">
         <v>Quentin</v>
       </c>
-      <c r="BW144" s="1">
+      <c r="CC144" s="1">
         <v>4.096774193548387</v>
       </c>
-      <c r="BX144" s="1">
+      <c r="CD144" s="1">
         <v>93</v>
       </c>
-      <c r="CA144" s="1" t="str">
+      <c r="CG144" s="1" t="str">
         <v>Stanislas</v>
       </c>
-      <c r="CB144" s="1">
+      <c r="CH144" s="1">
         <v>4.4814814814814818</v>
       </c>
     </row>
-    <row r="145" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:86" x14ac:dyDescent="0.3">
       <c r="A145" s="1" t="s">
         <v>7</v>
       </c>
@@ -10945,23 +10980,23 @@
       <c r="P145" s="1">
         <v>2</v>
       </c>
-      <c r="BV145" s="1" t="str">
+      <c r="CB145" s="1" t="str">
         <v>Luca</v>
       </c>
-      <c r="BW145" s="1">
+      <c r="CC145" s="1">
         <v>3.0112359550561796</v>
       </c>
-      <c r="BX145" s="1">
+      <c r="CD145" s="1">
         <v>178</v>
       </c>
-      <c r="CA145" s="1" t="str">
+      <c r="CG145" s="1" t="str">
         <v>Marie</v>
       </c>
-      <c r="CB145" s="1">
+      <c r="CH145" s="1">
         <v>4.328125</v>
       </c>
     </row>
-    <row r="146" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:86" x14ac:dyDescent="0.3">
       <c r="A146" s="1" t="s">
         <v>7</v>
       </c>
@@ -10992,23 +11027,23 @@
       <c r="J146" s="1">
         <v>13</v>
       </c>
-      <c r="BV146" s="1" t="str">
+      <c r="CB146" s="1" t="str">
         <v>Fantinne</v>
       </c>
-      <c r="BW146" s="1">
+      <c r="CC146" s="1">
         <v>2.9607843137254903</v>
       </c>
-      <c r="BX146" s="1">
+      <c r="CD146" s="1">
         <v>51</v>
       </c>
-      <c r="CA146" s="1" t="str">
+      <c r="CG146" s="1" t="str">
         <v>Quentin</v>
       </c>
-      <c r="CB146" s="1">
+      <c r="CH146" s="1">
         <v>4.096774193548387</v>
       </c>
     </row>
-    <row r="147" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:86" x14ac:dyDescent="0.3">
       <c r="A147" s="1" t="s">
         <v>7</v>
       </c>
@@ -11039,23 +11074,23 @@
       <c r="X147" s="1">
         <v>9</v>
       </c>
-      <c r="BV147" s="1" t="str">
+      <c r="CB147" s="1" t="str">
         <v>Loulou</v>
       </c>
-      <c r="BW147" s="1">
+      <c r="CC147" s="1">
         <v>2.0746268656716418</v>
       </c>
-      <c r="BX147" s="1">
+      <c r="CD147" s="1">
         <v>67</v>
       </c>
-      <c r="CA147" s="1" t="str">
+      <c r="CG147" s="1" t="str">
         <v>Luca</v>
       </c>
-      <c r="CB147" s="1">
+      <c r="CH147" s="1">
         <v>3.0112359550561796</v>
       </c>
     </row>
-    <row r="148" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:86" x14ac:dyDescent="0.3">
       <c r="A148" s="1" t="s">
         <v>7</v>
       </c>
@@ -11086,14 +11121,14 @@
       <c r="J148" s="1">
         <v>11</v>
       </c>
-      <c r="CA148" s="1" t="str">
+      <c r="CG148" s="1" t="str">
         <v>Fantinne</v>
       </c>
-      <c r="CB148" s="1">
+      <c r="CH148" s="1">
         <v>2.9607843137254903</v>
       </c>
     </row>
-    <row r="149" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:86" x14ac:dyDescent="0.3">
       <c r="A149" s="1" t="s">
         <v>7</v>
       </c>
@@ -11124,14 +11159,14 @@
       <c r="N149" s="1">
         <v>13</v>
       </c>
-      <c r="CA149" s="1" t="str">
+      <c r="CG149" s="1" t="str">
         <v>Loulou</v>
       </c>
-      <c r="CB149" s="1">
+      <c r="CH149" s="1">
         <v>2.0746268656716418</v>
       </c>
     </row>
-    <row r="150" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:86" x14ac:dyDescent="0.3">
       <c r="A150" s="1" t="s">
         <v>7</v>
       </c>
@@ -11163,7 +11198,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="151" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:86" x14ac:dyDescent="0.3">
       <c r="A151" s="1" t="s">
         <v>7</v>
       </c>
@@ -11199,7 +11234,10 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A140:AM151">
     <sortCondition descending="1" ref="B140:B151"/>
   </sortState>
-  <mergeCells count="28">
+  <mergeCells count="31">
+    <mergeCell ref="BG9:BH9"/>
+    <mergeCell ref="BI9:BJ9"/>
+    <mergeCell ref="BK9:BL9"/>
     <mergeCell ref="BA9:BB9"/>
     <mergeCell ref="BC9:BD9"/>
     <mergeCell ref="BE9:BF9"/>
@@ -11286,7 +11324,7 @@
       <formula>(C10/D10)&gt;10</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BO72:BO100">
+  <conditionalFormatting sqref="BU72:BU100">
     <cfRule type="cellIs" dxfId="7" priority="3" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
@@ -11311,7 +11349,7 @@
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BT72:BT93">
+  <conditionalFormatting sqref="BZ72:BZ93">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="between">
       <formula>1</formula>
       <formula>10</formula>
@@ -11355,13 +11393,13 @@
         <v>42</v>
       </c>
       <c r="F1" t="str" cm="1">
-        <f t="array" ref="F1:F10">'All stat'!BP59:BP68</f>
+        <f t="array" ref="F1:F10">'All stat'!BV59:BV68</f>
         <v>légende</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="25" cm="1">
-        <f t="array" ref="A2:D21">_xlfn.ANCHORARRAY('All stat'!BL72)</f>
+        <f t="array" ref="A2:D21">_xlfn.ANCHORARRAY('All stat'!BR72)</f>
         <v>1</v>
       </c>
       <c r="B2" s="25" t="str">
@@ -11385,17 +11423,17 @@
         <v>Boris</v>
       </c>
       <c r="C3" s="25" t="str">
-        <v>7.196</v>
+        <v>7.190</v>
       </c>
       <c r="D3" s="25">
-        <v>1031</v>
+        <v>1039</v>
       </c>
       <c r="F3" t="str">
         <v>entre 1 et 10</v>
       </c>
       <c r="G3" s="23"/>
       <c r="H3" t="str" cm="1">
-        <f t="array" ref="H3:I10">'All stat'!BR61:BS68</f>
+        <f t="array" ref="H3:I10">'All stat'!BX61:BY68</f>
         <v>anecdotique</v>
       </c>
       <c r="I3" t="str">
@@ -11431,13 +11469,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="25" t="str">
-        <v>Tom</v>
+        <v>Célian</v>
       </c>
       <c r="C5" s="25" t="str">
-        <v>6.158</v>
+        <v>6.111</v>
       </c>
       <c r="D5" s="25">
-        <v>209</v>
+        <v>262</v>
       </c>
       <c r="F5" t="str">
         <v>entre 20 et 50</v>
@@ -11455,13 +11493,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="25" t="str">
-        <v>Célian</v>
+        <v>William</v>
       </c>
       <c r="C6" s="25" t="str">
-        <v>6.111</v>
+        <v>6.069</v>
       </c>
       <c r="D6" s="25">
-        <v>262</v>
+        <v>29</v>
       </c>
       <c r="F6" t="str">
         <v>entre 50 et 100</v>
@@ -11479,13 +11517,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="25" t="str">
-        <v>William</v>
+        <v>Tom</v>
       </c>
       <c r="C7" s="25" t="str">
-        <v>6.069</v>
+        <v>6.046</v>
       </c>
       <c r="D7" s="25">
-        <v>29</v>
+        <v>217</v>
       </c>
       <c r="F7" t="str">
         <v>entre 100 et 250</v>
@@ -11578,10 +11616,10 @@
         <v>Damien</v>
       </c>
       <c r="C11" s="25" t="str">
-        <v>5.439</v>
+        <v>5.474</v>
       </c>
       <c r="D11" s="25">
-        <v>635</v>
+        <v>643</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">

--- a/classement_whist_2023_2025.xlsx
+++ b/classement_whist_2023_2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/A20B8382962B136A/Bureau/loisir/whist/projet_application_streamlit/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="14_{D8C30FC8-DD4A-4CBA-A5BF-091BFC36F9C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{754371CA-87D8-450E-B2F8-FE4EA38100DA}"/>
+  <xr:revisionPtr revIDLastSave="31" documentId="14_{D8C30FC8-DD4A-4CBA-A5BF-091BFC36F9C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE7D86D8-FB2D-44B3-AAC5-9EA736DFC562}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="C1" s="1">
         <f t="shared" ref="C1" si="0">IF(D2&gt;19,C2/D2,"/")</f>
-        <v>5.3470873786407767</v>
+        <v>5.4065138721351023</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="G1" s="1">
         <f t="shared" ref="G1" si="2">IF(H2&gt;19,G2/H2,"/")</f>
-        <v>7.1900866217516839</v>
+        <v>7.1877376425855513</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>2</v>
@@ -1189,14 +1189,14 @@
       </c>
       <c r="K1" s="1">
         <f t="shared" ref="K1" si="4">IF(L2&gt;19,K2/L2,"/")</f>
-        <v>6.2019230769230766</v>
+        <v>5.8899082568807337</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="M1" s="1">
         <f t="shared" ref="M1" si="5">IF(N2&gt;19,M2/N2,"/")</f>
-        <v>5.4743390357698285</v>
+        <v>5.5238095238095237</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>2</v>
@@ -1210,14 +1210,14 @@
       </c>
       <c r="Q1" s="1">
         <f t="shared" ref="Q1" si="7">IF(R2&gt;19,Q2/R2,"/")</f>
-        <v>6.1106870229007635</v>
+        <v>6.0861423220973787</v>
       </c>
       <c r="R1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="S1" s="1">
         <f t="shared" ref="S1" si="8">IF(T2&gt;19,S2/T2,"/")</f>
-        <v>6.0460829493087553</v>
+        <v>6.0533333333333337</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>2</v>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="BE1" s="1">
         <f t="shared" ref="BE1" si="26">IF(BF2&gt;19,BE2/BF2,"/")</f>
-        <v>5.5526315789473681</v>
+        <v>5.1547619047619051</v>
       </c>
       <c r="BF1" s="1" t="s">
         <v>2</v>
@@ -1362,11 +1362,11 @@
       </c>
       <c r="C2" s="1">
         <f>C4+C6+C8</f>
-        <v>4406</v>
+        <v>4482</v>
       </c>
       <c r="D2" s="1">
         <f>D4+D6+D8</f>
-        <v>824</v>
+        <v>829</v>
       </c>
       <c r="E2" s="1">
         <f t="shared" ref="E2:J2" si="27">E4+E6+E8</f>
@@ -1378,11 +1378,11 @@
       </c>
       <c r="G2" s="1">
         <f t="shared" si="27"/>
-        <v>7470.5</v>
+        <v>7561.5</v>
       </c>
       <c r="H2" s="1">
         <f t="shared" si="27"/>
-        <v>1039</v>
+        <v>1052</v>
       </c>
       <c r="I2" s="1">
         <f t="shared" si="27"/>
@@ -1394,19 +1394,19 @@
       </c>
       <c r="K2" s="1">
         <f t="shared" ref="K2:AZ2" si="28">K4+K6+K8</f>
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="L2" s="1">
         <f t="shared" si="28"/>
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="M2" s="1">
         <f t="shared" si="28"/>
-        <v>3520</v>
+        <v>3596</v>
       </c>
       <c r="N2" s="1">
         <f t="shared" si="28"/>
-        <v>643</v>
+        <v>651</v>
       </c>
       <c r="O2" s="1">
         <f t="shared" si="28"/>
@@ -1418,19 +1418,19 @@
       </c>
       <c r="Q2" s="1">
         <f t="shared" si="28"/>
-        <v>1601</v>
+        <v>1625</v>
       </c>
       <c r="R2" s="1">
         <f t="shared" si="28"/>
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="S2" s="1">
         <f t="shared" si="28"/>
-        <v>1312</v>
+        <v>1362</v>
       </c>
       <c r="T2" s="1">
         <f t="shared" si="28"/>
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="U2" s="1">
         <f t="shared" si="28"/>
@@ -1578,11 +1578,11 @@
       </c>
       <c r="BE2" s="1">
         <f t="shared" ref="BE2:BF2" si="30">BE4+BE6+BE8</f>
-        <v>422</v>
+        <v>433</v>
       </c>
       <c r="BF2" s="1">
         <f t="shared" si="30"/>
-        <v>76</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:69" x14ac:dyDescent="0.3">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="C7" s="15">
         <f>C8/D8</f>
-        <v>6.2131661442006267</v>
+        <v>6.3518518518518521</v>
       </c>
       <c r="D7" s="15" t="s">
         <v>2</v>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="G7" s="15">
         <f t="shared" ref="G7" si="94">G8/H8</f>
-        <v>7.4270428015564205</v>
+        <v>7.4165085388994312</v>
       </c>
       <c r="H7" s="15" t="s">
         <v>2</v>
@@ -2506,14 +2506,14 @@
       </c>
       <c r="K7" s="15">
         <f t="shared" ref="K7" si="96">K8/L8</f>
-        <v>4.8636363636363633</v>
+        <v>3.8518518518518516</v>
       </c>
       <c r="L7" s="15" t="s">
         <v>2</v>
       </c>
       <c r="M7" s="15">
         <f t="shared" ref="M7" si="97">M8/N8</f>
-        <v>5.9428571428571431</v>
+        <v>6.004319654427646</v>
       </c>
       <c r="N7" s="15" t="s">
         <v>2</v>
@@ -2527,14 +2527,14 @@
       </c>
       <c r="Q7" s="15">
         <f t="shared" ref="Q7" si="99">Q8/R8</f>
-        <v>6.2299465240641707</v>
+        <v>6.192708333333333</v>
       </c>
       <c r="R7" s="15" t="s">
         <v>2</v>
       </c>
       <c r="S7" s="15">
         <f t="shared" ref="S7" si="100">S8/T8</f>
-        <v>5.0360360360360357</v>
+        <v>5.117647058823529</v>
       </c>
       <c r="T7" s="15" t="s">
         <v>2</v>
@@ -2667,7 +2667,7 @@
       </c>
       <c r="BE7" s="15">
         <f t="shared" ref="BE7" si="119">BE8/BF8</f>
-        <v>5.5526315789473681</v>
+        <v>5.1547619047619051</v>
       </c>
       <c r="BF7" s="15" t="s">
         <v>2</v>
@@ -2680,11 +2680,11 @@
       </c>
       <c r="C8" s="15">
         <f>SUM(C10:C94)</f>
-        <v>1982</v>
+        <v>2058</v>
       </c>
       <c r="D8" s="15">
         <f>SUM(D10:D94)</f>
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="E8" s="15">
         <f t="shared" ref="E8:J8" si="120">SUM(E10:E94)</f>
@@ -2696,11 +2696,11 @@
       </c>
       <c r="G8" s="15">
         <f t="shared" si="120"/>
-        <v>3817.5</v>
+        <v>3908.5</v>
       </c>
       <c r="H8" s="15">
         <f t="shared" si="120"/>
-        <v>514</v>
+        <v>527</v>
       </c>
       <c r="I8" s="15">
         <f t="shared" si="120"/>
@@ -2712,19 +2712,19 @@
       </c>
       <c r="K8" s="15">
         <f t="shared" ref="K8:AZ8" si="121">SUM(K10:K94)</f>
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="L8" s="15">
         <f t="shared" si="121"/>
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="M8" s="15">
         <f t="shared" si="121"/>
-        <v>2704</v>
+        <v>2780</v>
       </c>
       <c r="N8" s="15">
         <f t="shared" si="121"/>
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="O8" s="15">
         <f t="shared" si="121"/>
@@ -2736,19 +2736,19 @@
       </c>
       <c r="Q8" s="15">
         <f t="shared" si="121"/>
-        <v>1165</v>
+        <v>1189</v>
       </c>
       <c r="R8" s="15">
         <f t="shared" si="121"/>
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="S8" s="15">
         <f t="shared" si="121"/>
-        <v>559</v>
+        <v>609</v>
       </c>
       <c r="T8" s="15">
         <f t="shared" si="121"/>
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="U8" s="15">
         <f t="shared" si="121"/>
@@ -2896,11 +2896,11 @@
       </c>
       <c r="BE8" s="15">
         <f t="shared" ref="BE8:BF8" si="123">SUM(BE10:BE94)</f>
-        <v>422</v>
+        <v>433</v>
       </c>
       <c r="BF8" s="15">
         <f t="shared" si="123"/>
-        <v>76</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:69" x14ac:dyDescent="0.3">
@@ -3058,6 +3058,30 @@
       <c r="B15" s="1">
         <v>135</v>
       </c>
+      <c r="G15" s="1">
+        <v>42</v>
+      </c>
+      <c r="H15" s="1">
+        <v>8</v>
+      </c>
+      <c r="M15" s="1">
+        <v>76</v>
+      </c>
+      <c r="N15" s="1">
+        <v>8</v>
+      </c>
+      <c r="S15" s="1">
+        <v>50</v>
+      </c>
+      <c r="T15" s="1">
+        <v>8</v>
+      </c>
+      <c r="BE15" s="1">
+        <v>11</v>
+      </c>
+      <c r="BF15" s="1">
+        <v>8</v>
+      </c>
     </row>
     <row r="16" spans="1:69" x14ac:dyDescent="0.3">
       <c r="B16" s="1">
@@ -3081,10 +3105,40 @@
       <c r="T16" s="1">
         <v>8</v>
       </c>
+      <c r="BG16" s="1">
+        <v>69</v>
+      </c>
+      <c r="BH16" s="1">
+        <v>8</v>
+      </c>
     </row>
     <row r="17" spans="1:58" x14ac:dyDescent="0.3">
       <c r="B17" s="1">
         <v>133</v>
+      </c>
+      <c r="C17" s="1">
+        <v>76</v>
+      </c>
+      <c r="D17" s="1">
+        <v>5</v>
+      </c>
+      <c r="G17" s="1">
+        <v>49</v>
+      </c>
+      <c r="H17" s="1">
+        <v>5</v>
+      </c>
+      <c r="K17" s="1">
+        <v>-3</v>
+      </c>
+      <c r="L17" s="1">
+        <v>5</v>
+      </c>
+      <c r="Q17" s="1">
+        <v>24</v>
+      </c>
+      <c r="R17" s="1">
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:58" x14ac:dyDescent="0.3">
@@ -5204,10 +5258,10 @@
         <v>Boris</v>
       </c>
       <c r="BT73" s="1" t="str">
-        <v>7.190</v>
+        <v>7.188</v>
       </c>
       <c r="BU73" s="1">
-        <v>1039</v>
+        <v>1052</v>
       </c>
       <c r="BW73" s="1">
         <v>2</v>
@@ -5225,7 +5279,7 @@
         <v>Boris</v>
       </c>
       <c r="CC73" s="1">
-        <v>7.1900866217516839</v>
+        <v>7.1877376425855513</v>
       </c>
     </row>
     <row r="74" spans="1:81" x14ac:dyDescent="0.3">
@@ -5267,13 +5321,13 @@
         <v>3</v>
       </c>
       <c r="BS74" s="1" t="str">
-        <v>Joachim</v>
+        <v>Célian</v>
       </c>
       <c r="BT74" s="1" t="str">
-        <v>6.202</v>
+        <v>6.086</v>
       </c>
       <c r="BU74" s="1">
-        <v>104</v>
+        <v>267</v>
       </c>
       <c r="BW74" s="1">
         <v>3</v>
@@ -5288,10 +5342,10 @@
         <v>17</v>
       </c>
       <c r="CB74" s="1" t="str">
-        <v>Joachim</v>
+        <v>Célian</v>
       </c>
       <c r="CC74" s="1">
-        <v>6.2019230769230766</v>
+        <v>6.0861423220973787</v>
       </c>
     </row>
     <row r="75" spans="1:81" x14ac:dyDescent="0.3">
@@ -5329,13 +5383,13 @@
         <v>4</v>
       </c>
       <c r="BS75" s="1" t="str">
-        <v>Célian</v>
+        <v>William</v>
       </c>
       <c r="BT75" s="1" t="str">
-        <v>6.111</v>
+        <v>6.069</v>
       </c>
       <c r="BU75" s="1">
-        <v>262</v>
+        <v>29</v>
       </c>
       <c r="BW75" s="1">
         <v>4</v>
@@ -5350,10 +5404,10 @@
         <v>5</v>
       </c>
       <c r="CB75" s="1" t="str">
-        <v>Célian</v>
+        <v>William</v>
       </c>
       <c r="CC75" s="1">
-        <v>6.1106870229007635</v>
+        <v>6.068965517241379</v>
       </c>
     </row>
     <row r="76" spans="1:81" x14ac:dyDescent="0.3">
@@ -5395,13 +5449,13 @@
         <v>5</v>
       </c>
       <c r="BS76" s="1" t="str">
-        <v>William</v>
+        <v>Tom</v>
       </c>
       <c r="BT76" s="1" t="str">
-        <v>6.069</v>
+        <v>6.053</v>
       </c>
       <c r="BU76" s="1">
-        <v>29</v>
+        <v>225</v>
       </c>
       <c r="BW76" s="1">
         <v>5</v>
@@ -5416,10 +5470,10 @@
         <v>13</v>
       </c>
       <c r="CB76" s="1" t="str">
-        <v>William</v>
+        <v>Tom</v>
       </c>
       <c r="CC76" s="1">
-        <v>6.068965517241379</v>
+        <v>6.0533333333333337</v>
       </c>
     </row>
     <row r="77" spans="1:81" x14ac:dyDescent="0.3">
@@ -5461,13 +5515,13 @@
         <v>6</v>
       </c>
       <c r="BS77" s="1" t="str">
-        <v>Tom</v>
+        <v>Samuel</v>
       </c>
       <c r="BT77" s="1" t="str">
-        <v>6.046</v>
+        <v>5.910</v>
       </c>
       <c r="BU77" s="1">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="BW77" s="1">
         <v>6</v>
@@ -5482,10 +5536,10 @@
         <v>5</v>
       </c>
       <c r="CB77" s="1" t="str">
-        <v>Tom</v>
+        <v>Samuel</v>
       </c>
       <c r="CC77" s="1">
-        <v>6.0460829493087553</v>
+        <v>5.9099526066350707</v>
       </c>
     </row>
     <row r="78" spans="1:81" x14ac:dyDescent="0.3">
@@ -5527,13 +5581,13 @@
         <v>7</v>
       </c>
       <c r="BS78" s="1" t="str">
-        <v>Samuel</v>
+        <v>Joachim</v>
       </c>
       <c r="BT78" s="1" t="str">
-        <v>5.910</v>
+        <v>5.890</v>
       </c>
       <c r="BU78" s="1">
-        <v>211</v>
+        <v>109</v>
       </c>
       <c r="BW78" s="1">
         <v>7</v>
@@ -5548,10 +5602,10 @@
         <v>11</v>
       </c>
       <c r="CB78" s="1" t="str">
-        <v>Samuel</v>
+        <v>Joachim</v>
       </c>
       <c r="CC78" s="1">
-        <v>5.9099526066350707</v>
+        <v>5.8899082568807337</v>
       </c>
     </row>
     <row r="79" spans="1:81" x14ac:dyDescent="0.3">
@@ -5700,19 +5754,19 @@
         <v>9</v>
       </c>
       <c r="BS80" s="1" t="str">
-        <v>Lou</v>
+        <v>Damien</v>
       </c>
       <c r="BT80" s="1" t="str">
-        <v>5.553</v>
+        <v>5.524</v>
       </c>
       <c r="BU80" s="1">
-        <v>76</v>
+        <v>651</v>
       </c>
       <c r="CB80" s="1" t="str">
-        <v>Lou</v>
+        <v>Damien</v>
       </c>
       <c r="CC80" s="1">
-        <v>5.5526315789473681</v>
+        <v>5.5238095238095237</v>
       </c>
     </row>
     <row r="81" spans="1:81" x14ac:dyDescent="0.3">
@@ -5795,19 +5849,19 @@
         <v>10</v>
       </c>
       <c r="BS81" s="1" t="str">
-        <v>Damien</v>
+        <v>Achille</v>
       </c>
       <c r="BT81" s="1" t="str">
-        <v>5.474</v>
+        <v>5.407</v>
       </c>
       <c r="BU81" s="1">
-        <v>643</v>
+        <v>829</v>
       </c>
       <c r="CB81" s="1" t="str">
-        <v>Damien</v>
+        <v>Achille</v>
       </c>
       <c r="CC81" s="1">
-        <v>5.4743390357698285</v>
+        <v>5.4065138721351023</v>
       </c>
     </row>
     <row r="82" spans="1:81" x14ac:dyDescent="0.3">
@@ -5890,19 +5944,19 @@
         <v>11</v>
       </c>
       <c r="BS82" s="1" t="str">
-        <v>Achille</v>
+        <v>Lou</v>
       </c>
       <c r="BT82" s="1" t="str">
-        <v>5.347</v>
+        <v>5.155</v>
       </c>
       <c r="BU82" s="1">
-        <v>824</v>
+        <v>84</v>
       </c>
       <c r="CB82" s="1" t="str">
-        <v>Achille</v>
+        <v>Lou</v>
       </c>
       <c r="CC82" s="1">
-        <v>5.3470873786407767</v>
+        <v>5.1547619047619051</v>
       </c>
     </row>
     <row r="83" spans="1:81" x14ac:dyDescent="0.3">
@@ -6077,7 +6131,7 @@
       </c>
       <c r="BP84" s="1">
         <f>AVERAGE(C1:BF1)</f>
-        <v>5.1199575943444193</v>
+        <v>5.088926053912485</v>
       </c>
       <c r="BR84" s="1">
         <v>13</v>
@@ -7879,10 +7933,10 @@
         <v>Boris</v>
       </c>
       <c r="CD105" s="1">
-        <v>7.19</v>
+        <v>7.1879999999999997</v>
       </c>
       <c r="CE105" s="1">
-        <v>1039</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="106" spans="1:83" x14ac:dyDescent="0.3">
@@ -7965,13 +8019,13 @@
         <v>3</v>
       </c>
       <c r="CC106" s="1" t="str">
-        <v>Joachim</v>
+        <v>Célian</v>
       </c>
       <c r="CD106" s="1">
-        <v>6.202</v>
+        <v>6.0860000000000003</v>
       </c>
       <c r="CE106" s="1">
-        <v>104</v>
+        <v>267</v>
       </c>
     </row>
     <row r="107" spans="1:83" x14ac:dyDescent="0.3">
@@ -8050,13 +8104,13 @@
         <v>4</v>
       </c>
       <c r="CC107" s="1" t="str">
-        <v>Célian</v>
+        <v>William</v>
       </c>
       <c r="CD107" s="1">
-        <v>6.1109999999999998</v>
+        <v>6.069</v>
       </c>
       <c r="CE107" s="1">
-        <v>262</v>
+        <v>29</v>
       </c>
     </row>
     <row r="108" spans="1:83" x14ac:dyDescent="0.3">
@@ -8135,13 +8189,13 @@
         <v>5</v>
       </c>
       <c r="CC108" s="1" t="str">
-        <v>William</v>
+        <v>Tom</v>
       </c>
       <c r="CD108" s="1">
-        <v>6.069</v>
+        <v>6.0529999999999999</v>
       </c>
       <c r="CE108" s="1">
-        <v>29</v>
+        <v>225</v>
       </c>
     </row>
     <row r="109" spans="1:83" x14ac:dyDescent="0.3">
@@ -8220,13 +8274,13 @@
         <v>6</v>
       </c>
       <c r="CC109" s="1" t="str">
-        <v>Tom</v>
+        <v>Samuel</v>
       </c>
       <c r="CD109" s="1">
-        <v>6.0460000000000003</v>
+        <v>5.91</v>
       </c>
       <c r="CE109" s="1">
-        <v>217</v>
+        <v>211</v>
       </c>
     </row>
     <row r="110" spans="1:83" x14ac:dyDescent="0.3">
@@ -8305,13 +8359,13 @@
         <v>7</v>
       </c>
       <c r="CC110" s="1" t="str">
-        <v>Samuel</v>
+        <v>Joachim</v>
       </c>
       <c r="CD110" s="1">
-        <v>5.91</v>
+        <v>5.89</v>
       </c>
       <c r="CE110" s="1">
-        <v>211</v>
+        <v>109</v>
       </c>
     </row>
     <row r="111" spans="1:83" x14ac:dyDescent="0.3">
@@ -8484,13 +8538,13 @@
         <v>9</v>
       </c>
       <c r="CC112" s="1" t="str">
-        <v>Lou</v>
+        <v>Damien</v>
       </c>
       <c r="CD112" s="1">
-        <v>5.5529999999999999</v>
+        <v>5.524</v>
       </c>
       <c r="CE112" s="1">
-        <v>76</v>
+        <v>651</v>
       </c>
     </row>
     <row r="113" spans="1:83" x14ac:dyDescent="0.3">
@@ -8573,13 +8627,13 @@
         <v>10</v>
       </c>
       <c r="CC113" s="1" t="str">
-        <v>Damien</v>
+        <v>Achille</v>
       </c>
       <c r="CD113" s="1">
-        <v>5.4740000000000002</v>
+        <v>5.407</v>
       </c>
       <c r="CE113" s="1">
-        <v>643</v>
+        <v>829</v>
       </c>
     </row>
     <row r="114" spans="1:83" x14ac:dyDescent="0.3">
@@ -8658,13 +8712,13 @@
         <v>11</v>
       </c>
       <c r="CC114" s="1" t="str">
-        <v>Achille</v>
+        <v>Lou</v>
       </c>
       <c r="CD114" s="1">
-        <v>5.3470000000000004</v>
+        <v>5.1550000000000002</v>
       </c>
       <c r="CE114" s="1">
-        <v>824</v>
+        <v>84</v>
       </c>
     </row>
     <row r="115" spans="1:83" x14ac:dyDescent="0.3">
@@ -10059,16 +10113,16 @@
         <v>Boris</v>
       </c>
       <c r="CC131" s="1">
-        <v>7.1900866217516839</v>
+        <v>7.1877376425855513</v>
       </c>
       <c r="CD131" s="1">
-        <v>1039</v>
+        <v>1052</v>
       </c>
       <c r="CG131" s="1" t="str">
         <v>Boris</v>
       </c>
       <c r="CH131" s="1">
-        <v>7.1900866217516839</v>
+        <v>7.1877376425855513</v>
       </c>
     </row>
     <row r="132" spans="1:86" x14ac:dyDescent="0.3">
@@ -10144,19 +10198,19 @@
       <c r="AX132" s="15"/>
       <c r="AY132" s="15"/>
       <c r="CB132" s="1" t="str">
-        <v>Joachim</v>
+        <v>Célian</v>
       </c>
       <c r="CC132" s="1">
-        <v>6.2019230769230766</v>
+        <v>6.0861423220973787</v>
       </c>
       <c r="CD132" s="1">
-        <v>104</v>
+        <v>267</v>
       </c>
       <c r="CG132" s="1" t="str">
-        <v>Joachim</v>
+        <v>Célian</v>
       </c>
       <c r="CH132" s="1">
-        <v>6.2019230769230766</v>
+        <v>6.0861423220973787</v>
       </c>
     </row>
     <row r="133" spans="1:86" x14ac:dyDescent="0.3">
@@ -10232,19 +10286,19 @@
       <c r="AX133" s="15"/>
       <c r="AY133" s="15"/>
       <c r="CB133" s="1" t="str">
-        <v>Célian</v>
+        <v>William</v>
       </c>
       <c r="CC133" s="1">
-        <v>6.1106870229007635</v>
+        <v>6.068965517241379</v>
       </c>
       <c r="CD133" s="1">
-        <v>262</v>
+        <v>29</v>
       </c>
       <c r="CG133" s="1" t="str">
-        <v>Célian</v>
+        <v>William</v>
       </c>
       <c r="CH133" s="1">
-        <v>6.1106870229007635</v>
+        <v>6.068965517241379</v>
       </c>
     </row>
     <row r="134" spans="1:86" x14ac:dyDescent="0.3">
@@ -10320,19 +10374,19 @@
       <c r="AX134" s="15"/>
       <c r="AY134" s="15"/>
       <c r="CB134" s="1" t="str">
-        <v>William</v>
+        <v>Tom</v>
       </c>
       <c r="CC134" s="1">
-        <v>6.068965517241379</v>
+        <v>6.0533333333333337</v>
       </c>
       <c r="CD134" s="1">
-        <v>29</v>
+        <v>225</v>
       </c>
       <c r="CG134" s="1" t="str">
-        <v>William</v>
+        <v>Tom</v>
       </c>
       <c r="CH134" s="1">
-        <v>6.068965517241379</v>
+        <v>6.0533333333333337</v>
       </c>
     </row>
     <row r="135" spans="1:86" x14ac:dyDescent="0.3">
@@ -10408,19 +10462,19 @@
       <c r="AX135" s="15"/>
       <c r="AY135" s="15"/>
       <c r="CB135" s="1" t="str">
-        <v>Tom</v>
+        <v>Samuel</v>
       </c>
       <c r="CC135" s="1">
-        <v>6.0460829493087553</v>
+        <v>5.9099526066350707</v>
       </c>
       <c r="CD135" s="1">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="CG135" s="1" t="str">
-        <v>Tom</v>
+        <v>Samuel</v>
       </c>
       <c r="CH135" s="1">
-        <v>6.0460829493087553</v>
+        <v>5.9099526066350707</v>
       </c>
     </row>
     <row r="136" spans="1:86" x14ac:dyDescent="0.3">
@@ -10496,19 +10550,19 @@
       <c r="AX136" s="15"/>
       <c r="AY136" s="15"/>
       <c r="CB136" s="1" t="str">
-        <v>Samuel</v>
+        <v>Joachim</v>
       </c>
       <c r="CC136" s="1">
-        <v>5.9099526066350707</v>
+        <v>5.8899082568807337</v>
       </c>
       <c r="CD136" s="1">
-        <v>211</v>
+        <v>109</v>
       </c>
       <c r="CG136" s="1" t="str">
-        <v>Samuel</v>
+        <v>Joachim</v>
       </c>
       <c r="CH136" s="1">
-        <v>5.9099526066350707</v>
+        <v>5.8899082568807337</v>
       </c>
     </row>
     <row r="137" spans="1:86" x14ac:dyDescent="0.3">
@@ -10679,16 +10733,16 @@
         <v>Damien</v>
       </c>
       <c r="CC138" s="1">
-        <v>5.4743390357698285</v>
+        <v>5.5238095238095237</v>
       </c>
       <c r="CD138" s="1">
-        <v>643</v>
+        <v>651</v>
       </c>
       <c r="CG138" s="1" t="str">
-        <v>Lou</v>
+        <v>Damien</v>
       </c>
       <c r="CH138" s="1">
-        <v>5.5526315789473681</v>
+        <v>5.5238095238095237</v>
       </c>
     </row>
     <row r="139" spans="1:86" x14ac:dyDescent="0.3">
@@ -10702,16 +10756,16 @@
         <v>Achille</v>
       </c>
       <c r="CC139" s="1">
-        <v>5.3470873786407767</v>
+        <v>5.4065138721351023</v>
       </c>
       <c r="CD139" s="1">
-        <v>824</v>
+        <v>829</v>
       </c>
       <c r="CG139" s="1" t="str">
-        <v>Damien</v>
+        <v>Achille</v>
       </c>
       <c r="CH139" s="1">
-        <v>5.4743390357698285</v>
+        <v>5.4065138721351023</v>
       </c>
     </row>
     <row r="140" spans="1:86" x14ac:dyDescent="0.3">
@@ -10755,10 +10809,10 @@
         <v>155</v>
       </c>
       <c r="CG140" s="1" t="str">
-        <v>Achille</v>
+        <v>Lou</v>
       </c>
       <c r="CH140" s="1">
-        <v>5.3470873786407767</v>
+        <v>5.1547619047619051</v>
       </c>
     </row>
     <row r="141" spans="1:86" x14ac:dyDescent="0.3">
@@ -11423,10 +11477,10 @@
         <v>Boris</v>
       </c>
       <c r="C3" s="25" t="str">
-        <v>7.190</v>
+        <v>7.188</v>
       </c>
       <c r="D3" s="25">
-        <v>1039</v>
+        <v>1052</v>
       </c>
       <c r="F3" t="str">
         <v>entre 1 et 10</v>
@@ -11445,13 +11499,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="25" t="str">
-        <v>Joachim</v>
+        <v>Célian</v>
       </c>
       <c r="C4" s="25" t="str">
-        <v>6.202</v>
+        <v>6.086</v>
       </c>
       <c r="D4" s="25">
-        <v>104</v>
+        <v>267</v>
       </c>
       <c r="F4" t="str">
         <v>entre 10 et 20</v>
@@ -11469,13 +11523,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="25" t="str">
-        <v>Célian</v>
+        <v>William</v>
       </c>
       <c r="C5" s="25" t="str">
-        <v>6.111</v>
+        <v>6.069</v>
       </c>
       <c r="D5" s="25">
-        <v>262</v>
+        <v>29</v>
       </c>
       <c r="F5" t="str">
         <v>entre 20 et 50</v>
@@ -11493,13 +11547,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="25" t="str">
-        <v>William</v>
+        <v>Tom</v>
       </c>
       <c r="C6" s="25" t="str">
-        <v>6.069</v>
+        <v>6.053</v>
       </c>
       <c r="D6" s="25">
-        <v>29</v>
+        <v>225</v>
       </c>
       <c r="F6" t="str">
         <v>entre 50 et 100</v>
@@ -11517,13 +11571,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="25" t="str">
-        <v>Tom</v>
+        <v>Samuel</v>
       </c>
       <c r="C7" s="25" t="str">
-        <v>6.046</v>
+        <v>5.910</v>
       </c>
       <c r="D7" s="25">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="F7" t="str">
         <v>entre 100 et 250</v>
@@ -11541,13 +11595,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="25" t="str">
-        <v>Samuel</v>
+        <v>Joachim</v>
       </c>
       <c r="C8" s="25" t="str">
-        <v>5.910</v>
+        <v>5.890</v>
       </c>
       <c r="D8" s="25">
-        <v>211</v>
+        <v>109</v>
       </c>
       <c r="F8" t="str">
         <v>entre 250 et 500</v>
@@ -11589,13 +11643,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="25" t="str">
-        <v>Lou</v>
+        <v>Damien</v>
       </c>
       <c r="C10" s="25" t="str">
-        <v>5.553</v>
+        <v>5.524</v>
       </c>
       <c r="D10" s="25">
-        <v>76</v>
+        <v>651</v>
       </c>
       <c r="F10" t="str">
         <v>plus de 1000</v>
@@ -11613,13 +11667,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="25" t="str">
-        <v>Damien</v>
+        <v>Achille</v>
       </c>
       <c r="C11" s="25" t="str">
-        <v>5.474</v>
+        <v>5.407</v>
       </c>
       <c r="D11" s="25">
-        <v>643</v>
+        <v>829</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
@@ -11627,13 +11681,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="25" t="str">
-        <v>Achille</v>
+        <v>Lou</v>
       </c>
       <c r="C12" s="25" t="str">
-        <v>5.347</v>
+        <v>5.155</v>
       </c>
       <c r="D12" s="25">
-        <v>824</v>
+        <v>84</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">

--- a/classement_whist_2023_2025.xlsx
+++ b/classement_whist_2023_2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/A20B8382962B136A/Bureau/loisir/whist/projet_application_streamlit/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="31" documentId="14_{D8C30FC8-DD4A-4CBA-A5BF-091BFC36F9C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE7D86D8-FB2D-44B3-AAC5-9EA736DFC562}"/>
+  <xr:revisionPtr revIDLastSave="36" documentId="14_{D8C30FC8-DD4A-4CBA-A5BF-091BFC36F9C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8E42337B-F0BC-4C8E-B111-9D1B806A0825}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="93">
   <si>
     <t>global</t>
   </si>
@@ -610,6 +610,14 @@
   <dxfs count="25">
     <dxf>
       <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB5E6A2"/>
+          <bgColor rgb="FFB5E6A2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
         <patternFill>
           <bgColor theme="0" tint="-0.24994659260841701"/>
         </patternFill>
@@ -733,14 +741,6 @@
         <patternFill patternType="solid">
           <fgColor rgb="FF92D050"/>
           <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB5E6A2"/>
-          <bgColor rgb="FFB5E6A2"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1355,6 +1355,27 @@
       <c r="BF1" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="BG1" s="1" t="str">
+        <f t="shared" ref="BG1" si="27">IF(BH2&gt;19,BG2/BH2,"/")</f>
+        <v>/</v>
+      </c>
+      <c r="BH1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="BI1" s="1" t="str">
+        <f t="shared" ref="BI1" si="28">IF(BJ2&gt;19,BI2/BJ2,"/")</f>
+        <v>/</v>
+      </c>
+      <c r="BJ1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="BK1" s="1" t="str">
+        <f t="shared" ref="BK1" si="29">IF(BL2&gt;19,BK2/BL2,"/")</f>
+        <v>/</v>
+      </c>
+      <c r="BL1" s="1" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="2" spans="1:69" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
@@ -1369,220 +1390,244 @@
         <v>829</v>
       </c>
       <c r="E2" s="1">
-        <f t="shared" ref="E2:J2" si="27">E4+E6+E8</f>
+        <f t="shared" ref="E2:J2" si="30">E4+E6+E8</f>
         <v>2429</v>
       </c>
       <c r="F2" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>421</v>
       </c>
       <c r="G2" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>7561.5</v>
       </c>
       <c r="H2" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>1052</v>
       </c>
       <c r="I2" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>1247</v>
       </c>
       <c r="J2" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>211</v>
       </c>
       <c r="K2" s="1">
-        <f t="shared" ref="K2:AZ2" si="28">K4+K6+K8</f>
+        <f t="shared" ref="K2:AZ2" si="31">K4+K6+K8</f>
         <v>642</v>
       </c>
       <c r="L2" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>109</v>
       </c>
       <c r="M2" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>3596</v>
       </c>
       <c r="N2" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>651</v>
       </c>
       <c r="O2" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>510</v>
       </c>
       <c r="P2" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>69</v>
       </c>
       <c r="Q2" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>1625</v>
       </c>
       <c r="R2" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>267</v>
       </c>
       <c r="S2" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>1362</v>
       </c>
       <c r="T2" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>225</v>
       </c>
       <c r="U2" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>536</v>
       </c>
       <c r="V2" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>178</v>
       </c>
       <c r="W2" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>139</v>
       </c>
       <c r="X2" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>67</v>
       </c>
       <c r="Y2" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>154</v>
       </c>
       <c r="Z2" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>32</v>
       </c>
       <c r="AA2" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>969.5</v>
       </c>
       <c r="AB2" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>224</v>
       </c>
       <c r="AC2" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>786</v>
       </c>
       <c r="AD2" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>155</v>
       </c>
       <c r="AE2" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>27</v>
       </c>
       <c r="AF2" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>5</v>
       </c>
       <c r="AG2" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>176</v>
       </c>
       <c r="AH2" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>29</v>
       </c>
       <c r="AI2" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>151</v>
       </c>
       <c r="AJ2" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>51</v>
       </c>
       <c r="AK2" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>121</v>
       </c>
       <c r="AL2" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>17</v>
       </c>
       <c r="AM2" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>387</v>
       </c>
       <c r="AN2" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>86</v>
       </c>
       <c r="AO2" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>-1</v>
       </c>
       <c r="AP2" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>12</v>
       </c>
       <c r="AQ2" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>381</v>
       </c>
       <c r="AR2" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>93</v>
       </c>
       <c r="AS2" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>8</v>
       </c>
       <c r="AT2" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>11</v>
       </c>
       <c r="AU2" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>34</v>
       </c>
       <c r="AV2" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>4</v>
       </c>
       <c r="AW2" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>14</v>
       </c>
       <c r="AX2" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>5</v>
       </c>
       <c r="AY2" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>43</v>
       </c>
       <c r="AZ2" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>13</v>
       </c>
       <c r="BA2" s="1">
-        <f t="shared" ref="BA2:BD2" si="29">BA4+BA6+BA8</f>
+        <f t="shared" ref="BA2:BD2" si="32">BA4+BA6+BA8</f>
         <v>34</v>
       </c>
       <c r="BB2" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>2</v>
       </c>
       <c r="BC2" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>121</v>
       </c>
       <c r="BD2" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>27</v>
       </c>
       <c r="BE2" s="1">
-        <f t="shared" ref="BE2:BF2" si="30">BE4+BE6+BE8</f>
+        <f t="shared" ref="BE2:BF2" si="33">BE4+BE6+BE8</f>
         <v>433</v>
       </c>
       <c r="BF2" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>84</v>
+      </c>
+      <c r="BG2" s="1">
+        <f t="shared" ref="BG2:BL2" si="34">BG4+BG6+BG8</f>
+        <v>69</v>
+      </c>
+      <c r="BH2" s="1">
+        <f t="shared" si="34"/>
+        <v>8</v>
+      </c>
+      <c r="BI2" s="1">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="BJ2" s="1">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="BK2" s="1">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="BL2" s="1">
+        <f t="shared" si="34"/>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:69" x14ac:dyDescent="0.3">
@@ -1600,192 +1645,213 @@
         <v>2</v>
       </c>
       <c r="E3" s="1">
-        <f t="shared" ref="E3" si="31">E4/F4</f>
+        <f t="shared" ref="E3" si="35">E4/F4</f>
         <v>3.3414634146341462</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="G3" s="1">
-        <f t="shared" ref="G3" si="32">G4/H4</f>
+        <f t="shared" ref="G3" si="36">G4/H4</f>
         <v>7.2666666666666666</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="I3" s="1">
-        <f t="shared" ref="I3" si="33">I4/J4</f>
+        <f t="shared" ref="I3" si="37">I4/J4</f>
         <v>7.78125</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="K3" s="1">
-        <f t="shared" ref="K3" si="34">K4/L4</f>
+        <f t="shared" ref="K3" si="38">K4/L4</f>
         <v>5.5</v>
       </c>
       <c r="L3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="M3" s="1">
-        <f t="shared" ref="M3" si="35">M4/N4</f>
+        <f t="shared" ref="M3" si="39">M4/N4</f>
         <v>5.9268292682926829</v>
       </c>
       <c r="N3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="O3" s="1">
-        <f t="shared" ref="O3" si="36">O4/P4</f>
+        <f t="shared" ref="O3" si="40">O4/P4</f>
         <v>6</v>
       </c>
       <c r="P3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="Q3" s="1" t="e">
-        <f t="shared" ref="Q3" si="37">Q4/R4</f>
+        <f t="shared" ref="Q3" si="41">Q4/R4</f>
         <v>#DIV/0!</v>
       </c>
       <c r="R3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="S3" s="1" t="e">
-        <f t="shared" ref="S3" si="38">S4/T4</f>
+        <f t="shared" ref="S3" si="42">S4/T4</f>
         <v>#DIV/0!</v>
       </c>
       <c r="T3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="U3" s="1">
-        <f t="shared" ref="U3" si="39">U4/V4</f>
+        <f t="shared" ref="U3" si="43">U4/V4</f>
         <v>5.8181818181818183</v>
       </c>
       <c r="V3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="W3" s="1">
-        <f t="shared" ref="W3" si="40">W4/X4</f>
+        <f t="shared" ref="W3" si="44">W4/X4</f>
         <v>6.1111111111111107</v>
       </c>
       <c r="X3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="Y3" s="1">
-        <f t="shared" ref="Y3" si="41">Y4/Z4</f>
+        <f t="shared" ref="Y3" si="45">Y4/Z4</f>
         <v>4.8125</v>
       </c>
       <c r="Z3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="AA3" s="1">
-        <f t="shared" ref="AA3" si="42">AA4/AB4</f>
+        <f t="shared" ref="AA3" si="46">AA4/AB4</f>
         <v>4.2380952380952381</v>
       </c>
       <c r="AB3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="AC3" s="1" t="e">
-        <f t="shared" ref="AC3" si="43">AC4/AD4</f>
+        <f t="shared" ref="AC3" si="47">AC4/AD4</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AD3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="AE3" s="1" t="e">
-        <f t="shared" ref="AE3" si="44">AE4/AF4</f>
+        <f t="shared" ref="AE3" si="48">AE4/AF4</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AF3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="AG3" s="1" t="e">
-        <f t="shared" ref="AG3" si="45">AG4/AH4</f>
+        <f t="shared" ref="AG3" si="49">AG4/AH4</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AH3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="AI3" s="1" t="e">
-        <f t="shared" ref="AI3" si="46">AI4/AJ4</f>
+        <f t="shared" ref="AI3" si="50">AI4/AJ4</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AJ3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="AK3" s="1" t="e">
-        <f t="shared" ref="AK3" si="47">AK4/AL4</f>
+        <f t="shared" ref="AK3" si="51">AK4/AL4</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AL3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="AM3" s="1" t="e">
-        <f t="shared" ref="AM3" si="48">AM4/AN4</f>
+        <f t="shared" ref="AM3" si="52">AM4/AN4</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AN3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="AO3" s="1" t="e">
-        <f t="shared" ref="AO3" si="49">AO4/AP4</f>
+        <f t="shared" ref="AO3" si="53">AO4/AP4</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AP3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="AQ3" s="1" t="e">
-        <f t="shared" ref="AQ3" si="50">AQ4/AR4</f>
+        <f t="shared" ref="AQ3" si="54">AQ4/AR4</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AR3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="AS3" s="1" t="e">
-        <f t="shared" ref="AS3" si="51">AS4/AT4</f>
+        <f t="shared" ref="AS3" si="55">AS4/AT4</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AT3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="AU3" s="1" t="e">
-        <f t="shared" ref="AU3" si="52">AU4/AV4</f>
+        <f t="shared" ref="AU3" si="56">AU4/AV4</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AV3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="AW3" s="1" t="e">
-        <f t="shared" ref="AW3" si="53">AW4/AX4</f>
+        <f t="shared" ref="AW3" si="57">AW4/AX4</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AX3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="AY3" s="1" t="e">
-        <f t="shared" ref="AY3" si="54">AY4/AZ4</f>
+        <f t="shared" ref="AY3" si="58">AY4/AZ4</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AZ3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="BA3" s="1" t="e">
-        <f t="shared" ref="BA3" si="55">BA4/BB4</f>
+        <f t="shared" ref="BA3" si="59">BA4/BB4</f>
         <v>#DIV/0!</v>
       </c>
       <c r="BB3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="BC3" s="1" t="e">
-        <f t="shared" ref="BC3" si="56">BC4/BD4</f>
+        <f t="shared" ref="BC3" si="60">BC4/BD4</f>
         <v>#DIV/0!</v>
       </c>
       <c r="BD3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="BE3" s="1" t="e">
-        <f t="shared" ref="BE3" si="57">BE4/BF4</f>
+        <f t="shared" ref="BE3" si="61">BE4/BF4</f>
         <v>#DIV/0!</v>
       </c>
       <c r="BF3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="BG3" s="1" t="e">
+        <f t="shared" ref="BG3" si="62">BG4/BH4</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BH3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="BI3" s="1" t="e">
+        <f t="shared" ref="BI3" si="63">BI4/BJ4</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BJ3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="BK3" s="1" t="e">
+        <f t="shared" ref="BK3" si="64">BK4/BL4</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BL3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="BO3" s="1" t="s">
@@ -1808,219 +1874,243 @@
         <v>135</v>
       </c>
       <c r="E4" s="1">
-        <f t="shared" ref="E4:J4" si="58">SUM(E140:E151)</f>
+        <f t="shared" ref="E4:J4" si="65">SUM(E140:E151)</f>
         <v>274</v>
       </c>
       <c r="F4" s="1">
-        <f t="shared" si="58"/>
+        <f t="shared" si="65"/>
         <v>82</v>
       </c>
       <c r="G4" s="1">
-        <f t="shared" si="58"/>
+        <f t="shared" si="65"/>
         <v>981</v>
       </c>
       <c r="H4" s="1">
-        <f t="shared" si="58"/>
+        <f t="shared" si="65"/>
         <v>135</v>
       </c>
       <c r="I4" s="1">
-        <f t="shared" si="58"/>
+        <f t="shared" si="65"/>
         <v>498</v>
       </c>
       <c r="J4" s="1">
-        <f t="shared" si="58"/>
+        <f t="shared" si="65"/>
         <v>64</v>
       </c>
       <c r="K4" s="1">
-        <f t="shared" ref="K4:AZ4" si="59">SUM(K140:K151)</f>
+        <f t="shared" ref="K4:AZ4" si="66">SUM(K140:K151)</f>
         <v>44</v>
       </c>
       <c r="L4" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="66"/>
         <v>8</v>
       </c>
       <c r="M4" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="66"/>
         <v>243</v>
       </c>
       <c r="N4" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="66"/>
         <v>41</v>
       </c>
       <c r="O4" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="66"/>
         <v>12</v>
       </c>
       <c r="P4" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="66"/>
         <v>2</v>
       </c>
       <c r="Q4" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="R4" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="S4" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="T4" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="U4" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="66"/>
         <v>64</v>
       </c>
       <c r="V4" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="66"/>
         <v>11</v>
       </c>
       <c r="W4" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="66"/>
         <v>55</v>
       </c>
       <c r="X4" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="66"/>
         <v>9</v>
       </c>
       <c r="Y4" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="66"/>
         <v>154</v>
       </c>
       <c r="Z4" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="66"/>
         <v>32</v>
       </c>
       <c r="AA4" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="66"/>
         <v>89</v>
       </c>
       <c r="AB4" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="66"/>
         <v>21</v>
       </c>
       <c r="AC4" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="AD4" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="AE4" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="AF4" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="AG4" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="AH4" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="AI4" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="AJ4" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="AK4" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="AL4" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="AM4" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="AN4" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="AO4" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="AP4" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="AQ4" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="AR4" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="AS4" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="AT4" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="AU4" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="AV4" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="AW4" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="AX4" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="AY4" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="AZ4" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="BA4" s="1">
-        <f t="shared" ref="BA4:BD4" si="60">SUM(BA140:BA151)</f>
+        <f t="shared" ref="BA4:BD4" si="67">SUM(BA140:BA151)</f>
         <v>0</v>
       </c>
       <c r="BB4" s="1">
-        <f t="shared" si="60"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="BC4" s="1">
-        <f t="shared" si="60"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="BD4" s="1">
-        <f t="shared" si="60"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="BE4" s="1">
-        <f t="shared" ref="BE4:BF4" si="61">SUM(BE140:BE151)</f>
+        <f t="shared" ref="BE4:BF4" si="68">SUM(BE140:BE151)</f>
         <v>0</v>
       </c>
       <c r="BF4" s="1">
-        <f t="shared" si="61"/>
+        <f t="shared" si="68"/>
+        <v>0</v>
+      </c>
+      <c r="BG4" s="1">
+        <f t="shared" ref="BG4:BL4" si="69">SUM(BG140:BG151)</f>
+        <v>0</v>
+      </c>
+      <c r="BH4" s="1">
+        <f t="shared" si="69"/>
+        <v>0</v>
+      </c>
+      <c r="BI4" s="1">
+        <f t="shared" si="69"/>
+        <v>0</v>
+      </c>
+      <c r="BJ4" s="1">
+        <f t="shared" si="69"/>
+        <v>0</v>
+      </c>
+      <c r="BK4" s="1">
+        <f t="shared" si="69"/>
+        <v>0</v>
+      </c>
+      <c r="BL4" s="1">
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="BP4" s="1" t="b">
@@ -2047,192 +2137,213 @@
         <v>2</v>
       </c>
       <c r="E5" s="1">
-        <f t="shared" ref="E5" si="62">E6/F6</f>
+        <f t="shared" ref="E5" si="70">E6/F6</f>
         <v>6.131455399061033</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>2</v>
       </c>
       <c r="G5" s="1">
-        <f t="shared" ref="G5" si="63">G6/H6</f>
+        <f t="shared" ref="G5" si="71">G6/H6</f>
         <v>6.8512820512820509</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>2</v>
       </c>
       <c r="I5" s="1">
-        <f t="shared" ref="I5" si="64">I6/J6</f>
+        <f t="shared" ref="I5" si="72">I6/J6</f>
         <v>6.5287356321839081</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>2</v>
       </c>
       <c r="K5" s="1">
-        <f t="shared" ref="K5" si="65">K6/L6</f>
+        <f t="shared" ref="K5" si="73">K6/L6</f>
         <v>6.6756756756756754</v>
       </c>
       <c r="L5" s="1" t="s">
         <v>2</v>
       </c>
       <c r="M5" s="1">
-        <f t="shared" ref="M5" si="66">M6/N6</f>
+        <f t="shared" ref="M5" si="74">M6/N6</f>
         <v>3.8979591836734695</v>
       </c>
       <c r="N5" s="1" t="s">
         <v>2</v>
       </c>
       <c r="O5" s="1">
-        <f t="shared" ref="O5" si="67">O6/P6</f>
+        <f t="shared" ref="O5" si="75">O6/P6</f>
         <v>5.85</v>
       </c>
       <c r="P5" s="1" t="s">
         <v>2</v>
       </c>
       <c r="Q5" s="1">
-        <f t="shared" ref="Q5" si="68">Q6/R6</f>
+        <f t="shared" ref="Q5" si="76">Q6/R6</f>
         <v>5.8133333333333335</v>
       </c>
       <c r="R5" s="1" t="s">
         <v>2</v>
       </c>
       <c r="S5" s="1">
-        <f t="shared" ref="S5" si="69">S6/T6</f>
+        <f t="shared" ref="S5" si="77">S6/T6</f>
         <v>7.1037735849056602</v>
       </c>
       <c r="T5" s="1" t="s">
         <v>2</v>
       </c>
       <c r="U5" s="1">
-        <f t="shared" ref="U5" si="70">U6/V6</f>
+        <f t="shared" ref="U5" si="78">U6/V6</f>
         <v>2.096774193548387</v>
       </c>
       <c r="V5" s="1" t="s">
         <v>2</v>
       </c>
       <c r="W5" s="1">
-        <f t="shared" ref="W5" si="71">W6/X6</f>
+        <f t="shared" ref="W5" si="79">W6/X6</f>
         <v>1.8214285714285714</v>
       </c>
       <c r="X5" s="1" t="s">
         <v>2</v>
       </c>
       <c r="Y5" s="1" t="e">
-        <f t="shared" ref="Y5" si="72">Y6/Z6</f>
+        <f t="shared" ref="Y5" si="80">Y6/Z6</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Z5" s="1" t="s">
         <v>2</v>
       </c>
       <c r="AA5" s="1">
-        <f t="shared" ref="AA5" si="73">AA6/AB6</f>
+        <f t="shared" ref="AA5" si="81">AA6/AB6</f>
         <v>2.0249999999999999</v>
       </c>
       <c r="AB5" s="1" t="s">
         <v>2</v>
       </c>
       <c r="AC5" s="1">
-        <f t="shared" ref="AC5" si="74">AC6/AD6</f>
+        <f t="shared" ref="AC5" si="82">AC6/AD6</f>
         <v>1.6</v>
       </c>
       <c r="AD5" s="1" t="s">
         <v>2</v>
       </c>
       <c r="AE5" s="1">
-        <f t="shared" ref="AE5" si="75">AE6/AF6</f>
+        <f t="shared" ref="AE5" si="83">AE6/AF6</f>
         <v>9</v>
       </c>
       <c r="AF5" s="1" t="s">
         <v>2</v>
       </c>
       <c r="AG5" s="1">
-        <f t="shared" ref="AG5" si="76">AG6/AH6</f>
+        <f t="shared" ref="AG5" si="84">AG6/AH6</f>
         <v>6.068965517241379</v>
       </c>
       <c r="AH5" s="1" t="s">
         <v>2</v>
       </c>
       <c r="AI5" s="1" t="e">
-        <f t="shared" ref="AI5" si="77">AI6/AJ6</f>
+        <f t="shared" ref="AI5" si="85">AI6/AJ6</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AJ5" s="1" t="s">
         <v>2</v>
       </c>
       <c r="AK5" s="1">
-        <f t="shared" ref="AK5" si="78">AK6/AL6</f>
+        <f t="shared" ref="AK5" si="86">AK6/AL6</f>
         <v>7.117647058823529</v>
       </c>
       <c r="AL5" s="1" t="s">
         <v>2</v>
       </c>
       <c r="AM5" s="1" t="e">
-        <f t="shared" ref="AM5" si="79">AM6/AN6</f>
+        <f t="shared" ref="AM5" si="87">AM6/AN6</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AN5" s="1" t="s">
         <v>2</v>
       </c>
       <c r="AO5" s="1" t="e">
-        <f t="shared" ref="AO5" si="80">AO6/AP6</f>
+        <f t="shared" ref="AO5" si="88">AO6/AP6</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AP5" s="1" t="s">
         <v>2</v>
       </c>
       <c r="AQ5" s="1">
-        <f t="shared" ref="AQ5" si="81">AQ6/AR6</f>
+        <f t="shared" ref="AQ5" si="89">AQ6/AR6</f>
         <v>3.75</v>
       </c>
       <c r="AR5" s="1" t="s">
         <v>2</v>
       </c>
       <c r="AS5" s="1" t="e">
-        <f t="shared" ref="AS5" si="82">AS6/AT6</f>
+        <f t="shared" ref="AS5" si="90">AS6/AT6</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AT5" s="1" t="s">
         <v>2</v>
       </c>
       <c r="AU5" s="1" t="e">
-        <f t="shared" ref="AU5" si="83">AU6/AV6</f>
+        <f t="shared" ref="AU5" si="91">AU6/AV6</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AV5" s="1" t="s">
         <v>2</v>
       </c>
       <c r="AW5" s="1" t="e">
-        <f t="shared" ref="AW5" si="84">AW6/AX6</f>
+        <f t="shared" ref="AW5" si="92">AW6/AX6</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AX5" s="1" t="s">
         <v>2</v>
       </c>
       <c r="AY5" s="1">
-        <f t="shared" ref="AY5" si="85">AY6/AZ6</f>
+        <f t="shared" ref="AY5" si="93">AY6/AZ6</f>
         <v>2.75</v>
       </c>
       <c r="AZ5" s="1" t="s">
         <v>2</v>
       </c>
       <c r="BA5" s="1" t="e">
-        <f t="shared" ref="BA5" si="86">BA6/BB6</f>
+        <f t="shared" ref="BA5" si="94">BA6/BB6</f>
         <v>#DIV/0!</v>
       </c>
       <c r="BB5" s="1" t="s">
         <v>2</v>
       </c>
       <c r="BC5" s="1" t="e">
-        <f t="shared" ref="BC5" si="87">BC6/BD6</f>
+        <f t="shared" ref="BC5" si="95">BC6/BD6</f>
         <v>#DIV/0!</v>
       </c>
       <c r="BD5" s="1" t="s">
         <v>2</v>
       </c>
       <c r="BE5" s="1" t="e">
-        <f t="shared" ref="BE5" si="88">BE6/BF6</f>
+        <f t="shared" ref="BE5" si="96">BE6/BF6</f>
         <v>#DIV/0!</v>
       </c>
       <c r="BF5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="BG5" s="1" t="e">
+        <f t="shared" ref="BG5" si="97">BG6/BH6</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BH5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="BI5" s="1" t="e">
+        <f t="shared" ref="BI5" si="98">BI6/BJ6</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BJ5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="BK5" s="1" t="e">
+        <f t="shared" ref="BK5" si="99">BK6/BL6</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BL5" s="1" t="s">
         <v>2</v>
       </c>
       <c r="BQ5" s="1" t="e">
@@ -2253,219 +2364,243 @@
         <v>370</v>
       </c>
       <c r="E6" s="1">
-        <f t="shared" ref="E6:J6" si="89">SUM(E96:E138)</f>
+        <f t="shared" ref="E6:J6" si="100">SUM(E96:E138)</f>
         <v>1306</v>
       </c>
       <c r="F6" s="1">
-        <f t="shared" si="89"/>
+        <f t="shared" si="100"/>
         <v>213</v>
       </c>
       <c r="G6" s="1">
-        <f t="shared" si="89"/>
+        <f t="shared" si="100"/>
         <v>2672</v>
       </c>
       <c r="H6" s="1">
-        <f t="shared" si="89"/>
+        <f t="shared" si="100"/>
         <v>390</v>
       </c>
       <c r="I6" s="1">
-        <f t="shared" si="89"/>
+        <f t="shared" si="100"/>
         <v>568</v>
       </c>
       <c r="J6" s="1">
-        <f t="shared" si="89"/>
+        <f t="shared" si="100"/>
         <v>87</v>
       </c>
       <c r="K6" s="1">
-        <f t="shared" ref="K6:AZ6" si="90">SUM(K96:K138)</f>
+        <f t="shared" ref="K6:AZ6" si="101">SUM(K96:K138)</f>
         <v>494</v>
       </c>
       <c r="L6" s="1">
-        <f t="shared" si="90"/>
+        <f t="shared" si="101"/>
         <v>74</v>
       </c>
       <c r="M6" s="1">
-        <f t="shared" si="90"/>
+        <f t="shared" si="101"/>
         <v>573</v>
       </c>
       <c r="N6" s="1">
-        <f t="shared" si="90"/>
+        <f t="shared" si="101"/>
         <v>147</v>
       </c>
       <c r="O6" s="1">
-        <f t="shared" si="90"/>
+        <f t="shared" si="101"/>
         <v>117</v>
       </c>
       <c r="P6" s="1">
-        <f t="shared" si="90"/>
+        <f t="shared" si="101"/>
         <v>20</v>
       </c>
       <c r="Q6" s="1">
-        <f t="shared" si="90"/>
+        <f t="shared" si="101"/>
         <v>436</v>
       </c>
       <c r="R6" s="1">
-        <f t="shared" si="90"/>
+        <f t="shared" si="101"/>
         <v>75</v>
       </c>
       <c r="S6" s="1">
-        <f t="shared" si="90"/>
+        <f t="shared" si="101"/>
         <v>753</v>
       </c>
       <c r="T6" s="1">
-        <f t="shared" si="90"/>
+        <f t="shared" si="101"/>
         <v>106</v>
       </c>
       <c r="U6" s="1">
-        <f t="shared" si="90"/>
+        <f t="shared" si="101"/>
         <v>65</v>
       </c>
       <c r="V6" s="1">
-        <f t="shared" si="90"/>
+        <f t="shared" si="101"/>
         <v>31</v>
       </c>
       <c r="W6" s="1">
-        <f t="shared" si="90"/>
+        <f t="shared" si="101"/>
         <v>51</v>
       </c>
       <c r="X6" s="1">
-        <f t="shared" si="90"/>
+        <f t="shared" si="101"/>
         <v>28</v>
       </c>
       <c r="Y6" s="1">
-        <f t="shared" si="90"/>
+        <f t="shared" si="101"/>
         <v>0</v>
       </c>
       <c r="Z6" s="1">
-        <f t="shared" si="90"/>
+        <f t="shared" si="101"/>
         <v>0</v>
       </c>
       <c r="AA6" s="1">
-        <f t="shared" si="90"/>
+        <f t="shared" si="101"/>
         <v>81</v>
       </c>
       <c r="AB6" s="1">
-        <f t="shared" si="90"/>
+        <f t="shared" si="101"/>
         <v>40</v>
       </c>
       <c r="AC6" s="1">
-        <f t="shared" si="90"/>
+        <f t="shared" si="101"/>
         <v>16</v>
       </c>
       <c r="AD6" s="1">
-        <f t="shared" si="90"/>
+        <f t="shared" si="101"/>
         <v>10</v>
       </c>
       <c r="AE6" s="1">
-        <f t="shared" si="90"/>
+        <f t="shared" si="101"/>
         <v>27</v>
       </c>
       <c r="AF6" s="1">
-        <f t="shared" si="90"/>
+        <f t="shared" si="101"/>
         <v>3</v>
       </c>
       <c r="AG6" s="1">
-        <f t="shared" si="90"/>
+        <f t="shared" si="101"/>
         <v>176</v>
       </c>
       <c r="AH6" s="1">
-        <f t="shared" si="90"/>
+        <f t="shared" si="101"/>
         <v>29</v>
       </c>
       <c r="AI6" s="1">
-        <f t="shared" si="90"/>
+        <f t="shared" si="101"/>
         <v>0</v>
       </c>
       <c r="AJ6" s="1">
-        <f t="shared" si="90"/>
+        <f t="shared" si="101"/>
         <v>0</v>
       </c>
       <c r="AK6" s="1">
-        <f t="shared" si="90"/>
+        <f t="shared" si="101"/>
         <v>121</v>
       </c>
       <c r="AL6" s="1">
-        <f t="shared" si="90"/>
+        <f t="shared" si="101"/>
         <v>17</v>
       </c>
       <c r="AM6" s="1">
-        <f t="shared" si="90"/>
+        <f t="shared" si="101"/>
         <v>0</v>
       </c>
       <c r="AN6" s="1">
-        <f t="shared" si="90"/>
+        <f t="shared" si="101"/>
         <v>0</v>
       </c>
       <c r="AO6" s="1">
-        <f t="shared" si="90"/>
+        <f t="shared" si="101"/>
         <v>0</v>
       </c>
       <c r="AP6" s="1">
-        <f t="shared" si="90"/>
+        <f t="shared" si="101"/>
         <v>0</v>
       </c>
       <c r="AQ6" s="1">
-        <f t="shared" si="90"/>
+        <f t="shared" si="101"/>
         <v>60</v>
       </c>
       <c r="AR6" s="1">
-        <f t="shared" si="90"/>
+        <f t="shared" si="101"/>
         <v>16</v>
       </c>
       <c r="AS6" s="1">
-        <f t="shared" si="90"/>
+        <f t="shared" si="101"/>
         <v>0</v>
       </c>
       <c r="AT6" s="1">
-        <f t="shared" si="90"/>
+        <f t="shared" si="101"/>
         <v>0</v>
       </c>
       <c r="AU6" s="1">
-        <f t="shared" si="90"/>
+        <f t="shared" si="101"/>
         <v>0</v>
       </c>
       <c r="AV6" s="1">
-        <f t="shared" si="90"/>
+        <f t="shared" si="101"/>
         <v>0</v>
       </c>
       <c r="AW6" s="1">
-        <f t="shared" si="90"/>
+        <f t="shared" si="101"/>
         <v>0</v>
       </c>
       <c r="AX6" s="1">
-        <f t="shared" si="90"/>
+        <f t="shared" si="101"/>
         <v>0</v>
       </c>
       <c r="AY6" s="1">
-        <f t="shared" si="90"/>
+        <f t="shared" si="101"/>
         <v>22</v>
       </c>
       <c r="AZ6" s="1">
-        <f t="shared" si="90"/>
+        <f t="shared" si="101"/>
         <v>8</v>
       </c>
       <c r="BA6" s="1">
-        <f t="shared" ref="BA6:BD6" si="91">SUM(BA96:BA138)</f>
+        <f t="shared" ref="BA6:BD6" si="102">SUM(BA96:BA138)</f>
         <v>0</v>
       </c>
       <c r="BB6" s="1">
-        <f t="shared" si="91"/>
+        <f t="shared" si="102"/>
         <v>0</v>
       </c>
       <c r="BC6" s="1">
-        <f t="shared" si="91"/>
+        <f t="shared" si="102"/>
         <v>0</v>
       </c>
       <c r="BD6" s="1">
-        <f t="shared" si="91"/>
+        <f t="shared" si="102"/>
         <v>0</v>
       </c>
       <c r="BE6" s="1">
-        <f t="shared" ref="BE6:BF6" si="92">SUM(BE96:BE138)</f>
+        <f t="shared" ref="BE6:BF6" si="103">SUM(BE96:BE138)</f>
         <v>0</v>
       </c>
       <c r="BF6" s="1">
-        <f t="shared" si="92"/>
+        <f t="shared" si="103"/>
+        <v>0</v>
+      </c>
+      <c r="BG6" s="1">
+        <f t="shared" ref="BG6:BL6" si="104">SUM(BG96:BG138)</f>
+        <v>0</v>
+      </c>
+      <c r="BH6" s="1">
+        <f t="shared" si="104"/>
+        <v>0</v>
+      </c>
+      <c r="BI6" s="1">
+        <f t="shared" si="104"/>
+        <v>0</v>
+      </c>
+      <c r="BJ6" s="1">
+        <f t="shared" si="104"/>
+        <v>0</v>
+      </c>
+      <c r="BK6" s="1">
+        <f t="shared" si="104"/>
+        <v>0</v>
+      </c>
+      <c r="BL6" s="1">
+        <f t="shared" si="104"/>
         <v>0</v>
       </c>
     </row>
@@ -2484,192 +2619,213 @@
         <v>2</v>
       </c>
       <c r="E7" s="15">
-        <f t="shared" ref="E7" si="93">E8/F8</f>
+        <f t="shared" ref="E7" si="105">E8/F8</f>
         <v>6.7380952380952381</v>
       </c>
       <c r="F7" s="15" t="s">
         <v>2</v>
       </c>
       <c r="G7" s="15">
-        <f t="shared" ref="G7" si="94">G8/H8</f>
+        <f t="shared" ref="G7" si="106">G8/H8</f>
         <v>7.4165085388994312</v>
       </c>
       <c r="H7" s="15" t="s">
         <v>2</v>
       </c>
       <c r="I7" s="15">
-        <f t="shared" ref="I7" si="95">I8/J8</f>
+        <f t="shared" ref="I7" si="107">I8/J8</f>
         <v>3.0166666666666666</v>
       </c>
       <c r="J7" s="15" t="s">
         <v>2</v>
       </c>
       <c r="K7" s="15">
-        <f t="shared" ref="K7" si="96">K8/L8</f>
+        <f t="shared" ref="K7" si="108">K8/L8</f>
         <v>3.8518518518518516</v>
       </c>
       <c r="L7" s="15" t="s">
         <v>2</v>
       </c>
       <c r="M7" s="15">
-        <f t="shared" ref="M7" si="97">M8/N8</f>
+        <f t="shared" ref="M7" si="109">M8/N8</f>
         <v>6.004319654427646</v>
       </c>
       <c r="N7" s="15" t="s">
         <v>2</v>
       </c>
       <c r="O7" s="15">
-        <f t="shared" ref="O7" si="98">O8/P8</f>
+        <f t="shared" ref="O7" si="110">O8/P8</f>
         <v>8.1063829787234045</v>
       </c>
       <c r="P7" s="15" t="s">
         <v>2</v>
       </c>
       <c r="Q7" s="15">
-        <f t="shared" ref="Q7" si="99">Q8/R8</f>
+        <f t="shared" ref="Q7" si="111">Q8/R8</f>
         <v>6.192708333333333</v>
       </c>
       <c r="R7" s="15" t="s">
         <v>2</v>
       </c>
       <c r="S7" s="15">
-        <f t="shared" ref="S7" si="100">S8/T8</f>
+        <f t="shared" ref="S7" si="112">S8/T8</f>
         <v>5.117647058823529</v>
       </c>
       <c r="T7" s="15" t="s">
         <v>2</v>
       </c>
       <c r="U7" s="15">
-        <f t="shared" ref="U7" si="101">U8/V8</f>
+        <f t="shared" ref="U7" si="113">U8/V8</f>
         <v>2.9926470588235294</v>
       </c>
       <c r="V7" s="15" t="s">
         <v>2</v>
       </c>
       <c r="W7" s="15">
-        <f t="shared" ref="W7" si="102">W8/X8</f>
+        <f t="shared" ref="W7" si="114">W8/X8</f>
         <v>1.1000000000000001</v>
       </c>
       <c r="X7" s="15" t="s">
         <v>2</v>
       </c>
       <c r="Y7" s="15" t="e">
-        <f t="shared" ref="Y7" si="103">Y8/Z8</f>
+        <f t="shared" ref="Y7" si="115">Y8/Z8</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Z7" s="15" t="s">
         <v>2</v>
       </c>
       <c r="AA7" s="15">
-        <f t="shared" ref="AA7" si="104">AA8/AB8</f>
+        <f t="shared" ref="AA7" si="116">AA8/AB8</f>
         <v>4.904907975460123</v>
       </c>
       <c r="AB7" s="15" t="s">
         <v>2</v>
       </c>
       <c r="AC7" s="15">
-        <f t="shared" ref="AC7" si="105">AC8/AD8</f>
+        <f t="shared" ref="AC7" si="117">AC8/AD8</f>
         <v>5.3103448275862073</v>
       </c>
       <c r="AD7" s="15" t="s">
         <v>2</v>
       </c>
       <c r="AE7" s="15">
-        <f t="shared" ref="AE7" si="106">AE8/AF8</f>
+        <f t="shared" ref="AE7" si="118">AE8/AF8</f>
         <v>0</v>
       </c>
       <c r="AF7" s="15" t="s">
         <v>2</v>
       </c>
       <c r="AG7" s="15" t="e">
-        <f t="shared" ref="AG7" si="107">AG8/AH8</f>
+        <f t="shared" ref="AG7" si="119">AG8/AH8</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AH7" s="15" t="s">
         <v>2</v>
       </c>
       <c r="AI7" s="15">
-        <f t="shared" ref="AI7" si="108">AI8/AJ8</f>
+        <f t="shared" ref="AI7" si="120">AI8/AJ8</f>
         <v>2.9607843137254903</v>
       </c>
       <c r="AJ7" s="15" t="s">
         <v>2</v>
       </c>
       <c r="AK7" s="15" t="e">
-        <f t="shared" ref="AK7" si="109">AK8/AL8</f>
+        <f t="shared" ref="AK7" si="121">AK8/AL8</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AL7" s="15" t="s">
         <v>2</v>
       </c>
       <c r="AM7" s="15">
-        <f t="shared" ref="AM7" si="110">AM8/AN8</f>
+        <f t="shared" ref="AM7" si="122">AM8/AN8</f>
         <v>4.5</v>
       </c>
       <c r="AN7" s="15" t="s">
         <v>2</v>
       </c>
       <c r="AO7" s="15">
-        <f t="shared" ref="AO7" si="111">AO8/AP8</f>
+        <f t="shared" ref="AO7" si="123">AO8/AP8</f>
         <v>-8.3333333333333329E-2</v>
       </c>
       <c r="AP7" s="15" t="s">
         <v>2</v>
       </c>
       <c r="AQ7" s="15">
-        <f t="shared" ref="AQ7" si="112">AQ8/AR8</f>
+        <f t="shared" ref="AQ7" si="124">AQ8/AR8</f>
         <v>4.1688311688311686</v>
       </c>
       <c r="AR7" s="15" t="s">
         <v>2</v>
       </c>
       <c r="AS7" s="15">
-        <f t="shared" ref="AS7" si="113">AS8/AT8</f>
+        <f t="shared" ref="AS7" si="125">AS8/AT8</f>
         <v>0.72727272727272729</v>
       </c>
       <c r="AT7" s="15" t="s">
         <v>2</v>
       </c>
       <c r="AU7" s="15">
-        <f t="shared" ref="AU7" si="114">AU8/AV8</f>
+        <f t="shared" ref="AU7" si="126">AU8/AV8</f>
         <v>8.5</v>
       </c>
       <c r="AV7" s="15" t="s">
         <v>2</v>
       </c>
       <c r="AW7" s="15">
-        <f t="shared" ref="AW7" si="115">AW8/AX8</f>
+        <f t="shared" ref="AW7" si="127">AW8/AX8</f>
         <v>2.8</v>
       </c>
       <c r="AX7" s="15" t="s">
         <v>2</v>
       </c>
       <c r="AY7" s="15">
-        <f t="shared" ref="AY7" si="116">AY8/AZ8</f>
+        <f t="shared" ref="AY7" si="128">AY8/AZ8</f>
         <v>4.2</v>
       </c>
       <c r="AZ7" s="15" t="s">
         <v>2</v>
       </c>
       <c r="BA7" s="15">
-        <f t="shared" ref="BA7" si="117">BA8/BB8</f>
+        <f t="shared" ref="BA7" si="129">BA8/BB8</f>
         <v>17</v>
       </c>
       <c r="BB7" s="15" t="s">
         <v>2</v>
       </c>
       <c r="BC7" s="15">
-        <f t="shared" ref="BC7" si="118">BC8/BD8</f>
+        <f t="shared" ref="BC7" si="130">BC8/BD8</f>
         <v>4.4814814814814818</v>
       </c>
       <c r="BD7" s="15" t="s">
         <v>2</v>
       </c>
       <c r="BE7" s="15">
-        <f t="shared" ref="BE7" si="119">BE8/BF8</f>
+        <f t="shared" ref="BE7" si="131">BE8/BF8</f>
         <v>5.1547619047619051</v>
       </c>
       <c r="BF7" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="BG7" s="15">
+        <f t="shared" ref="BG7" si="132">BG8/BH8</f>
+        <v>8.625</v>
+      </c>
+      <c r="BH7" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="BI7" s="15" t="e">
+        <f t="shared" ref="BI7" si="133">BI8/BJ8</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BJ7" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="BK7" s="15" t="e">
+        <f t="shared" ref="BK7" si="134">BK8/BL8</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BL7" s="15" t="s">
         <v>2</v>
       </c>
     </row>
@@ -2687,220 +2843,244 @@
         <v>324</v>
       </c>
       <c r="E8" s="15">
-        <f t="shared" ref="E8:J8" si="120">SUM(E10:E94)</f>
+        <f t="shared" ref="E8:J8" si="135">SUM(E10:E94)</f>
         <v>849</v>
       </c>
       <c r="F8" s="15">
-        <f t="shared" si="120"/>
+        <f t="shared" si="135"/>
         <v>126</v>
       </c>
       <c r="G8" s="15">
-        <f t="shared" si="120"/>
+        <f t="shared" si="135"/>
         <v>3908.5</v>
       </c>
       <c r="H8" s="15">
-        <f t="shared" si="120"/>
+        <f t="shared" si="135"/>
         <v>527</v>
       </c>
       <c r="I8" s="15">
-        <f t="shared" si="120"/>
+        <f t="shared" si="135"/>
         <v>181</v>
       </c>
       <c r="J8" s="15">
-        <f t="shared" si="120"/>
+        <f t="shared" si="135"/>
         <v>60</v>
       </c>
       <c r="K8" s="15">
-        <f t="shared" ref="K8:AZ8" si="121">SUM(K10:K94)</f>
+        <f t="shared" ref="K8:AZ8" si="136">SUM(K10:K94)</f>
         <v>104</v>
       </c>
       <c r="L8" s="15">
-        <f t="shared" si="121"/>
+        <f t="shared" si="136"/>
         <v>27</v>
       </c>
       <c r="M8" s="15">
-        <f t="shared" si="121"/>
+        <f t="shared" si="136"/>
         <v>2780</v>
       </c>
       <c r="N8" s="15">
-        <f t="shared" si="121"/>
+        <f t="shared" si="136"/>
         <v>463</v>
       </c>
       <c r="O8" s="15">
-        <f t="shared" si="121"/>
+        <f t="shared" si="136"/>
         <v>381</v>
       </c>
       <c r="P8" s="15">
-        <f t="shared" si="121"/>
+        <f t="shared" si="136"/>
         <v>47</v>
       </c>
       <c r="Q8" s="15">
-        <f t="shared" si="121"/>
+        <f t="shared" si="136"/>
         <v>1189</v>
       </c>
       <c r="R8" s="15">
-        <f t="shared" si="121"/>
+        <f t="shared" si="136"/>
         <v>192</v>
       </c>
       <c r="S8" s="15">
-        <f t="shared" si="121"/>
+        <f t="shared" si="136"/>
         <v>609</v>
       </c>
       <c r="T8" s="15">
-        <f t="shared" si="121"/>
+        <f t="shared" si="136"/>
         <v>119</v>
       </c>
       <c r="U8" s="15">
-        <f t="shared" si="121"/>
+        <f t="shared" si="136"/>
         <v>407</v>
       </c>
       <c r="V8" s="15">
-        <f t="shared" si="121"/>
+        <f t="shared" si="136"/>
         <v>136</v>
       </c>
       <c r="W8" s="15">
-        <f t="shared" si="121"/>
+        <f t="shared" si="136"/>
         <v>33</v>
       </c>
       <c r="X8" s="15">
-        <f t="shared" si="121"/>
+        <f t="shared" si="136"/>
         <v>30</v>
       </c>
       <c r="Y8" s="15">
-        <f t="shared" si="121"/>
+        <f t="shared" si="136"/>
         <v>0</v>
       </c>
       <c r="Z8" s="15">
-        <f t="shared" si="121"/>
+        <f t="shared" si="136"/>
         <v>0</v>
       </c>
       <c r="AA8" s="15">
-        <f t="shared" si="121"/>
+        <f t="shared" si="136"/>
         <v>799.5</v>
       </c>
       <c r="AB8" s="15">
-        <f t="shared" si="121"/>
+        <f t="shared" si="136"/>
         <v>163</v>
       </c>
       <c r="AC8" s="15">
-        <f t="shared" si="121"/>
+        <f t="shared" si="136"/>
         <v>770</v>
       </c>
       <c r="AD8" s="15">
-        <f t="shared" si="121"/>
+        <f t="shared" si="136"/>
         <v>145</v>
       </c>
       <c r="AE8" s="15">
-        <f t="shared" si="121"/>
+        <f t="shared" si="136"/>
         <v>0</v>
       </c>
       <c r="AF8" s="15">
-        <f t="shared" si="121"/>
+        <f t="shared" si="136"/>
         <v>2</v>
       </c>
       <c r="AG8" s="15">
-        <f t="shared" si="121"/>
+        <f t="shared" si="136"/>
         <v>0</v>
       </c>
       <c r="AH8" s="15">
-        <f t="shared" si="121"/>
+        <f t="shared" si="136"/>
         <v>0</v>
       </c>
       <c r="AI8" s="15">
-        <f t="shared" si="121"/>
+        <f t="shared" si="136"/>
         <v>151</v>
       </c>
       <c r="AJ8" s="15">
-        <f t="shared" si="121"/>
+        <f t="shared" si="136"/>
         <v>51</v>
       </c>
       <c r="AK8" s="15">
-        <f t="shared" si="121"/>
+        <f t="shared" si="136"/>
         <v>0</v>
       </c>
       <c r="AL8" s="15">
-        <f t="shared" si="121"/>
+        <f t="shared" si="136"/>
         <v>0</v>
       </c>
       <c r="AM8" s="15">
-        <f t="shared" si="121"/>
+        <f t="shared" si="136"/>
         <v>387</v>
       </c>
       <c r="AN8" s="15">
-        <f t="shared" si="121"/>
+        <f t="shared" si="136"/>
         <v>86</v>
       </c>
       <c r="AO8" s="15">
-        <f t="shared" si="121"/>
+        <f t="shared" si="136"/>
         <v>-1</v>
       </c>
       <c r="AP8" s="15">
-        <f t="shared" si="121"/>
+        <f t="shared" si="136"/>
         <v>12</v>
       </c>
       <c r="AQ8" s="15">
-        <f t="shared" si="121"/>
+        <f t="shared" si="136"/>
         <v>321</v>
       </c>
       <c r="AR8" s="15">
-        <f t="shared" si="121"/>
+        <f t="shared" si="136"/>
         <v>77</v>
       </c>
       <c r="AS8" s="15">
-        <f t="shared" si="121"/>
+        <f t="shared" si="136"/>
         <v>8</v>
       </c>
       <c r="AT8" s="15">
-        <f t="shared" si="121"/>
+        <f t="shared" si="136"/>
         <v>11</v>
       </c>
       <c r="AU8" s="15">
-        <f t="shared" si="121"/>
+        <f t="shared" si="136"/>
         <v>34</v>
       </c>
       <c r="AV8" s="15">
-        <f t="shared" si="121"/>
+        <f t="shared" si="136"/>
         <v>4</v>
       </c>
       <c r="AW8" s="15">
-        <f t="shared" si="121"/>
+        <f t="shared" si="136"/>
         <v>14</v>
       </c>
       <c r="AX8" s="15">
-        <f t="shared" si="121"/>
+        <f t="shared" si="136"/>
         <v>5</v>
       </c>
       <c r="AY8" s="15">
-        <f t="shared" si="121"/>
+        <f t="shared" si="136"/>
         <v>21</v>
       </c>
       <c r="AZ8" s="15">
-        <f t="shared" si="121"/>
+        <f t="shared" si="136"/>
         <v>5</v>
       </c>
       <c r="BA8" s="15">
-        <f t="shared" ref="BA8:BD8" si="122">SUM(BA10:BA94)</f>
+        <f t="shared" ref="BA8:BD8" si="137">SUM(BA10:BA94)</f>
         <v>34</v>
       </c>
       <c r="BB8" s="15">
-        <f t="shared" si="122"/>
+        <f t="shared" si="137"/>
         <v>2</v>
       </c>
       <c r="BC8" s="15">
-        <f t="shared" si="122"/>
+        <f t="shared" si="137"/>
         <v>121</v>
       </c>
       <c r="BD8" s="15">
-        <f t="shared" si="122"/>
+        <f t="shared" si="137"/>
         <v>27</v>
       </c>
       <c r="BE8" s="15">
-        <f t="shared" ref="BE8:BF8" si="123">SUM(BE10:BE94)</f>
+        <f t="shared" ref="BE8:BF8" si="138">SUM(BE10:BE94)</f>
         <v>433</v>
       </c>
       <c r="BF8" s="15">
-        <f t="shared" si="123"/>
+        <f t="shared" si="138"/>
         <v>84</v>
+      </c>
+      <c r="BG8" s="15">
+        <f t="shared" ref="BG8:BL8" si="139">SUM(BG10:BG94)</f>
+        <v>69</v>
+      </c>
+      <c r="BH8" s="15">
+        <f t="shared" si="139"/>
+        <v>8</v>
+      </c>
+      <c r="BI8" s="15">
+        <f t="shared" si="139"/>
+        <v>0</v>
+      </c>
+      <c r="BJ8" s="15">
+        <f t="shared" si="139"/>
+        <v>0</v>
+      </c>
+      <c r="BK8" s="15">
+        <f t="shared" si="139"/>
+        <v>0</v>
+      </c>
+      <c r="BL8" s="15">
+        <f t="shared" si="139"/>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:69" x14ac:dyDescent="0.3">
@@ -11321,7 +11501,7 @@
     <mergeCell ref="AS9:AT9"/>
     <mergeCell ref="AU9:AV9"/>
   </mergeCells>
-  <conditionalFormatting sqref="C1 E1 G1 I1 K1 M1 O1 Q1 S1 U1 W1 Y1 AA1 AC1 AE1 AG1 AI1 AK1 AM1 AO1 AQ1 AS1 AU1 AW1 AY1 BA1 BC1 BE1 C9:AM9 AO9 AQ9 AS9 AU9 AW9 AY9 BA9 BC9 BE9">
+  <conditionalFormatting sqref="C1 E1 G1 I1 K1 M1 O1 Q1 S1 U1 W1 Y1 AA1 AC1 AE1 AG1 AI1 AK1 AM1 AO1 AQ1 AS1 AU1 AW1 AY1 BA1 BC1 BE1 C9:AM9 AO9 AQ9 AS9 AU9 AW9 AY9 BA9 BC9 BE9 BG1 BI1 BK1">
     <cfRule type="expression" dxfId="24" priority="41" stopIfTrue="1">
       <formula>NOT(OR("/"=C$1,AVERAGE($C$1:$AZ$1)&lt;C$1,SMALL($C$1:$AZ$1,1)=C$1,SMALL($C$1:$AZ$1,2)=C$1,SMALL($C$1:$AZ$1,3)=C$1,LARGE($C$1:$AZ$1,1)=C$1,LARGE($C$1:$AZ$1,2)=C$1,LARGE($C$1:$AZ$1,3)=C$1))</formula>
     </cfRule>
@@ -11340,77 +11520,79 @@
     <cfRule type="expression" dxfId="19" priority="84" stopIfTrue="1">
       <formula>SMALL($C$1:$AZ$1,1)=C$1</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="85" stopIfTrue="1">
-      <formula>LARGE($C$1:$AZ$1,3)=C$1</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="17" priority="86" stopIfTrue="1">
+    <cfRule type="expression" dxfId="18" priority="86" stopIfTrue="1">
       <formula>LARGE($C$1:$AZ$1,2)=C$1</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="87" stopIfTrue="1">
+    <cfRule type="expression" dxfId="17" priority="87" stopIfTrue="1">
       <formula>MAX($C$1:$AZ$1)=C$1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G10:G58 I10:I58 K10:K58 M10:M58 C10:C151 E10:E151 O10:O151 Q10:Q151 S10:S151 U10:U151 W10:W151 Y10:Y151 AA10:AA151 AC10:AC151 AE10:AE151 AG10:AG151 AI10:AI151 AK10:AK151 AM10:AM151 AO10:AO151 AQ10:AQ151 AS10:AS151 AU10:AU151 AW10:AW151 AY10:AY151 BA10:BA151 BC10:BC151 BE10:BE151 G60:G151 I60:I151 K60:K151 M60:M151">
-    <cfRule type="expression" dxfId="15" priority="26" stopIfTrue="1">
+    <cfRule type="expression" dxfId="16" priority="26" stopIfTrue="1">
       <formula>(C10/D10)&gt;12</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="28" stopIfTrue="1">
+    <cfRule type="expression" dxfId="15" priority="28" stopIfTrue="1">
       <formula>(C10/D10)&lt;-2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="30" stopIfTrue="1">
+    <cfRule type="expression" dxfId="14" priority="30" stopIfTrue="1">
       <formula>(C10/D10)&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="32" stopIfTrue="1">
+    <cfRule type="expression" dxfId="13" priority="32" stopIfTrue="1">
       <formula>(C10/D10)&gt;10</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H10:H58 J10:J58 L10:L58 N10:N58 D10:D151 F10:F151 P10:P151 R10:R151 T10:T151 V10:V151 X10:X151 Z10:Z151 AB10:AB151 AD10:AD151 AF10:AF151 AH10:AH151 AJ10:AJ151 AL10:AL151 AN10:AN151 AP10:AP151 AR10:AR151 AT10:AT151 AV10:AV151 AX10:AX151 AZ10:AZ151 BB10:BB151 BD10:BD151 BF10:BF151 H60:H151 J60:J151 L60:L151 N60:N151">
-    <cfRule type="expression" dxfId="11" priority="25" stopIfTrue="1">
+    <cfRule type="expression" dxfId="12" priority="25" stopIfTrue="1">
       <formula>(C10/D10)&gt;12</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="27" stopIfTrue="1">
+    <cfRule type="expression" dxfId="11" priority="27" stopIfTrue="1">
       <formula>(C10/D10)&lt;-2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="29" stopIfTrue="1">
+    <cfRule type="expression" dxfId="10" priority="29" stopIfTrue="1">
       <formula>(C10/D10)&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="31" stopIfTrue="1">
+    <cfRule type="expression" dxfId="9" priority="31" stopIfTrue="1">
       <formula>(C10/D10)&gt;10</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BU72:BU100">
-    <cfRule type="cellIs" dxfId="7" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="8" priority="3" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="4" operator="between">
+    <cfRule type="cellIs" dxfId="7" priority="4" operator="between">
       <formula>20</formula>
       <formula>50</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="5" operator="between">
+    <cfRule type="cellIs" dxfId="6" priority="5" operator="between">
       <formula>50</formula>
       <formula>100</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="6" operator="between">
+    <cfRule type="cellIs" dxfId="5" priority="6" operator="between">
       <formula>100</formula>
       <formula>250</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="7" operator="between">
+    <cfRule type="cellIs" dxfId="4" priority="7" operator="between">
       <formula>250</formula>
       <formula>500</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="8" operator="between">
+    <cfRule type="cellIs" dxfId="3" priority="8" operator="between">
       <formula>500</formula>
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BZ72:BZ93">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="between">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="between">
       <formula>1</formula>
       <formula>10</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="between">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="between">
       <formula>10</formula>
       <formula>20</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C1 E1 G1 I1 K1 M1 O1 Q1 S1 U1 W1 Y1 AA1 AC1 AE1 AG1 AI1 AK1 AM1 AO1 AQ1 AS1 AU1 AW1 AY1 BA1 BC1 BE1 C9:AM9 AO9 AQ9 AS9 AU9 AW9 AY9 BA9 BC9 BE9 BG1 BI1 BK1 BG9 BI9 BK9">
+    <cfRule type="expression" dxfId="0" priority="85" stopIfTrue="1">
+      <formula>LARGE($C$1:$AZ$1,3)=C$1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.70000000000000007" right="0.70000000000000007" top="0.75" bottom="0.75" header="0.30000000000000004" footer="0.30000000000000004"/>
@@ -11803,16 +11985,16 @@
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21">
+      <c r="A21" s="25">
         <v>20</v>
       </c>
-      <c r="B21" t="str">
+      <c r="B21" s="25" t="str">
         <v>Loulou</v>
       </c>
-      <c r="C21" t="str">
+      <c r="C21" s="25" t="str">
         <v>2.075</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="25">
         <v>67</v>
       </c>
     </row>

--- a/classement_whist_2023_2025.xlsx
+++ b/classement_whist_2023_2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a20b8382962b136a/Bureau/loisir/whist/projet_application_streamlit/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="74" documentId="14_{D8C30FC8-DD4A-4CBA-A5BF-091BFC36F9C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A12E765D-502C-46EC-84AB-168FF519C6F5}"/>
+  <xr:revisionPtr revIDLastSave="101" documentId="14_{D8C30FC8-DD4A-4CBA-A5BF-091BFC36F9C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D3A69E8C-0E86-42AB-87D6-B9767DBC2D38}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="93">
   <si>
     <t>global</t>
   </si>
@@ -1196,28 +1196,28 @@
       </c>
       <c r="M1" s="1">
         <f t="shared" ref="M1" si="5">IF(N2&gt;19,M2/N2,"/")</f>
-        <v>5.3891402714932131</v>
+        <v>5.365925925925926</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="O1" s="1">
         <f t="shared" ref="O1" si="6">IF(P2&gt;19,O2/P2,"/")</f>
-        <v>7.2531645569620249</v>
+        <v>6.8620689655172411</v>
       </c>
       <c r="P1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="Q1" s="1">
         <f t="shared" ref="Q1" si="7">IF(R2&gt;19,Q2/R2,"/")</f>
-        <v>6.1811594202898554</v>
+        <v>6.2635135135135132</v>
       </c>
       <c r="R1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="S1" s="1">
         <f t="shared" ref="S1" si="8">IF(T2&gt;19,S2/T2,"/")</f>
-        <v>5.9367088607594933</v>
+        <v>5.9554655870445341</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>2</v>
@@ -1245,14 +1245,14 @@
       </c>
       <c r="AA1" s="1">
         <f t="shared" ref="AA1" si="12">IF(AB2&gt;19,AA2/AB2,"/")</f>
-        <v>4.328125</v>
+        <v>4.3098290598290596</v>
       </c>
       <c r="AB1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="AC1" s="1">
         <f>IF(AD2&gt;19,AC2/AD2,"/")</f>
-        <v>5.475903614457831</v>
+        <v>5.6988636363636367</v>
       </c>
       <c r="AD1" s="1" t="s">
         <v>2</v>
@@ -1423,35 +1423,35 @@
       </c>
       <c r="M2" s="1">
         <f t="shared" si="31"/>
-        <v>3573</v>
+        <v>3622</v>
       </c>
       <c r="N2" s="1">
         <f t="shared" si="31"/>
-        <v>663</v>
+        <v>675</v>
       </c>
       <c r="O2" s="1">
         <f t="shared" si="31"/>
-        <v>573</v>
+        <v>597</v>
       </c>
       <c r="P2" s="1">
         <f t="shared" si="31"/>
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="Q2" s="1">
         <f t="shared" si="31"/>
-        <v>1706</v>
+        <v>1854</v>
       </c>
       <c r="R2" s="1">
         <f t="shared" si="31"/>
-        <v>276</v>
+        <v>296</v>
       </c>
       <c r="S2" s="1">
         <f t="shared" si="31"/>
-        <v>1407</v>
+        <v>1471</v>
       </c>
       <c r="T2" s="1">
         <f t="shared" si="31"/>
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="U2" s="1">
         <f t="shared" si="31"/>
@@ -1479,19 +1479,19 @@
       </c>
       <c r="AA2" s="1">
         <f t="shared" si="31"/>
-        <v>969.5</v>
+        <v>1008.5</v>
       </c>
       <c r="AB2" s="1">
         <f t="shared" si="31"/>
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="AC2" s="1">
         <f t="shared" si="31"/>
-        <v>909</v>
+        <v>1003</v>
       </c>
       <c r="AD2" s="1">
         <f t="shared" si="31"/>
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="AE2" s="1">
         <f t="shared" si="31"/>
@@ -2648,28 +2648,28 @@
       </c>
       <c r="M7" s="15">
         <f t="shared" ref="M7" si="109">M8/N8</f>
-        <v>5.8042105263157895</v>
+        <v>5.7618069815195074</v>
       </c>
       <c r="N7" s="15" t="s">
         <v>2</v>
       </c>
       <c r="O7" s="15">
         <f t="shared" ref="O7" si="110">O8/P8</f>
-        <v>7.7894736842105265</v>
+        <v>7.2</v>
       </c>
       <c r="P7" s="15" t="s">
         <v>2</v>
       </c>
       <c r="Q7" s="15">
         <f t="shared" ref="Q7" si="111">Q8/R8</f>
-        <v>6.3184079601990053</v>
+        <v>6.4162895927601813</v>
       </c>
       <c r="R7" s="15" t="s">
         <v>2</v>
       </c>
       <c r="S7" s="15">
         <f t="shared" ref="S7" si="112">S8/T8</f>
-        <v>4.9923664122137401</v>
+        <v>5.0921985815602833</v>
       </c>
       <c r="T7" s="15" t="s">
         <v>2</v>
@@ -2697,14 +2697,14 @@
       </c>
       <c r="AA7" s="15">
         <f t="shared" ref="AA7" si="116">AA8/AB8</f>
-        <v>4.904907975460123</v>
+        <v>4.8468208092485545</v>
       </c>
       <c r="AB7" s="15" t="s">
         <v>2</v>
       </c>
       <c r="AC7" s="15">
         <f t="shared" ref="AC7" si="117">AC8/AD8</f>
-        <v>5.7243589743589745</v>
+        <v>5.9457831325301207</v>
       </c>
       <c r="AD7" s="15" t="s">
         <v>2</v>
@@ -2876,35 +2876,35 @@
       </c>
       <c r="M8" s="15">
         <f t="shared" si="136"/>
-        <v>2757</v>
+        <v>2806</v>
       </c>
       <c r="N8" s="15">
         <f t="shared" si="136"/>
-        <v>475</v>
+        <v>487</v>
       </c>
       <c r="O8" s="15">
         <f t="shared" si="136"/>
-        <v>444</v>
+        <v>468</v>
       </c>
       <c r="P8" s="15">
         <f t="shared" si="136"/>
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="Q8" s="15">
         <f t="shared" si="136"/>
-        <v>1270</v>
+        <v>1418</v>
       </c>
       <c r="R8" s="15">
         <f t="shared" si="136"/>
-        <v>201</v>
+        <v>221</v>
       </c>
       <c r="S8" s="15">
         <f t="shared" si="136"/>
-        <v>654</v>
+        <v>718</v>
       </c>
       <c r="T8" s="15">
         <f t="shared" si="136"/>
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="U8" s="15">
         <f t="shared" si="136"/>
@@ -2932,19 +2932,19 @@
       </c>
       <c r="AA8" s="15">
         <f t="shared" si="136"/>
-        <v>799.5</v>
+        <v>838.5</v>
       </c>
       <c r="AB8" s="15">
         <f t="shared" si="136"/>
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="AC8" s="15">
         <f t="shared" si="136"/>
-        <v>893</v>
+        <v>987</v>
       </c>
       <c r="AD8" s="15">
         <f t="shared" si="136"/>
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="AE8" s="15">
         <f t="shared" si="136"/>
@@ -3238,24 +3238,96 @@
       <c r="B15" s="1">
         <v>141</v>
       </c>
+      <c r="M15" s="1">
+        <v>11</v>
+      </c>
+      <c r="N15" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q15" s="1">
+        <v>0</v>
+      </c>
+      <c r="R15" s="1">
+        <v>2</v>
+      </c>
+      <c r="S15" s="1">
+        <v>11</v>
+      </c>
+      <c r="T15" s="1">
+        <v>2</v>
+      </c>
+      <c r="AC15" s="1">
+        <v>18</v>
+      </c>
+      <c r="AD15" s="1">
+        <v>2</v>
+      </c>
     </row>
     <row r="16" spans="1:69" x14ac:dyDescent="0.3">
       <c r="B16" s="1">
         <v>140</v>
       </c>
+      <c r="O16" s="1">
+        <v>24</v>
+      </c>
+      <c r="P16" s="1">
+        <v>8</v>
+      </c>
+      <c r="Q16" s="1">
+        <v>28</v>
+      </c>
+      <c r="R16" s="1">
+        <v>8</v>
+      </c>
+      <c r="S16" s="1">
+        <v>53</v>
+      </c>
+      <c r="T16" s="1">
+        <v>8</v>
+      </c>
+      <c r="AC16" s="1">
+        <v>76</v>
+      </c>
+      <c r="AD16" s="1">
+        <v>8</v>
+      </c>
     </row>
     <row r="17" spans="1:60" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="B17" s="1">
         <v>139</v>
       </c>
+      <c r="M17" s="1">
+        <v>38</v>
+      </c>
+      <c r="N17" s="1">
+        <v>10</v>
+      </c>
       <c r="O17" s="1">
         <v>63</v>
       </c>
       <c r="P17" s="1">
         <v>10</v>
       </c>
+      <c r="Q17" s="1">
+        <v>120</v>
+      </c>
+      <c r="R17" s="1">
+        <v>10</v>
+      </c>
+      <c r="AA17" s="1">
+        <v>39</v>
+      </c>
+      <c r="AB17" s="1">
+        <v>10</v>
+      </c>
     </row>
     <row r="18" spans="1:60" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="B18" s="1">
         <v>138</v>
       </c>
@@ -3285,6 +3357,9 @@
       </c>
     </row>
     <row r="19" spans="1:60" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="B19" s="1">
         <v>137</v>
       </c>
@@ -3314,6 +3389,9 @@
       </c>
     </row>
     <row r="20" spans="1:60" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="B20" s="1">
         <v>136</v>
       </c>
@@ -5470,13 +5548,13 @@
         <v>1</v>
       </c>
       <c r="BS78" s="1" t="str">
-        <v>Gauthier</v>
+        <v>Boris</v>
       </c>
       <c r="BT78" s="1" t="str">
-        <v>7.253</v>
+        <v>7.177</v>
       </c>
       <c r="BU78" s="1">
-        <v>79</v>
+        <v>1056</v>
       </c>
       <c r="BW78" s="1" cm="1">
         <f t="array" ref="BW78:BZ85">_xlfn.LET(
@@ -5510,10 +5588,10 @@
       </c>
       <c r="CB78" s="1" t="str" cm="1">
         <f t="array" ref="CB78:CC105">_xlfn.LET(  _xlpm.noms, TRANSPOSE(INDEX(C9:BF9,_xlfn.SEQUENCE(1,COLUMNS(C9:BF9)/2,1,2))),_xlpm.moy,  TRANSPOSE(INDEX(C1:BF1,,_xlfn.SEQUENCE(1,COLUMNS(C1:BF1)/2,1,2))),_xlfn.SORTBY(CHOOSE({1,2}, _xlpm.noms, _xlpm.moy), IF(ISNUMBER(_xlpm.moy), _xlpm.moy, -1E+99), -1))</f>
-        <v>Gauthier</v>
+        <v>Boris</v>
       </c>
       <c r="CC78" s="1">
-        <v>7.2531645569620249</v>
+        <v>7.1766098484848486</v>
       </c>
     </row>
     <row r="79" spans="1:81" x14ac:dyDescent="0.3">
@@ -5555,13 +5633,13 @@
         <v>2</v>
       </c>
       <c r="BS79" s="1" t="str">
-        <v>Boris</v>
+        <v>Gauthier</v>
       </c>
       <c r="BT79" s="1" t="str">
-        <v>7.177</v>
+        <v>6.862</v>
       </c>
       <c r="BU79" s="1">
-        <v>1056</v>
+        <v>87</v>
       </c>
       <c r="BW79" s="1">
         <v>2</v>
@@ -5576,10 +5654,10 @@
         <v>4</v>
       </c>
       <c r="CB79" s="1" t="str">
-        <v>Boris</v>
+        <v>Gauthier</v>
       </c>
       <c r="CC79" s="1">
-        <v>7.1766098484848486</v>
+        <v>6.8620689655172411</v>
       </c>
     </row>
     <row r="80" spans="1:81" x14ac:dyDescent="0.3">
@@ -5624,10 +5702,10 @@
         <v>Célian</v>
       </c>
       <c r="BT80" s="1" t="str">
-        <v>6.181</v>
+        <v>6.264</v>
       </c>
       <c r="BU80" s="1">
-        <v>276</v>
+        <v>296</v>
       </c>
       <c r="BW80" s="1">
         <v>3</v>
@@ -5645,7 +5723,7 @@
         <v>Célian</v>
       </c>
       <c r="CC80" s="1">
-        <v>6.1811594202898554</v>
+        <v>6.2635135135135132</v>
       </c>
     </row>
     <row r="81" spans="1:81" x14ac:dyDescent="0.3">
@@ -5752,10 +5830,10 @@
         <v>Tom</v>
       </c>
       <c r="BT82" s="1" t="str">
-        <v>5.937</v>
+        <v>5.955</v>
       </c>
       <c r="BU82" s="1">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="BW82" s="1">
         <v>5</v>
@@ -5773,7 +5851,7 @@
         <v>Tom</v>
       </c>
       <c r="CC82" s="1">
-        <v>5.9367088607594933</v>
+        <v>5.9554655870445341</v>
       </c>
     </row>
     <row r="83" spans="1:81" x14ac:dyDescent="0.3">
@@ -6057,16 +6135,16 @@
         <v>Jules</v>
       </c>
       <c r="BT86" s="1" t="str">
-        <v>5.476</v>
+        <v>5.699</v>
       </c>
       <c r="BU86" s="1">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="CB86" s="1" t="str">
         <v>Jules</v>
       </c>
       <c r="CC86" s="1">
-        <v>5.475903614457831</v>
+        <v>5.6988636363636367</v>
       </c>
     </row>
     <row r="87" spans="1:81" x14ac:dyDescent="0.3">
@@ -6247,16 +6325,16 @@
         <v>Damien</v>
       </c>
       <c r="BT88" s="1" t="str">
-        <v>5.389</v>
+        <v>5.366</v>
       </c>
       <c r="BU88" s="1">
-        <v>663</v>
+        <v>675</v>
       </c>
       <c r="CB88" s="1" t="str">
         <v>Damien</v>
       </c>
       <c r="CC88" s="1">
-        <v>5.3891402714932131</v>
+        <v>5.365925925925926</v>
       </c>
     </row>
     <row r="89" spans="1:81" x14ac:dyDescent="0.3">
@@ -6431,7 +6509,7 @@
       </c>
       <c r="BP90" s="1">
         <f>AVERAGE(C1:BF1)</f>
-        <v>5.1019184112826022</v>
+        <v>5.0964916594941752</v>
       </c>
       <c r="BR90" s="1">
         <v>13</v>
@@ -6720,16 +6798,16 @@
         <v>Marie</v>
       </c>
       <c r="BT93" s="1" t="str">
-        <v>4.328</v>
+        <v>4.310</v>
       </c>
       <c r="BU93" s="1">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="CB93" s="1" t="str">
         <v>Marie</v>
       </c>
       <c r="CC93" s="1">
-        <v>4.328125</v>
+        <v>4.3098290598290596</v>
       </c>
     </row>
     <row r="94" spans="1:81" x14ac:dyDescent="0.3">
@@ -8141,13 +8219,13 @@
         <v>1</v>
       </c>
       <c r="CC110" s="1" t="str">
-        <v>Gauthier</v>
+        <v>Boris</v>
       </c>
       <c r="CD110" s="1">
-        <v>7.2530000000000001</v>
+        <v>7.1769999999999996</v>
       </c>
       <c r="CE110" s="1">
-        <v>79</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="111" spans="1:83" x14ac:dyDescent="0.3">
@@ -8230,13 +8308,13 @@
         <v>2</v>
       </c>
       <c r="CC111" s="1" t="str">
-        <v>Boris</v>
+        <v>Gauthier</v>
       </c>
       <c r="CD111" s="1">
-        <v>7.1769999999999996</v>
+        <v>6.8620000000000001</v>
       </c>
       <c r="CE111" s="1">
-        <v>1056</v>
+        <v>87</v>
       </c>
     </row>
     <row r="112" spans="1:83" x14ac:dyDescent="0.3">
@@ -8322,10 +8400,10 @@
         <v>Célian</v>
       </c>
       <c r="CD112" s="1">
-        <v>6.181</v>
+        <v>6.2640000000000002</v>
       </c>
       <c r="CE112" s="1">
-        <v>276</v>
+        <v>296</v>
       </c>
     </row>
     <row r="113" spans="1:83" x14ac:dyDescent="0.3">
@@ -8492,10 +8570,10 @@
         <v>Tom</v>
       </c>
       <c r="CD114" s="1">
-        <v>5.9370000000000003</v>
+        <v>5.9550000000000001</v>
       </c>
       <c r="CE114" s="1">
-        <v>237</v>
+        <v>247</v>
       </c>
     </row>
     <row r="115" spans="1:83" x14ac:dyDescent="0.3">
@@ -8841,10 +8919,10 @@
         <v>Jules</v>
       </c>
       <c r="CD118" s="1">
-        <v>5.476</v>
+        <v>5.6989999999999998</v>
       </c>
       <c r="CE118" s="1">
-        <v>166</v>
+        <v>176</v>
       </c>
     </row>
     <row r="119" spans="1:83" x14ac:dyDescent="0.3">
@@ -9015,10 +9093,10 @@
         <v>Damien</v>
       </c>
       <c r="CD120" s="1">
-        <v>5.3890000000000002</v>
+        <v>5.3659999999999997</v>
       </c>
       <c r="CE120" s="1">
-        <v>663</v>
+        <v>675</v>
       </c>
     </row>
     <row r="121" spans="1:83" x14ac:dyDescent="0.3">
@@ -9440,10 +9518,10 @@
         <v>Marie</v>
       </c>
       <c r="CD125" s="1">
-        <v>4.3280000000000003</v>
+        <v>4.3099999999999996</v>
       </c>
       <c r="CE125" s="1">
-        <v>224</v>
+        <v>234</v>
       </c>
     </row>
     <row r="126" spans="1:83" x14ac:dyDescent="0.3">
@@ -10321,20 +10399,20 @@
   _xlpm.ok, ISNUMBER(_xlpm.moy),
   _xlfn._xlws.SORT(CHOOSE({1,2,3}, _xlfn._xlws.FILTER(_xlpm.noms,_xlpm.ok), _xlfn._xlws.FILTER(_xlpm.moy,_xlpm.ok), _xlfn._xlws.FILTER(_xlpm.parties,_xlpm.ok)), 2, -1)
 )</f>
-        <v>Gauthier</v>
+        <v>Boris</v>
       </c>
       <c r="CC136" s="1">
-        <v>7.2531645569620249</v>
+        <v>7.1766098484848486</v>
       </c>
       <c r="CD136" s="1">
-        <v>79</v>
+        <v>1056</v>
       </c>
       <c r="CG136" s="1" t="str" cm="1">
         <f t="array" ref="CG136:CH155">_xlfn.LET(  _xlpm.noms, TRANSPOSE(INDEX(C9:BF9,_xlfn.SEQUENCE(1,COLUMNS(C9:BF9)/2,1,2))),_xlpm.moy,  TRANSPOSE(INDEX(C1:BF1,,_xlfn.SEQUENCE(1,COLUMNS(C1:BF1)/2,1,2))),_xlpm.ok, ISNUMBER(_xlpm.moy),_xlfn._xlws.SORT(CHOOSE({1,2}, _xlfn._xlws.FILTER(_xlpm.noms, _xlpm.ok), _xlfn._xlws.FILTER(_xlpm.moy, _xlpm.ok)), 2, -1))</f>
-        <v>Gauthier</v>
+        <v>Boris</v>
       </c>
       <c r="CH136" s="1">
-        <v>7.2531645569620249</v>
+        <v>7.1766098484848486</v>
       </c>
     </row>
     <row r="137" spans="1:86" x14ac:dyDescent="0.3">
@@ -10410,19 +10488,19 @@
       <c r="AX137" s="15"/>
       <c r="AY137" s="15"/>
       <c r="CB137" s="1" t="str">
-        <v>Boris</v>
+        <v>Gauthier</v>
       </c>
       <c r="CC137" s="1">
-        <v>7.1766098484848486</v>
+        <v>6.8620689655172411</v>
       </c>
       <c r="CD137" s="1">
-        <v>1056</v>
+        <v>87</v>
       </c>
       <c r="CG137" s="1" t="str">
-        <v>Boris</v>
+        <v>Gauthier</v>
       </c>
       <c r="CH137" s="1">
-        <v>7.1766098484848486</v>
+        <v>6.8620689655172411</v>
       </c>
     </row>
     <row r="138" spans="1:86" x14ac:dyDescent="0.3">
@@ -10501,16 +10579,16 @@
         <v>Célian</v>
       </c>
       <c r="CC138" s="1">
-        <v>6.1811594202898554</v>
+        <v>6.2635135135135132</v>
       </c>
       <c r="CD138" s="1">
-        <v>276</v>
+        <v>296</v>
       </c>
       <c r="CG138" s="1" t="str">
         <v>Célian</v>
       </c>
       <c r="CH138" s="1">
-        <v>6.1811594202898554</v>
+        <v>6.2635135135135132</v>
       </c>
     </row>
     <row r="139" spans="1:86" x14ac:dyDescent="0.3">
@@ -10677,16 +10755,16 @@
         <v>Tom</v>
       </c>
       <c r="CC140" s="1">
-        <v>5.9367088607594933</v>
+        <v>5.9554655870445341</v>
       </c>
       <c r="CD140" s="1">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="CG140" s="1" t="str">
         <v>Tom</v>
       </c>
       <c r="CH140" s="1">
-        <v>5.9367088607594933</v>
+        <v>5.9554655870445341</v>
       </c>
     </row>
     <row r="141" spans="1:86" x14ac:dyDescent="0.3">
@@ -11033,16 +11111,16 @@
         <v>Jules</v>
       </c>
       <c r="CC144" s="1">
-        <v>5.475903614457831</v>
+        <v>5.6988636363636367</v>
       </c>
       <c r="CD144" s="1">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="CG144" s="1" t="str">
         <v>Jules</v>
       </c>
       <c r="CH144" s="1">
-        <v>5.475903614457831</v>
+        <v>5.6988636363636367</v>
       </c>
     </row>
     <row r="145" spans="1:86" x14ac:dyDescent="0.3">
@@ -11103,16 +11181,16 @@
         <v>Damien</v>
       </c>
       <c r="CC146" s="1">
-        <v>5.3891402714932131</v>
+        <v>5.365925925925926</v>
       </c>
       <c r="CD146" s="1">
-        <v>663</v>
+        <v>675</v>
       </c>
       <c r="CG146" s="1" t="str">
         <v>Damien</v>
       </c>
       <c r="CH146" s="1">
-        <v>5.3891402714932131</v>
+        <v>5.365925925925926</v>
       </c>
     </row>
     <row r="147" spans="1:86" x14ac:dyDescent="0.3">
@@ -11244,10 +11322,10 @@
         <v>Marie</v>
       </c>
       <c r="CC149" s="1">
-        <v>4.328125</v>
+        <v>4.3098290598290596</v>
       </c>
       <c r="CD149" s="1">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="CG149" s="1" t="str">
         <v>Joey</v>
@@ -11347,7 +11425,7 @@
         <v>Marie</v>
       </c>
       <c r="CH151" s="1">
-        <v>4.328125</v>
+        <v>4.3098290598290596</v>
       </c>
     </row>
     <row r="152" spans="1:86" x14ac:dyDescent="0.3">
@@ -11589,6 +11667,24 @@
     <sortCondition descending="1" ref="B146:B157"/>
   </sortState>
   <mergeCells count="31">
+    <mergeCell ref="BG9:BH9"/>
+    <mergeCell ref="BI9:BJ9"/>
+    <mergeCell ref="BK9:BL9"/>
+    <mergeCell ref="BA9:BB9"/>
+    <mergeCell ref="BC9:BD9"/>
+    <mergeCell ref="BE9:BF9"/>
+    <mergeCell ref="Y9:Z9"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="K9:L9"/>
+    <mergeCell ref="M9:N9"/>
+    <mergeCell ref="O9:P9"/>
+    <mergeCell ref="Q9:R9"/>
+    <mergeCell ref="S9:T9"/>
+    <mergeCell ref="U9:V9"/>
+    <mergeCell ref="W9:X9"/>
     <mergeCell ref="AW9:AX9"/>
     <mergeCell ref="AY9:AZ9"/>
     <mergeCell ref="AA9:AB9"/>
@@ -11602,24 +11698,6 @@
     <mergeCell ref="AQ9:AR9"/>
     <mergeCell ref="AS9:AT9"/>
     <mergeCell ref="AU9:AV9"/>
-    <mergeCell ref="Y9:Z9"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="K9:L9"/>
-    <mergeCell ref="M9:N9"/>
-    <mergeCell ref="O9:P9"/>
-    <mergeCell ref="Q9:R9"/>
-    <mergeCell ref="S9:T9"/>
-    <mergeCell ref="U9:V9"/>
-    <mergeCell ref="W9:X9"/>
-    <mergeCell ref="BG9:BH9"/>
-    <mergeCell ref="BI9:BJ9"/>
-    <mergeCell ref="BK9:BL9"/>
-    <mergeCell ref="BA9:BB9"/>
-    <mergeCell ref="BC9:BD9"/>
-    <mergeCell ref="BE9:BF9"/>
   </mergeCells>
   <conditionalFormatting sqref="C1 E1 G1 I1 K1 M1 O1 Q1 S1 U1 W1 Y1 AA1 AC1 AE1 AG1 AI1 AK1 AM1 AO1 AQ1 AS1 AU1 AW1 AY1 BA1 BC1 BE1 BG1 BI1 BK1 C9:AM9 AO9 AQ9 AS9 AU9 AW9 AY9 BA9 BC9 BE9 BG9 BI9 BK9">
     <cfRule type="expression" dxfId="24" priority="41" stopIfTrue="1">
@@ -11757,13 +11835,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="25" t="str">
-        <v>Gauthier</v>
+        <v>Boris</v>
       </c>
       <c r="C2" s="25" t="str">
-        <v>7.253</v>
+        <v>7.177</v>
       </c>
       <c r="D2" s="25">
-        <v>79</v>
+        <v>1056</v>
       </c>
       <c r="F2" t="str">
         <v>nombre de parties</v>
@@ -11774,13 +11852,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="25" t="str">
-        <v>Boris</v>
+        <v>Gauthier</v>
       </c>
       <c r="C3" s="25" t="str">
-        <v>7.177</v>
+        <v>6.862</v>
       </c>
       <c r="D3" s="25">
-        <v>1056</v>
+        <v>87</v>
       </c>
       <c r="F3" t="str">
         <v>entre 1 et 10</v>
@@ -11802,10 +11880,10 @@
         <v>Célian</v>
       </c>
       <c r="C4" s="25" t="str">
-        <v>6.181</v>
+        <v>6.264</v>
       </c>
       <c r="D4" s="25">
-        <v>276</v>
+        <v>296</v>
       </c>
       <c r="F4" t="str">
         <v>entre 10 et 20</v>
@@ -11850,10 +11928,10 @@
         <v>Tom</v>
       </c>
       <c r="C6" s="25" t="str">
-        <v>5.937</v>
+        <v>5.955</v>
       </c>
       <c r="D6" s="25">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="F6" t="str">
         <v>entre 50 et 100</v>
@@ -11946,10 +12024,10 @@
         <v>Jules</v>
       </c>
       <c r="C10" s="25" t="str">
-        <v>5.476</v>
+        <v>5.699</v>
       </c>
       <c r="D10" s="25">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="F10" t="str">
         <v>plus de 1000</v>
@@ -11984,10 +12062,10 @@
         <v>Damien</v>
       </c>
       <c r="C12" s="25" t="str">
-        <v>5.389</v>
+        <v>5.366</v>
       </c>
       <c r="D12" s="25">
-        <v>663</v>
+        <v>675</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
@@ -12054,10 +12132,10 @@
         <v>Marie</v>
       </c>
       <c r="C17" s="25" t="str">
-        <v>4.328</v>
+        <v>4.310</v>
       </c>
       <c r="D17" s="25">
-        <v>224</v>
+        <v>234</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">

--- a/classement_whist_2023_2025.xlsx
+++ b/classement_whist_2023_2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a20b8382962b136a/Bureau/loisir/whist/projet_application_streamlit/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="101" documentId="14_{D8C30FC8-DD4A-4CBA-A5BF-091BFC36F9C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D3A69E8C-0E86-42AB-87D6-B9767DBC2D38}"/>
+  <xr:revisionPtr revIDLastSave="105" documentId="14_{D8C30FC8-DD4A-4CBA-A5BF-091BFC36F9C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2FD7FBA5-82DE-4BE1-8777-2925546356E8}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1196,14 +1196,14 @@
       </c>
       <c r="M1" s="1">
         <f t="shared" ref="M1" si="5">IF(N2&gt;19,M2/N2,"/")</f>
-        <v>5.365925925925926</v>
+        <v>5.3382137628111277</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="O1" s="1">
         <f t="shared" ref="O1" si="6">IF(P2&gt;19,O2/P2,"/")</f>
-        <v>6.8620689655172411</v>
+        <v>7.2531645569620249</v>
       </c>
       <c r="P1" s="1" t="s">
         <v>2</v>
@@ -1423,19 +1423,19 @@
       </c>
       <c r="M2" s="1">
         <f t="shared" si="31"/>
-        <v>3622</v>
+        <v>3646</v>
       </c>
       <c r="N2" s="1">
         <f t="shared" si="31"/>
-        <v>675</v>
+        <v>683</v>
       </c>
       <c r="O2" s="1">
         <f t="shared" si="31"/>
-        <v>597</v>
+        <v>573</v>
       </c>
       <c r="P2" s="1">
         <f t="shared" si="31"/>
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="Q2" s="1">
         <f t="shared" si="31"/>
@@ -2648,14 +2648,14 @@
       </c>
       <c r="M7" s="15">
         <f t="shared" ref="M7" si="109">M8/N8</f>
-        <v>5.7618069815195074</v>
+        <v>5.7171717171717171</v>
       </c>
       <c r="N7" s="15" t="s">
         <v>2</v>
       </c>
       <c r="O7" s="15">
         <f t="shared" ref="O7" si="110">O8/P8</f>
-        <v>7.2</v>
+        <v>7.7894736842105265</v>
       </c>
       <c r="P7" s="15" t="s">
         <v>2</v>
@@ -2876,19 +2876,19 @@
       </c>
       <c r="M8" s="15">
         <f t="shared" si="136"/>
-        <v>2806</v>
+        <v>2830</v>
       </c>
       <c r="N8" s="15">
         <f t="shared" si="136"/>
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="O8" s="15">
         <f t="shared" si="136"/>
-        <v>468</v>
+        <v>444</v>
       </c>
       <c r="P8" s="15">
         <f t="shared" si="136"/>
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="Q8" s="15">
         <f t="shared" si="136"/>
@@ -3267,10 +3267,10 @@
       <c r="B16" s="1">
         <v>140</v>
       </c>
-      <c r="O16" s="1">
+      <c r="M16" s="1">
         <v>24</v>
       </c>
-      <c r="P16" s="1">
+      <c r="N16" s="1">
         <v>8</v>
       </c>
       <c r="Q16" s="1">
@@ -5548,13 +5548,13 @@
         <v>1</v>
       </c>
       <c r="BS78" s="1" t="str">
-        <v>Boris</v>
+        <v>Gauthier</v>
       </c>
       <c r="BT78" s="1" t="str">
-        <v>7.177</v>
+        <v>7.253</v>
       </c>
       <c r="BU78" s="1">
-        <v>1056</v>
+        <v>79</v>
       </c>
       <c r="BW78" s="1" cm="1">
         <f t="array" ref="BW78:BZ85">_xlfn.LET(
@@ -5588,10 +5588,10 @@
       </c>
       <c r="CB78" s="1" t="str" cm="1">
         <f t="array" ref="CB78:CC105">_xlfn.LET(  _xlpm.noms, TRANSPOSE(INDEX(C9:BF9,_xlfn.SEQUENCE(1,COLUMNS(C9:BF9)/2,1,2))),_xlpm.moy,  TRANSPOSE(INDEX(C1:BF1,,_xlfn.SEQUENCE(1,COLUMNS(C1:BF1)/2,1,2))),_xlfn.SORTBY(CHOOSE({1,2}, _xlpm.noms, _xlpm.moy), IF(ISNUMBER(_xlpm.moy), _xlpm.moy, -1E+99), -1))</f>
-        <v>Boris</v>
+        <v>Gauthier</v>
       </c>
       <c r="CC78" s="1">
-        <v>7.1766098484848486</v>
+        <v>7.2531645569620249</v>
       </c>
     </row>
     <row r="79" spans="1:81" x14ac:dyDescent="0.3">
@@ -5633,13 +5633,13 @@
         <v>2</v>
       </c>
       <c r="BS79" s="1" t="str">
-        <v>Gauthier</v>
+        <v>Boris</v>
       </c>
       <c r="BT79" s="1" t="str">
-        <v>6.862</v>
+        <v>7.177</v>
       </c>
       <c r="BU79" s="1">
-        <v>87</v>
+        <v>1056</v>
       </c>
       <c r="BW79" s="1">
         <v>2</v>
@@ -5654,10 +5654,10 @@
         <v>4</v>
       </c>
       <c r="CB79" s="1" t="str">
-        <v>Gauthier</v>
+        <v>Boris</v>
       </c>
       <c r="CC79" s="1">
-        <v>6.8620689655172411</v>
+        <v>7.1766098484848486</v>
       </c>
     </row>
     <row r="80" spans="1:81" x14ac:dyDescent="0.3">
@@ -6325,16 +6325,16 @@
         <v>Damien</v>
       </c>
       <c r="BT88" s="1" t="str">
-        <v>5.366</v>
+        <v>5.338</v>
       </c>
       <c r="BU88" s="1">
-        <v>675</v>
+        <v>683</v>
       </c>
       <c r="CB88" s="1" t="str">
         <v>Damien</v>
       </c>
       <c r="CC88" s="1">
-        <v>5.365925925925926</v>
+        <v>5.3382137628111277</v>
       </c>
     </row>
     <row r="89" spans="1:81" x14ac:dyDescent="0.3">
@@ -6509,7 +6509,7 @@
       </c>
       <c r="BP90" s="1">
         <f>AVERAGE(C1:BF1)</f>
-        <v>5.0964916594941752</v>
+        <v>5.1146608309106742</v>
       </c>
       <c r="BR90" s="1">
         <v>13</v>
@@ -8219,13 +8219,13 @@
         <v>1</v>
       </c>
       <c r="CC110" s="1" t="str">
-        <v>Boris</v>
+        <v>Gauthier</v>
       </c>
       <c r="CD110" s="1">
-        <v>7.1769999999999996</v>
+        <v>7.2530000000000001</v>
       </c>
       <c r="CE110" s="1">
-        <v>1056</v>
+        <v>79</v>
       </c>
     </row>
     <row r="111" spans="1:83" x14ac:dyDescent="0.3">
@@ -8308,13 +8308,13 @@
         <v>2</v>
       </c>
       <c r="CC111" s="1" t="str">
-        <v>Gauthier</v>
+        <v>Boris</v>
       </c>
       <c r="CD111" s="1">
-        <v>6.8620000000000001</v>
+        <v>7.1769999999999996</v>
       </c>
       <c r="CE111" s="1">
-        <v>87</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="112" spans="1:83" x14ac:dyDescent="0.3">
@@ -9093,10 +9093,10 @@
         <v>Damien</v>
       </c>
       <c r="CD120" s="1">
-        <v>5.3659999999999997</v>
+        <v>5.3380000000000001</v>
       </c>
       <c r="CE120" s="1">
-        <v>675</v>
+        <v>683</v>
       </c>
     </row>
     <row r="121" spans="1:83" x14ac:dyDescent="0.3">
@@ -10399,20 +10399,20 @@
   _xlpm.ok, ISNUMBER(_xlpm.moy),
   _xlfn._xlws.SORT(CHOOSE({1,2,3}, _xlfn._xlws.FILTER(_xlpm.noms,_xlpm.ok), _xlfn._xlws.FILTER(_xlpm.moy,_xlpm.ok), _xlfn._xlws.FILTER(_xlpm.parties,_xlpm.ok)), 2, -1)
 )</f>
-        <v>Boris</v>
+        <v>Gauthier</v>
       </c>
       <c r="CC136" s="1">
-        <v>7.1766098484848486</v>
+        <v>7.2531645569620249</v>
       </c>
       <c r="CD136" s="1">
-        <v>1056</v>
+        <v>79</v>
       </c>
       <c r="CG136" s="1" t="str" cm="1">
         <f t="array" ref="CG136:CH155">_xlfn.LET(  _xlpm.noms, TRANSPOSE(INDEX(C9:BF9,_xlfn.SEQUENCE(1,COLUMNS(C9:BF9)/2,1,2))),_xlpm.moy,  TRANSPOSE(INDEX(C1:BF1,,_xlfn.SEQUENCE(1,COLUMNS(C1:BF1)/2,1,2))),_xlpm.ok, ISNUMBER(_xlpm.moy),_xlfn._xlws.SORT(CHOOSE({1,2}, _xlfn._xlws.FILTER(_xlpm.noms, _xlpm.ok), _xlfn._xlws.FILTER(_xlpm.moy, _xlpm.ok)), 2, -1))</f>
-        <v>Boris</v>
+        <v>Gauthier</v>
       </c>
       <c r="CH136" s="1">
-        <v>7.1766098484848486</v>
+        <v>7.2531645569620249</v>
       </c>
     </row>
     <row r="137" spans="1:86" x14ac:dyDescent="0.3">
@@ -10488,19 +10488,19 @@
       <c r="AX137" s="15"/>
       <c r="AY137" s="15"/>
       <c r="CB137" s="1" t="str">
-        <v>Gauthier</v>
+        <v>Boris</v>
       </c>
       <c r="CC137" s="1">
-        <v>6.8620689655172411</v>
+        <v>7.1766098484848486</v>
       </c>
       <c r="CD137" s="1">
-        <v>87</v>
+        <v>1056</v>
       </c>
       <c r="CG137" s="1" t="str">
-        <v>Gauthier</v>
+        <v>Boris</v>
       </c>
       <c r="CH137" s="1">
-        <v>6.8620689655172411</v>
+        <v>7.1766098484848486</v>
       </c>
     </row>
     <row r="138" spans="1:86" x14ac:dyDescent="0.3">
@@ -11181,16 +11181,16 @@
         <v>Damien</v>
       </c>
       <c r="CC146" s="1">
-        <v>5.365925925925926</v>
+        <v>5.3382137628111277</v>
       </c>
       <c r="CD146" s="1">
-        <v>675</v>
+        <v>683</v>
       </c>
       <c r="CG146" s="1" t="str">
         <v>Damien</v>
       </c>
       <c r="CH146" s="1">
-        <v>5.365925925925926</v>
+        <v>5.3382137628111277</v>
       </c>
     </row>
     <row r="147" spans="1:86" x14ac:dyDescent="0.3">
@@ -11835,13 +11835,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="25" t="str">
-        <v>Boris</v>
+        <v>Gauthier</v>
       </c>
       <c r="C2" s="25" t="str">
-        <v>7.177</v>
+        <v>7.253</v>
       </c>
       <c r="D2" s="25">
-        <v>1056</v>
+        <v>79</v>
       </c>
       <c r="F2" t="str">
         <v>nombre de parties</v>
@@ -11852,13 +11852,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="25" t="str">
-        <v>Gauthier</v>
+        <v>Boris</v>
       </c>
       <c r="C3" s="25" t="str">
-        <v>6.862</v>
+        <v>7.177</v>
       </c>
       <c r="D3" s="25">
-        <v>87</v>
+        <v>1056</v>
       </c>
       <c r="F3" t="str">
         <v>entre 1 et 10</v>
@@ -12062,10 +12062,10 @@
         <v>Damien</v>
       </c>
       <c r="C12" s="25" t="str">
-        <v>5.366</v>
+        <v>5.338</v>
       </c>
       <c r="D12" s="25">
-        <v>675</v>
+        <v>683</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">

--- a/classement_whist_2023_2025.xlsx
+++ b/classement_whist_2023_2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a20b8382962b136a/Bureau/loisir/whist/projet_application_streamlit/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="105" documentId="14_{D8C30FC8-DD4A-4CBA-A5BF-091BFC36F9C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2FD7FBA5-82DE-4BE1-8777-2925546356E8}"/>
+  <xr:revisionPtr revIDLastSave="114" documentId="14_{D8C30FC8-DD4A-4CBA-A5BF-091BFC36F9C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{183DE1E1-37AD-4184-B02A-C2EF5C0D92C2}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="94">
   <si>
     <t>global</t>
   </si>
@@ -335,6 +335,9 @@
   </si>
   <si>
     <t>?</t>
+  </si>
+  <si>
+    <t>gaspard</t>
   </si>
 </sst>
 </file>
@@ -1175,7 +1178,7 @@
       </c>
       <c r="G1" s="1">
         <f t="shared" ref="G1" si="2">IF(H2&gt;19,G2/H2,"/")</f>
-        <v>7.1766098484848486</v>
+        <v>7.1705827067669174</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>2</v>
@@ -1231,7 +1234,7 @@
       </c>
       <c r="W1" s="1">
         <f t="shared" ref="W1" si="10">IF(X2&gt;19,W2/X2,"/")</f>
-        <v>2.0746268656716418</v>
+        <v>2.4266666666666667</v>
       </c>
       <c r="X1" s="1" t="s">
         <v>2</v>
@@ -1252,7 +1255,7 @@
       </c>
       <c r="AC1" s="1">
         <f>IF(AD2&gt;19,AC2/AD2,"/")</f>
-        <v>5.6988636363636367</v>
+        <v>5.625</v>
       </c>
       <c r="AD1" s="1" t="s">
         <v>2</v>
@@ -1399,11 +1402,11 @@
       </c>
       <c r="G2" s="1">
         <f t="shared" si="30"/>
-        <v>7578.5</v>
+        <v>7629.5</v>
       </c>
       <c r="H2" s="1">
         <f t="shared" si="30"/>
-        <v>1056</v>
+        <v>1064</v>
       </c>
       <c r="I2" s="1">
         <f t="shared" si="30"/>
@@ -1463,11 +1466,11 @@
       </c>
       <c r="W2" s="1">
         <f t="shared" si="31"/>
-        <v>139</v>
+        <v>182</v>
       </c>
       <c r="X2" s="1">
         <f t="shared" si="31"/>
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="Y2" s="1">
         <f t="shared" si="31"/>
@@ -1487,11 +1490,11 @@
       </c>
       <c r="AC2" s="1">
         <f t="shared" si="31"/>
-        <v>1003</v>
+        <v>1035</v>
       </c>
       <c r="AD2" s="1">
         <f t="shared" si="31"/>
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="AE2" s="1">
         <f t="shared" si="31"/>
@@ -1615,11 +1618,11 @@
       </c>
       <c r="BI2" s="1">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="BJ2" s="1">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BK2" s="1">
         <f t="shared" si="34"/>
@@ -2627,7 +2630,7 @@
       </c>
       <c r="G7" s="15">
         <f t="shared" ref="G7" si="106">G8/H8</f>
-        <v>7.3926553672316384</v>
+        <v>7.3775510204081636</v>
       </c>
       <c r="H7" s="15" t="s">
         <v>2</v>
@@ -2683,7 +2686,7 @@
       </c>
       <c r="W7" s="15">
         <f t="shared" ref="W7" si="114">W8/X8</f>
-        <v>1.1000000000000001</v>
+        <v>2</v>
       </c>
       <c r="X7" s="15" t="s">
         <v>2</v>
@@ -2704,7 +2707,7 @@
       </c>
       <c r="AC7" s="15">
         <f t="shared" ref="AC7" si="117">AC8/AD8</f>
-        <v>5.9457831325301207</v>
+        <v>5.8563218390804597</v>
       </c>
       <c r="AD7" s="15" t="s">
         <v>2</v>
@@ -2814,9 +2817,9 @@
       <c r="BH7" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="BI7" s="15" t="e">
+      <c r="BI7" s="15">
         <f t="shared" ref="BI7" si="133">BI8/BJ8</f>
-        <v>#DIV/0!</v>
+        <v>6.75</v>
       </c>
       <c r="BJ7" s="15" t="s">
         <v>2</v>
@@ -2852,11 +2855,11 @@
       </c>
       <c r="G8" s="15">
         <f t="shared" si="135"/>
-        <v>3925.5</v>
+        <v>3976.5</v>
       </c>
       <c r="H8" s="15">
         <f t="shared" si="135"/>
-        <v>531</v>
+        <v>539</v>
       </c>
       <c r="I8" s="15">
         <f t="shared" si="135"/>
@@ -2916,11 +2919,11 @@
       </c>
       <c r="W8" s="15">
         <f t="shared" si="136"/>
-        <v>33</v>
+        <v>76</v>
       </c>
       <c r="X8" s="15">
         <f t="shared" si="136"/>
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="Y8" s="15">
         <f t="shared" si="136"/>
@@ -2940,11 +2943,11 @@
       </c>
       <c r="AC8" s="15">
         <f t="shared" si="136"/>
-        <v>987</v>
+        <v>1019</v>
       </c>
       <c r="AD8" s="15">
         <f t="shared" si="136"/>
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="AE8" s="15">
         <f t="shared" si="136"/>
@@ -3068,11 +3071,11 @@
       </c>
       <c r="BI8" s="15">
         <f t="shared" si="139"/>
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="BJ8" s="15">
         <f t="shared" si="139"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BK8" s="15">
         <f t="shared" si="139"/>
@@ -3201,7 +3204,7 @@
       </c>
       <c r="BH9" s="26"/>
       <c r="BI9" s="27" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="BJ9" s="27"/>
       <c r="BK9" s="27" t="s">
@@ -3232,6 +3235,30 @@
     <row r="14" spans="1:69" x14ac:dyDescent="0.3">
       <c r="B14" s="1">
         <v>142</v>
+      </c>
+      <c r="G14" s="1">
+        <v>51</v>
+      </c>
+      <c r="H14" s="1">
+        <v>8</v>
+      </c>
+      <c r="W14" s="1">
+        <v>43</v>
+      </c>
+      <c r="X14" s="1">
+        <v>8</v>
+      </c>
+      <c r="AC14" s="1">
+        <v>32</v>
+      </c>
+      <c r="AD14" s="1">
+        <v>8</v>
+      </c>
+      <c r="BI14" s="1">
+        <v>54</v>
+      </c>
+      <c r="BJ14" s="1">
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:69" x14ac:dyDescent="0.3">
@@ -5636,10 +5663,10 @@
         <v>Boris</v>
       </c>
       <c r="BT79" s="1" t="str">
-        <v>7.177</v>
+        <v>7.171</v>
       </c>
       <c r="BU79" s="1">
-        <v>1056</v>
+        <v>1064</v>
       </c>
       <c r="BW79" s="1">
         <v>2</v>
@@ -5657,7 +5684,7 @@
         <v>Boris</v>
       </c>
       <c r="CC79" s="1">
-        <v>7.1766098484848486</v>
+        <v>7.1705827067669174</v>
       </c>
     </row>
     <row r="80" spans="1:81" x14ac:dyDescent="0.3">
@@ -6135,16 +6162,16 @@
         <v>Jules</v>
       </c>
       <c r="BT86" s="1" t="str">
-        <v>5.699</v>
+        <v>5.625</v>
       </c>
       <c r="BU86" s="1">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="CB86" s="1" t="str">
         <v>Jules</v>
       </c>
       <c r="CC86" s="1">
-        <v>5.6988636363636367</v>
+        <v>5.625</v>
       </c>
     </row>
     <row r="87" spans="1:81" x14ac:dyDescent="0.3">
@@ -6509,7 +6536,7 @@
       </c>
       <c r="BP90" s="1">
         <f>AVERAGE(C1:BF1)</f>
-        <v>5.1146608309106742</v>
+        <v>5.1282682820563474</v>
       </c>
       <c r="BR90" s="1">
         <v>13</v>
@@ -7190,16 +7217,16 @@
         <v>Loulou</v>
       </c>
       <c r="BT97" s="1" t="str">
-        <v>2.075</v>
+        <v>2.427</v>
       </c>
       <c r="BU97" s="1">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="CB97" s="1" t="str">
         <v>Loulou</v>
       </c>
       <c r="CC97" s="1">
-        <v>2.0746268656716418</v>
+        <v>2.4266666666666667</v>
       </c>
     </row>
     <row r="98" spans="1:83" x14ac:dyDescent="0.3">
@@ -8311,10 +8338,10 @@
         <v>Boris</v>
       </c>
       <c r="CD111" s="1">
-        <v>7.1769999999999996</v>
+        <v>7.1710000000000003</v>
       </c>
       <c r="CE111" s="1">
-        <v>1056</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="112" spans="1:83" x14ac:dyDescent="0.3">
@@ -8919,10 +8946,10 @@
         <v>Jules</v>
       </c>
       <c r="CD118" s="1">
-        <v>5.6989999999999998</v>
+        <v>5.625</v>
       </c>
       <c r="CE118" s="1">
-        <v>176</v>
+        <v>184</v>
       </c>
     </row>
     <row r="119" spans="1:83" x14ac:dyDescent="0.3">
@@ -9870,10 +9897,10 @@
         <v>Loulou</v>
       </c>
       <c r="CD129" s="1">
-        <v>2.0750000000000002</v>
+        <v>2.427</v>
       </c>
       <c r="CE129" s="1">
-        <v>67</v>
+        <v>75</v>
       </c>
     </row>
     <row r="130" spans="1:86" x14ac:dyDescent="0.3">
@@ -10491,16 +10518,16 @@
         <v>Boris</v>
       </c>
       <c r="CC137" s="1">
-        <v>7.1766098484848486</v>
+        <v>7.1705827067669174</v>
       </c>
       <c r="CD137" s="1">
-        <v>1056</v>
+        <v>1064</v>
       </c>
       <c r="CG137" s="1" t="str">
         <v>Boris</v>
       </c>
       <c r="CH137" s="1">
-        <v>7.1766098484848486</v>
+        <v>7.1705827067669174</v>
       </c>
     </row>
     <row r="138" spans="1:86" x14ac:dyDescent="0.3">
@@ -11111,16 +11138,16 @@
         <v>Jules</v>
       </c>
       <c r="CC144" s="1">
-        <v>5.6988636363636367</v>
+        <v>5.625</v>
       </c>
       <c r="CD144" s="1">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="CG144" s="1" t="str">
         <v>Jules</v>
       </c>
       <c r="CH144" s="1">
-        <v>5.6988636363636367</v>
+        <v>5.625</v>
       </c>
     </row>
     <row r="145" spans="1:86" x14ac:dyDescent="0.3">
@@ -11510,10 +11537,10 @@
         <v>Loulou</v>
       </c>
       <c r="CC153" s="1">
-        <v>2.0746268656716418</v>
+        <v>2.4266666666666667</v>
       </c>
       <c r="CD153" s="1">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="CG153" s="1" t="str">
         <v>Luca</v>
@@ -11595,7 +11622,7 @@
         <v>Loulou</v>
       </c>
       <c r="CH155" s="1">
-        <v>2.0746268656716418</v>
+        <v>2.4266666666666667</v>
       </c>
     </row>
     <row r="156" spans="1:86" x14ac:dyDescent="0.3">
@@ -11667,24 +11694,6 @@
     <sortCondition descending="1" ref="B146:B157"/>
   </sortState>
   <mergeCells count="31">
-    <mergeCell ref="BG9:BH9"/>
-    <mergeCell ref="BI9:BJ9"/>
-    <mergeCell ref="BK9:BL9"/>
-    <mergeCell ref="BA9:BB9"/>
-    <mergeCell ref="BC9:BD9"/>
-    <mergeCell ref="BE9:BF9"/>
-    <mergeCell ref="Y9:Z9"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="K9:L9"/>
-    <mergeCell ref="M9:N9"/>
-    <mergeCell ref="O9:P9"/>
-    <mergeCell ref="Q9:R9"/>
-    <mergeCell ref="S9:T9"/>
-    <mergeCell ref="U9:V9"/>
-    <mergeCell ref="W9:X9"/>
     <mergeCell ref="AW9:AX9"/>
     <mergeCell ref="AY9:AZ9"/>
     <mergeCell ref="AA9:AB9"/>
@@ -11698,6 +11707,24 @@
     <mergeCell ref="AQ9:AR9"/>
     <mergeCell ref="AS9:AT9"/>
     <mergeCell ref="AU9:AV9"/>
+    <mergeCell ref="Y9:Z9"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="K9:L9"/>
+    <mergeCell ref="M9:N9"/>
+    <mergeCell ref="O9:P9"/>
+    <mergeCell ref="Q9:R9"/>
+    <mergeCell ref="S9:T9"/>
+    <mergeCell ref="U9:V9"/>
+    <mergeCell ref="W9:X9"/>
+    <mergeCell ref="BG9:BH9"/>
+    <mergeCell ref="BI9:BJ9"/>
+    <mergeCell ref="BK9:BL9"/>
+    <mergeCell ref="BA9:BB9"/>
+    <mergeCell ref="BC9:BD9"/>
+    <mergeCell ref="BE9:BF9"/>
   </mergeCells>
   <conditionalFormatting sqref="C1 E1 G1 I1 K1 M1 O1 Q1 S1 U1 W1 Y1 AA1 AC1 AE1 AG1 AI1 AK1 AM1 AO1 AQ1 AS1 AU1 AW1 AY1 BA1 BC1 BE1 BG1 BI1 BK1 C9:AM9 AO9 AQ9 AS9 AU9 AW9 AY9 BA9 BC9 BE9 BG9 BI9 BK9">
     <cfRule type="expression" dxfId="24" priority="41" stopIfTrue="1">
@@ -11855,10 +11882,10 @@
         <v>Boris</v>
       </c>
       <c r="C3" s="25" t="str">
-        <v>7.177</v>
+        <v>7.171</v>
       </c>
       <c r="D3" s="25">
-        <v>1056</v>
+        <v>1064</v>
       </c>
       <c r="F3" t="str">
         <v>entre 1 et 10</v>
@@ -12024,10 +12051,10 @@
         <v>Jules</v>
       </c>
       <c r="C10" s="25" t="str">
-        <v>5.699</v>
+        <v>5.625</v>
       </c>
       <c r="D10" s="25">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="F10" t="str">
         <v>plus de 1000</v>
@@ -12188,10 +12215,10 @@
         <v>Loulou</v>
       </c>
       <c r="C21" s="25" t="str">
-        <v>2.075</v>
+        <v>2.427</v>
       </c>
       <c r="D21" s="25">
-        <v>67</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/classement_whist_2023_2025.xlsx
+++ b/classement_whist_2023_2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a20b8382962b136a/Bureau/loisir/whist/projet_application_streamlit/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="114" documentId="14_{D8C30FC8-DD4A-4CBA-A5BF-091BFC36F9C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{183DE1E1-37AD-4184-B02A-C2EF5C0D92C2}"/>
+  <xr:revisionPtr revIDLastSave="124" documentId="14_{D8C30FC8-DD4A-4CBA-A5BF-091BFC36F9C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{766502F9-2D18-4698-9F8C-3B1BCDFCE4CC}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="G1" s="1">
         <f t="shared" ref="G1" si="2">IF(H2&gt;19,G2/H2,"/")</f>
-        <v>7.1705827067669174</v>
+        <v>7.2070093457943925</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>2</v>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="M1" s="1">
         <f t="shared" ref="M1" si="5">IF(N2&gt;19,M2/N2,"/")</f>
-        <v>5.3382137628111277</v>
+        <v>5.3710144927536234</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>2</v>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="S1" s="1">
         <f t="shared" ref="S1" si="8">IF(T2&gt;19,S2/T2,"/")</f>
-        <v>5.9554655870445341</v>
+        <v>5.8300395256916993</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>2</v>
@@ -1248,14 +1248,14 @@
       </c>
       <c r="AA1" s="1">
         <f t="shared" ref="AA1" si="12">IF(AB2&gt;19,AA2/AB2,"/")</f>
-        <v>4.3098290598290596</v>
+        <v>4.46875</v>
       </c>
       <c r="AB1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="AC1" s="1">
         <f>IF(AD2&gt;19,AC2/AD2,"/")</f>
-        <v>5.625</v>
+        <v>5.4869109947643979</v>
       </c>
       <c r="AD1" s="1" t="s">
         <v>2</v>
@@ -1402,11 +1402,11 @@
       </c>
       <c r="G2" s="1">
         <f t="shared" si="30"/>
-        <v>7629.5</v>
+        <v>7711.5</v>
       </c>
       <c r="H2" s="1">
         <f t="shared" si="30"/>
-        <v>1064</v>
+        <v>1070</v>
       </c>
       <c r="I2" s="1">
         <f t="shared" si="30"/>
@@ -1426,11 +1426,11 @@
       </c>
       <c r="M2" s="1">
         <f t="shared" si="31"/>
-        <v>3646</v>
+        <v>3706</v>
       </c>
       <c r="N2" s="1">
         <f t="shared" si="31"/>
-        <v>683</v>
+        <v>690</v>
       </c>
       <c r="O2" s="1">
         <f t="shared" si="31"/>
@@ -1450,11 +1450,11 @@
       </c>
       <c r="S2" s="1">
         <f t="shared" si="31"/>
-        <v>1471</v>
+        <v>1475</v>
       </c>
       <c r="T2" s="1">
         <f t="shared" si="31"/>
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="U2" s="1">
         <f t="shared" si="31"/>
@@ -1482,19 +1482,19 @@
       </c>
       <c r="AA2" s="1">
         <f t="shared" si="31"/>
-        <v>1008.5</v>
+        <v>1072.5</v>
       </c>
       <c r="AB2" s="1">
         <f t="shared" si="31"/>
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="AC2" s="1">
         <f t="shared" si="31"/>
-        <v>1035</v>
+        <v>1048</v>
       </c>
       <c r="AD2" s="1">
         <f t="shared" si="31"/>
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="AE2" s="1">
         <f t="shared" si="31"/>
@@ -2630,7 +2630,7 @@
       </c>
       <c r="G7" s="15">
         <f t="shared" ref="G7" si="106">G8/H8</f>
-        <v>7.3775510204081636</v>
+        <v>7.4467889908256879</v>
       </c>
       <c r="H7" s="15" t="s">
         <v>2</v>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="M7" s="15">
         <f t="shared" ref="M7" si="109">M8/N8</f>
-        <v>5.7171717171717171</v>
+        <v>5.7569721115537851</v>
       </c>
       <c r="N7" s="15" t="s">
         <v>2</v>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="S7" s="15">
         <f t="shared" ref="S7" si="112">S8/T8</f>
-        <v>5.0921985815602833</v>
+        <v>4.9115646258503398</v>
       </c>
       <c r="T7" s="15" t="s">
         <v>2</v>
@@ -2700,14 +2700,14 @@
       </c>
       <c r="AA7" s="15">
         <f t="shared" ref="AA7" si="116">AA8/AB8</f>
-        <v>4.8468208092485545</v>
+        <v>5.0418994413407825</v>
       </c>
       <c r="AB7" s="15" t="s">
         <v>2</v>
       </c>
       <c r="AC7" s="15">
         <f t="shared" ref="AC7" si="117">AC8/AD8</f>
-        <v>5.8563218390804597</v>
+        <v>5.7016574585635356</v>
       </c>
       <c r="AD7" s="15" t="s">
         <v>2</v>
@@ -2855,11 +2855,11 @@
       </c>
       <c r="G8" s="15">
         <f t="shared" si="135"/>
-        <v>3976.5</v>
+        <v>4058.5</v>
       </c>
       <c r="H8" s="15">
         <f t="shared" si="135"/>
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="I8" s="15">
         <f t="shared" si="135"/>
@@ -2879,11 +2879,11 @@
       </c>
       <c r="M8" s="15">
         <f t="shared" si="136"/>
-        <v>2830</v>
+        <v>2890</v>
       </c>
       <c r="N8" s="15">
         <f t="shared" si="136"/>
-        <v>495</v>
+        <v>502</v>
       </c>
       <c r="O8" s="15">
         <f t="shared" si="136"/>
@@ -2903,11 +2903,11 @@
       </c>
       <c r="S8" s="15">
         <f t="shared" si="136"/>
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="T8" s="15">
         <f t="shared" si="136"/>
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="U8" s="15">
         <f t="shared" si="136"/>
@@ -2935,19 +2935,19 @@
       </c>
       <c r="AA8" s="15">
         <f t="shared" si="136"/>
-        <v>838.5</v>
+        <v>902.5</v>
       </c>
       <c r="AB8" s="15">
         <f t="shared" si="136"/>
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="AC8" s="15">
         <f t="shared" si="136"/>
-        <v>1019</v>
+        <v>1032</v>
       </c>
       <c r="AD8" s="15">
         <f t="shared" si="136"/>
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="AE8" s="15">
         <f t="shared" si="136"/>
@@ -3230,6 +3230,36 @@
     <row r="13" spans="1:69" x14ac:dyDescent="0.3">
       <c r="B13" s="1">
         <v>143</v>
+      </c>
+      <c r="G13" s="1">
+        <v>82</v>
+      </c>
+      <c r="H13" s="1">
+        <v>6</v>
+      </c>
+      <c r="M13" s="1">
+        <v>60</v>
+      </c>
+      <c r="N13" s="1">
+        <v>7</v>
+      </c>
+      <c r="S13" s="1">
+        <v>4</v>
+      </c>
+      <c r="T13" s="1">
+        <v>6</v>
+      </c>
+      <c r="AA13" s="1">
+        <v>64</v>
+      </c>
+      <c r="AB13" s="1">
+        <v>6</v>
+      </c>
+      <c r="AC13" s="1">
+        <v>13</v>
+      </c>
+      <c r="AD13" s="1">
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:69" x14ac:dyDescent="0.3">
@@ -5663,10 +5693,10 @@
         <v>Boris</v>
       </c>
       <c r="BT79" s="1" t="str">
-        <v>7.171</v>
+        <v>7.207</v>
       </c>
       <c r="BU79" s="1">
-        <v>1064</v>
+        <v>1070</v>
       </c>
       <c r="BW79" s="1">
         <v>2</v>
@@ -5684,7 +5714,7 @@
         <v>Boris</v>
       </c>
       <c r="CC79" s="1">
-        <v>7.1705827067669174</v>
+        <v>7.2070093457943925</v>
       </c>
     </row>
     <row r="80" spans="1:81" x14ac:dyDescent="0.3">
@@ -5854,13 +5884,13 @@
         <v>5</v>
       </c>
       <c r="BS82" s="1" t="str">
-        <v>Tom</v>
+        <v>Samuel</v>
       </c>
       <c r="BT82" s="1" t="str">
-        <v>5.955</v>
+        <v>5.910</v>
       </c>
       <c r="BU82" s="1">
-        <v>247</v>
+        <v>211</v>
       </c>
       <c r="BW82" s="1">
         <v>5</v>
@@ -5875,10 +5905,10 @@
         <v>13</v>
       </c>
       <c r="CB82" s="1" t="str">
-        <v>Tom</v>
+        <v>Samuel</v>
       </c>
       <c r="CC82" s="1">
-        <v>5.9554655870445341</v>
+        <v>5.9099526066350707</v>
       </c>
     </row>
     <row r="83" spans="1:81" x14ac:dyDescent="0.3">
@@ -5920,13 +5950,13 @@
         <v>6</v>
       </c>
       <c r="BS83" s="1" t="str">
-        <v>Samuel</v>
+        <v>Joachim</v>
       </c>
       <c r="BT83" s="1" t="str">
-        <v>5.910</v>
+        <v>5.890</v>
       </c>
       <c r="BU83" s="1">
-        <v>211</v>
+        <v>109</v>
       </c>
       <c r="BW83" s="1">
         <v>6</v>
@@ -5941,10 +5971,10 @@
         <v>5</v>
       </c>
       <c r="CB83" s="1" t="str">
-        <v>Samuel</v>
+        <v>Joachim</v>
       </c>
       <c r="CC83" s="1">
-        <v>5.9099526066350707</v>
+        <v>5.8899082568807337</v>
       </c>
     </row>
     <row r="84" spans="1:81" x14ac:dyDescent="0.3">
@@ -5986,13 +6016,13 @@
         <v>7</v>
       </c>
       <c r="BS84" s="1" t="str">
-        <v>Joachim</v>
+        <v>Tom</v>
       </c>
       <c r="BT84" s="1" t="str">
-        <v>5.890</v>
+        <v>5.830</v>
       </c>
       <c r="BU84" s="1">
-        <v>109</v>
+        <v>253</v>
       </c>
       <c r="BW84" s="1">
         <v>7</v>
@@ -6007,10 +6037,10 @@
         <v>11</v>
       </c>
       <c r="CB84" s="1" t="str">
-        <v>Joachim</v>
+        <v>Tom</v>
       </c>
       <c r="CC84" s="1">
-        <v>5.8899082568807337</v>
+        <v>5.8300395256916993</v>
       </c>
     </row>
     <row r="85" spans="1:81" x14ac:dyDescent="0.3">
@@ -6162,16 +6192,16 @@
         <v>Jules</v>
       </c>
       <c r="BT86" s="1" t="str">
-        <v>5.625</v>
+        <v>5.487</v>
       </c>
       <c r="BU86" s="1">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="CB86" s="1" t="str">
         <v>Jules</v>
       </c>
       <c r="CC86" s="1">
-        <v>5.625</v>
+        <v>5.4869109947643979</v>
       </c>
     </row>
     <row r="87" spans="1:81" x14ac:dyDescent="0.3">
@@ -6352,16 +6382,16 @@
         <v>Damien</v>
       </c>
       <c r="BT88" s="1" t="str">
-        <v>5.338</v>
+        <v>5.371</v>
       </c>
       <c r="BU88" s="1">
-        <v>683</v>
+        <v>690</v>
       </c>
       <c r="CB88" s="1" t="str">
         <v>Damien</v>
       </c>
       <c r="CC88" s="1">
-        <v>5.3382137628111277</v>
+        <v>5.3710144927536234</v>
       </c>
     </row>
     <row r="89" spans="1:81" x14ac:dyDescent="0.3">
@@ -6536,7 +6566,7 @@
       </c>
       <c r="BP90" s="1">
         <f>AVERAGE(C1:BF1)</f>
-        <v>5.1282682820563474</v>
+        <v>5.1264999441839709</v>
       </c>
       <c r="BR90" s="1">
         <v>13</v>
@@ -6825,16 +6855,16 @@
         <v>Marie</v>
       </c>
       <c r="BT93" s="1" t="str">
-        <v>4.310</v>
+        <v>4.469</v>
       </c>
       <c r="BU93" s="1">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="CB93" s="1" t="str">
         <v>Marie</v>
       </c>
       <c r="CC93" s="1">
-        <v>4.3098290598290596</v>
+        <v>4.46875</v>
       </c>
     </row>
     <row r="94" spans="1:81" x14ac:dyDescent="0.3">
@@ -8338,10 +8368,10 @@
         <v>Boris</v>
       </c>
       <c r="CD111" s="1">
-        <v>7.1710000000000003</v>
+        <v>7.2069999999999999</v>
       </c>
       <c r="CE111" s="1">
-        <v>1064</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="112" spans="1:83" x14ac:dyDescent="0.3">
@@ -8594,13 +8624,13 @@
         <v>5</v>
       </c>
       <c r="CC114" s="1" t="str">
-        <v>Tom</v>
+        <v>Samuel</v>
       </c>
       <c r="CD114" s="1">
-        <v>5.9550000000000001</v>
+        <v>5.91</v>
       </c>
       <c r="CE114" s="1">
-        <v>247</v>
+        <v>211</v>
       </c>
     </row>
     <row r="115" spans="1:83" x14ac:dyDescent="0.3">
@@ -8679,13 +8709,13 @@
         <v>6</v>
       </c>
       <c r="CC115" s="1" t="str">
-        <v>Samuel</v>
+        <v>Joachim</v>
       </c>
       <c r="CD115" s="1">
-        <v>5.91</v>
+        <v>5.89</v>
       </c>
       <c r="CE115" s="1">
-        <v>211</v>
+        <v>109</v>
       </c>
     </row>
     <row r="116" spans="1:83" x14ac:dyDescent="0.3">
@@ -8764,13 +8794,13 @@
         <v>7</v>
       </c>
       <c r="CC116" s="1" t="str">
-        <v>Joachim</v>
+        <v>Tom</v>
       </c>
       <c r="CD116" s="1">
-        <v>5.89</v>
+        <v>5.83</v>
       </c>
       <c r="CE116" s="1">
-        <v>109</v>
+        <v>253</v>
       </c>
     </row>
     <row r="117" spans="1:83" x14ac:dyDescent="0.3">
@@ -8946,10 +8976,10 @@
         <v>Jules</v>
       </c>
       <c r="CD118" s="1">
-        <v>5.625</v>
+        <v>5.4870000000000001</v>
       </c>
       <c r="CE118" s="1">
-        <v>184</v>
+        <v>191</v>
       </c>
     </row>
     <row r="119" spans="1:83" x14ac:dyDescent="0.3">
@@ -9120,10 +9150,10 @@
         <v>Damien</v>
       </c>
       <c r="CD120" s="1">
-        <v>5.3380000000000001</v>
+        <v>5.3710000000000004</v>
       </c>
       <c r="CE120" s="1">
-        <v>683</v>
+        <v>690</v>
       </c>
     </row>
     <row r="121" spans="1:83" x14ac:dyDescent="0.3">
@@ -9545,10 +9575,10 @@
         <v>Marie</v>
       </c>
       <c r="CD125" s="1">
-        <v>4.3099999999999996</v>
+        <v>4.4690000000000003</v>
       </c>
       <c r="CE125" s="1">
-        <v>234</v>
+        <v>240</v>
       </c>
     </row>
     <row r="126" spans="1:83" x14ac:dyDescent="0.3">
@@ -10518,16 +10548,16 @@
         <v>Boris</v>
       </c>
       <c r="CC137" s="1">
-        <v>7.1705827067669174</v>
+        <v>7.2070093457943925</v>
       </c>
       <c r="CD137" s="1">
-        <v>1064</v>
+        <v>1070</v>
       </c>
       <c r="CG137" s="1" t="str">
         <v>Boris</v>
       </c>
       <c r="CH137" s="1">
-        <v>7.1705827067669174</v>
+        <v>7.2070093457943925</v>
       </c>
     </row>
     <row r="138" spans="1:86" x14ac:dyDescent="0.3">
@@ -10779,19 +10809,19 @@
       <c r="AX140" s="15"/>
       <c r="AY140" s="15"/>
       <c r="CB140" s="1" t="str">
-        <v>Tom</v>
+        <v>Samuel</v>
       </c>
       <c r="CC140" s="1">
-        <v>5.9554655870445341</v>
+        <v>5.9099526066350707</v>
       </c>
       <c r="CD140" s="1">
-        <v>247</v>
+        <v>211</v>
       </c>
       <c r="CG140" s="1" t="str">
-        <v>Tom</v>
+        <v>Samuel</v>
       </c>
       <c r="CH140" s="1">
-        <v>5.9554655870445341</v>
+        <v>5.9099526066350707</v>
       </c>
     </row>
     <row r="141" spans="1:86" x14ac:dyDescent="0.3">
@@ -10867,19 +10897,19 @@
       <c r="AX141" s="15"/>
       <c r="AY141" s="15"/>
       <c r="CB141" s="1" t="str">
-        <v>Samuel</v>
+        <v>Joachim</v>
       </c>
       <c r="CC141" s="1">
-        <v>5.9099526066350707</v>
+        <v>5.8899082568807337</v>
       </c>
       <c r="CD141" s="1">
-        <v>211</v>
+        <v>109</v>
       </c>
       <c r="CG141" s="1" t="str">
-        <v>Samuel</v>
+        <v>Joachim</v>
       </c>
       <c r="CH141" s="1">
-        <v>5.9099526066350707</v>
+        <v>5.8899082568807337</v>
       </c>
     </row>
     <row r="142" spans="1:86" x14ac:dyDescent="0.3">
@@ -10955,19 +10985,19 @@
       <c r="AX142" s="15"/>
       <c r="AY142" s="15"/>
       <c r="CB142" s="1" t="str">
-        <v>Joachim</v>
+        <v>Tom</v>
       </c>
       <c r="CC142" s="1">
-        <v>5.8899082568807337</v>
+        <v>5.8300395256916993</v>
       </c>
       <c r="CD142" s="1">
-        <v>109</v>
+        <v>253</v>
       </c>
       <c r="CG142" s="1" t="str">
-        <v>Joachim</v>
+        <v>Tom</v>
       </c>
       <c r="CH142" s="1">
-        <v>5.8899082568807337</v>
+        <v>5.8300395256916993</v>
       </c>
     </row>
     <row r="143" spans="1:86" x14ac:dyDescent="0.3">
@@ -11138,16 +11168,16 @@
         <v>Jules</v>
       </c>
       <c r="CC144" s="1">
-        <v>5.625</v>
+        <v>5.4869109947643979</v>
       </c>
       <c r="CD144" s="1">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="CG144" s="1" t="str">
         <v>Jules</v>
       </c>
       <c r="CH144" s="1">
-        <v>5.625</v>
+        <v>5.4869109947643979</v>
       </c>
     </row>
     <row r="145" spans="1:86" x14ac:dyDescent="0.3">
@@ -11208,16 +11238,16 @@
         <v>Damien</v>
       </c>
       <c r="CC146" s="1">
-        <v>5.3382137628111277</v>
+        <v>5.3710144927536234</v>
       </c>
       <c r="CD146" s="1">
-        <v>683</v>
+        <v>690</v>
       </c>
       <c r="CG146" s="1" t="str">
         <v>Damien</v>
       </c>
       <c r="CH146" s="1">
-        <v>5.3382137628111277</v>
+        <v>5.3710144927536234</v>
       </c>
     </row>
     <row r="147" spans="1:86" x14ac:dyDescent="0.3">
@@ -11349,10 +11379,10 @@
         <v>Marie</v>
       </c>
       <c r="CC149" s="1">
-        <v>4.3098290598290596</v>
+        <v>4.46875</v>
       </c>
       <c r="CD149" s="1">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="CG149" s="1" t="str">
         <v>Joey</v>
@@ -11452,7 +11482,7 @@
         <v>Marie</v>
       </c>
       <c r="CH151" s="1">
-        <v>4.3098290598290596</v>
+        <v>4.46875</v>
       </c>
     </row>
     <row r="152" spans="1:86" x14ac:dyDescent="0.3">
@@ -11882,10 +11912,10 @@
         <v>Boris</v>
       </c>
       <c r="C3" s="25" t="str">
-        <v>7.171</v>
+        <v>7.207</v>
       </c>
       <c r="D3" s="25">
-        <v>1064</v>
+        <v>1070</v>
       </c>
       <c r="F3" t="str">
         <v>entre 1 et 10</v>
@@ -11952,13 +11982,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="25" t="str">
-        <v>Tom</v>
+        <v>Samuel</v>
       </c>
       <c r="C6" s="25" t="str">
-        <v>5.955</v>
+        <v>5.910</v>
       </c>
       <c r="D6" s="25">
-        <v>247</v>
+        <v>211</v>
       </c>
       <c r="F6" t="str">
         <v>entre 50 et 100</v>
@@ -11976,13 +12006,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="25" t="str">
-        <v>Samuel</v>
+        <v>Joachim</v>
       </c>
       <c r="C7" s="25" t="str">
-        <v>5.910</v>
+        <v>5.890</v>
       </c>
       <c r="D7" s="25">
-        <v>211</v>
+        <v>109</v>
       </c>
       <c r="F7" t="str">
         <v>entre 100 et 250</v>
@@ -12000,13 +12030,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="25" t="str">
-        <v>Joachim</v>
+        <v>Tom</v>
       </c>
       <c r="C8" s="25" t="str">
-        <v>5.890</v>
+        <v>5.830</v>
       </c>
       <c r="D8" s="25">
-        <v>109</v>
+        <v>253</v>
       </c>
       <c r="F8" t="str">
         <v>entre 250 et 500</v>
@@ -12051,10 +12081,10 @@
         <v>Jules</v>
       </c>
       <c r="C10" s="25" t="str">
-        <v>5.625</v>
+        <v>5.487</v>
       </c>
       <c r="D10" s="25">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="F10" t="str">
         <v>plus de 1000</v>
@@ -12089,10 +12119,10 @@
         <v>Damien</v>
       </c>
       <c r="C12" s="25" t="str">
-        <v>5.338</v>
+        <v>5.371</v>
       </c>
       <c r="D12" s="25">
-        <v>683</v>
+        <v>690</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
@@ -12159,10 +12189,10 @@
         <v>Marie</v>
       </c>
       <c r="C17" s="25" t="str">
-        <v>4.310</v>
+        <v>4.469</v>
       </c>
       <c r="D17" s="25">
-        <v>234</v>
+        <v>240</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">

--- a/classement_whist_2023_2025.xlsx
+++ b/classement_whist_2023_2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a20b8382962b136a/Bureau/loisir/whist/projet_application_streamlit/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="87" documentId="14_{742E47F6-EB2A-4991-A9B8-D2681BB3B4C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD2DADF1-509D-4F3A-AAAB-8F69F3CA684E}"/>
+  <xr:revisionPtr revIDLastSave="68" documentId="14_{167F2DC3-291A-4B33-AB7D-1A6E034E4A5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DCAB125B-195D-4C4D-AC11-8D6BB835EA71}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="98">
   <si>
     <t>global</t>
   </si>
@@ -339,6 +339,18 @@
   <si>
     <t>ethan</t>
   </si>
+  <si>
+    <t>?</t>
+  </si>
+  <si>
+    <t>Romain</t>
+  </si>
+  <si>
+    <t>Sam</t>
+  </si>
+  <si>
+    <t>Vincent</t>
+  </si>
 </sst>
 </file>
 
@@ -610,7 +622,559 @@
     <cellStyle name="cf7" xfId="7" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="25">
+  <dxfs count="100">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF00B0F0"/>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF00B0F0"/>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC000"/>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF9900"/>
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB5E6A2"/>
+          <bgColor rgb="FFB5E6A2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF92D050"/>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF00B050"/>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF5050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF5050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF00B050"/>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF5050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF5050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF92D050"/>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB5E6A2"/>
+          <bgColor rgb="FFB5E6A2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF9900"/>
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC000"/>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF00B0F0"/>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF00B0F0"/>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF00B050"/>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF5050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF5050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF92D050"/>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB5E6A2"/>
+          <bgColor rgb="FFB5E6A2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF9900"/>
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC000"/>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF00B0F0"/>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF00B0F0"/>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1134,28 +1698,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:CH172"/>
+  <dimension ref="A1:CR172"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.5546875" style="1" customWidth="1"/>
     <col min="2" max="2" width="16.77734375" style="1" customWidth="1"/>
-    <col min="3" max="65" width="5.77734375" style="1" customWidth="1"/>
-    <col min="66" max="66" width="11.5546875" style="1"/>
-    <col min="67" max="68" width="20.6640625" style="1" customWidth="1"/>
-    <col min="69" max="69" width="11.5546875" style="1"/>
-    <col min="70" max="70" width="16.88671875" style="1" customWidth="1"/>
-    <col min="71" max="72" width="11.5546875" style="1"/>
-    <col min="73" max="73" width="20.33203125" style="1" customWidth="1"/>
-    <col min="74" max="74" width="23.6640625" style="1" customWidth="1"/>
-    <col min="75" max="75" width="21.109375" style="1" customWidth="1"/>
-    <col min="76" max="76" width="20.33203125" style="1" customWidth="1"/>
-    <col min="77" max="77" width="19.21875" style="1" customWidth="1"/>
-    <col min="78" max="78" width="20.77734375" style="1" customWidth="1"/>
-    <col min="79" max="79" width="15.77734375" style="1" customWidth="1"/>
-    <col min="80" max="16384" width="11.5546875" style="1"/>
+    <col min="3" max="75" width="5.77734375" style="1" customWidth="1"/>
+    <col min="76" max="76" width="11.5546875" style="1"/>
+    <col min="77" max="78" width="20.6640625" style="1" customWidth="1"/>
+    <col min="79" max="79" width="11.5546875" style="1"/>
+    <col min="80" max="80" width="16.88671875" style="1" customWidth="1"/>
+    <col min="81" max="82" width="11.5546875" style="1"/>
+    <col min="83" max="83" width="20.33203125" style="1" customWidth="1"/>
+    <col min="84" max="84" width="23.6640625" style="1" customWidth="1"/>
+    <col min="85" max="85" width="21.109375" style="1" customWidth="1"/>
+    <col min="86" max="86" width="20.33203125" style="1" customWidth="1"/>
+    <col min="87" max="87" width="19.21875" style="1" customWidth="1"/>
+    <col min="88" max="88" width="20.77734375" style="1" customWidth="1"/>
+    <col min="89" max="89" width="15.77734375" style="1" customWidth="1"/>
+    <col min="90" max="16384" width="11.5546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:69" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:79" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1171,14 +1735,14 @@
       </c>
       <c r="E1" s="1">
         <f t="shared" ref="E1" si="1">IF(F2&gt;19,E2/F2,"/")</f>
-        <v>5.7695961995249405</v>
+        <v>5.7018779342723001</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="G1" s="1">
         <f t="shared" ref="G1" si="2">IF(H2&gt;19,G2/H2,"/")</f>
-        <v>7.1647111913357397</v>
+        <v>7.1504385964912283</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>2</v>
@@ -1199,7 +1763,7 @@
       </c>
       <c r="M1" s="1">
         <f t="shared" ref="M1" si="5">IF(N2&gt;19,M2/N2,"/")</f>
-        <v>5.4482758620689653</v>
+        <v>5.4311050477489768</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>2</v>
@@ -1213,7 +1777,7 @@
       </c>
       <c r="Q1" s="1">
         <f t="shared" ref="Q1" si="7">IF(R2&gt;19,Q2/R2,"/")</f>
-        <v>6.5094936708860756</v>
+        <v>6.2550143266475642</v>
       </c>
       <c r="R1" s="1" t="s">
         <v>2</v>
@@ -1227,7 +1791,7 @@
       </c>
       <c r="U1" s="1">
         <f t="shared" ref="U1" si="9">IF(V2&gt;19,U2/V2,"/")</f>
-        <v>3.0112359550561796</v>
+        <v>3.129032258064516</v>
       </c>
       <c r="V1" s="1" t="s">
         <v>2</v>
@@ -1248,7 +1812,7 @@
       </c>
       <c r="AA1" s="1">
         <f t="shared" ref="AA1" si="12">IF(AB2&gt;19,AA2/AB2,"/")</f>
-        <v>4.469811320754717</v>
+        <v>4.6173469387755102</v>
       </c>
       <c r="AB1" s="1" t="s">
         <v>2</v>
@@ -1379,8 +1943,43 @@
       <c r="BL1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:69" x14ac:dyDescent="0.3">
+      <c r="BM1" s="1" t="str">
+        <f t="shared" ref="BM1" si="30">IF(BN2&gt;19,BM2/BN2,"/")</f>
+        <v>/</v>
+      </c>
+      <c r="BN1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="BO1" s="1" t="str">
+        <f t="shared" ref="BO1" si="31">IF(BP2&gt;19,BO2/BP2,"/")</f>
+        <v>/</v>
+      </c>
+      <c r="BP1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="BQ1" s="1">
+        <f t="shared" ref="BQ1" si="32">IF(BR2&gt;19,BQ2/BR2,"/")</f>
+        <v>6.75</v>
+      </c>
+      <c r="BR1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="BS1" s="1" t="str">
+        <f t="shared" ref="BS1" si="33">IF(BT2&gt;19,BS2/BT2,"/")</f>
+        <v>/</v>
+      </c>
+      <c r="BT1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="BU1" s="1" t="str">
+        <f t="shared" ref="BU1" si="34">IF(BV2&gt;19,BU2/BV2,"/")</f>
+        <v>/</v>
+      </c>
+      <c r="BV1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:79" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1393,247 +1992,287 @@
         <v>829</v>
       </c>
       <c r="E2" s="1">
-        <f t="shared" ref="E2:J2" si="30">E4+E6+E8</f>
+        <f t="shared" ref="E2:J2" si="35">E4+E6+E8</f>
         <v>2429</v>
       </c>
       <c r="F2" s="1">
-        <f t="shared" si="30"/>
-        <v>421</v>
+        <f t="shared" si="35"/>
+        <v>426</v>
       </c>
       <c r="G2" s="1">
-        <f t="shared" si="30"/>
-        <v>7938.5</v>
+        <f t="shared" si="35"/>
+        <v>8151.5</v>
       </c>
       <c r="H2" s="1">
-        <f t="shared" si="30"/>
-        <v>1108</v>
+        <f t="shared" si="35"/>
+        <v>1140</v>
       </c>
       <c r="I2" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="35"/>
         <v>1247</v>
       </c>
       <c r="J2" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" si="35"/>
         <v>211</v>
       </c>
       <c r="K2" s="1">
-        <f t="shared" ref="K2:AZ2" si="31">K4+K6+K8</f>
+        <f t="shared" ref="K2:AZ2" si="36">K4+K6+K8</f>
         <v>642</v>
       </c>
       <c r="L2" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="36"/>
         <v>109</v>
       </c>
       <c r="M2" s="1">
-        <f t="shared" si="31"/>
-        <v>3950</v>
+        <f t="shared" si="36"/>
+        <v>3981</v>
       </c>
       <c r="N2" s="1">
-        <f t="shared" si="31"/>
-        <v>725</v>
+        <f t="shared" si="36"/>
+        <v>733</v>
       </c>
       <c r="O2" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="36"/>
         <v>573</v>
       </c>
       <c r="P2" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="36"/>
         <v>79</v>
       </c>
       <c r="Q2" s="1">
-        <f t="shared" si="31"/>
-        <v>2057</v>
+        <f t="shared" si="36"/>
+        <v>2183</v>
       </c>
       <c r="R2" s="1">
-        <f t="shared" si="31"/>
-        <v>316</v>
+        <f t="shared" si="36"/>
+        <v>349</v>
       </c>
       <c r="S2" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="36"/>
         <v>1714</v>
       </c>
       <c r="T2" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="36"/>
         <v>286</v>
       </c>
       <c r="U2" s="1">
-        <f t="shared" si="31"/>
-        <v>536</v>
+        <f t="shared" si="36"/>
+        <v>582</v>
       </c>
       <c r="V2" s="1">
-        <f t="shared" si="31"/>
-        <v>178</v>
+        <f t="shared" si="36"/>
+        <v>186</v>
       </c>
       <c r="W2" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="36"/>
         <v>182</v>
       </c>
       <c r="X2" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="36"/>
         <v>75</v>
       </c>
       <c r="Y2" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="36"/>
         <v>154</v>
       </c>
       <c r="Z2" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="36"/>
         <v>32</v>
       </c>
       <c r="AA2" s="1">
-        <f t="shared" si="31"/>
-        <v>1184.5</v>
+        <f t="shared" si="36"/>
+        <v>1357.5</v>
       </c>
       <c r="AB2" s="1">
-        <f t="shared" si="31"/>
-        <v>265</v>
+        <f t="shared" si="36"/>
+        <v>294</v>
       </c>
       <c r="AC2" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="36"/>
         <v>1315</v>
       </c>
       <c r="AD2" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="36"/>
         <v>235</v>
       </c>
       <c r="AE2" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="36"/>
         <v>27</v>
       </c>
       <c r="AF2" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="36"/>
         <v>5</v>
       </c>
       <c r="AG2" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="36"/>
         <v>176</v>
       </c>
       <c r="AH2" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="36"/>
         <v>29</v>
       </c>
       <c r="AI2" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="36"/>
         <v>151</v>
       </c>
       <c r="AJ2" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="36"/>
         <v>51</v>
       </c>
       <c r="AK2" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="36"/>
         <v>121</v>
       </c>
       <c r="AL2" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="36"/>
         <v>17</v>
       </c>
       <c r="AM2" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="36"/>
         <v>387</v>
       </c>
       <c r="AN2" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="36"/>
         <v>86</v>
       </c>
       <c r="AO2" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="36"/>
         <v>-1</v>
       </c>
       <c r="AP2" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="36"/>
         <v>12</v>
       </c>
       <c r="AQ2" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="36"/>
         <v>381</v>
       </c>
       <c r="AR2" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="36"/>
         <v>93</v>
       </c>
       <c r="AS2" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="36"/>
         <v>8</v>
       </c>
       <c r="AT2" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="36"/>
         <v>11</v>
       </c>
       <c r="AU2" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="36"/>
         <v>34</v>
       </c>
       <c r="AV2" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="36"/>
         <v>4</v>
       </c>
       <c r="AW2" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="36"/>
         <v>14</v>
       </c>
       <c r="AX2" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="36"/>
         <v>5</v>
       </c>
       <c r="AY2" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="36"/>
         <v>43</v>
       </c>
       <c r="AZ2" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="36"/>
         <v>13</v>
       </c>
       <c r="BA2" s="1">
-        <f t="shared" ref="BA2:BD2" si="32">BA4+BA6+BA8</f>
+        <f t="shared" ref="BA2:BD2" si="37">BA4+BA6+BA8</f>
         <v>34</v>
       </c>
       <c r="BB2" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="37"/>
         <v>2</v>
       </c>
       <c r="BC2" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="37"/>
         <v>121</v>
       </c>
       <c r="BD2" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="37"/>
         <v>27</v>
       </c>
       <c r="BE2" s="1">
-        <f t="shared" ref="BE2:BF2" si="33">BE4+BE6+BE8</f>
+        <f t="shared" ref="BE2:BF2" si="38">BE4+BE6+BE8</f>
         <v>594</v>
       </c>
       <c r="BF2" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v>120</v>
       </c>
       <c r="BG2" s="1">
-        <f t="shared" ref="BG2:BL2" si="34">BG4+BG6+BG8</f>
+        <f t="shared" ref="BG2:BL2" si="39">BG4+BG6+BG8</f>
         <v>82</v>
       </c>
       <c r="BH2" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="39"/>
         <v>15</v>
       </c>
       <c r="BI2" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="39"/>
         <v>63</v>
       </c>
       <c r="BJ2" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="39"/>
         <v>16</v>
       </c>
       <c r="BK2" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="BL2" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="39"/>
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:69" x14ac:dyDescent="0.3">
+      <c r="BM2" s="1">
+        <f t="shared" ref="BM2:BV2" si="40">BM4+BM6+BM8</f>
+        <v>53</v>
+      </c>
+      <c r="BN2" s="1">
+        <f t="shared" si="40"/>
+        <v>5</v>
+      </c>
+      <c r="BO2" s="1">
+        <f t="shared" si="40"/>
+        <v>33</v>
+      </c>
+      <c r="BP2" s="1">
+        <f t="shared" si="40"/>
+        <v>4</v>
+      </c>
+      <c r="BQ2" s="1">
+        <f t="shared" si="40"/>
+        <v>135</v>
+      </c>
+      <c r="BR2" s="1">
+        <f t="shared" si="40"/>
+        <v>20</v>
+      </c>
+      <c r="BS2" s="1">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="BT2" s="1">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="BU2" s="1">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="BV2" s="1">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:79" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1648,223 +2287,258 @@
         <v>2</v>
       </c>
       <c r="E3" s="1">
-        <f t="shared" ref="E3" si="35">E4/F4</f>
+        <f t="shared" ref="E3" si="41">E4/F4</f>
         <v>3.3414634146341462</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="G3" s="1">
-        <f t="shared" ref="G3" si="36">G4/H4</f>
+        <f t="shared" ref="G3" si="42">G4/H4</f>
         <v>7.2666666666666666</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="I3" s="1">
-        <f t="shared" ref="I3" si="37">I4/J4</f>
+        <f t="shared" ref="I3" si="43">I4/J4</f>
         <v>7.78125</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="K3" s="1">
-        <f t="shared" ref="K3" si="38">K4/L4</f>
+        <f t="shared" ref="K3" si="44">K4/L4</f>
         <v>5.5</v>
       </c>
       <c r="L3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="M3" s="1">
-        <f t="shared" ref="M3" si="39">M4/N4</f>
+        <f t="shared" ref="M3" si="45">M4/N4</f>
         <v>5.9268292682926829</v>
       </c>
       <c r="N3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="O3" s="1">
-        <f t="shared" ref="O3" si="40">O4/P4</f>
+        <f t="shared" ref="O3" si="46">O4/P4</f>
         <v>6</v>
       </c>
       <c r="P3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="Q3" s="1" t="e">
-        <f t="shared" ref="Q3" si="41">Q4/R4</f>
+        <f t="shared" ref="Q3" si="47">Q4/R4</f>
         <v>#DIV/0!</v>
       </c>
       <c r="R3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="S3" s="1" t="e">
-        <f t="shared" ref="S3" si="42">S4/T4</f>
+        <f t="shared" ref="S3" si="48">S4/T4</f>
         <v>#DIV/0!</v>
       </c>
       <c r="T3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="U3" s="1">
-        <f t="shared" ref="U3" si="43">U4/V4</f>
+        <f t="shared" ref="U3" si="49">U4/V4</f>
         <v>5.8181818181818183</v>
       </c>
       <c r="V3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="W3" s="1">
-        <f t="shared" ref="W3" si="44">W4/X4</f>
+        <f t="shared" ref="W3" si="50">W4/X4</f>
         <v>6.1111111111111107</v>
       </c>
       <c r="X3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="Y3" s="1">
-        <f t="shared" ref="Y3" si="45">Y4/Z4</f>
+        <f t="shared" ref="Y3" si="51">Y4/Z4</f>
         <v>4.8125</v>
       </c>
       <c r="Z3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="AA3" s="1">
-        <f t="shared" ref="AA3" si="46">AA4/AB4</f>
+        <f t="shared" ref="AA3" si="52">AA4/AB4</f>
         <v>4.2380952380952381</v>
       </c>
       <c r="AB3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="AC3" s="1" t="e">
-        <f t="shared" ref="AC3" si="47">AC4/AD4</f>
+        <f t="shared" ref="AC3" si="53">AC4/AD4</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AD3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="AE3" s="1" t="e">
-        <f t="shared" ref="AE3" si="48">AE4/AF4</f>
+        <f t="shared" ref="AE3" si="54">AE4/AF4</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AF3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="AG3" s="1" t="e">
-        <f t="shared" ref="AG3" si="49">AG4/AH4</f>
+        <f t="shared" ref="AG3" si="55">AG4/AH4</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AH3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="AI3" s="1" t="e">
-        <f t="shared" ref="AI3" si="50">AI4/AJ4</f>
+        <f t="shared" ref="AI3" si="56">AI4/AJ4</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AJ3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="AK3" s="1" t="e">
-        <f t="shared" ref="AK3" si="51">AK4/AL4</f>
+        <f t="shared" ref="AK3" si="57">AK4/AL4</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AL3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="AM3" s="1" t="e">
-        <f t="shared" ref="AM3" si="52">AM4/AN4</f>
+        <f t="shared" ref="AM3" si="58">AM4/AN4</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AN3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="AO3" s="1" t="e">
-        <f t="shared" ref="AO3" si="53">AO4/AP4</f>
+        <f t="shared" ref="AO3" si="59">AO4/AP4</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AP3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="AQ3" s="1" t="e">
-        <f t="shared" ref="AQ3" si="54">AQ4/AR4</f>
+        <f t="shared" ref="AQ3" si="60">AQ4/AR4</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AR3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="AS3" s="1" t="e">
-        <f t="shared" ref="AS3" si="55">AS4/AT4</f>
+        <f t="shared" ref="AS3" si="61">AS4/AT4</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AT3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="AU3" s="1" t="e">
-        <f t="shared" ref="AU3" si="56">AU4/AV4</f>
+        <f t="shared" ref="AU3" si="62">AU4/AV4</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AV3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="AW3" s="1" t="e">
-        <f t="shared" ref="AW3" si="57">AW4/AX4</f>
+        <f t="shared" ref="AW3" si="63">AW4/AX4</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AX3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="AY3" s="1" t="e">
-        <f t="shared" ref="AY3" si="58">AY4/AZ4</f>
+        <f t="shared" ref="AY3" si="64">AY4/AZ4</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AZ3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="BA3" s="1" t="e">
-        <f t="shared" ref="BA3" si="59">BA4/BB4</f>
+        <f t="shared" ref="BA3" si="65">BA4/BB4</f>
         <v>#DIV/0!</v>
       </c>
       <c r="BB3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="BC3" s="1" t="e">
-        <f t="shared" ref="BC3" si="60">BC4/BD4</f>
+        <f t="shared" ref="BC3" si="66">BC4/BD4</f>
         <v>#DIV/0!</v>
       </c>
       <c r="BD3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="BE3" s="1" t="e">
-        <f t="shared" ref="BE3" si="61">BE4/BF4</f>
+        <f t="shared" ref="BE3" si="67">BE4/BF4</f>
         <v>#DIV/0!</v>
       </c>
       <c r="BF3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="BG3" s="1" t="e">
-        <f t="shared" ref="BG3" si="62">BG4/BH4</f>
+        <f t="shared" ref="BG3" si="68">BG4/BH4</f>
         <v>#DIV/0!</v>
       </c>
       <c r="BH3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="BI3" s="1" t="e">
-        <f t="shared" ref="BI3" si="63">BI4/BJ4</f>
+        <f t="shared" ref="BI3" si="69">BI4/BJ4</f>
         <v>#DIV/0!</v>
       </c>
       <c r="BJ3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="BK3" s="1" t="e">
-        <f t="shared" ref="BK3" si="64">BK4/BL4</f>
+        <f t="shared" ref="BK3" si="70">BK4/BL4</f>
         <v>#DIV/0!</v>
       </c>
       <c r="BL3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="BO3" s="1" t="s">
+      <c r="BM3" s="1" t="e">
+        <f t="shared" ref="BM3" si="71">BM4/BN4</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BN3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="BO3" s="1" t="e">
+        <f t="shared" ref="BO3" si="72">BO4/BP4</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BP3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="BQ3" s="1" t="e">
+        <f t="shared" ref="BQ3" si="73">BQ4/BR4</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BR3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="BS3" s="1" t="e">
+        <f t="shared" ref="BS3" si="74">BS4/BT4</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BT3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="BU3" s="1" t="e">
+        <f t="shared" ref="BU3" si="75">BU4/BV4</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BV3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="BY3" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="BQ3" s="1" t="s">
+      <c r="CA3" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:69" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:79" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
         <v>3</v>
       </c>
@@ -1877,255 +2551,295 @@
         <v>135</v>
       </c>
       <c r="E4" s="1">
-        <f t="shared" ref="E4:J4" si="65">SUM(E161:E172)</f>
+        <f t="shared" ref="E4:J4" si="76">SUM(E161:E172)</f>
         <v>274</v>
       </c>
       <c r="F4" s="1">
-        <f t="shared" si="65"/>
+        <f t="shared" si="76"/>
         <v>82</v>
       </c>
       <c r="G4" s="1">
-        <f t="shared" si="65"/>
+        <f t="shared" si="76"/>
         <v>981</v>
       </c>
       <c r="H4" s="1">
-        <f t="shared" si="65"/>
+        <f t="shared" si="76"/>
         <v>135</v>
       </c>
       <c r="I4" s="1">
-        <f t="shared" si="65"/>
+        <f t="shared" si="76"/>
         <v>498</v>
       </c>
       <c r="J4" s="1">
-        <f t="shared" si="65"/>
+        <f t="shared" si="76"/>
         <v>64</v>
       </c>
       <c r="K4" s="1">
-        <f t="shared" ref="K4:AZ4" si="66">SUM(K161:K172)</f>
+        <f t="shared" ref="K4:AZ4" si="77">SUM(K161:K172)</f>
         <v>44</v>
       </c>
       <c r="L4" s="1">
-        <f t="shared" si="66"/>
+        <f t="shared" si="77"/>
         <v>8</v>
       </c>
       <c r="M4" s="1">
-        <f t="shared" si="66"/>
+        <f t="shared" si="77"/>
         <v>243</v>
       </c>
       <c r="N4" s="1">
-        <f t="shared" si="66"/>
+        <f t="shared" si="77"/>
         <v>41</v>
       </c>
       <c r="O4" s="1">
-        <f t="shared" si="66"/>
+        <f t="shared" si="77"/>
         <v>12</v>
       </c>
       <c r="P4" s="1">
-        <f t="shared" si="66"/>
+        <f t="shared" si="77"/>
         <v>2</v>
       </c>
       <c r="Q4" s="1">
-        <f t="shared" si="66"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="R4" s="1">
-        <f t="shared" si="66"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="S4" s="1">
-        <f t="shared" si="66"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="T4" s="1">
-        <f t="shared" si="66"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="U4" s="1">
-        <f t="shared" si="66"/>
+        <f t="shared" si="77"/>
         <v>64</v>
       </c>
       <c r="V4" s="1">
-        <f t="shared" si="66"/>
+        <f t="shared" si="77"/>
         <v>11</v>
       </c>
       <c r="W4" s="1">
-        <f t="shared" si="66"/>
+        <f t="shared" si="77"/>
         <v>55</v>
       </c>
       <c r="X4" s="1">
-        <f t="shared" si="66"/>
+        <f t="shared" si="77"/>
         <v>9</v>
       </c>
       <c r="Y4" s="1">
-        <f t="shared" si="66"/>
+        <f t="shared" si="77"/>
         <v>154</v>
       </c>
       <c r="Z4" s="1">
-        <f t="shared" si="66"/>
+        <f t="shared" si="77"/>
         <v>32</v>
       </c>
       <c r="AA4" s="1">
-        <f t="shared" si="66"/>
+        <f t="shared" si="77"/>
         <v>89</v>
       </c>
       <c r="AB4" s="1">
-        <f t="shared" si="66"/>
+        <f t="shared" si="77"/>
         <v>21</v>
       </c>
       <c r="AC4" s="1">
-        <f t="shared" si="66"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="AD4" s="1">
-        <f t="shared" si="66"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="AE4" s="1">
-        <f t="shared" si="66"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="AF4" s="1">
-        <f t="shared" si="66"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="AG4" s="1">
-        <f t="shared" si="66"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="AH4" s="1">
-        <f t="shared" si="66"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="AI4" s="1">
-        <f t="shared" si="66"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="AJ4" s="1">
-        <f t="shared" si="66"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="AK4" s="1">
-        <f t="shared" si="66"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="AL4" s="1">
-        <f t="shared" si="66"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="AM4" s="1">
-        <f t="shared" si="66"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="AN4" s="1">
-        <f t="shared" si="66"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="AO4" s="1">
-        <f t="shared" si="66"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="AP4" s="1">
-        <f t="shared" si="66"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="AQ4" s="1">
-        <f t="shared" si="66"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="AR4" s="1">
-        <f t="shared" si="66"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="AS4" s="1">
-        <f t="shared" si="66"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="AT4" s="1">
-        <f t="shared" si="66"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="AU4" s="1">
-        <f t="shared" si="66"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="AV4" s="1">
-        <f t="shared" si="66"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="AW4" s="1">
-        <f t="shared" si="66"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="AX4" s="1">
-        <f t="shared" si="66"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="AY4" s="1">
-        <f t="shared" si="66"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="AZ4" s="1">
-        <f t="shared" si="66"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="BA4" s="1">
-        <f t="shared" ref="BA4:BD4" si="67">SUM(BA161:BA172)</f>
+        <f t="shared" ref="BA4:BD4" si="78">SUM(BA161:BA172)</f>
         <v>0</v>
       </c>
       <c r="BB4" s="1">
-        <f t="shared" si="67"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="BC4" s="1">
-        <f t="shared" si="67"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="BD4" s="1">
-        <f t="shared" si="67"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="BE4" s="1">
-        <f t="shared" ref="BE4:BF4" si="68">SUM(BE161:BE172)</f>
+        <f t="shared" ref="BE4:BF4" si="79">SUM(BE161:BE172)</f>
         <v>0</v>
       </c>
       <c r="BF4" s="1">
-        <f t="shared" si="68"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="BG4" s="1">
-        <f t="shared" ref="BG4:BL4" si="69">SUM(BG161:BG172)</f>
+        <f t="shared" ref="BG4:BL4" si="80">SUM(BG161:BG172)</f>
         <v>0</v>
       </c>
       <c r="BH4" s="1">
-        <f t="shared" si="69"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="BI4" s="1">
-        <f t="shared" si="69"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="BJ4" s="1">
-        <f t="shared" si="69"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="BK4" s="1">
-        <f t="shared" si="69"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="BL4" s="1">
-        <f t="shared" si="69"/>
-        <v>0</v>
-      </c>
-      <c r="BP4" s="1" t="b">
+        <f t="shared" si="80"/>
+        <v>0</v>
+      </c>
+      <c r="BM4" s="1">
+        <f t="shared" ref="BM4:BV4" si="81">SUM(BM161:BM172)</f>
+        <v>0</v>
+      </c>
+      <c r="BN4" s="1">
+        <f t="shared" si="81"/>
+        <v>0</v>
+      </c>
+      <c r="BO4" s="1">
+        <f t="shared" si="81"/>
+        <v>0</v>
+      </c>
+      <c r="BP4" s="1">
+        <f t="shared" si="81"/>
+        <v>0</v>
+      </c>
+      <c r="BQ4" s="1">
+        <f t="shared" si="81"/>
+        <v>0</v>
+      </c>
+      <c r="BR4" s="1">
+        <f t="shared" si="81"/>
+        <v>0</v>
+      </c>
+      <c r="BS4" s="1">
+        <f t="shared" si="81"/>
+        <v>0</v>
+      </c>
+      <c r="BT4" s="1">
+        <f t="shared" si="81"/>
+        <v>0</v>
+      </c>
+      <c r="BU4" s="1">
+        <f t="shared" si="81"/>
+        <v>0</v>
+      </c>
+      <c r="BV4" s="1">
+        <f t="shared" si="81"/>
+        <v>0</v>
+      </c>
+      <c r="BZ4" s="1" t="b">
         <f>NOT(OR("/",AVERAGE($C$1:$AL$1)&gt;AC$1,SMALL($C$1:$AL$1,1)=AC$1,SMALL($C$1:$AL$1,2)=AC$1,SMALL($C$1:$AL$1,3)=AC$1,LARGE($C$1:$AL$1,1)=AC$1,LARGE($C$1:$AL$1,2)=AC$1,LARGE($C$1:$AL$1,3)=AC$1))</f>
         <v>1</v>
       </c>
-      <c r="BQ4" s="1" t="e">
+      <c r="CA4" s="1" t="e">
         <f>$C$10:$C$172,$E$10:$E$172,$G$10:$G$172,$I$10:$I$172,$K$10:$K$172,$M$10:$M$172,$O$10:$O$172,$Q$10:$Q$172,$S$10:$S$172,$U$10:$U$172,$W$10:$W$172,$Y$10:$Y$172,$AA$10:$AA$172,$AC$10:$AC$172,$AE$10:$AE$172,$AG$10:$AG$172,$AI$10:$AI$172,$AK$10:$AK$172,$AM$10:$AM$172,$AO$10:$AO$172,$AQ$10:$AQ$172,$AS$10:$AS$172,$AU$10:$AU$172,$AW$10:$AW$172,$AY$10:$AY$172,$BA$10:$BA$172,$BC$10:$BC$172,$BE$10:$BE$172</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="5" spans="1:69" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:79" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -2140,221 +2854,256 @@
         <v>2</v>
       </c>
       <c r="E5" s="1">
-        <f t="shared" ref="E5" si="70">E6/F6</f>
+        <f t="shared" ref="E5" si="82">E6/F6</f>
         <v>6.131455399061033</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>2</v>
       </c>
       <c r="G5" s="1">
-        <f t="shared" ref="G5" si="71">G6/H6</f>
+        <f t="shared" ref="G5" si="83">G6/H6</f>
         <v>6.8512820512820509</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>2</v>
       </c>
       <c r="I5" s="1">
-        <f t="shared" ref="I5" si="72">I6/J6</f>
+        <f t="shared" ref="I5" si="84">I6/J6</f>
         <v>6.5287356321839081</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>2</v>
       </c>
       <c r="K5" s="1">
-        <f t="shared" ref="K5" si="73">K6/L6</f>
+        <f t="shared" ref="K5" si="85">K6/L6</f>
         <v>6.6756756756756754</v>
       </c>
       <c r="L5" s="1" t="s">
         <v>2</v>
       </c>
       <c r="M5" s="1">
-        <f t="shared" ref="M5" si="74">M6/N6</f>
+        <f t="shared" ref="M5" si="86">M6/N6</f>
         <v>3.8979591836734695</v>
       </c>
       <c r="N5" s="1" t="s">
         <v>2</v>
       </c>
       <c r="O5" s="1">
-        <f t="shared" ref="O5" si="75">O6/P6</f>
+        <f t="shared" ref="O5" si="87">O6/P6</f>
         <v>5.85</v>
       </c>
       <c r="P5" s="1" t="s">
         <v>2</v>
       </c>
       <c r="Q5" s="1">
-        <f t="shared" ref="Q5" si="76">Q6/R6</f>
+        <f t="shared" ref="Q5" si="88">Q6/R6</f>
         <v>5.8133333333333335</v>
       </c>
       <c r="R5" s="1" t="s">
         <v>2</v>
       </c>
       <c r="S5" s="1">
-        <f t="shared" ref="S5" si="77">S6/T6</f>
+        <f t="shared" ref="S5" si="89">S6/T6</f>
         <v>7.1037735849056602</v>
       </c>
       <c r="T5" s="1" t="s">
         <v>2</v>
       </c>
       <c r="U5" s="1">
-        <f t="shared" ref="U5" si="78">U6/V6</f>
+        <f t="shared" ref="U5" si="90">U6/V6</f>
         <v>2.096774193548387</v>
       </c>
       <c r="V5" s="1" t="s">
         <v>2</v>
       </c>
       <c r="W5" s="1">
-        <f t="shared" ref="W5" si="79">W6/X6</f>
+        <f t="shared" ref="W5" si="91">W6/X6</f>
         <v>1.8214285714285714</v>
       </c>
       <c r="X5" s="1" t="s">
         <v>2</v>
       </c>
       <c r="Y5" s="1" t="e">
-        <f t="shared" ref="Y5" si="80">Y6/Z6</f>
+        <f t="shared" ref="Y5" si="92">Y6/Z6</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Z5" s="1" t="s">
         <v>2</v>
       </c>
       <c r="AA5" s="1">
-        <f t="shared" ref="AA5" si="81">AA6/AB6</f>
+        <f t="shared" ref="AA5" si="93">AA6/AB6</f>
         <v>2.0249999999999999</v>
       </c>
       <c r="AB5" s="1" t="s">
         <v>2</v>
       </c>
       <c r="AC5" s="1">
-        <f t="shared" ref="AC5" si="82">AC6/AD6</f>
+        <f t="shared" ref="AC5" si="94">AC6/AD6</f>
         <v>1.6</v>
       </c>
       <c r="AD5" s="1" t="s">
         <v>2</v>
       </c>
       <c r="AE5" s="1">
-        <f t="shared" ref="AE5" si="83">AE6/AF6</f>
+        <f t="shared" ref="AE5" si="95">AE6/AF6</f>
         <v>9</v>
       </c>
       <c r="AF5" s="1" t="s">
         <v>2</v>
       </c>
       <c r="AG5" s="1">
-        <f t="shared" ref="AG5" si="84">AG6/AH6</f>
+        <f t="shared" ref="AG5" si="96">AG6/AH6</f>
         <v>6.068965517241379</v>
       </c>
       <c r="AH5" s="1" t="s">
         <v>2</v>
       </c>
       <c r="AI5" s="1" t="e">
-        <f t="shared" ref="AI5" si="85">AI6/AJ6</f>
+        <f t="shared" ref="AI5" si="97">AI6/AJ6</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AJ5" s="1" t="s">
         <v>2</v>
       </c>
       <c r="AK5" s="1">
-        <f t="shared" ref="AK5" si="86">AK6/AL6</f>
+        <f t="shared" ref="AK5" si="98">AK6/AL6</f>
         <v>7.117647058823529</v>
       </c>
       <c r="AL5" s="1" t="s">
         <v>2</v>
       </c>
       <c r="AM5" s="1" t="e">
-        <f t="shared" ref="AM5" si="87">AM6/AN6</f>
+        <f t="shared" ref="AM5" si="99">AM6/AN6</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AN5" s="1" t="s">
         <v>2</v>
       </c>
       <c r="AO5" s="1" t="e">
-        <f t="shared" ref="AO5" si="88">AO6/AP6</f>
+        <f t="shared" ref="AO5" si="100">AO6/AP6</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AP5" s="1" t="s">
         <v>2</v>
       </c>
       <c r="AQ5" s="1">
-        <f t="shared" ref="AQ5" si="89">AQ6/AR6</f>
+        <f t="shared" ref="AQ5" si="101">AQ6/AR6</f>
         <v>3.75</v>
       </c>
       <c r="AR5" s="1" t="s">
         <v>2</v>
       </c>
       <c r="AS5" s="1" t="e">
-        <f t="shared" ref="AS5" si="90">AS6/AT6</f>
+        <f t="shared" ref="AS5" si="102">AS6/AT6</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AT5" s="1" t="s">
         <v>2</v>
       </c>
       <c r="AU5" s="1" t="e">
-        <f t="shared" ref="AU5" si="91">AU6/AV6</f>
+        <f t="shared" ref="AU5" si="103">AU6/AV6</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AV5" s="1" t="s">
         <v>2</v>
       </c>
       <c r="AW5" s="1" t="e">
-        <f t="shared" ref="AW5" si="92">AW6/AX6</f>
+        <f t="shared" ref="AW5" si="104">AW6/AX6</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AX5" s="1" t="s">
         <v>2</v>
       </c>
       <c r="AY5" s="1">
-        <f t="shared" ref="AY5" si="93">AY6/AZ6</f>
+        <f t="shared" ref="AY5" si="105">AY6/AZ6</f>
         <v>2.75</v>
       </c>
       <c r="AZ5" s="1" t="s">
         <v>2</v>
       </c>
       <c r="BA5" s="1" t="e">
-        <f t="shared" ref="BA5" si="94">BA6/BB6</f>
+        <f t="shared" ref="BA5" si="106">BA6/BB6</f>
         <v>#DIV/0!</v>
       </c>
       <c r="BB5" s="1" t="s">
         <v>2</v>
       </c>
       <c r="BC5" s="1" t="e">
-        <f t="shared" ref="BC5" si="95">BC6/BD6</f>
+        <f t="shared" ref="BC5" si="107">BC6/BD6</f>
         <v>#DIV/0!</v>
       </c>
       <c r="BD5" s="1" t="s">
         <v>2</v>
       </c>
       <c r="BE5" s="1" t="e">
-        <f t="shared" ref="BE5" si="96">BE6/BF6</f>
+        <f t="shared" ref="BE5" si="108">BE6/BF6</f>
         <v>#DIV/0!</v>
       </c>
       <c r="BF5" s="1" t="s">
         <v>2</v>
       </c>
       <c r="BG5" s="1" t="e">
-        <f t="shared" ref="BG5" si="97">BG6/BH6</f>
+        <f t="shared" ref="BG5" si="109">BG6/BH6</f>
         <v>#DIV/0!</v>
       </c>
       <c r="BH5" s="1" t="s">
         <v>2</v>
       </c>
       <c r="BI5" s="1" t="e">
-        <f t="shared" ref="BI5" si="98">BI6/BJ6</f>
+        <f t="shared" ref="BI5" si="110">BI6/BJ6</f>
         <v>#DIV/0!</v>
       </c>
       <c r="BJ5" s="1" t="s">
         <v>2</v>
       </c>
       <c r="BK5" s="1" t="e">
-        <f t="shared" ref="BK5" si="99">BK6/BL6</f>
+        <f t="shared" ref="BK5" si="111">BK6/BL6</f>
         <v>#DIV/0!</v>
       </c>
       <c r="BL5" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="BM5" s="1" t="e">
+        <f t="shared" ref="BM5" si="112">BM6/BN6</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BN5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="BO5" s="1" t="e">
+        <f t="shared" ref="BO5" si="113">BO6/BP6</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BP5" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="BQ5" s="1" t="e">
+        <f t="shared" ref="BQ5" si="114">BQ6/BR6</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BR5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="BS5" s="1" t="e">
+        <f t="shared" ref="BS5" si="115">BS6/BT6</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BT5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="BU5" s="1" t="e">
+        <f t="shared" ref="BU5" si="116">BU6/BV6</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BV5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="CA5" s="1" t="e">
         <f>$D$10:$D$172,$F$10:$F$172,$H$10:$H$172,$J$10:$J$172,$L$10:$L$172,$N$10:$N$172,$P$10:$P$172,$R$10:$R$172,$T$10:$T$172,$V$10:$V$172,$X$10:$X$172,$Z$10:$Z$172,$AB$10:$AB$172,$AD$10:$AD$172,$AF$10:$AF$172,$AH$10:$AH$172,$AJ$10:$AJ$172,$AL$10:$AL$172,$AN$10:$AN$172,$AP$10:$AP$172,$AR$10:$AR$172,$AT$10:$AT$172,$AV$10:$AV$172,$AX$10:$AX$172,$AZ$10:$AZ$172,$BB$10:$BB$172,$BD$10:$BD$172,$BF$10:$BF$172</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="6" spans="1:69" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:79" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
         <v>3</v>
       </c>
@@ -2367,247 +3116,287 @@
         <v>370</v>
       </c>
       <c r="E6" s="1">
-        <f t="shared" ref="E6:J6" si="100">SUM(E117:E159)</f>
+        <f t="shared" ref="E6:J6" si="117">SUM(E117:E159)</f>
         <v>1306</v>
       </c>
       <c r="F6" s="1">
-        <f t="shared" si="100"/>
+        <f t="shared" si="117"/>
         <v>213</v>
       </c>
       <c r="G6" s="1">
-        <f t="shared" si="100"/>
+        <f t="shared" si="117"/>
         <v>2672</v>
       </c>
       <c r="H6" s="1">
-        <f t="shared" si="100"/>
+        <f t="shared" si="117"/>
         <v>390</v>
       </c>
       <c r="I6" s="1">
-        <f t="shared" si="100"/>
+        <f t="shared" si="117"/>
         <v>568</v>
       </c>
       <c r="J6" s="1">
-        <f t="shared" si="100"/>
+        <f t="shared" si="117"/>
         <v>87</v>
       </c>
       <c r="K6" s="1">
-        <f t="shared" ref="K6:AZ6" si="101">SUM(K117:K159)</f>
+        <f t="shared" ref="K6:AZ6" si="118">SUM(K117:K159)</f>
         <v>494</v>
       </c>
       <c r="L6" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="118"/>
         <v>74</v>
       </c>
       <c r="M6" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="118"/>
         <v>573</v>
       </c>
       <c r="N6" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="118"/>
         <v>147</v>
       </c>
       <c r="O6" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="118"/>
         <v>117</v>
       </c>
       <c r="P6" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="118"/>
         <v>20</v>
       </c>
       <c r="Q6" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="118"/>
         <v>436</v>
       </c>
       <c r="R6" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="118"/>
         <v>75</v>
       </c>
       <c r="S6" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="118"/>
         <v>753</v>
       </c>
       <c r="T6" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="118"/>
         <v>106</v>
       </c>
       <c r="U6" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="118"/>
         <v>65</v>
       </c>
       <c r="V6" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="118"/>
         <v>31</v>
       </c>
       <c r="W6" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="118"/>
         <v>51</v>
       </c>
       <c r="X6" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="118"/>
         <v>28</v>
       </c>
       <c r="Y6" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="118"/>
         <v>0</v>
       </c>
       <c r="Z6" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="118"/>
         <v>0</v>
       </c>
       <c r="AA6" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="118"/>
         <v>81</v>
       </c>
       <c r="AB6" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="118"/>
         <v>40</v>
       </c>
       <c r="AC6" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="118"/>
         <v>16</v>
       </c>
       <c r="AD6" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="118"/>
         <v>10</v>
       </c>
       <c r="AE6" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="118"/>
         <v>27</v>
       </c>
       <c r="AF6" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="118"/>
         <v>3</v>
       </c>
       <c r="AG6" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="118"/>
         <v>176</v>
       </c>
       <c r="AH6" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="118"/>
         <v>29</v>
       </c>
       <c r="AI6" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="118"/>
         <v>0</v>
       </c>
       <c r="AJ6" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="118"/>
         <v>0</v>
       </c>
       <c r="AK6" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="118"/>
         <v>121</v>
       </c>
       <c r="AL6" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="118"/>
         <v>17</v>
       </c>
       <c r="AM6" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="118"/>
         <v>0</v>
       </c>
       <c r="AN6" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="118"/>
         <v>0</v>
       </c>
       <c r="AO6" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="118"/>
         <v>0</v>
       </c>
       <c r="AP6" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="118"/>
         <v>0</v>
       </c>
       <c r="AQ6" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="118"/>
         <v>60</v>
       </c>
       <c r="AR6" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="118"/>
         <v>16</v>
       </c>
       <c r="AS6" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="118"/>
         <v>0</v>
       </c>
       <c r="AT6" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="118"/>
         <v>0</v>
       </c>
       <c r="AU6" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="118"/>
         <v>0</v>
       </c>
       <c r="AV6" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="118"/>
         <v>0</v>
       </c>
       <c r="AW6" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="118"/>
         <v>0</v>
       </c>
       <c r="AX6" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="118"/>
         <v>0</v>
       </c>
       <c r="AY6" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="118"/>
         <v>22</v>
       </c>
       <c r="AZ6" s="1">
-        <f t="shared" si="101"/>
+        <f t="shared" si="118"/>
         <v>8</v>
       </c>
       <c r="BA6" s="1">
-        <f t="shared" ref="BA6:BD6" si="102">SUM(BA117:BA159)</f>
+        <f t="shared" ref="BA6:BD6" si="119">SUM(BA117:BA159)</f>
         <v>0</v>
       </c>
       <c r="BB6" s="1">
-        <f t="shared" si="102"/>
+        <f t="shared" si="119"/>
         <v>0</v>
       </c>
       <c r="BC6" s="1">
-        <f t="shared" si="102"/>
+        <f t="shared" si="119"/>
         <v>0</v>
       </c>
       <c r="BD6" s="1">
-        <f t="shared" si="102"/>
+        <f t="shared" si="119"/>
         <v>0</v>
       </c>
       <c r="BE6" s="1">
-        <f t="shared" ref="BE6:BF6" si="103">SUM(BE117:BE159)</f>
+        <f t="shared" ref="BE6:BF6" si="120">SUM(BE117:BE159)</f>
         <v>0</v>
       </c>
       <c r="BF6" s="1">
-        <f t="shared" si="103"/>
+        <f t="shared" si="120"/>
         <v>0</v>
       </c>
       <c r="BG6" s="1">
-        <f t="shared" ref="BG6:BL6" si="104">SUM(BG117:BG159)</f>
+        <f t="shared" ref="BG6:BL6" si="121">SUM(BG117:BG159)</f>
         <v>0</v>
       </c>
       <c r="BH6" s="1">
-        <f t="shared" si="104"/>
+        <f t="shared" si="121"/>
         <v>0</v>
       </c>
       <c r="BI6" s="1">
-        <f t="shared" si="104"/>
+        <f t="shared" si="121"/>
         <v>0</v>
       </c>
       <c r="BJ6" s="1">
-        <f t="shared" si="104"/>
+        <f t="shared" si="121"/>
         <v>0</v>
       </c>
       <c r="BK6" s="1">
-        <f t="shared" si="104"/>
+        <f t="shared" si="121"/>
         <v>0</v>
       </c>
       <c r="BL6" s="1">
-        <f t="shared" si="104"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:69" x14ac:dyDescent="0.3">
+        <f t="shared" si="121"/>
+        <v>0</v>
+      </c>
+      <c r="BM6" s="1">
+        <f t="shared" ref="BM6:BV6" si="122">SUM(BM117:BM159)</f>
+        <v>0</v>
+      </c>
+      <c r="BN6" s="1">
+        <f t="shared" si="122"/>
+        <v>0</v>
+      </c>
+      <c r="BO6" s="1">
+        <f t="shared" si="122"/>
+        <v>0</v>
+      </c>
+      <c r="BP6" s="1">
+        <f t="shared" si="122"/>
+        <v>0</v>
+      </c>
+      <c r="BQ6" s="1">
+        <f t="shared" si="122"/>
+        <v>0</v>
+      </c>
+      <c r="BR6" s="1">
+        <f t="shared" si="122"/>
+        <v>0</v>
+      </c>
+      <c r="BS6" s="1">
+        <f t="shared" si="122"/>
+        <v>0</v>
+      </c>
+      <c r="BT6" s="1">
+        <f t="shared" si="122"/>
+        <v>0</v>
+      </c>
+      <c r="BU6" s="1">
+        <f t="shared" si="122"/>
+        <v>0</v>
+      </c>
+      <c r="BV6" s="1">
+        <f t="shared" si="122"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:79" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
         <v>27</v>
       </c>
@@ -2622,217 +3411,252 @@
         <v>2</v>
       </c>
       <c r="E7" s="15">
-        <f t="shared" ref="E7" si="105">E8/F8</f>
-        <v>6.7380952380952381</v>
+        <f t="shared" ref="E7" si="123">E8/F8</f>
+        <v>6.4809160305343507</v>
       </c>
       <c r="F7" s="15" t="s">
         <v>2</v>
       </c>
       <c r="G7" s="15">
-        <f t="shared" ref="G7" si="106">G8/H8</f>
-        <v>7.3507718696397939</v>
+        <f t="shared" ref="G7" si="124">G8/H8</f>
+        <v>7.3146341463414632</v>
       </c>
       <c r="H7" s="15" t="s">
         <v>2</v>
       </c>
       <c r="I7" s="15">
-        <f t="shared" ref="I7" si="107">I8/J8</f>
+        <f t="shared" ref="I7" si="125">I8/J8</f>
         <v>3.0166666666666666</v>
       </c>
       <c r="J7" s="15" t="s">
         <v>2</v>
       </c>
       <c r="K7" s="15">
-        <f t="shared" ref="K7" si="108">K8/L8</f>
+        <f t="shared" ref="K7" si="126">K8/L8</f>
         <v>3.8518518518518516</v>
       </c>
       <c r="L7" s="15" t="s">
         <v>2</v>
       </c>
       <c r="M7" s="15">
-        <f t="shared" ref="M7" si="109">M8/N8</f>
-        <v>5.8361266294227185</v>
+        <f t="shared" ref="M7" si="127">M8/N8</f>
+        <v>5.807339449541284</v>
       </c>
       <c r="N7" s="15" t="s">
         <v>2</v>
       </c>
       <c r="O7" s="15">
-        <f t="shared" ref="O7" si="110">O8/P8</f>
+        <f t="shared" ref="O7" si="128">O8/P8</f>
         <v>7.7894736842105265</v>
       </c>
       <c r="P7" s="15" t="s">
         <v>2</v>
       </c>
       <c r="Q7" s="15">
-        <f t="shared" ref="Q7" si="111">Q8/R8</f>
-        <v>6.7261410788381744</v>
+        <f t="shared" ref="Q7" si="129">Q8/R8</f>
+        <v>6.3759124087591239</v>
       </c>
       <c r="R7" s="15" t="s">
         <v>2</v>
       </c>
       <c r="S7" s="15">
-        <f t="shared" ref="S7" si="112">S8/T8</f>
+        <f t="shared" ref="S7" si="130">S8/T8</f>
         <v>5.3388888888888886</v>
       </c>
       <c r="T7" s="15" t="s">
         <v>2</v>
       </c>
       <c r="U7" s="15">
-        <f t="shared" ref="U7" si="113">U8/V8</f>
-        <v>2.9926470588235294</v>
+        <f t="shared" ref="U7" si="131">U8/V8</f>
+        <v>3.1458333333333335</v>
       </c>
       <c r="V7" s="15" t="s">
         <v>2</v>
       </c>
       <c r="W7" s="15">
-        <f t="shared" ref="W7" si="114">W8/X8</f>
+        <f t="shared" ref="W7" si="132">W8/X8</f>
         <v>2</v>
       </c>
       <c r="X7" s="15" t="s">
         <v>2</v>
       </c>
       <c r="Y7" s="15" t="e">
-        <f t="shared" ref="Y7" si="115">Y8/Z8</f>
+        <f t="shared" ref="Y7" si="133">Y8/Z8</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Z7" s="15" t="s">
         <v>2</v>
       </c>
       <c r="AA7" s="15">
-        <f t="shared" ref="AA7" si="116">AA8/AB8</f>
-        <v>4.9730392156862742</v>
+        <f t="shared" ref="AA7" si="134">AA8/AB8</f>
+        <v>5.0965665236051505</v>
       </c>
       <c r="AB7" s="15" t="s">
         <v>2</v>
       </c>
       <c r="AC7" s="15">
-        <f t="shared" ref="AC7" si="117">AC8/AD8</f>
+        <f t="shared" ref="AC7" si="135">AC8/AD8</f>
         <v>5.7733333333333334</v>
       </c>
       <c r="AD7" s="15" t="s">
         <v>2</v>
       </c>
       <c r="AE7" s="15">
-        <f t="shared" ref="AE7" si="118">AE8/AF8</f>
+        <f t="shared" ref="AE7" si="136">AE8/AF8</f>
         <v>0</v>
       </c>
       <c r="AF7" s="15" t="s">
         <v>2</v>
       </c>
       <c r="AG7" s="15" t="e">
-        <f t="shared" ref="AG7" si="119">AG8/AH8</f>
+        <f t="shared" ref="AG7" si="137">AG8/AH8</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AH7" s="15" t="s">
         <v>2</v>
       </c>
       <c r="AI7" s="15">
-        <f t="shared" ref="AI7" si="120">AI8/AJ8</f>
+        <f t="shared" ref="AI7" si="138">AI8/AJ8</f>
         <v>2.9607843137254903</v>
       </c>
       <c r="AJ7" s="15" t="s">
         <v>2</v>
       </c>
       <c r="AK7" s="15" t="e">
-        <f t="shared" ref="AK7" si="121">AK8/AL8</f>
+        <f t="shared" ref="AK7" si="139">AK8/AL8</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AL7" s="15" t="s">
         <v>2</v>
       </c>
       <c r="AM7" s="15">
-        <f t="shared" ref="AM7" si="122">AM8/AN8</f>
+        <f t="shared" ref="AM7" si="140">AM8/AN8</f>
         <v>4.5</v>
       </c>
       <c r="AN7" s="15" t="s">
         <v>2</v>
       </c>
       <c r="AO7" s="15">
-        <f t="shared" ref="AO7" si="123">AO8/AP8</f>
+        <f t="shared" ref="AO7" si="141">AO8/AP8</f>
         <v>-8.3333333333333329E-2</v>
       </c>
       <c r="AP7" s="15" t="s">
         <v>2</v>
       </c>
       <c r="AQ7" s="15">
-        <f t="shared" ref="AQ7" si="124">AQ8/AR8</f>
+        <f t="shared" ref="AQ7" si="142">AQ8/AR8</f>
         <v>4.1688311688311686</v>
       </c>
       <c r="AR7" s="15" t="s">
         <v>2</v>
       </c>
       <c r="AS7" s="15">
-        <f t="shared" ref="AS7" si="125">AS8/AT8</f>
+        <f t="shared" ref="AS7" si="143">AS8/AT8</f>
         <v>0.72727272727272729</v>
       </c>
       <c r="AT7" s="15" t="s">
         <v>2</v>
       </c>
       <c r="AU7" s="15">
-        <f t="shared" ref="AU7" si="126">AU8/AV8</f>
+        <f t="shared" ref="AU7" si="144">AU8/AV8</f>
         <v>8.5</v>
       </c>
       <c r="AV7" s="15" t="s">
         <v>2</v>
       </c>
       <c r="AW7" s="15">
-        <f t="shared" ref="AW7" si="127">AW8/AX8</f>
+        <f t="shared" ref="AW7" si="145">AW8/AX8</f>
         <v>2.8</v>
       </c>
       <c r="AX7" s="15" t="s">
         <v>2</v>
       </c>
       <c r="AY7" s="15">
-        <f t="shared" ref="AY7" si="128">AY8/AZ8</f>
+        <f t="shared" ref="AY7" si="146">AY8/AZ8</f>
         <v>4.2</v>
       </c>
       <c r="AZ7" s="15" t="s">
         <v>2</v>
       </c>
       <c r="BA7" s="15">
-        <f t="shared" ref="BA7" si="129">BA8/BB8</f>
+        <f t="shared" ref="BA7" si="147">BA8/BB8</f>
         <v>17</v>
       </c>
       <c r="BB7" s="15" t="s">
         <v>2</v>
       </c>
       <c r="BC7" s="15">
-        <f t="shared" ref="BC7" si="130">BC8/BD8</f>
+        <f t="shared" ref="BC7" si="148">BC8/BD8</f>
         <v>4.4814814814814818</v>
       </c>
       <c r="BD7" s="15" t="s">
         <v>2</v>
       </c>
       <c r="BE7" s="15">
-        <f t="shared" ref="BE7" si="131">BE8/BF8</f>
+        <f t="shared" ref="BE7" si="149">BE8/BF8</f>
         <v>4.95</v>
       </c>
       <c r="BF7" s="15" t="s">
         <v>2</v>
       </c>
       <c r="BG7" s="15">
-        <f t="shared" ref="BG7" si="132">BG8/BH8</f>
+        <f t="shared" ref="BG7" si="150">BG8/BH8</f>
         <v>5.4666666666666668</v>
       </c>
       <c r="BH7" s="15" t="s">
         <v>2</v>
       </c>
       <c r="BI7" s="15">
-        <f t="shared" ref="BI7" si="133">BI8/BJ8</f>
+        <f t="shared" ref="BI7" si="151">BI8/BJ8</f>
         <v>3.9375</v>
       </c>
       <c r="BJ7" s="15" t="s">
         <v>2</v>
       </c>
       <c r="BK7" s="15">
-        <f t="shared" ref="BK7" si="134">BK8/BL8</f>
+        <f t="shared" ref="BK7" si="152">BK8/BL8</f>
         <v>0</v>
       </c>
       <c r="BL7" s="15" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="8" spans="1:69" x14ac:dyDescent="0.3">
+      <c r="BM7" s="15">
+        <f t="shared" ref="BM7" si="153">BM8/BN8</f>
+        <v>10.6</v>
+      </c>
+      <c r="BN7" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="BO7" s="15">
+        <f t="shared" ref="BO7" si="154">BO8/BP8</f>
+        <v>8.25</v>
+      </c>
+      <c r="BP7" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="BQ7" s="15">
+        <f t="shared" ref="BQ7" si="155">BQ8/BR8</f>
+        <v>6.75</v>
+      </c>
+      <c r="BR7" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="BS7" s="15" t="e">
+        <f t="shared" ref="BS7" si="156">BS8/BT8</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BT7" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="BU7" s="15" t="e">
+        <f t="shared" ref="BU7" si="157">BU8/BV8</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BV7" s="15" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:79" x14ac:dyDescent="0.3">
       <c r="A8" s="15"/>
       <c r="B8" s="15" t="s">
         <v>3</v>
@@ -2846,247 +3670,287 @@
         <v>324</v>
       </c>
       <c r="E8" s="15">
-        <f t="shared" ref="E8:J8" si="135">SUM(E10:E115)</f>
+        <f t="shared" ref="E8:J8" si="158">SUM(E10:E115)</f>
         <v>849</v>
       </c>
       <c r="F8" s="15">
-        <f t="shared" si="135"/>
-        <v>126</v>
+        <f t="shared" si="158"/>
+        <v>131</v>
       </c>
       <c r="G8" s="15">
-        <f t="shared" si="135"/>
-        <v>4285.5</v>
+        <f t="shared" si="158"/>
+        <v>4498.5</v>
       </c>
       <c r="H8" s="15">
-        <f t="shared" si="135"/>
-        <v>583</v>
+        <f t="shared" si="158"/>
+        <v>615</v>
       </c>
       <c r="I8" s="15">
-        <f t="shared" si="135"/>
+        <f t="shared" si="158"/>
         <v>181</v>
       </c>
       <c r="J8" s="15">
-        <f t="shared" si="135"/>
+        <f t="shared" si="158"/>
         <v>60</v>
       </c>
       <c r="K8" s="15">
-        <f t="shared" ref="K8:AZ8" si="136">SUM(K10:K115)</f>
+        <f t="shared" ref="K8:AZ8" si="159">SUM(K10:K115)</f>
         <v>104</v>
       </c>
       <c r="L8" s="15">
-        <f t="shared" si="136"/>
+        <f t="shared" si="159"/>
         <v>27</v>
       </c>
       <c r="M8" s="15">
-        <f t="shared" si="136"/>
-        <v>3134</v>
+        <f t="shared" si="159"/>
+        <v>3165</v>
       </c>
       <c r="N8" s="15">
-        <f t="shared" si="136"/>
-        <v>537</v>
+        <f t="shared" si="159"/>
+        <v>545</v>
       </c>
       <c r="O8" s="15">
-        <f t="shared" si="136"/>
+        <f t="shared" si="159"/>
         <v>444</v>
       </c>
       <c r="P8" s="15">
-        <f t="shared" si="136"/>
+        <f t="shared" si="159"/>
         <v>57</v>
       </c>
       <c r="Q8" s="15">
-        <f t="shared" si="136"/>
-        <v>1621</v>
+        <f t="shared" si="159"/>
+        <v>1747</v>
       </c>
       <c r="R8" s="15">
-        <f t="shared" si="136"/>
-        <v>241</v>
+        <f t="shared" si="159"/>
+        <v>274</v>
       </c>
       <c r="S8" s="15">
-        <f t="shared" si="136"/>
+        <f t="shared" si="159"/>
         <v>961</v>
       </c>
       <c r="T8" s="15">
-        <f t="shared" si="136"/>
+        <f t="shared" si="159"/>
         <v>180</v>
       </c>
       <c r="U8" s="15">
-        <f t="shared" si="136"/>
-        <v>407</v>
+        <f t="shared" si="159"/>
+        <v>453</v>
       </c>
       <c r="V8" s="15">
-        <f t="shared" si="136"/>
-        <v>136</v>
+        <f t="shared" si="159"/>
+        <v>144</v>
       </c>
       <c r="W8" s="15">
-        <f t="shared" si="136"/>
+        <f t="shared" si="159"/>
         <v>76</v>
       </c>
       <c r="X8" s="15">
-        <f t="shared" si="136"/>
+        <f t="shared" si="159"/>
         <v>38</v>
       </c>
       <c r="Y8" s="15">
-        <f t="shared" si="136"/>
+        <f t="shared" si="159"/>
         <v>0</v>
       </c>
       <c r="Z8" s="15">
-        <f t="shared" si="136"/>
+        <f t="shared" si="159"/>
         <v>0</v>
       </c>
       <c r="AA8" s="15">
-        <f t="shared" si="136"/>
-        <v>1014.5</v>
+        <f t="shared" si="159"/>
+        <v>1187.5</v>
       </c>
       <c r="AB8" s="15">
-        <f t="shared" si="136"/>
-        <v>204</v>
+        <f t="shared" si="159"/>
+        <v>233</v>
       </c>
       <c r="AC8" s="15">
-        <f t="shared" si="136"/>
+        <f t="shared" si="159"/>
         <v>1299</v>
       </c>
       <c r="AD8" s="15">
-        <f t="shared" si="136"/>
+        <f t="shared" si="159"/>
         <v>225</v>
       </c>
       <c r="AE8" s="15">
-        <f t="shared" si="136"/>
+        <f t="shared" si="159"/>
         <v>0</v>
       </c>
       <c r="AF8" s="15">
-        <f t="shared" si="136"/>
+        <f t="shared" si="159"/>
         <v>2</v>
       </c>
       <c r="AG8" s="15">
-        <f t="shared" si="136"/>
+        <f t="shared" si="159"/>
         <v>0</v>
       </c>
       <c r="AH8" s="15">
-        <f t="shared" si="136"/>
+        <f t="shared" si="159"/>
         <v>0</v>
       </c>
       <c r="AI8" s="15">
-        <f t="shared" si="136"/>
+        <f t="shared" si="159"/>
         <v>151</v>
       </c>
       <c r="AJ8" s="15">
-        <f t="shared" si="136"/>
+        <f t="shared" si="159"/>
         <v>51</v>
       </c>
       <c r="AK8" s="15">
-        <f t="shared" si="136"/>
+        <f t="shared" si="159"/>
         <v>0</v>
       </c>
       <c r="AL8" s="15">
-        <f t="shared" si="136"/>
+        <f t="shared" si="159"/>
         <v>0</v>
       </c>
       <c r="AM8" s="15">
-        <f t="shared" si="136"/>
+        <f t="shared" si="159"/>
         <v>387</v>
       </c>
       <c r="AN8" s="15">
-        <f t="shared" si="136"/>
+        <f t="shared" si="159"/>
         <v>86</v>
       </c>
       <c r="AO8" s="15">
-        <f t="shared" si="136"/>
+        <f t="shared" si="159"/>
         <v>-1</v>
       </c>
       <c r="AP8" s="15">
-        <f t="shared" si="136"/>
+        <f t="shared" si="159"/>
         <v>12</v>
       </c>
       <c r="AQ8" s="15">
-        <f t="shared" si="136"/>
+        <f t="shared" si="159"/>
         <v>321</v>
       </c>
       <c r="AR8" s="15">
-        <f t="shared" si="136"/>
+        <f t="shared" si="159"/>
         <v>77</v>
       </c>
       <c r="AS8" s="15">
-        <f t="shared" si="136"/>
+        <f t="shared" si="159"/>
         <v>8</v>
       </c>
       <c r="AT8" s="15">
-        <f t="shared" si="136"/>
+        <f t="shared" si="159"/>
         <v>11</v>
       </c>
       <c r="AU8" s="15">
-        <f t="shared" si="136"/>
+        <f t="shared" si="159"/>
         <v>34</v>
       </c>
       <c r="AV8" s="15">
-        <f t="shared" si="136"/>
+        <f t="shared" si="159"/>
         <v>4</v>
       </c>
       <c r="AW8" s="15">
-        <f t="shared" si="136"/>
+        <f t="shared" si="159"/>
         <v>14</v>
       </c>
       <c r="AX8" s="15">
-        <f t="shared" si="136"/>
+        <f t="shared" si="159"/>
         <v>5</v>
       </c>
       <c r="AY8" s="15">
-        <f t="shared" si="136"/>
+        <f t="shared" si="159"/>
         <v>21</v>
       </c>
       <c r="AZ8" s="15">
-        <f t="shared" si="136"/>
+        <f t="shared" si="159"/>
         <v>5</v>
       </c>
       <c r="BA8" s="15">
-        <f t="shared" ref="BA8:BD8" si="137">SUM(BA10:BA115)</f>
+        <f t="shared" ref="BA8:BD8" si="160">SUM(BA10:BA115)</f>
         <v>34</v>
       </c>
       <c r="BB8" s="15">
-        <f t="shared" si="137"/>
+        <f t="shared" si="160"/>
         <v>2</v>
       </c>
       <c r="BC8" s="15">
-        <f t="shared" si="137"/>
+        <f t="shared" si="160"/>
         <v>121</v>
       </c>
       <c r="BD8" s="15">
-        <f t="shared" si="137"/>
+        <f t="shared" si="160"/>
         <v>27</v>
       </c>
       <c r="BE8" s="15">
-        <f t="shared" ref="BE8:BF8" si="138">SUM(BE10:BE115)</f>
+        <f t="shared" ref="BE8:BF8" si="161">SUM(BE10:BE115)</f>
         <v>594</v>
       </c>
       <c r="BF8" s="15">
-        <f t="shared" si="138"/>
+        <f t="shared" si="161"/>
         <v>120</v>
       </c>
       <c r="BG8" s="15">
-        <f t="shared" ref="BG8:BL8" si="139">SUM(BG10:BG115)</f>
+        <f t="shared" ref="BG8:BL8" si="162">SUM(BG10:BG115)</f>
         <v>82</v>
       </c>
       <c r="BH8" s="15">
-        <f t="shared" si="139"/>
+        <f t="shared" si="162"/>
         <v>15</v>
       </c>
       <c r="BI8" s="15">
-        <f t="shared" si="139"/>
+        <f t="shared" si="162"/>
         <v>63</v>
       </c>
       <c r="BJ8" s="15">
-        <f t="shared" si="139"/>
+        <f t="shared" si="162"/>
         <v>16</v>
       </c>
       <c r="BK8" s="15">
-        <f t="shared" si="139"/>
+        <f t="shared" si="162"/>
         <v>0</v>
       </c>
       <c r="BL8" s="15">
-        <f t="shared" si="139"/>
+        <f t="shared" si="162"/>
         <v>6</v>
       </c>
-    </row>
-    <row r="9" spans="1:69" x14ac:dyDescent="0.3">
+      <c r="BM8" s="15">
+        <f t="shared" ref="BM8:BV8" si="163">SUM(BM10:BM115)</f>
+        <v>53</v>
+      </c>
+      <c r="BN8" s="15">
+        <f t="shared" si="163"/>
+        <v>5</v>
+      </c>
+      <c r="BO8" s="15">
+        <f t="shared" si="163"/>
+        <v>33</v>
+      </c>
+      <c r="BP8" s="15">
+        <f t="shared" si="163"/>
+        <v>4</v>
+      </c>
+      <c r="BQ8" s="15">
+        <f t="shared" si="163"/>
+        <v>135</v>
+      </c>
+      <c r="BR8" s="15">
+        <f t="shared" si="163"/>
+        <v>20</v>
+      </c>
+      <c r="BS8" s="15">
+        <f t="shared" si="163"/>
+        <v>0</v>
+      </c>
+      <c r="BT8" s="15">
+        <f t="shared" si="163"/>
+        <v>0</v>
+      </c>
+      <c r="BU8" s="15">
+        <f t="shared" si="163"/>
+        <v>0</v>
+      </c>
+      <c r="BV8" s="15">
+        <f t="shared" si="163"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:79" x14ac:dyDescent="0.3">
       <c r="C9" s="27" t="s">
         <v>70</v>
       </c>
@@ -3211,63 +4075,191 @@
         <v>93</v>
       </c>
       <c r="BL9" s="27"/>
-    </row>
-    <row r="10" spans="1:69" x14ac:dyDescent="0.3">
+      <c r="BM9" s="27" t="s">
+        <v>95</v>
+      </c>
+      <c r="BN9" s="27"/>
+      <c r="BO9" s="27" t="s">
+        <v>96</v>
+      </c>
+      <c r="BP9" s="27"/>
+      <c r="BQ9" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="BR9" s="27"/>
+      <c r="BS9" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="BT9" s="27"/>
+      <c r="BU9" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="BV9" s="27"/>
+    </row>
+    <row r="10" spans="1:79" x14ac:dyDescent="0.3">
       <c r="B10" s="1">
         <v>161</v>
       </c>
     </row>
-    <row r="11" spans="1:69" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:79" x14ac:dyDescent="0.3">
       <c r="B11" s="1">
         <v>160</v>
       </c>
     </row>
-    <row r="12" spans="1:69" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:79" x14ac:dyDescent="0.3">
       <c r="B12" s="1">
         <v>159</v>
       </c>
     </row>
-    <row r="13" spans="1:69" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:79" x14ac:dyDescent="0.3">
       <c r="B13" s="1">
         <v>158</v>
       </c>
     </row>
-    <row r="14" spans="1:69" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:79" x14ac:dyDescent="0.3">
       <c r="B14" s="1">
         <v>157</v>
       </c>
     </row>
-    <row r="15" spans="1:69" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:79" x14ac:dyDescent="0.3">
       <c r="B15" s="1">
         <v>156</v>
       </c>
     </row>
-    <row r="16" spans="1:69" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:79" x14ac:dyDescent="0.3">
       <c r="B16" s="1">
         <v>155</v>
       </c>
     </row>
-    <row r="17" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:70" x14ac:dyDescent="0.3">
       <c r="B17" s="1">
         <v>154</v>
       </c>
-    </row>
-    <row r="18" spans="1:64" x14ac:dyDescent="0.3">
+      <c r="G17" s="1">
+        <v>110</v>
+      </c>
+      <c r="H17" s="1">
+        <v>20</v>
+      </c>
+      <c r="Q17" s="1">
+        <v>88</v>
+      </c>
+      <c r="R17" s="1">
+        <v>20</v>
+      </c>
+      <c r="AA17" s="1">
+        <v>127</v>
+      </c>
+      <c r="AB17" s="1">
+        <v>20</v>
+      </c>
+      <c r="BQ17" s="1">
+        <v>135</v>
+      </c>
+      <c r="BR17" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:70" x14ac:dyDescent="0.3">
       <c r="B18" s="1">
         <v>153</v>
       </c>
-    </row>
-    <row r="19" spans="1:64" x14ac:dyDescent="0.3">
+      <c r="E18" s="1">
+        <v>11</v>
+      </c>
+      <c r="F18" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q18" s="1">
+        <v>-11</v>
+      </c>
+      <c r="R18" s="1">
+        <v>1</v>
+      </c>
+      <c r="AA18" s="1">
+        <v>11</v>
+      </c>
+      <c r="AB18" s="1">
+        <v>1</v>
+      </c>
+      <c r="BM18" s="1">
+        <v>-11</v>
+      </c>
+      <c r="BN18" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:70" x14ac:dyDescent="0.3">
       <c r="B19" s="1">
         <v>152</v>
       </c>
-    </row>
-    <row r="20" spans="1:64" x14ac:dyDescent="0.3">
+      <c r="E19" s="1">
+        <v>-11</v>
+      </c>
+      <c r="F19" s="1">
+        <v>4</v>
+      </c>
+      <c r="G19" s="1">
+        <v>38</v>
+      </c>
+      <c r="H19" s="1">
+        <v>4</v>
+      </c>
+      <c r="Q19" s="1">
+        <v>-13</v>
+      </c>
+      <c r="R19" s="1">
+        <v>4</v>
+      </c>
+      <c r="BM19" s="1">
+        <v>64</v>
+      </c>
+      <c r="BN19" s="1">
+        <v>4</v>
+      </c>
+      <c r="BO19" s="1">
+        <v>33</v>
+      </c>
+      <c r="BP19" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:70" x14ac:dyDescent="0.3">
       <c r="B20" s="1">
         <v>151</v>
       </c>
-    </row>
-    <row r="21" spans="1:64" x14ac:dyDescent="0.3">
+      <c r="G20" s="1">
+        <v>65</v>
+      </c>
+      <c r="H20" s="1">
+        <v>8</v>
+      </c>
+      <c r="M20" s="1">
+        <v>31</v>
+      </c>
+      <c r="N20" s="1">
+        <v>8</v>
+      </c>
+      <c r="Q20" s="1">
+        <v>62</v>
+      </c>
+      <c r="R20" s="1">
+        <v>8</v>
+      </c>
+      <c r="U20" s="1">
+        <v>46</v>
+      </c>
+      <c r="V20" s="1">
+        <v>8</v>
+      </c>
+      <c r="AA20" s="1">
+        <v>35</v>
+      </c>
+      <c r="AB20" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>7</v>
       </c>
@@ -3299,7 +4291,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>7</v>
       </c>
@@ -3337,7 +4329,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>7</v>
       </c>
@@ -3381,7 +4373,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>7</v>
       </c>
@@ -3413,7 +4405,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="25" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>7</v>
       </c>
@@ -3445,7 +4437,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>7</v>
       </c>
@@ -3477,7 +4469,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>7</v>
       </c>
@@ -3509,7 +4501,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>7</v>
       </c>
@@ -3547,7 +4539,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>7</v>
       </c>
@@ -3579,7 +4571,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>7</v>
       </c>
@@ -3611,7 +4603,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>7</v>
       </c>
@@ -3643,7 +4635,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="32" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>7</v>
       </c>
@@ -4762,7 +5754,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="65" spans="1:76" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:86" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
         <v>7</v>
       </c>
@@ -4794,7 +5786,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="66" spans="1:76" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:86" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
         <v>7</v>
       </c>
@@ -4832,7 +5824,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="67" spans="1:76" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:86" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
         <v>7</v>
       </c>
@@ -4864,7 +5856,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="68" spans="1:76" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:86" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
         <v>7</v>
       </c>
@@ -4902,7 +5894,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="69" spans="1:76" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:86" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
         <v>7</v>
       </c>
@@ -4934,7 +5926,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="70" spans="1:76" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:86" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
         <v>7</v>
       </c>
@@ -4972,7 +5964,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="71" spans="1:76" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:86" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
         <v>7</v>
       </c>
@@ -5013,7 +6005,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="72" spans="1:76" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:86" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
         <v>7</v>
       </c>
@@ -5045,7 +6037,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="73" spans="1:76" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:86" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
         <v>7</v>
       </c>
@@ -5077,7 +6069,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="74" spans="1:76" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:86" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
         <v>7</v>
       </c>
@@ -5109,7 +6101,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="75" spans="1:76" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:86" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
         <v>7</v>
       </c>
@@ -5141,7 +6133,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="76" spans="1:76" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:86" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
         <v>7</v>
       </c>
@@ -5173,7 +6165,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="77" spans="1:76" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:86" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
         <v>7</v>
       </c>
@@ -5205,7 +6197,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="78" spans="1:76" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:86" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
         <v>7</v>
       </c>
@@ -5237,7 +6229,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="79" spans="1:76" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:86" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
         <v>7</v>
       </c>
@@ -5269,7 +6261,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="80" spans="1:76" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:86" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
         <v>7</v>
       </c>
@@ -5300,14 +6292,14 @@
       <c r="AB80" s="1">
         <v>16</v>
       </c>
-      <c r="BV80" s="1" t="s">
+      <c r="CF80" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="BX80" s="1" t="s">
+      <c r="CH80" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="81" spans="1:81" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:91" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
         <v>7</v>
       </c>
@@ -5338,11 +6330,11 @@
       <c r="V81" s="1">
         <v>12</v>
       </c>
-      <c r="BV81" s="1" t="s">
+      <c r="CF81" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="82" spans="1:81" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:91" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
         <v>7</v>
       </c>
@@ -5373,18 +6365,18 @@
       <c r="R82" s="1">
         <v>5</v>
       </c>
-      <c r="BV82" s="1" t="s">
+      <c r="CF82" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="BW82" s="23"/>
-      <c r="BX82" s="1" t="s">
+      <c r="CG82" s="23"/>
+      <c r="CH82" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="BY82" s="1" t="s">
+      <c r="CI82" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="83" spans="1:81" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:91" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
         <v>7</v>
       </c>
@@ -5415,18 +6407,18 @@
       <c r="T83" s="1">
         <v>4</v>
       </c>
-      <c r="BV83" s="1" t="s">
+      <c r="CF83" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="BW83" s="24"/>
-      <c r="BX83" s="1" t="s">
+      <c r="CG83" s="24"/>
+      <c r="CH83" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="BY83" s="1" t="s">
+      <c r="CI83" s="1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="84" spans="1:81" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:91" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
         <v>7</v>
       </c>
@@ -5457,18 +6449,18 @@
       <c r="N84" s="1">
         <v>3</v>
       </c>
-      <c r="BV84" s="1" t="s">
+      <c r="CF84" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="BW84" s="17"/>
-      <c r="BX84" s="1" t="s">
+      <c r="CG84" s="17"/>
+      <c r="CH84" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="BY84" s="1" t="s">
+      <c r="CI84" s="1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="85" spans="1:81" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:91" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
         <v>7</v>
       </c>
@@ -5499,18 +6491,18 @@
       <c r="L85" s="1">
         <v>4</v>
       </c>
-      <c r="BV85" s="1" t="s">
+      <c r="CF85" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="BW85" s="18"/>
-      <c r="BX85" s="1" t="s">
+      <c r="CG85" s="18"/>
+      <c r="CH85" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="BY85" s="1" t="s">
+      <c r="CI85" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="86" spans="1:81" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:91" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
         <v>7</v>
       </c>
@@ -5541,18 +6533,18 @@
       <c r="AB86" s="1">
         <v>8</v>
       </c>
-      <c r="BV86" s="1" t="s">
+      <c r="CF86" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="BW86" s="21"/>
-      <c r="BX86" s="1" t="s">
+      <c r="CG86" s="21"/>
+      <c r="CH86" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="BY86" s="1" t="s">
+      <c r="CI86" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="87" spans="1:81" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:91" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
         <v>7</v>
       </c>
@@ -5589,18 +6581,18 @@
       <c r="AB87" s="1">
         <v>8</v>
       </c>
-      <c r="BV87" s="1" t="s">
+      <c r="CF87" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="BW87" s="19"/>
-      <c r="BX87" s="1" t="s">
+      <c r="CG87" s="19"/>
+      <c r="CH87" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="BY87" s="1" t="s">
+      <c r="CI87" s="1" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="88" spans="1:81" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:91" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
         <v>7</v>
       </c>
@@ -5631,18 +6623,18 @@
       <c r="T88" s="1">
         <v>8</v>
       </c>
-      <c r="BV88" s="1" t="s">
+      <c r="CF88" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="BW88" s="20"/>
-      <c r="BX88" s="1" t="s">
+      <c r="CG88" s="20"/>
+      <c r="CH88" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="BY88" s="1" t="s">
+      <c r="CI88" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="89" spans="1:81" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:91" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
         <v>7</v>
       </c>
@@ -5673,18 +6665,18 @@
       <c r="AJ89" s="1">
         <v>12</v>
       </c>
-      <c r="BV89" s="1" t="s">
+      <c r="CF89" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="BW89" s="22"/>
-      <c r="BX89" s="1" t="s">
+      <c r="CG89" s="22"/>
+      <c r="CH89" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="BY89" s="1" t="s">
+      <c r="CI89" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="90" spans="1:81" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:91" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
         <v>7</v>
       </c>
@@ -5728,7 +6720,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="91" spans="1:81" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:91" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
         <v>7</v>
       </c>
@@ -5765,35 +6757,35 @@
       <c r="V91" s="1">
         <v>7</v>
       </c>
-      <c r="BR91" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="BS91" s="1" t="s">
+      <c r="CB91" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="CC91" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="BT91" s="1" t="s">
+      <c r="CD91" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="BU91" s="1" t="s">
+      <c r="CE91" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="BW91" s="1" t="s">
+      <c r="CG91" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="BX91" s="1" t="s">
+      <c r="CH91" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="BY91" s="1" t="s">
+      <c r="CI91" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="BZ91" s="1" t="s">
+      <c r="CJ91" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="CB91" s="1" t="s">
+      <c r="CL91" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="92" spans="1:81" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:91" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
         <v>7</v>
       </c>
@@ -5825,7 +6817,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="93" spans="1:81" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:91" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
         <v>7</v>
       </c>
@@ -5874,17 +6866,17 @@
       <c r="BB93" s="1">
         <v>2</v>
       </c>
-      <c r="BO93" s="2"/>
-      <c r="BP93" s="1" t="s">
+      <c r="BY93" s="2"/>
+      <c r="BZ93" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="BR93" s="1" cm="1">
-        <f t="array" ref="BR93:BU112">_xlfn.LET(
-  _xlpm.cols_impairs, _xlfn.SEQUENCE(1,COLUMNS(C1:BF1)/2,1,2),
-  _xlpm.cols_pairs,   _xlfn.SEQUENCE(1,COLUMNS(C2:BF2)/2,2,2),
-  _xlpm.noms,     TRANSPOSE(INDEX(C9:BF9,,_xlpm.cols_impairs)),
-  _xlpm.moy,      TRANSPOSE(INDEX(C1:BF1,,_xlpm.cols_impairs)),
-  _xlpm.parties,  TRANSPOSE(INDEX(C2:BF2,,_xlpm.cols_pairs)),
+      <c r="CB93" s="1" cm="1">
+        <f t="array" ref="CB93:CE113">_xlfn.LET(
+  _xlpm.cols_impairs, _xlfn.SEQUENCE(1,COLUMNS(C1:BV1)/2,1,2),
+  _xlpm.cols_pairs,   _xlfn.SEQUENCE(1,COLUMNS(C2:BV2)/2,2,2),
+  _xlpm.noms,     TRANSPOSE(INDEX(C9:BV9,,_xlpm.cols_impairs)),
+  _xlpm.moy,      TRANSPOSE(INDEX(C1:BV1,,_xlpm.cols_impairs)),
+  _xlpm.parties,  TRANSPOSE(INDEX(C2:BV2,,_xlpm.cols_pairs)),
   _xlpm.ok, ISNUMBER(_xlpm.moy),
   _xlpm.nomsF,    _xlfn._xlws.FILTER(_xlpm.noms, _xlpm.ok),
   _xlpm.moyF,     _xlfn._xlws.FILTER(_xlpm.moy, _xlpm.ok),
@@ -5898,17 +6890,17 @@
 )</f>
         <v>1</v>
       </c>
-      <c r="BS93" s="1" t="str">
+      <c r="CC93" s="1" t="str">
         <v>Gauthier</v>
       </c>
-      <c r="BT93" s="1" t="str">
+      <c r="CD93" s="1" t="str">
         <v>7.253</v>
       </c>
-      <c r="BU93" s="1">
+      <c r="CE93" s="1">
         <v>79</v>
       </c>
-      <c r="BW93" s="1" cm="1">
-        <f t="array" ref="BW93:BZ100">_xlfn.LET(
+      <c r="CG93" s="1" cm="1">
+        <f t="array" ref="CG93:CJ100">_xlfn.LET(
   _xlpm.cols_impairs, _xlfn.SEQUENCE(1,COLUMNS(C1:BF1)/2,1,2),
   _xlpm.cols_pairs,   _xlfn.SEQUENCE(1,COLUMNS(C2:BF2)/2,2,2),
   _xlpm.noms,     TRANSPOSE(INDEX(C9:BF9,,_xlpm.cols_impairs)),
@@ -5928,24 +6920,24 @@
 )</f>
         <v>1</v>
       </c>
-      <c r="BX93" s="1" t="str">
+      <c r="CH93" s="1" t="str">
         <v>Amélie</v>
       </c>
-      <c r="BY93" s="1" t="str">
+      <c r="CI93" s="1" t="str">
         <v>17.000</v>
       </c>
-      <c r="BZ93" s="1">
-        <v>2</v>
-      </c>
-      <c r="CB93" s="1" t="str" cm="1">
-        <f t="array" ref="CB93:CC120">_xlfn.LET(  _xlpm.noms, TRANSPOSE(INDEX(C9:BF9,_xlfn.SEQUENCE(1,COLUMNS(C9:BF9)/2,1,2))),_xlpm.moy,  TRANSPOSE(INDEX(C1:BF1,,_xlfn.SEQUENCE(1,COLUMNS(C1:BF1)/2,1,2))),_xlfn.SORTBY(CHOOSE({1,2}, _xlpm.noms, _xlpm.moy), IF(ISNUMBER(_xlpm.moy), _xlpm.moy, -1E+99), -1))</f>
+      <c r="CJ93" s="1">
+        <v>2</v>
+      </c>
+      <c r="CL93" s="1" t="str" cm="1">
+        <f t="array" ref="CL93:CM120">_xlfn.LET(  _xlpm.noms, TRANSPOSE(INDEX(C9:BF9,_xlfn.SEQUENCE(1,COLUMNS(C9:BF9)/2,1,2))),_xlpm.moy,  TRANSPOSE(INDEX(C1:BF1,,_xlfn.SEQUENCE(1,COLUMNS(C1:BF1)/2,1,2))),_xlfn.SORTBY(CHOOSE({1,2}, _xlpm.noms, _xlpm.moy), IF(ISNUMBER(_xlpm.moy), _xlpm.moy, -1E+99), -1))</f>
         <v>Gauthier</v>
       </c>
-      <c r="CC93" s="1">
+      <c r="CM93" s="1">
         <v>7.2531645569620249</v>
       </c>
     </row>
-    <row r="94" spans="1:81" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:91" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
         <v>24</v>
       </c>
@@ -5976,42 +6968,42 @@
       <c r="AB94" s="1">
         <v>8</v>
       </c>
-      <c r="BO94" s="3"/>
-      <c r="BP94" s="1" t="s">
+      <c r="BY94" s="3"/>
+      <c r="BZ94" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="BR94" s="1">
-        <v>2</v>
-      </c>
-      <c r="BS94" s="1" t="str">
+      <c r="CB94" s="1">
+        <v>2</v>
+      </c>
+      <c r="CC94" s="1" t="str">
         <v>Boris</v>
       </c>
-      <c r="BT94" s="1" t="str">
-        <v>7.165</v>
-      </c>
-      <c r="BU94" s="1">
-        <v>1108</v>
-      </c>
-      <c r="BW94" s="1">
-        <v>2</v>
-      </c>
-      <c r="BX94" s="1" t="str">
+      <c r="CD94" s="1" t="str">
+        <v>7.150</v>
+      </c>
+      <c r="CE94" s="1">
+        <v>1140</v>
+      </c>
+      <c r="CG94" s="1">
+        <v>2</v>
+      </c>
+      <c r="CH94" s="1" t="str">
         <v>Maxime_Ca</v>
       </c>
-      <c r="BY94" s="1" t="str">
+      <c r="CI94" s="1" t="str">
         <v>8.500</v>
       </c>
-      <c r="BZ94" s="1">
+      <c r="CJ94" s="1">
         <v>4</v>
       </c>
-      <c r="CB94" s="1" t="str">
+      <c r="CL94" s="1" t="str">
         <v>Boris</v>
       </c>
-      <c r="CC94" s="1">
-        <v>7.1647111913357397</v>
-      </c>
-    </row>
-    <row r="95" spans="1:81" x14ac:dyDescent="0.3">
+      <c r="CM94" s="1">
+        <v>7.1504385964912283</v>
+      </c>
+    </row>
+    <row r="95" spans="1:91" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
         <v>24</v>
       </c>
@@ -6042,42 +7034,42 @@
       <c r="AJ95" s="1">
         <v>4</v>
       </c>
-      <c r="BO95" s="4"/>
-      <c r="BP95" s="1" t="s">
+      <c r="BY95" s="4"/>
+      <c r="BZ95" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="BR95" s="1">
+      <c r="CB95" s="1">
         <v>3</v>
       </c>
-      <c r="BS95" s="1" t="str">
+      <c r="CC95" s="1" t="str">
+        <v>Vincent</v>
+      </c>
+      <c r="CD95" s="1" t="str">
+        <v>6.750</v>
+      </c>
+      <c r="CE95" s="1">
+        <v>20</v>
+      </c>
+      <c r="CG95" s="1">
+        <v>3</v>
+      </c>
+      <c r="CH95" s="1" t="str">
+        <v>Pascale</v>
+      </c>
+      <c r="CI95" s="1" t="str">
+        <v>7.118</v>
+      </c>
+      <c r="CJ95" s="1">
+        <v>17</v>
+      </c>
+      <c r="CL95" s="1" t="str">
         <v>Célian</v>
       </c>
-      <c r="BT95" s="1" t="str">
-        <v>6.509</v>
-      </c>
-      <c r="BU95" s="1">
-        <v>316</v>
-      </c>
-      <c r="BW95" s="1">
-        <v>3</v>
-      </c>
-      <c r="BX95" s="1" t="str">
-        <v>Pascale</v>
-      </c>
-      <c r="BY95" s="1" t="str">
-        <v>7.118</v>
-      </c>
-      <c r="BZ95" s="1">
-        <v>17</v>
-      </c>
-      <c r="CB95" s="1" t="str">
-        <v>Célian</v>
-      </c>
-      <c r="CC95" s="1">
-        <v>6.5094936708860756</v>
-      </c>
-    </row>
-    <row r="96" spans="1:81" x14ac:dyDescent="0.3">
+      <c r="CM95" s="1">
+        <v>6.2550143266475642</v>
+      </c>
+    </row>
+    <row r="96" spans="1:91" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
         <v>22</v>
       </c>
@@ -6108,38 +7100,38 @@
       <c r="AV96" s="1">
         <v>4</v>
       </c>
-      <c r="BR96" s="1">
+      <c r="CB96" s="1">
         <v>4</v>
       </c>
-      <c r="BS96" s="1" t="str">
+      <c r="CC96" s="1" t="str">
+        <v>Célian</v>
+      </c>
+      <c r="CD96" s="1" t="str">
+        <v>6.255</v>
+      </c>
+      <c r="CE96" s="1">
+        <v>349</v>
+      </c>
+      <c r="CG96" s="1">
+        <v>4</v>
+      </c>
+      <c r="CH96" s="1" t="str">
+        <v>Harrison</v>
+      </c>
+      <c r="CI96" s="1" t="str">
+        <v>5.400</v>
+      </c>
+      <c r="CJ96" s="1">
+        <v>5</v>
+      </c>
+      <c r="CL96" s="1" t="str">
         <v>William</v>
       </c>
-      <c r="BT96" s="1" t="str">
-        <v>6.069</v>
-      </c>
-      <c r="BU96" s="1">
-        <v>29</v>
-      </c>
-      <c r="BW96" s="1">
-        <v>4</v>
-      </c>
-      <c r="BX96" s="1" t="str">
-        <v>Harrison</v>
-      </c>
-      <c r="BY96" s="1" t="str">
-        <v>5.400</v>
-      </c>
-      <c r="BZ96" s="1">
-        <v>5</v>
-      </c>
-      <c r="CB96" s="1" t="str">
-        <v>William</v>
-      </c>
-      <c r="CC96" s="1">
+      <c r="CM96" s="1">
         <v>6.068965517241379</v>
       </c>
     </row>
-    <row r="97" spans="1:81" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:91" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
         <v>7</v>
       </c>
@@ -6170,42 +7162,42 @@
       <c r="V97" s="1">
         <v>4</v>
       </c>
-      <c r="BO97" s="5"/>
-      <c r="BP97" s="1" t="s">
+      <c r="BY97" s="5"/>
+      <c r="BZ97" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="BR97" s="1">
+      <c r="CB97" s="1">
         <v>5</v>
       </c>
-      <c r="BS97" s="1" t="str">
+      <c r="CC97" s="1" t="str">
+        <v>William</v>
+      </c>
+      <c r="CD97" s="1" t="str">
+        <v>6.069</v>
+      </c>
+      <c r="CE97" s="1">
+        <v>29</v>
+      </c>
+      <c r="CG97" s="1">
+        <v>5</v>
+      </c>
+      <c r="CH97" s="1" t="str">
+        <v>Émile</v>
+      </c>
+      <c r="CI97" s="1" t="str">
+        <v>3.308</v>
+      </c>
+      <c r="CJ97" s="1">
+        <v>13</v>
+      </c>
+      <c r="CL97" s="1" t="str">
         <v>Tom</v>
       </c>
-      <c r="BT97" s="1" t="str">
-        <v>5.993</v>
-      </c>
-      <c r="BU97" s="1">
-        <v>286</v>
-      </c>
-      <c r="BW97" s="1">
-        <v>5</v>
-      </c>
-      <c r="BX97" s="1" t="str">
-        <v>Émile</v>
-      </c>
-      <c r="BY97" s="1" t="str">
-        <v>3.308</v>
-      </c>
-      <c r="BZ97" s="1">
-        <v>13</v>
-      </c>
-      <c r="CB97" s="1" t="str">
-        <v>Tom</v>
-      </c>
-      <c r="CC97" s="1">
+      <c r="CM97" s="1">
         <v>5.9930069930069934</v>
       </c>
     </row>
-    <row r="98" spans="1:81" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:91" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
         <v>7</v>
       </c>
@@ -6236,42 +7228,42 @@
       <c r="AB98" s="1">
         <v>7</v>
       </c>
-      <c r="BO98" s="10"/>
-      <c r="BP98" s="1" t="s">
+      <c r="BY98" s="10"/>
+      <c r="BZ98" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="BR98" s="1">
+      <c r="CB98" s="1">
         <v>6</v>
       </c>
-      <c r="BS98" s="1" t="str">
+      <c r="CC98" s="1" t="str">
+        <v>Tom</v>
+      </c>
+      <c r="CD98" s="1" t="str">
+        <v>5.993</v>
+      </c>
+      <c r="CE98" s="1">
+        <v>286</v>
+      </c>
+      <c r="CG98" s="1">
+        <v>6</v>
+      </c>
+      <c r="CH98" s="1" t="str">
+        <v>Aurélien</v>
+      </c>
+      <c r="CI98" s="1" t="str">
+        <v>2.800</v>
+      </c>
+      <c r="CJ98" s="1">
+        <v>5</v>
+      </c>
+      <c r="CL98" s="1" t="str">
         <v>Samuel</v>
       </c>
-      <c r="BT98" s="1" t="str">
-        <v>5.910</v>
-      </c>
-      <c r="BU98" s="1">
-        <v>211</v>
-      </c>
-      <c r="BW98" s="1">
-        <v>6</v>
-      </c>
-      <c r="BX98" s="1" t="str">
-        <v>Aurélien</v>
-      </c>
-      <c r="BY98" s="1" t="str">
-        <v>2.800</v>
-      </c>
-      <c r="BZ98" s="1">
-        <v>5</v>
-      </c>
-      <c r="CB98" s="1" t="str">
-        <v>Samuel</v>
-      </c>
-      <c r="CC98" s="1">
+      <c r="CM98" s="1">
         <v>5.9099526066350707</v>
       </c>
     </row>
-    <row r="99" spans="1:81" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:91" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
         <v>7</v>
       </c>
@@ -6302,42 +7294,42 @@
       <c r="V99" s="1">
         <v>1</v>
       </c>
-      <c r="BO99" s="6"/>
-      <c r="BP99" s="1" t="s">
+      <c r="BY99" s="6"/>
+      <c r="BZ99" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="BR99" s="1">
-        <v>7</v>
-      </c>
-      <c r="BS99" s="1" t="str">
+      <c r="CB99" s="1">
+        <v>7</v>
+      </c>
+      <c r="CC99" s="1" t="str">
+        <v>Samuel</v>
+      </c>
+      <c r="CD99" s="1" t="str">
+        <v>5.910</v>
+      </c>
+      <c r="CE99" s="1">
+        <v>211</v>
+      </c>
+      <c r="CG99" s="1">
+        <v>7</v>
+      </c>
+      <c r="CH99" s="1" t="str">
+        <v>Maxime_Go</v>
+      </c>
+      <c r="CI99" s="1" t="str">
+        <v>0.727</v>
+      </c>
+      <c r="CJ99" s="1">
+        <v>11</v>
+      </c>
+      <c r="CL99" s="1" t="str">
         <v>Joachim</v>
       </c>
-      <c r="BT99" s="1" t="str">
-        <v>5.890</v>
-      </c>
-      <c r="BU99" s="1">
-        <v>109</v>
-      </c>
-      <c r="BW99" s="1">
-        <v>7</v>
-      </c>
-      <c r="BX99" s="1" t="str">
-        <v>Maxime_Go</v>
-      </c>
-      <c r="BY99" s="1" t="str">
-        <v>0.727</v>
-      </c>
-      <c r="BZ99" s="1">
-        <v>11</v>
-      </c>
-      <c r="CB99" s="1" t="str">
-        <v>Joachim</v>
-      </c>
-      <c r="CC99" s="1">
+      <c r="CM99" s="1">
         <v>5.8899082568807337</v>
       </c>
     </row>
-    <row r="100" spans="1:81" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:91" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
         <v>7</v>
       </c>
@@ -6368,38 +7360,38 @@
       <c r="AX100" s="1">
         <v>5</v>
       </c>
-      <c r="BR100" s="1">
-        <v>8</v>
-      </c>
-      <c r="BS100" s="1" t="str">
+      <c r="CB100" s="1">
+        <v>8</v>
+      </c>
+      <c r="CC100" s="1" t="str">
+        <v>Joachim</v>
+      </c>
+      <c r="CD100" s="1" t="str">
+        <v>5.890</v>
+      </c>
+      <c r="CE100" s="1">
+        <v>109</v>
+      </c>
+      <c r="CG100" s="1">
+        <v>8</v>
+      </c>
+      <c r="CH100" s="1" t="str">
+        <v>Robin</v>
+      </c>
+      <c r="CI100" s="1" t="str">
+        <v>-0.083</v>
+      </c>
+      <c r="CJ100" s="1">
+        <v>12</v>
+      </c>
+      <c r="CL100" s="1" t="str">
         <v>Mehdi</v>
       </c>
-      <c r="BT100" s="1" t="str">
-        <v>5.770</v>
-      </c>
-      <c r="BU100" s="1">
-        <v>421</v>
-      </c>
-      <c r="BW100" s="1">
-        <v>8</v>
-      </c>
-      <c r="BX100" s="1" t="str">
-        <v>Robin</v>
-      </c>
-      <c r="BY100" s="1" t="str">
-        <v>-0.083</v>
-      </c>
-      <c r="BZ100" s="1">
-        <v>12</v>
-      </c>
-      <c r="CB100" s="1" t="str">
-        <v>Mehdi</v>
-      </c>
-      <c r="CC100" s="1">
-        <v>5.7695961995249405</v>
-      </c>
-    </row>
-    <row r="101" spans="1:81" x14ac:dyDescent="0.3">
+      <c r="CM100" s="1">
+        <v>5.7018779342723001</v>
+      </c>
+    </row>
+    <row r="101" spans="1:91" x14ac:dyDescent="0.3">
       <c r="A101" s="15" t="s">
         <v>7</v>
       </c>
@@ -6475,30 +7467,30 @@
       <c r="AW101" s="15"/>
       <c r="AX101" s="15"/>
       <c r="AY101" s="15"/>
-      <c r="BO101" s="7"/>
-      <c r="BP101" s="1" t="s">
+      <c r="BY101" s="7"/>
+      <c r="BZ101" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="BR101" s="1">
+      <c r="CB101" s="1">
         <v>9</v>
       </c>
-      <c r="BS101" s="1" t="str">
+      <c r="CC101" s="1" t="str">
+        <v>Mehdi</v>
+      </c>
+      <c r="CD101" s="1" t="str">
+        <v>5.702</v>
+      </c>
+      <c r="CE101" s="1">
+        <v>426</v>
+      </c>
+      <c r="CL101" s="1" t="str">
         <v>Jules</v>
       </c>
-      <c r="BT101" s="1" t="str">
-        <v>5.596</v>
-      </c>
-      <c r="BU101" s="1">
-        <v>235</v>
-      </c>
-      <c r="CB101" s="1" t="str">
-        <v>Jules</v>
-      </c>
-      <c r="CC101" s="1">
+      <c r="CM101" s="1">
         <v>5.5957446808510642</v>
       </c>
     </row>
-    <row r="102" spans="1:81" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:91" x14ac:dyDescent="0.3">
       <c r="A102" s="15" t="s">
         <v>7</v>
       </c>
@@ -6570,30 +7562,30 @@
       <c r="AW102" s="15"/>
       <c r="AX102" s="15"/>
       <c r="AY102" s="15"/>
-      <c r="BO102" s="8"/>
-      <c r="BP102" s="1" t="s">
+      <c r="BY102" s="8"/>
+      <c r="BZ102" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="BR102" s="1">
+      <c r="CB102" s="1">
         <v>10</v>
       </c>
-      <c r="BS102" s="1" t="str">
+      <c r="CC102" s="1" t="str">
+        <v>Jules</v>
+      </c>
+      <c r="CD102" s="1" t="str">
+        <v>5.596</v>
+      </c>
+      <c r="CE102" s="1">
+        <v>235</v>
+      </c>
+      <c r="CL102" s="1" t="str">
         <v>Damien</v>
       </c>
-      <c r="BT102" s="1" t="str">
-        <v>5.448</v>
-      </c>
-      <c r="BU102" s="1">
-        <v>725</v>
-      </c>
-      <c r="CB102" s="1" t="str">
-        <v>Damien</v>
-      </c>
-      <c r="CC102" s="1">
-        <v>5.4482758620689653</v>
-      </c>
-    </row>
-    <row r="103" spans="1:81" x14ac:dyDescent="0.3">
+      <c r="CM102" s="1">
+        <v>5.4311050477489768</v>
+      </c>
+    </row>
+    <row r="103" spans="1:91" x14ac:dyDescent="0.3">
       <c r="A103" s="15" t="s">
         <v>7</v>
       </c>
@@ -6665,30 +7657,30 @@
       <c r="AW103" s="15"/>
       <c r="AX103" s="15"/>
       <c r="AY103" s="15"/>
-      <c r="BO103" s="9"/>
-      <c r="BP103" s="1" t="s">
+      <c r="BY103" s="9"/>
+      <c r="BZ103" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="BR103" s="1">
+      <c r="CB103" s="1">
         <v>11</v>
       </c>
-      <c r="BS103" s="1" t="str">
+      <c r="CC103" s="1" t="str">
+        <v>Damien</v>
+      </c>
+      <c r="CD103" s="1" t="str">
+        <v>5.431</v>
+      </c>
+      <c r="CE103" s="1">
+        <v>733</v>
+      </c>
+      <c r="CL103" s="1" t="str">
         <v>Achille</v>
       </c>
-      <c r="BT103" s="1" t="str">
-        <v>5.407</v>
-      </c>
-      <c r="BU103" s="1">
-        <v>829</v>
-      </c>
-      <c r="CB103" s="1" t="str">
-        <v>Achille</v>
-      </c>
-      <c r="CC103" s="1">
+      <c r="CM103" s="1">
         <v>5.4065138721351023</v>
       </c>
     </row>
-    <row r="104" spans="1:81" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:91" x14ac:dyDescent="0.3">
       <c r="A104" s="15" t="s">
         <v>7</v>
       </c>
@@ -6760,26 +7752,26 @@
       <c r="AW104" s="15"/>
       <c r="AX104" s="15"/>
       <c r="AY104" s="15"/>
-      <c r="BR104" s="1">
+      <c r="CB104" s="1">
         <v>12</v>
       </c>
-      <c r="BS104" s="1" t="str">
+      <c r="CC104" s="1" t="str">
+        <v>Achille</v>
+      </c>
+      <c r="CD104" s="1" t="str">
+        <v>5.407</v>
+      </c>
+      <c r="CE104" s="1">
+        <v>829</v>
+      </c>
+      <c r="CL104" s="1" t="str">
         <v>Lou</v>
       </c>
-      <c r="BT104" s="1" t="str">
-        <v>4.950</v>
-      </c>
-      <c r="BU104" s="1">
-        <v>120</v>
-      </c>
-      <c r="CB104" s="1" t="str">
-        <v>Lou</v>
-      </c>
-      <c r="CC104" s="1">
+      <c r="CM104" s="1">
         <v>4.95</v>
       </c>
     </row>
-    <row r="105" spans="1:81" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:91" x14ac:dyDescent="0.3">
       <c r="A105" s="15" t="s">
         <v>7</v>
       </c>
@@ -6855,33 +7847,33 @@
       <c r="AW105" s="15"/>
       <c r="AX105" s="15"/>
       <c r="AY105" s="15"/>
-      <c r="BO105" s="1" t="s">
+      <c r="BY105" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="BP105" s="1">
+      <c r="BZ105" s="1">
         <f>AVERAGE(C1:BF1)</f>
-        <v>5.1359293669380506</v>
-      </c>
-      <c r="BR105" s="1">
+        <v>5.1315139120567252</v>
+      </c>
+      <c r="CB105" s="1">
         <v>13</v>
       </c>
-      <c r="BS105" s="1" t="str">
+      <c r="CC105" s="1" t="str">
+        <v>Lou</v>
+      </c>
+      <c r="CD105" s="1" t="str">
+        <v>4.950</v>
+      </c>
+      <c r="CE105" s="1">
+        <v>120</v>
+      </c>
+      <c r="CL105" s="1" t="str">
         <v>Paul</v>
       </c>
-      <c r="BT105" s="1" t="str">
-        <v>4.813</v>
-      </c>
-      <c r="BU105" s="1">
-        <v>32</v>
-      </c>
-      <c r="CB105" s="1" t="str">
-        <v>Paul</v>
-      </c>
-      <c r="CC105" s="1">
+      <c r="CM105" s="1">
         <v>4.8125</v>
       </c>
     </row>
-    <row r="106" spans="1:81" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:91" x14ac:dyDescent="0.3">
       <c r="A106" s="15" t="s">
         <v>7</v>
       </c>
@@ -6953,26 +7945,26 @@
       <c r="AW106" s="15"/>
       <c r="AX106" s="15"/>
       <c r="AY106" s="15"/>
-      <c r="BR106" s="1">
+      <c r="CB106" s="1">
         <v>14</v>
       </c>
-      <c r="BS106" s="1" t="str">
-        <v>Joey</v>
-      </c>
-      <c r="BT106" s="1" t="str">
-        <v>4.500</v>
-      </c>
-      <c r="BU106" s="1">
-        <v>86</v>
-      </c>
-      <c r="CB106" s="1" t="str">
-        <v>Joey</v>
-      </c>
-      <c r="CC106" s="1">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="107" spans="1:81" x14ac:dyDescent="0.3">
+      <c r="CC106" s="1" t="str">
+        <v>Paul</v>
+      </c>
+      <c r="CD106" s="1" t="str">
+        <v>4.813</v>
+      </c>
+      <c r="CE106" s="1">
+        <v>32</v>
+      </c>
+      <c r="CL106" s="1" t="str">
+        <v>Marie</v>
+      </c>
+      <c r="CM106" s="1">
+        <v>4.6173469387755102</v>
+      </c>
+    </row>
+    <row r="107" spans="1:91" x14ac:dyDescent="0.3">
       <c r="A107" s="15" t="s">
         <v>23</v>
       </c>
@@ -7048,26 +8040,26 @@
       <c r="AW107" s="15"/>
       <c r="AX107" s="15"/>
       <c r="AY107" s="15"/>
-      <c r="BR107" s="1">
+      <c r="CB107" s="1">
         <v>15</v>
       </c>
-      <c r="BS107" s="1" t="str">
-        <v>Stanislas</v>
-      </c>
-      <c r="BT107" s="1" t="str">
-        <v>4.481</v>
-      </c>
-      <c r="BU107" s="1">
-        <v>27</v>
-      </c>
-      <c r="CB107" s="1" t="str">
-        <v>Stanislas</v>
-      </c>
-      <c r="CC107" s="1">
-        <v>4.4814814814814818</v>
-      </c>
-    </row>
-    <row r="108" spans="1:81" x14ac:dyDescent="0.3">
+      <c r="CC107" s="1" t="str">
+        <v>Marie</v>
+      </c>
+      <c r="CD107" s="1" t="str">
+        <v>4.617</v>
+      </c>
+      <c r="CE107" s="1">
+        <v>294</v>
+      </c>
+      <c r="CL107" s="1" t="str">
+        <v>Joey</v>
+      </c>
+      <c r="CM107" s="1">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="108" spans="1:91" x14ac:dyDescent="0.3">
       <c r="A108" s="15" t="s">
         <v>23</v>
       </c>
@@ -7139,29 +8131,29 @@
       <c r="AW108" s="15"/>
       <c r="AX108" s="15"/>
       <c r="AY108" s="15"/>
-      <c r="BP108" s="1" t="s">
+      <c r="BZ108" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="BR108" s="1">
+      <c r="CB108" s="1">
         <v>16</v>
       </c>
-      <c r="BS108" s="1" t="str">
-        <v>Marie</v>
-      </c>
-      <c r="BT108" s="1" t="str">
-        <v>4.470</v>
-      </c>
-      <c r="BU108" s="1">
-        <v>265</v>
-      </c>
-      <c r="CB108" s="1" t="str">
-        <v>Marie</v>
-      </c>
-      <c r="CC108" s="1">
-        <v>4.469811320754717</v>
-      </c>
-    </row>
-    <row r="109" spans="1:81" x14ac:dyDescent="0.3">
+      <c r="CC108" s="1" t="str">
+        <v>Joey</v>
+      </c>
+      <c r="CD108" s="1" t="str">
+        <v>4.500</v>
+      </c>
+      <c r="CE108" s="1">
+        <v>86</v>
+      </c>
+      <c r="CL108" s="1" t="str">
+        <v>Stanislas</v>
+      </c>
+      <c r="CM108" s="1">
+        <v>4.4814814814814818</v>
+      </c>
+    </row>
+    <row r="109" spans="1:91" x14ac:dyDescent="0.3">
       <c r="A109" s="15" t="s">
         <v>7</v>
       </c>
@@ -7241,30 +8233,30 @@
       <c r="AW109" s="15"/>
       <c r="AX109" s="15"/>
       <c r="AY109" s="15"/>
-      <c r="BO109" s="11"/>
-      <c r="BP109" s="1" t="s">
+      <c r="BY109" s="11"/>
+      <c r="BZ109" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="BR109" s="1">
+      <c r="CB109" s="1">
         <v>17</v>
       </c>
-      <c r="BS109" s="1" t="str">
+      <c r="CC109" s="1" t="str">
+        <v>Stanislas</v>
+      </c>
+      <c r="CD109" s="1" t="str">
+        <v>4.481</v>
+      </c>
+      <c r="CE109" s="1">
+        <v>27</v>
+      </c>
+      <c r="CL109" s="1" t="str">
         <v>Quentin</v>
       </c>
-      <c r="BT109" s="1" t="str">
-        <v>4.097</v>
-      </c>
-      <c r="BU109" s="1">
-        <v>93</v>
-      </c>
-      <c r="CB109" s="1" t="str">
-        <v>Quentin</v>
-      </c>
-      <c r="CC109" s="1">
+      <c r="CM109" s="1">
         <v>4.096774193548387</v>
       </c>
     </row>
-    <row r="110" spans="1:81" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:91" x14ac:dyDescent="0.3">
       <c r="A110" s="15" t="s">
         <v>7</v>
       </c>
@@ -7336,30 +8328,30 @@
       <c r="AW110" s="15"/>
       <c r="AX110" s="15"/>
       <c r="AY110" s="15"/>
-      <c r="BO110" s="14"/>
-      <c r="BP110" s="1" t="s">
+      <c r="BY110" s="14"/>
+      <c r="BZ110" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="BR110" s="1">
+      <c r="CB110" s="1">
         <v>18</v>
       </c>
-      <c r="BS110" s="1" t="str">
+      <c r="CC110" s="1" t="str">
+        <v>Quentin</v>
+      </c>
+      <c r="CD110" s="1" t="str">
+        <v>4.097</v>
+      </c>
+      <c r="CE110" s="1">
+        <v>93</v>
+      </c>
+      <c r="CL110" s="1" t="str">
         <v>Luca</v>
       </c>
-      <c r="BT110" s="1" t="str">
-        <v>3.011</v>
-      </c>
-      <c r="BU110" s="1">
-        <v>178</v>
-      </c>
-      <c r="CB110" s="1" t="str">
-        <v>Luca</v>
-      </c>
-      <c r="CC110" s="1">
-        <v>3.0112359550561796</v>
-      </c>
-    </row>
-    <row r="111" spans="1:81" x14ac:dyDescent="0.3">
+      <c r="CM110" s="1">
+        <v>3.129032258064516</v>
+      </c>
+    </row>
+    <row r="111" spans="1:91" x14ac:dyDescent="0.3">
       <c r="A111" s="15" t="s">
         <v>7</v>
       </c>
@@ -7435,30 +8427,30 @@
       <c r="AW111" s="15"/>
       <c r="AX111" s="15"/>
       <c r="AY111" s="15"/>
-      <c r="BO111" s="13"/>
-      <c r="BP111" s="1" t="s">
+      <c r="BY111" s="13"/>
+      <c r="BZ111" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="BR111" s="1">
+      <c r="CB111" s="1">
         <v>19</v>
       </c>
-      <c r="BS111" s="1" t="str">
+      <c r="CC111" s="1" t="str">
+        <v>Luca</v>
+      </c>
+      <c r="CD111" s="1" t="str">
+        <v>3.129</v>
+      </c>
+      <c r="CE111" s="1">
+        <v>186</v>
+      </c>
+      <c r="CL111" s="1" t="str">
         <v>Fantinne</v>
       </c>
-      <c r="BT111" s="1" t="str">
-        <v>2.961</v>
-      </c>
-      <c r="BU111" s="1">
-        <v>51</v>
-      </c>
-      <c r="CB111" s="1" t="str">
-        <v>Fantinne</v>
-      </c>
-      <c r="CC111" s="1">
+      <c r="CM111" s="1">
         <v>2.9607843137254903</v>
       </c>
     </row>
-    <row r="112" spans="1:81" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:91" x14ac:dyDescent="0.3">
       <c r="A112" s="15" t="s">
         <v>7</v>
       </c>
@@ -7530,30 +8522,30 @@
       <c r="AW112" s="15"/>
       <c r="AX112" s="15"/>
       <c r="AY112" s="15"/>
-      <c r="BO112" s="12"/>
-      <c r="BP112" s="1" t="s">
+      <c r="BY112" s="12"/>
+      <c r="BZ112" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="BR112" s="1">
+      <c r="CB112" s="1">
         <v>20</v>
       </c>
-      <c r="BS112" s="1" t="str">
+      <c r="CC112" s="1" t="str">
+        <v>Fantinne</v>
+      </c>
+      <c r="CD112" s="1" t="str">
+        <v>2.961</v>
+      </c>
+      <c r="CE112" s="1">
+        <v>51</v>
+      </c>
+      <c r="CL112" s="1" t="str">
         <v>Loulou</v>
       </c>
-      <c r="BT112" s="1" t="str">
-        <v>2.427</v>
-      </c>
-      <c r="BU112" s="1">
-        <v>75</v>
-      </c>
-      <c r="CB112" s="1" t="str">
-        <v>Loulou</v>
-      </c>
-      <c r="CC112" s="1">
+      <c r="CM112" s="1">
         <v>2.4266666666666667</v>
       </c>
     </row>
-    <row r="113" spans="1:83" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:93" x14ac:dyDescent="0.3">
       <c r="A113" s="15" t="s">
         <v>7</v>
       </c>
@@ -7625,14 +8617,26 @@
       <c r="AW113" s="15"/>
       <c r="AX113" s="15"/>
       <c r="AY113" s="15"/>
-      <c r="CB113" s="1" t="str">
+      <c r="CB113" s="1">
+        <v>21</v>
+      </c>
+      <c r="CC113" s="1" t="str">
+        <v>Loulou</v>
+      </c>
+      <c r="CD113" s="1" t="str">
+        <v>2.427</v>
+      </c>
+      <c r="CE113" s="1">
+        <v>75</v>
+      </c>
+      <c r="CL113" s="1" t="str">
         <v>Harrison</v>
       </c>
-      <c r="CC113" s="1" t="str">
+      <c r="CM113" s="1" t="str">
         <v>/</v>
       </c>
     </row>
-    <row r="114" spans="1:83" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:93" x14ac:dyDescent="0.3">
       <c r="A114" s="15" t="s">
         <v>7</v>
       </c>
@@ -7708,14 +8712,14 @@
       <c r="AW114" s="15"/>
       <c r="AX114" s="15"/>
       <c r="AY114" s="15"/>
-      <c r="CB114" s="1" t="str">
+      <c r="CL114" s="1" t="str">
         <v>Pascale</v>
       </c>
-      <c r="CC114" s="1" t="str">
+      <c r="CM114" s="1" t="str">
         <v>/</v>
       </c>
     </row>
-    <row r="115" spans="1:83" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:93" x14ac:dyDescent="0.3">
       <c r="A115" s="15" t="s">
         <v>7</v>
       </c>
@@ -7791,14 +8795,14 @@
       <c r="AW115" s="15"/>
       <c r="AX115" s="15"/>
       <c r="AY115" s="15"/>
-      <c r="CB115" s="1" t="str">
+      <c r="CL115" s="1" t="str">
         <v>Robin</v>
       </c>
-      <c r="CC115" s="1" t="str">
+      <c r="CM115" s="1" t="str">
         <v>/</v>
       </c>
     </row>
-    <row r="116" spans="1:83" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:93" x14ac:dyDescent="0.3">
       <c r="A116" s="15" t="s">
         <v>25</v>
       </c>
@@ -7854,14 +8858,14 @@
       <c r="AW116" s="15"/>
       <c r="AX116" s="15"/>
       <c r="AY116" s="15"/>
-      <c r="CB116" s="1" t="str">
+      <c r="CL116" s="1" t="str">
         <v>Maxime_Go</v>
       </c>
-      <c r="CC116" s="1" t="str">
+      <c r="CM116" s="1" t="str">
         <v>/</v>
       </c>
     </row>
-    <row r="117" spans="1:83" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:93" x14ac:dyDescent="0.3">
       <c r="A117" s="15" t="s">
         <v>7</v>
       </c>
@@ -7933,14 +8937,14 @@
       <c r="AW117" s="15"/>
       <c r="AX117" s="15"/>
       <c r="AY117" s="15"/>
-      <c r="CB117" s="1" t="str">
+      <c r="CL117" s="1" t="str">
         <v>Maxime_Ca</v>
       </c>
-      <c r="CC117" s="1" t="str">
+      <c r="CM117" s="1" t="str">
         <v>/</v>
       </c>
     </row>
-    <row r="118" spans="1:83" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:93" x14ac:dyDescent="0.3">
       <c r="A118" s="15" t="s">
         <v>7</v>
       </c>
@@ -8016,14 +9020,14 @@
       <c r="AW118" s="15"/>
       <c r="AX118" s="15"/>
       <c r="AY118" s="15"/>
-      <c r="CB118" s="1" t="str">
+      <c r="CL118" s="1" t="str">
         <v>Aurélien</v>
       </c>
-      <c r="CC118" s="1" t="str">
+      <c r="CM118" s="1" t="str">
         <v>/</v>
       </c>
     </row>
-    <row r="119" spans="1:83" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:93" x14ac:dyDescent="0.3">
       <c r="A119" s="15" t="s">
         <v>7</v>
       </c>
@@ -8095,14 +9099,14 @@
       <c r="AW119" s="15"/>
       <c r="AX119" s="15"/>
       <c r="AY119" s="15"/>
-      <c r="CB119" s="1" t="str">
+      <c r="CL119" s="1" t="str">
         <v>Émile</v>
       </c>
-      <c r="CC119" s="1" t="str">
+      <c r="CM119" s="1" t="str">
         <v>/</v>
       </c>
     </row>
-    <row r="120" spans="1:83" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:93" x14ac:dyDescent="0.3">
       <c r="A120" s="15" t="s">
         <v>7</v>
       </c>
@@ -8174,14 +9178,14 @@
       <c r="AW120" s="15"/>
       <c r="AX120" s="15"/>
       <c r="AY120" s="15"/>
-      <c r="CB120" s="1" t="str">
+      <c r="CL120" s="1" t="str">
         <v>Amélie</v>
       </c>
-      <c r="CC120" s="1" t="str">
+      <c r="CM120" s="1" t="str">
         <v>/</v>
       </c>
     </row>
-    <row r="121" spans="1:83" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:93" x14ac:dyDescent="0.3">
       <c r="A121" s="15" t="s">
         <v>7</v>
       </c>
@@ -8254,7 +9258,7 @@
       <c r="AX121" s="15"/>
       <c r="AY121" s="15"/>
     </row>
-    <row r="122" spans="1:83" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:93" x14ac:dyDescent="0.3">
       <c r="A122" s="15" t="s">
         <v>7</v>
       </c>
@@ -8327,7 +9331,7 @@
       <c r="AX122" s="15"/>
       <c r="AY122" s="15"/>
     </row>
-    <row r="123" spans="1:83" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:93" x14ac:dyDescent="0.3">
       <c r="A123" s="15" t="s">
         <v>7</v>
       </c>
@@ -8404,7 +9408,7 @@
       <c r="AX123" s="15"/>
       <c r="AY123" s="15"/>
     </row>
-    <row r="124" spans="1:83" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:93" x14ac:dyDescent="0.3">
       <c r="A124" s="15" t="s">
         <v>7</v>
       </c>
@@ -8477,7 +9481,7 @@
       <c r="AX124" s="15"/>
       <c r="AY124" s="15"/>
     </row>
-    <row r="125" spans="1:83" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:93" x14ac:dyDescent="0.3">
       <c r="A125" s="15" t="s">
         <v>7</v>
       </c>
@@ -8549,8 +9553,8 @@
       <c r="AW125" s="15"/>
       <c r="AX125" s="15"/>
       <c r="AY125" s="15"/>
-      <c r="CB125" s="1" cm="1">
-        <f t="array" ref="CB125:CE144">_xlfn.LET(
+      <c r="CL125" s="1" cm="1">
+        <f t="array" ref="CL125:CO144">_xlfn.LET(
   _xlpm.cols_impairs, _xlfn.SEQUENCE(1,COLUMNS(C1:BF1)/2,1,2),
   _xlpm.cols_pairs,   _xlfn.SEQUENCE(1,COLUMNS(C2:BF2)/2,2,2),
   _xlpm.noms,     TRANSPOSE(INDEX(C9:BF9,,_xlpm.cols_impairs)),
@@ -8569,17 +9573,17 @@
 )</f>
         <v>1</v>
       </c>
-      <c r="CC125" s="1" t="str">
+      <c r="CM125" s="1" t="str">
         <v>Gauthier</v>
       </c>
-      <c r="CD125" s="1">
+      <c r="CN125" s="1">
         <v>7.2530000000000001</v>
       </c>
-      <c r="CE125" s="1">
+      <c r="CO125" s="1">
         <v>79</v>
       </c>
     </row>
-    <row r="126" spans="1:83" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:93" x14ac:dyDescent="0.3">
       <c r="A126" s="15" t="s">
         <v>7</v>
       </c>
@@ -8655,20 +9659,20 @@
       <c r="AW126" s="15"/>
       <c r="AX126" s="15"/>
       <c r="AY126" s="15"/>
-      <c r="CB126" s="1">
-        <v>2</v>
-      </c>
-      <c r="CC126" s="1" t="str">
+      <c r="CL126" s="1">
+        <v>2</v>
+      </c>
+      <c r="CM126" s="1" t="str">
         <v>Boris</v>
       </c>
-      <c r="CD126" s="1">
-        <v>7.165</v>
-      </c>
-      <c r="CE126" s="1">
-        <v>1108</v>
-      </c>
-    </row>
-    <row r="127" spans="1:83" x14ac:dyDescent="0.3">
+      <c r="CN126" s="1">
+        <v>7.15</v>
+      </c>
+      <c r="CO126" s="1">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="127" spans="1:93" x14ac:dyDescent="0.3">
       <c r="A127" s="15" t="s">
         <v>7</v>
       </c>
@@ -8744,20 +9748,20 @@
       <c r="AW127" s="15"/>
       <c r="AX127" s="15"/>
       <c r="AY127" s="15"/>
-      <c r="CB127" s="1">
+      <c r="CL127" s="1">
         <v>3</v>
       </c>
-      <c r="CC127" s="1" t="str">
+      <c r="CM127" s="1" t="str">
         <v>Célian</v>
       </c>
-      <c r="CD127" s="1">
-        <v>6.5090000000000003</v>
-      </c>
-      <c r="CE127" s="1">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="128" spans="1:83" x14ac:dyDescent="0.3">
+      <c r="CN127" s="1">
+        <v>6.2549999999999999</v>
+      </c>
+      <c r="CO127" s="1">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="128" spans="1:93" x14ac:dyDescent="0.3">
       <c r="A128" s="15" t="s">
         <v>7</v>
       </c>
@@ -8829,20 +9833,20 @@
       <c r="AW128" s="15"/>
       <c r="AX128" s="15"/>
       <c r="AY128" s="15"/>
-      <c r="CB128" s="1">
+      <c r="CL128" s="1">
         <v>4</v>
       </c>
-      <c r="CC128" s="1" t="str">
+      <c r="CM128" s="1" t="str">
         <v>William</v>
       </c>
-      <c r="CD128" s="1">
+      <c r="CN128" s="1">
         <v>6.069</v>
       </c>
-      <c r="CE128" s="1">
+      <c r="CO128" s="1">
         <v>29</v>
       </c>
     </row>
-    <row r="129" spans="1:83" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:93" x14ac:dyDescent="0.3">
       <c r="A129" s="15" t="s">
         <v>7</v>
       </c>
@@ -8914,20 +9918,20 @@
       <c r="AW129" s="15"/>
       <c r="AX129" s="15"/>
       <c r="AY129" s="15"/>
-      <c r="CB129" s="1">
+      <c r="CL129" s="1">
         <v>5</v>
       </c>
-      <c r="CC129" s="1" t="str">
+      <c r="CM129" s="1" t="str">
         <v>Tom</v>
       </c>
-      <c r="CD129" s="1">
+      <c r="CN129" s="1">
         <v>5.9930000000000003</v>
       </c>
-      <c r="CE129" s="1">
+      <c r="CO129" s="1">
         <v>286</v>
       </c>
     </row>
-    <row r="130" spans="1:83" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:93" x14ac:dyDescent="0.3">
       <c r="A130" s="15" t="s">
         <v>7</v>
       </c>
@@ -8999,20 +10003,20 @@
       <c r="AW130" s="15"/>
       <c r="AX130" s="15"/>
       <c r="AY130" s="15"/>
-      <c r="CB130" s="1">
+      <c r="CL130" s="1">
         <v>6</v>
       </c>
-      <c r="CC130" s="1" t="str">
+      <c r="CM130" s="1" t="str">
         <v>Samuel</v>
       </c>
-      <c r="CD130" s="1">
+      <c r="CN130" s="1">
         <v>5.91</v>
       </c>
-      <c r="CE130" s="1">
+      <c r="CO130" s="1">
         <v>211</v>
       </c>
     </row>
-    <row r="131" spans="1:83" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:93" x14ac:dyDescent="0.3">
       <c r="A131" s="15" t="s">
         <v>7</v>
       </c>
@@ -9084,20 +10088,20 @@
       <c r="AW131" s="15"/>
       <c r="AX131" s="15"/>
       <c r="AY131" s="15"/>
-      <c r="CB131" s="1">
-        <v>7</v>
-      </c>
-      <c r="CC131" s="1" t="str">
+      <c r="CL131" s="1">
+        <v>7</v>
+      </c>
+      <c r="CM131" s="1" t="str">
         <v>Joachim</v>
       </c>
-      <c r="CD131" s="1">
+      <c r="CN131" s="1">
         <v>5.89</v>
       </c>
-      <c r="CE131" s="1">
+      <c r="CO131" s="1">
         <v>109</v>
       </c>
     </row>
-    <row r="132" spans="1:83" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:93" x14ac:dyDescent="0.3">
       <c r="A132" s="15" t="s">
         <v>7</v>
       </c>
@@ -9174,20 +10178,20 @@
       <c r="AZ132" s="15">
         <v>8</v>
       </c>
-      <c r="CB132" s="1">
-        <v>8</v>
-      </c>
-      <c r="CC132" s="1" t="str">
+      <c r="CL132" s="1">
+        <v>8</v>
+      </c>
+      <c r="CM132" s="1" t="str">
         <v>Mehdi</v>
       </c>
-      <c r="CD132" s="1">
-        <v>5.77</v>
-      </c>
-      <c r="CE132" s="1">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="133" spans="1:83" x14ac:dyDescent="0.3">
+      <c r="CN132" s="1">
+        <v>5.702</v>
+      </c>
+      <c r="CO132" s="1">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="133" spans="1:93" x14ac:dyDescent="0.3">
       <c r="A133" s="15" t="s">
         <v>7</v>
       </c>
@@ -9263,20 +10267,20 @@
       <c r="AW133" s="15"/>
       <c r="AX133" s="15"/>
       <c r="AY133" s="15"/>
-      <c r="CB133" s="1">
+      <c r="CL133" s="1">
         <v>9</v>
       </c>
-      <c r="CC133" s="1" t="str">
+      <c r="CM133" s="1" t="str">
         <v>Jules</v>
       </c>
-      <c r="CD133" s="1">
+      <c r="CN133" s="1">
         <v>5.5960000000000001</v>
       </c>
-      <c r="CE133" s="1">
+      <c r="CO133" s="1">
         <v>235</v>
       </c>
     </row>
-    <row r="134" spans="1:83" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:93" x14ac:dyDescent="0.3">
       <c r="A134" s="15" t="s">
         <v>7</v>
       </c>
@@ -9352,20 +10356,20 @@
       <c r="AW134" s="15"/>
       <c r="AX134" s="15"/>
       <c r="AY134" s="15"/>
-      <c r="CB134" s="1">
+      <c r="CL134" s="1">
         <v>10</v>
       </c>
-      <c r="CC134" s="1" t="str">
+      <c r="CM134" s="1" t="str">
         <v>Damien</v>
       </c>
-      <c r="CD134" s="1">
-        <v>5.4480000000000004</v>
-      </c>
-      <c r="CE134" s="1">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="135" spans="1:83" x14ac:dyDescent="0.3">
+      <c r="CN134" s="1">
+        <v>5.431</v>
+      </c>
+      <c r="CO134" s="1">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="135" spans="1:93" x14ac:dyDescent="0.3">
       <c r="A135" s="15" t="s">
         <v>7</v>
       </c>
@@ -9437,20 +10441,20 @@
       <c r="AW135" s="15"/>
       <c r="AX135" s="15"/>
       <c r="AY135" s="15"/>
-      <c r="CB135" s="1">
+      <c r="CL135" s="1">
         <v>11</v>
       </c>
-      <c r="CC135" s="1" t="str">
+      <c r="CM135" s="1" t="str">
         <v>Achille</v>
       </c>
-      <c r="CD135" s="1">
+      <c r="CN135" s="1">
         <v>5.407</v>
       </c>
-      <c r="CE135" s="1">
+      <c r="CO135" s="1">
         <v>829</v>
       </c>
     </row>
-    <row r="136" spans="1:83" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:93" x14ac:dyDescent="0.3">
       <c r="A136" s="15" t="s">
         <v>7</v>
       </c>
@@ -9522,20 +10526,20 @@
       <c r="AW136" s="15"/>
       <c r="AX136" s="15"/>
       <c r="AY136" s="15"/>
-      <c r="CB136" s="1">
+      <c r="CL136" s="1">
         <v>12</v>
       </c>
-      <c r="CC136" s="1" t="str">
+      <c r="CM136" s="1" t="str">
         <v>Lou</v>
       </c>
-      <c r="CD136" s="1">
+      <c r="CN136" s="1">
         <v>4.95</v>
       </c>
-      <c r="CE136" s="1">
+      <c r="CO136" s="1">
         <v>120</v>
       </c>
     </row>
-    <row r="137" spans="1:83" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:93" x14ac:dyDescent="0.3">
       <c r="A137" s="15" t="s">
         <v>7</v>
       </c>
@@ -9603,20 +10607,20 @@
       <c r="AW137" s="15"/>
       <c r="AX137" s="15"/>
       <c r="AY137" s="15"/>
-      <c r="CB137" s="1">
+      <c r="CL137" s="1">
         <v>13</v>
       </c>
-      <c r="CC137" s="1" t="str">
+      <c r="CM137" s="1" t="str">
         <v>Paul</v>
       </c>
-      <c r="CD137" s="1">
+      <c r="CN137" s="1">
         <v>4.8129999999999997</v>
       </c>
-      <c r="CE137" s="1">
+      <c r="CO137" s="1">
         <v>32</v>
       </c>
     </row>
-    <row r="138" spans="1:83" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:93" x14ac:dyDescent="0.3">
       <c r="A138" s="15" t="s">
         <v>7</v>
       </c>
@@ -9692,20 +10696,20 @@
       <c r="AW138" s="15"/>
       <c r="AX138" s="15"/>
       <c r="AY138" s="15"/>
-      <c r="CB138" s="1">
+      <c r="CL138" s="1">
         <v>14</v>
       </c>
-      <c r="CC138" s="1" t="str">
-        <v>Joey</v>
-      </c>
-      <c r="CD138" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="CE138" s="1">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="139" spans="1:83" x14ac:dyDescent="0.3">
+      <c r="CM138" s="1" t="str">
+        <v>Marie</v>
+      </c>
+      <c r="CN138" s="1">
+        <v>4.617</v>
+      </c>
+      <c r="CO138" s="1">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="139" spans="1:93" x14ac:dyDescent="0.3">
       <c r="A139" s="15" t="s">
         <v>7</v>
       </c>
@@ -9777,20 +10781,20 @@
       <c r="AW139" s="15"/>
       <c r="AX139" s="15"/>
       <c r="AY139" s="15"/>
-      <c r="CB139" s="1">
+      <c r="CL139" s="1">
         <v>15</v>
       </c>
-      <c r="CC139" s="1" t="str">
-        <v>Stanislas</v>
-      </c>
-      <c r="CD139" s="1">
-        <v>4.4809999999999999</v>
-      </c>
-      <c r="CE139" s="1">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="140" spans="1:83" x14ac:dyDescent="0.3">
+      <c r="CM139" s="1" t="str">
+        <v>Joey</v>
+      </c>
+      <c r="CN139" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="CO139" s="1">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="140" spans="1:93" x14ac:dyDescent="0.3">
       <c r="A140" s="15" t="s">
         <v>7</v>
       </c>
@@ -9862,20 +10866,20 @@
       <c r="AW140" s="15"/>
       <c r="AX140" s="15"/>
       <c r="AY140" s="15"/>
-      <c r="CB140" s="1">
+      <c r="CL140" s="1">
         <v>16</v>
       </c>
-      <c r="CC140" s="1" t="str">
-        <v>Marie</v>
-      </c>
-      <c r="CD140" s="1">
-        <v>4.47</v>
-      </c>
-      <c r="CE140" s="1">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="141" spans="1:83" x14ac:dyDescent="0.3">
+      <c r="CM140" s="1" t="str">
+        <v>Stanislas</v>
+      </c>
+      <c r="CN140" s="1">
+        <v>4.4809999999999999</v>
+      </c>
+      <c r="CO140" s="1">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="141" spans="1:93" x14ac:dyDescent="0.3">
       <c r="A141" s="15" t="s">
         <v>7</v>
       </c>
@@ -9947,20 +10951,20 @@
       <c r="AW141" s="15"/>
       <c r="AX141" s="15"/>
       <c r="AY141" s="15"/>
-      <c r="CB141" s="1">
+      <c r="CL141" s="1">
         <v>17</v>
       </c>
-      <c r="CC141" s="1" t="str">
+      <c r="CM141" s="1" t="str">
         <v>Quentin</v>
       </c>
-      <c r="CD141" s="1">
+      <c r="CN141" s="1">
         <v>4.0970000000000004</v>
       </c>
-      <c r="CE141" s="1">
+      <c r="CO141" s="1">
         <v>93</v>
       </c>
     </row>
-    <row r="142" spans="1:83" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:93" x14ac:dyDescent="0.3">
       <c r="A142" s="15" t="s">
         <v>7</v>
       </c>
@@ -10040,20 +11044,20 @@
       <c r="AW142" s="15"/>
       <c r="AX142" s="15"/>
       <c r="AY142" s="15"/>
-      <c r="CB142" s="1">
+      <c r="CL142" s="1">
         <v>18</v>
       </c>
-      <c r="CC142" s="1" t="str">
+      <c r="CM142" s="1" t="str">
         <v>Luca</v>
       </c>
-      <c r="CD142" s="1">
-        <v>3.0110000000000001</v>
-      </c>
-      <c r="CE142" s="1">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="143" spans="1:83" x14ac:dyDescent="0.3">
+      <c r="CN142" s="1">
+        <v>3.129</v>
+      </c>
+      <c r="CO142" s="1">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="143" spans="1:93" x14ac:dyDescent="0.3">
       <c r="A143" s="15" t="s">
         <v>7</v>
       </c>
@@ -10125,20 +11129,20 @@
       <c r="AW143" s="15"/>
       <c r="AX143" s="15"/>
       <c r="AY143" s="15"/>
-      <c r="CB143" s="1">
+      <c r="CL143" s="1">
         <v>19</v>
       </c>
-      <c r="CC143" s="1" t="str">
+      <c r="CM143" s="1" t="str">
         <v>Fantinne</v>
       </c>
-      <c r="CD143" s="1">
+      <c r="CN143" s="1">
         <v>2.9609999999999999</v>
       </c>
-      <c r="CE143" s="1">
+      <c r="CO143" s="1">
         <v>51</v>
       </c>
     </row>
-    <row r="144" spans="1:83" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:93" x14ac:dyDescent="0.3">
       <c r="A144" s="15" t="s">
         <v>7</v>
       </c>
@@ -10214,20 +11218,20 @@
       <c r="AW144" s="15"/>
       <c r="AX144" s="15"/>
       <c r="AY144" s="15"/>
-      <c r="CB144" s="1">
+      <c r="CL144" s="1">
         <v>20</v>
       </c>
-      <c r="CC144" s="1" t="str">
+      <c r="CM144" s="1" t="str">
         <v>Loulou</v>
       </c>
-      <c r="CD144" s="1">
+      <c r="CN144" s="1">
         <v>2.427</v>
       </c>
-      <c r="CE144" s="1">
+      <c r="CO144" s="1">
         <v>75</v>
       </c>
     </row>
-    <row r="145" spans="1:86" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A145" s="15" t="s">
         <v>7</v>
       </c>
@@ -10300,7 +11304,7 @@
       <c r="AX145" s="15"/>
       <c r="AY145" s="15"/>
     </row>
-    <row r="146" spans="1:86" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A146" s="15" t="s">
         <v>7</v>
       </c>
@@ -10377,7 +11381,7 @@
       <c r="AX146" s="15"/>
       <c r="AY146" s="15"/>
     </row>
-    <row r="147" spans="1:86" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A147" s="15" t="s">
         <v>7</v>
       </c>
@@ -10450,7 +11454,7 @@
       <c r="AX147" s="15"/>
       <c r="AY147" s="15"/>
     </row>
-    <row r="148" spans="1:86" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A148" s="15" t="s">
         <v>7</v>
       </c>
@@ -10523,7 +11527,7 @@
       <c r="AX148" s="15"/>
       <c r="AY148" s="15"/>
     </row>
-    <row r="149" spans="1:86" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A149" s="15" t="s">
         <v>7</v>
       </c>
@@ -10596,7 +11600,7 @@
       <c r="AX149" s="15"/>
       <c r="AY149" s="15"/>
     </row>
-    <row r="150" spans="1:86" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A150" s="15" t="s">
         <v>7</v>
       </c>
@@ -10669,7 +11673,7 @@
       <c r="AX150" s="15"/>
       <c r="AY150" s="15"/>
     </row>
-    <row r="151" spans="1:86" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A151" s="15" t="s">
         <v>7</v>
       </c>
@@ -10741,8 +11745,8 @@
       <c r="AW151" s="15"/>
       <c r="AX151" s="15"/>
       <c r="AY151" s="15"/>
-      <c r="CB151" s="1" t="str" cm="1">
-        <f t="array" ref="CB151:CD168">_xlfn.LET(_xlpm.cols_impairs, _xlfn.SEQUENCE(1,COLUMNS(C1:AZ1)/2,1,2),
+      <c r="CL151" s="1" t="str" cm="1">
+        <f t="array" ref="CL151:CN168">_xlfn.LET(_xlpm.cols_impairs, _xlfn.SEQUENCE(1,COLUMNS(C1:AZ1)/2,1,2),
   _xlpm.cols_pairs,   _xlfn.SEQUENCE(1,COLUMNS(C2:AZ2)/2,2,2),
   _xlpm.noms,     TRANSPOSE(INDEX(C9:AZ9,,_xlpm.cols_impairs)),
   _xlpm.moy,      TRANSPOSE(INDEX(C1:AZ1,,_xlpm.cols_impairs)),
@@ -10752,21 +11756,21 @@
 )</f>
         <v>Gauthier</v>
       </c>
-      <c r="CC151" s="1">
+      <c r="CM151" s="1">
         <v>7.2531645569620249</v>
       </c>
-      <c r="CD151" s="1">
+      <c r="CN151" s="1">
         <v>79</v>
       </c>
-      <c r="CG151" s="1" t="str" cm="1">
-        <f t="array" ref="CG151:CH170">_xlfn.LET(  _xlpm.noms, TRANSPOSE(INDEX(C9:BF9,_xlfn.SEQUENCE(1,COLUMNS(C9:BF9)/2,1,2))),_xlpm.moy,  TRANSPOSE(INDEX(C1:BF1,,_xlfn.SEQUENCE(1,COLUMNS(C1:BF1)/2,1,2))),_xlpm.ok, ISNUMBER(_xlpm.moy),_xlfn._xlws.SORT(CHOOSE({1,2}, _xlfn._xlws.FILTER(_xlpm.noms, _xlpm.ok), _xlfn._xlws.FILTER(_xlpm.moy, _xlpm.ok)), 2, -1))</f>
+      <c r="CQ151" s="1" t="str" cm="1">
+        <f t="array" ref="CQ151:CR170">_xlfn.LET(  _xlpm.noms, TRANSPOSE(INDEX(C9:BF9,_xlfn.SEQUENCE(1,COLUMNS(C9:BF9)/2,1,2))),_xlpm.moy,  TRANSPOSE(INDEX(C1:BF1,,_xlfn.SEQUENCE(1,COLUMNS(C1:BF1)/2,1,2))),_xlpm.ok, ISNUMBER(_xlpm.moy),_xlfn._xlws.SORT(CHOOSE({1,2}, _xlfn._xlws.FILTER(_xlpm.noms, _xlpm.ok), _xlfn._xlws.FILTER(_xlpm.moy, _xlpm.ok)), 2, -1))</f>
         <v>Gauthier</v>
       </c>
-      <c r="CH151" s="1">
+      <c r="CR151" s="1">
         <v>7.2531645569620249</v>
       </c>
     </row>
-    <row r="152" spans="1:86" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A152" s="15" t="s">
         <v>7</v>
       </c>
@@ -10838,23 +11842,23 @@
       <c r="AW152" s="15"/>
       <c r="AX152" s="15"/>
       <c r="AY152" s="15"/>
-      <c r="CB152" s="1" t="str">
+      <c r="CL152" s="1" t="str">
         <v>Boris</v>
       </c>
-      <c r="CC152" s="1">
-        <v>7.1647111913357397</v>
-      </c>
-      <c r="CD152" s="1">
-        <v>1108</v>
-      </c>
-      <c r="CG152" s="1" t="str">
+      <c r="CM152" s="1">
+        <v>7.1504385964912283</v>
+      </c>
+      <c r="CN152" s="1">
+        <v>1140</v>
+      </c>
+      <c r="CQ152" s="1" t="str">
         <v>Boris</v>
       </c>
-      <c r="CH152" s="1">
-        <v>7.1647111913357397</v>
-      </c>
-    </row>
-    <row r="153" spans="1:86" x14ac:dyDescent="0.3">
+      <c r="CR152" s="1">
+        <v>7.1504385964912283</v>
+      </c>
+    </row>
+    <row r="153" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A153" s="15" t="s">
         <v>7</v>
       </c>
@@ -10926,23 +11930,23 @@
       <c r="AW153" s="15"/>
       <c r="AX153" s="15"/>
       <c r="AY153" s="15"/>
-      <c r="CB153" s="1" t="str">
+      <c r="CL153" s="1" t="str">
         <v>Célian</v>
       </c>
-      <c r="CC153" s="1">
-        <v>6.5094936708860756</v>
-      </c>
-      <c r="CD153" s="1">
-        <v>316</v>
-      </c>
-      <c r="CG153" s="1" t="str">
+      <c r="CM153" s="1">
+        <v>6.2550143266475642</v>
+      </c>
+      <c r="CN153" s="1">
+        <v>349</v>
+      </c>
+      <c r="CQ153" s="1" t="str">
         <v>Célian</v>
       </c>
-      <c r="CH153" s="1">
-        <v>6.5094936708860756</v>
-      </c>
-    </row>
-    <row r="154" spans="1:86" x14ac:dyDescent="0.3">
+      <c r="CR153" s="1">
+        <v>6.2550143266475642</v>
+      </c>
+    </row>
+    <row r="154" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A154" s="15" t="s">
         <v>7</v>
       </c>
@@ -11014,23 +12018,23 @@
       <c r="AW154" s="15"/>
       <c r="AX154" s="15"/>
       <c r="AY154" s="15"/>
-      <c r="CB154" s="1" t="str">
+      <c r="CL154" s="1" t="str">
         <v>William</v>
       </c>
-      <c r="CC154" s="1">
+      <c r="CM154" s="1">
         <v>6.068965517241379</v>
       </c>
-      <c r="CD154" s="1">
+      <c r="CN154" s="1">
         <v>29</v>
       </c>
-      <c r="CG154" s="1" t="str">
+      <c r="CQ154" s="1" t="str">
         <v>William</v>
       </c>
-      <c r="CH154" s="1">
+      <c r="CR154" s="1">
         <v>6.068965517241379</v>
       </c>
     </row>
-    <row r="155" spans="1:86" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A155" s="15" t="s">
         <v>7</v>
       </c>
@@ -11102,23 +12106,23 @@
       <c r="AW155" s="15"/>
       <c r="AX155" s="15"/>
       <c r="AY155" s="15"/>
-      <c r="CB155" s="1" t="str">
+      <c r="CL155" s="1" t="str">
         <v>Tom</v>
       </c>
-      <c r="CC155" s="1">
+      <c r="CM155" s="1">
         <v>5.9930069930069934</v>
       </c>
-      <c r="CD155" s="1">
+      <c r="CN155" s="1">
         <v>286</v>
       </c>
-      <c r="CG155" s="1" t="str">
+      <c r="CQ155" s="1" t="str">
         <v>Tom</v>
       </c>
-      <c r="CH155" s="1">
+      <c r="CR155" s="1">
         <v>5.9930069930069934</v>
       </c>
     </row>
-    <row r="156" spans="1:86" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A156" s="15" t="s">
         <v>7</v>
       </c>
@@ -11190,23 +12194,23 @@
       <c r="AW156" s="15"/>
       <c r="AX156" s="15"/>
       <c r="AY156" s="15"/>
-      <c r="CB156" s="1" t="str">
+      <c r="CL156" s="1" t="str">
         <v>Samuel</v>
       </c>
-      <c r="CC156" s="1">
+      <c r="CM156" s="1">
         <v>5.9099526066350707</v>
       </c>
-      <c r="CD156" s="1">
+      <c r="CN156" s="1">
         <v>211</v>
       </c>
-      <c r="CG156" s="1" t="str">
+      <c r="CQ156" s="1" t="str">
         <v>Samuel</v>
       </c>
-      <c r="CH156" s="1">
+      <c r="CR156" s="1">
         <v>5.9099526066350707</v>
       </c>
     </row>
-    <row r="157" spans="1:86" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A157" s="15" t="s">
         <v>7</v>
       </c>
@@ -11278,23 +12282,23 @@
       <c r="AW157" s="15"/>
       <c r="AX157" s="15"/>
       <c r="AY157" s="15"/>
-      <c r="CB157" s="1" t="str">
+      <c r="CL157" s="1" t="str">
         <v>Joachim</v>
       </c>
-      <c r="CC157" s="1">
+      <c r="CM157" s="1">
         <v>5.8899082568807337</v>
       </c>
-      <c r="CD157" s="1">
+      <c r="CN157" s="1">
         <v>109</v>
       </c>
-      <c r="CG157" s="1" t="str">
+      <c r="CQ157" s="1" t="str">
         <v>Joachim</v>
       </c>
-      <c r="CH157" s="1">
+      <c r="CR157" s="1">
         <v>5.8899082568807337</v>
       </c>
     </row>
-    <row r="158" spans="1:86" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A158" s="15" t="s">
         <v>7</v>
       </c>
@@ -11370,23 +12374,23 @@
       <c r="AW158" s="15"/>
       <c r="AX158" s="15"/>
       <c r="AY158" s="15"/>
-      <c r="CB158" s="1" t="str">
+      <c r="CL158" s="1" t="str">
         <v>Mehdi</v>
       </c>
-      <c r="CC158" s="1">
-        <v>5.7695961995249405</v>
-      </c>
-      <c r="CD158" s="1">
-        <v>421</v>
-      </c>
-      <c r="CG158" s="1" t="str">
+      <c r="CM158" s="1">
+        <v>5.7018779342723001</v>
+      </c>
+      <c r="CN158" s="1">
+        <v>426</v>
+      </c>
+      <c r="CQ158" s="1" t="str">
         <v>Mehdi</v>
       </c>
-      <c r="CH158" s="1">
-        <v>5.7695961995249405</v>
-      </c>
-    </row>
-    <row r="159" spans="1:86" x14ac:dyDescent="0.3">
+      <c r="CR158" s="1">
+        <v>5.7018779342723001</v>
+      </c>
+    </row>
+    <row r="159" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A159" s="15" t="s">
         <v>7</v>
       </c>
@@ -11458,46 +12462,46 @@
       <c r="AW159" s="15"/>
       <c r="AX159" s="15"/>
       <c r="AY159" s="15"/>
-      <c r="CB159" s="1" t="str">
+      <c r="CL159" s="1" t="str">
         <v>Jules</v>
       </c>
-      <c r="CC159" s="1">
+      <c r="CM159" s="1">
         <v>5.5957446808510642</v>
       </c>
-      <c r="CD159" s="1">
+      <c r="CN159" s="1">
         <v>235</v>
       </c>
-      <c r="CG159" s="1" t="str">
+      <c r="CQ159" s="1" t="str">
         <v>Jules</v>
       </c>
-      <c r="CH159" s="1">
+      <c r="CR159" s="1">
         <v>5.5957446808510642</v>
       </c>
     </row>
-    <row r="160" spans="1:86" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A160" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B160" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="CB160" s="1" t="str">
+      <c r="CL160" s="1" t="str">
         <v>Damien</v>
       </c>
-      <c r="CC160" s="1">
-        <v>5.4482758620689653</v>
-      </c>
-      <c r="CD160" s="1">
-        <v>725</v>
-      </c>
-      <c r="CG160" s="1" t="str">
+      <c r="CM160" s="1">
+        <v>5.4311050477489768</v>
+      </c>
+      <c r="CN160" s="1">
+        <v>733</v>
+      </c>
+      <c r="CQ160" s="1" t="str">
         <v>Damien</v>
       </c>
-      <c r="CH160" s="1">
-        <v>5.4482758620689653</v>
-      </c>
-    </row>
-    <row r="161" spans="1:86" x14ac:dyDescent="0.3">
+      <c r="CR160" s="1">
+        <v>5.4311050477489768</v>
+      </c>
+    </row>
+    <row r="161" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A161" s="1" t="s">
         <v>7</v>
       </c>
@@ -11528,23 +12532,23 @@
       <c r="Z161" s="1">
         <v>11</v>
       </c>
-      <c r="CB161" s="1" t="str">
+      <c r="CL161" s="1" t="str">
         <v>Achille</v>
       </c>
-      <c r="CC161" s="1">
+      <c r="CM161" s="1">
         <v>5.4065138721351023</v>
       </c>
-      <c r="CD161" s="1">
+      <c r="CN161" s="1">
         <v>829</v>
       </c>
-      <c r="CG161" s="1" t="str">
+      <c r="CQ161" s="1" t="str">
         <v>Achille</v>
       </c>
-      <c r="CH161" s="1">
+      <c r="CR161" s="1">
         <v>5.4065138721351023</v>
       </c>
     </row>
-    <row r="162" spans="1:86" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A162" s="1" t="s">
         <v>7</v>
       </c>
@@ -11575,23 +12579,23 @@
       <c r="N162" s="1">
         <v>20</v>
       </c>
-      <c r="CB162" s="1" t="str">
+      <c r="CL162" s="1" t="str">
         <v>Paul</v>
       </c>
-      <c r="CC162" s="1">
+      <c r="CM162" s="1">
         <v>4.8125</v>
       </c>
-      <c r="CD162" s="1">
+      <c r="CN162" s="1">
         <v>32</v>
       </c>
-      <c r="CG162" s="1" t="str">
+      <c r="CQ162" s="1" t="str">
         <v>Lou</v>
       </c>
-      <c r="CH162" s="1">
+      <c r="CR162" s="1">
         <v>4.95</v>
       </c>
     </row>
-    <row r="163" spans="1:86" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A163" s="1" t="s">
         <v>7</v>
       </c>
@@ -11622,23 +12626,23 @@
       <c r="N163" s="1">
         <v>8</v>
       </c>
-      <c r="CB163" s="1" t="str">
-        <v>Joey</v>
-      </c>
-      <c r="CC163" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="CD163" s="1">
-        <v>86</v>
-      </c>
-      <c r="CG163" s="1" t="str">
+      <c r="CL163" s="1" t="str">
+        <v>Marie</v>
+      </c>
+      <c r="CM163" s="1">
+        <v>4.6173469387755102</v>
+      </c>
+      <c r="CN163" s="1">
+        <v>294</v>
+      </c>
+      <c r="CQ163" s="1" t="str">
         <v>Paul</v>
       </c>
-      <c r="CH163" s="1">
+      <c r="CR163" s="1">
         <v>4.8125</v>
       </c>
     </row>
-    <row r="164" spans="1:86" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A164" s="1" t="s">
         <v>7</v>
       </c>
@@ -11669,23 +12673,23 @@
       <c r="AB164" s="1">
         <v>9</v>
       </c>
-      <c r="CB164" s="1" t="str">
+      <c r="CL164" s="1" t="str">
+        <v>Joey</v>
+      </c>
+      <c r="CM164" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="CN164" s="1">
+        <v>86</v>
+      </c>
+      <c r="CQ164" s="1" t="str">
         <v>Marie</v>
       </c>
-      <c r="CC164" s="1">
-        <v>4.469811320754717</v>
-      </c>
-      <c r="CD164" s="1">
-        <v>265</v>
-      </c>
-      <c r="CG164" s="1" t="str">
-        <v>Joey</v>
-      </c>
-      <c r="CH164" s="1">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="165" spans="1:86" x14ac:dyDescent="0.3">
+      <c r="CR164" s="1">
+        <v>4.6173469387755102</v>
+      </c>
+    </row>
+    <row r="165" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A165" s="1" t="s">
         <v>7</v>
       </c>
@@ -11716,23 +12720,23 @@
       <c r="AB165" s="1">
         <v>12</v>
       </c>
-      <c r="CB165" s="1" t="str">
+      <c r="CL165" s="1" t="str">
         <v>Quentin</v>
       </c>
-      <c r="CC165" s="1">
+      <c r="CM165" s="1">
         <v>4.096774193548387</v>
       </c>
-      <c r="CD165" s="1">
+      <c r="CN165" s="1">
         <v>93</v>
       </c>
-      <c r="CG165" s="1" t="str">
-        <v>Stanislas</v>
-      </c>
-      <c r="CH165" s="1">
-        <v>4.4814814814814818</v>
-      </c>
-    </row>
-    <row r="166" spans="1:86" x14ac:dyDescent="0.3">
+      <c r="CQ165" s="1" t="str">
+        <v>Joey</v>
+      </c>
+      <c r="CR165" s="1">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="166" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A166" s="1" t="s">
         <v>7</v>
       </c>
@@ -11763,23 +12767,23 @@
       <c r="P166" s="1">
         <v>2</v>
       </c>
-      <c r="CB166" s="1" t="str">
+      <c r="CL166" s="1" t="str">
         <v>Luca</v>
       </c>
-      <c r="CC166" s="1">
-        <v>3.0112359550561796</v>
-      </c>
-      <c r="CD166" s="1">
-        <v>178</v>
-      </c>
-      <c r="CG166" s="1" t="str">
-        <v>Marie</v>
-      </c>
-      <c r="CH166" s="1">
-        <v>4.469811320754717</v>
-      </c>
-    </row>
-    <row r="167" spans="1:86" x14ac:dyDescent="0.3">
+      <c r="CM166" s="1">
+        <v>3.129032258064516</v>
+      </c>
+      <c r="CN166" s="1">
+        <v>186</v>
+      </c>
+      <c r="CQ166" s="1" t="str">
+        <v>Stanislas</v>
+      </c>
+      <c r="CR166" s="1">
+        <v>4.4814814814814818</v>
+      </c>
+    </row>
+    <row r="167" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A167" s="1" t="s">
         <v>7</v>
       </c>
@@ -11810,23 +12814,23 @@
       <c r="J167" s="1">
         <v>13</v>
       </c>
-      <c r="CB167" s="1" t="str">
+      <c r="CL167" s="1" t="str">
         <v>Fantinne</v>
       </c>
-      <c r="CC167" s="1">
+      <c r="CM167" s="1">
         <v>2.9607843137254903</v>
       </c>
-      <c r="CD167" s="1">
+      <c r="CN167" s="1">
         <v>51</v>
       </c>
-      <c r="CG167" s="1" t="str">
+      <c r="CQ167" s="1" t="str">
         <v>Quentin</v>
       </c>
-      <c r="CH167" s="1">
+      <c r="CR167" s="1">
         <v>4.096774193548387</v>
       </c>
     </row>
-    <row r="168" spans="1:86" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A168" s="1" t="s">
         <v>7</v>
       </c>
@@ -11857,23 +12861,23 @@
       <c r="X168" s="1">
         <v>9</v>
       </c>
-      <c r="CB168" s="1" t="str">
+      <c r="CL168" s="1" t="str">
         <v>Loulou</v>
       </c>
-      <c r="CC168" s="1">
+      <c r="CM168" s="1">
         <v>2.4266666666666667</v>
       </c>
-      <c r="CD168" s="1">
+      <c r="CN168" s="1">
         <v>75</v>
       </c>
-      <c r="CG168" s="1" t="str">
+      <c r="CQ168" s="1" t="str">
         <v>Luca</v>
       </c>
-      <c r="CH168" s="1">
-        <v>3.0112359550561796</v>
-      </c>
-    </row>
-    <row r="169" spans="1:86" x14ac:dyDescent="0.3">
+      <c r="CR168" s="1">
+        <v>3.129032258064516</v>
+      </c>
+    </row>
+    <row r="169" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A169" s="1" t="s">
         <v>7</v>
       </c>
@@ -11904,14 +12908,14 @@
       <c r="J169" s="1">
         <v>11</v>
       </c>
-      <c r="CG169" s="1" t="str">
+      <c r="CQ169" s="1" t="str">
         <v>Fantinne</v>
       </c>
-      <c r="CH169" s="1">
+      <c r="CR169" s="1">
         <v>2.9607843137254903</v>
       </c>
     </row>
-    <row r="170" spans="1:86" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A170" s="1" t="s">
         <v>7</v>
       </c>
@@ -11942,14 +12946,14 @@
       <c r="N170" s="1">
         <v>13</v>
       </c>
-      <c r="CG170" s="1" t="str">
+      <c r="CQ170" s="1" t="str">
         <v>Loulou</v>
       </c>
-      <c r="CH170" s="1">
+      <c r="CR170" s="1">
         <v>2.4266666666666667</v>
       </c>
     </row>
-    <row r="171" spans="1:86" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A171" s="1" t="s">
         <v>7</v>
       </c>
@@ -11981,7 +12985,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="172" spans="1:86" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A172" s="1" t="s">
         <v>7</v>
       </c>
@@ -12017,25 +13021,12 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A161:AM172">
     <sortCondition descending="1" ref="B161:B172"/>
   </sortState>
-  <mergeCells count="31">
-    <mergeCell ref="BG9:BH9"/>
-    <mergeCell ref="BI9:BJ9"/>
-    <mergeCell ref="BK9:BL9"/>
-    <mergeCell ref="BA9:BB9"/>
-    <mergeCell ref="BC9:BD9"/>
-    <mergeCell ref="BE9:BF9"/>
-    <mergeCell ref="Y9:Z9"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="K9:L9"/>
-    <mergeCell ref="M9:N9"/>
-    <mergeCell ref="O9:P9"/>
-    <mergeCell ref="Q9:R9"/>
-    <mergeCell ref="S9:T9"/>
-    <mergeCell ref="U9:V9"/>
-    <mergeCell ref="W9:X9"/>
+  <mergeCells count="36">
+    <mergeCell ref="BM9:BN9"/>
+    <mergeCell ref="BO9:BP9"/>
+    <mergeCell ref="BQ9:BR9"/>
+    <mergeCell ref="BS9:BT9"/>
+    <mergeCell ref="BU9:BV9"/>
     <mergeCell ref="AW9:AX9"/>
     <mergeCell ref="AY9:AZ9"/>
     <mergeCell ref="AA9:AB9"/>
@@ -12049,97 +13040,115 @@
     <mergeCell ref="AQ9:AR9"/>
     <mergeCell ref="AS9:AT9"/>
     <mergeCell ref="AU9:AV9"/>
+    <mergeCell ref="Y9:Z9"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="K9:L9"/>
+    <mergeCell ref="M9:N9"/>
+    <mergeCell ref="O9:P9"/>
+    <mergeCell ref="Q9:R9"/>
+    <mergeCell ref="S9:T9"/>
+    <mergeCell ref="U9:V9"/>
+    <mergeCell ref="W9:X9"/>
+    <mergeCell ref="BG9:BH9"/>
+    <mergeCell ref="BI9:BJ9"/>
+    <mergeCell ref="BK9:BL9"/>
+    <mergeCell ref="BA9:BB9"/>
+    <mergeCell ref="BC9:BD9"/>
+    <mergeCell ref="BE9:BF9"/>
   </mergeCells>
-  <conditionalFormatting sqref="C1 E1 G1 I1 K1 M1 O1 Q1 S1 U1 W1 Y1 AA1 AC1 AE1 AG1 AI1 AK1 AM1 AO1 AQ1 AS1 AU1 AW1 AY1 BA1 BC1 BE1 BG1 BI1 BK1 C9:AM9 AO9 AQ9 AS9 AU9 AW9 AY9 BA9 BC9 BE9 BG9 BI9 BK9">
-    <cfRule type="expression" dxfId="24" priority="41" stopIfTrue="1">
-      <formula>NOT(OR("/"=C$1,AVERAGE($C$1:$AZ$1)&lt;C$1,SMALL($C$1:$AZ$1,1)=C$1,SMALL($C$1:$AZ$1,2)=C$1,SMALL($C$1:$AZ$1,3)=C$1,LARGE($C$1:$AZ$1,1)=C$1,LARGE($C$1:$AZ$1,2)=C$1,LARGE($C$1:$AZ$1,3)=C$1))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="23" priority="43" stopIfTrue="1">
-      <formula>("/"=C$1)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="22" priority="44" stopIfTrue="1">
-      <formula>NOT(OR("/"=C$1,AVERAGE($C$1:$AZ$1)&gt;C$1,SMALL($C$1:$AZ$1,1)=C$1,SMALL($C$1:$AZ$1,2)=C$1,SMALL($C$1:$AZ$1,3)=C$1,LARGE($C$1:$AZ$1,1)=C$1,LARGE($C$1:$AZ$1,2)=C$1,LARGE($C$1:$AZ$1,3)=C$1))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="21" priority="82" stopIfTrue="1">
-      <formula>SMALL($C$1:$AZ$1,3)=C$1</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="20" priority="83" stopIfTrue="1">
-      <formula>SMALL($C$1:$AZ$1,2)=C$1</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="19" priority="84" stopIfTrue="1">
-      <formula>SMALL($C$1:$AZ$1,1)=C$1</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="18" priority="85" stopIfTrue="1">
-      <formula>LARGE($C$1:$AZ$1,3)=C$1</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="17" priority="86" stopIfTrue="1">
-      <formula>LARGE($C$1:$AZ$1,2)=C$1</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="16" priority="87" stopIfTrue="1">
-      <formula>MAX($C$1:$AZ$1)=C$1</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="G10:G79 I10:I79 K10:K79 M10:M79 C10:C172 E10:E172 O10:O172 Q10:Q172 S10:S172 U10:U172 W10:W172 Y10:Y172 AA10:AA172 AC10:AC172 AE10:AE172 AG10:AG172 AI10:AI172 AK10:AK172 AM10:AM172 AO10:AO172 AQ10:AQ172 AS10:AS172 AU10:AU172 AW10:AW172 AY10:AY172 BA10:BA172 BC10:BC172 BE10:BE172 G81:G172 I81:I172 K81:K172 M81:M172">
-    <cfRule type="expression" dxfId="15" priority="26" stopIfTrue="1">
+    <cfRule type="expression" dxfId="24" priority="26" stopIfTrue="1">
       <formula>(C10/D10)&gt;12</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="28" stopIfTrue="1">
+    <cfRule type="expression" dxfId="23" priority="28" stopIfTrue="1">
       <formula>(C10/D10)&lt;-2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="30" stopIfTrue="1">
+    <cfRule type="expression" dxfId="22" priority="30" stopIfTrue="1">
       <formula>(C10/D10)&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="32" stopIfTrue="1">
+    <cfRule type="expression" dxfId="21" priority="32" stopIfTrue="1">
       <formula>(C10/D10)&gt;10</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H10:H79 J10:J79 L10:L79 N10:N79 D10:D172 F10:F172 P10:P172 R10:R172 T10:T172 V10:V172 X10:X172 Z10:Z172 AB10:AB172 AD10:AD172 AF10:AF172 AH10:AH172 AJ10:AJ172 AL10:AL172 AN10:AN172 AP10:AP172 AR10:AR172 AT10:AT172 AV10:AV172 AX10:AX172 AZ10:AZ172 BB10:BB172 BD10:BD172 BF10:BF172 H81:H172 J81:J172 L81:L172 N81:N172">
-    <cfRule type="expression" dxfId="11" priority="25" stopIfTrue="1">
+    <cfRule type="expression" dxfId="20" priority="25" stopIfTrue="1">
       <formula>(C10/D10)&gt;12</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="27" stopIfTrue="1">
+    <cfRule type="expression" dxfId="19" priority="27" stopIfTrue="1">
       <formula>(C10/D10)&lt;-2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="29" stopIfTrue="1">
+    <cfRule type="expression" dxfId="18" priority="29" stopIfTrue="1">
       <formula>(C10/D10)&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="31" stopIfTrue="1">
+    <cfRule type="expression" dxfId="17" priority="31" stopIfTrue="1">
       <formula>(C10/D10)&gt;10</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BU93:BU121">
-    <cfRule type="cellIs" dxfId="7" priority="3" operator="greaterThan">
+  <conditionalFormatting sqref="CE93:CE121">
+    <cfRule type="cellIs" dxfId="16" priority="3" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="4" operator="between">
+    <cfRule type="cellIs" dxfId="15" priority="4" operator="between">
       <formula>20</formula>
       <formula>50</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="5" operator="between">
+    <cfRule type="cellIs" dxfId="14" priority="5" operator="between">
       <formula>50</formula>
       <formula>100</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="6" operator="between">
+    <cfRule type="cellIs" dxfId="13" priority="6" operator="between">
       <formula>100</formula>
       <formula>250</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="7" operator="between">
+    <cfRule type="cellIs" dxfId="12" priority="7" operator="between">
       <formula>250</formula>
       <formula>500</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="8" operator="between">
+    <cfRule type="cellIs" dxfId="11" priority="8" operator="between">
       <formula>500</formula>
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BZ93:BZ114">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="between">
+  <conditionalFormatting sqref="CJ93:CJ114">
+    <cfRule type="cellIs" dxfId="10" priority="1" operator="between">
       <formula>1</formula>
       <formula>10</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="between">
+    <cfRule type="cellIs" dxfId="9" priority="2" operator="between">
       <formula>10</formula>
       <formula>20</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C1 E1 G1 I1 K1 M1 O1 Q1 S1 U1 W1 Y1 AA1 AC1 AE1 AG1 AI1 AK1 AM1 AO1 AQ1 AS1 AU1 AW1 AY1 BA1 BC1 BE1 BG1 BI1 BK1 C9:AM9 AO9 AQ9 AS9 AU9 AW9 AY9 BA9 BC9 BE9 BG9 BI9 BK9 BM9 BO9 BQ9 BS9 BU9 BM1 BO1 BQ1 BS1 BU1">
+    <cfRule type="expression" dxfId="8" priority="87" stopIfTrue="1">
+      <formula>MAX($C$1:$AZ$1)=C$1</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="7" priority="86" stopIfTrue="1">
+      <formula>LARGE($C$1:$AZ$1,2)=C$1</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="6" priority="85" stopIfTrue="1">
+      <formula>LARGE($C$1:$AZ$1,3)=C$1</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="84" stopIfTrue="1">
+      <formula>SMALL($C$1:$AZ$1,1)=C$1</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="83" stopIfTrue="1">
+      <formula>SMALL($C$1:$AZ$1,2)=C$1</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="3" priority="82" stopIfTrue="1">
+      <formula>SMALL($C$1:$AZ$1,3)=C$1</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="44" stopIfTrue="1">
+      <formula>NOT(OR("/"=C$1,AVERAGE($C$1:$AZ$1)&gt;C$1,SMALL($C$1:$AZ$1,1)=C$1,SMALL($C$1:$AZ$1,2)=C$1,SMALL($C$1:$AZ$1,3)=C$1,LARGE($C$1:$AZ$1,1)=C$1,LARGE($C$1:$AZ$1,2)=C$1,LARGE($C$1:$AZ$1,3)=C$1))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="43" stopIfTrue="1">
+      <formula>("/"=C$1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="41" stopIfTrue="1">
+      <formula>NOT(OR("/"=C$1,AVERAGE($C$1:$AZ$1)&lt;C$1,SMALL($C$1:$AZ$1,1)=C$1,SMALL($C$1:$AZ$1,2)=C$1,SMALL($C$1:$AZ$1,3)=C$1,LARGE($C$1:$AZ$1,1)=C$1,LARGE($C$1:$AZ$1,2)=C$1,LARGE($C$1:$AZ$1,3)=C$1))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.70000000000000007" right="0.70000000000000007" top="0.75" bottom="0.75" header="0.30000000000000004" footer="0.30000000000000004"/>
@@ -12149,7 +13158,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22D977F6-AD3F-47F0-926D-61192148887D}">
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="13.6640625" customWidth="1"/>
@@ -12176,13 +13185,13 @@
         <v>42</v>
       </c>
       <c r="F1" t="str" cm="1">
-        <f t="array" ref="F1:F10">'All stat'!BV80:BV89</f>
+        <f t="array" ref="F1:F10">'All stat'!CF80:CF89</f>
         <v>légende</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="25" cm="1">
-        <f t="array" ref="A2:D21">_xlfn.ANCHORARRAY('All stat'!BR93)</f>
+        <f t="array" ref="A2:D22">_xlfn.ANCHORARRAY('All stat'!CB93)</f>
         <v>1</v>
       </c>
       <c r="B2" s="25" t="str">
@@ -12206,17 +13215,17 @@
         <v>Boris</v>
       </c>
       <c r="C3" s="25" t="str">
-        <v>7.165</v>
+        <v>7.150</v>
       </c>
       <c r="D3" s="25">
-        <v>1108</v>
+        <v>1140</v>
       </c>
       <c r="F3" t="str">
         <v>entre 1 et 10</v>
       </c>
       <c r="G3" s="23"/>
       <c r="H3" t="str" cm="1">
-        <f t="array" ref="H3:I10">'All stat'!BX82:BY89</f>
+        <f t="array" ref="H3:I10">'All stat'!CH82:CI89</f>
         <v>anecdotique</v>
       </c>
       <c r="I3" t="str">
@@ -12228,13 +13237,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="25" t="str">
-        <v>Célian</v>
+        <v>Vincent</v>
       </c>
       <c r="C4" s="25" t="str">
-        <v>6.509</v>
+        <v>6.750</v>
       </c>
       <c r="D4" s="25">
-        <v>316</v>
+        <v>20</v>
       </c>
       <c r="F4" t="str">
         <v>entre 10 et 20</v>
@@ -12252,13 +13261,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="25" t="str">
-        <v>William</v>
+        <v>Célian</v>
       </c>
       <c r="C5" s="25" t="str">
-        <v>6.069</v>
+        <v>6.255</v>
       </c>
       <c r="D5" s="25">
-        <v>29</v>
+        <v>349</v>
       </c>
       <c r="F5" t="str">
         <v>entre 20 et 50</v>
@@ -12276,13 +13285,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="25" t="str">
-        <v>Tom</v>
+        <v>William</v>
       </c>
       <c r="C6" s="25" t="str">
-        <v>5.993</v>
+        <v>6.069</v>
       </c>
       <c r="D6" s="25">
-        <v>286</v>
+        <v>29</v>
       </c>
       <c r="F6" t="str">
         <v>entre 50 et 100</v>
@@ -12300,13 +13309,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="25" t="str">
-        <v>Samuel</v>
+        <v>Tom</v>
       </c>
       <c r="C7" s="25" t="str">
-        <v>5.910</v>
+        <v>5.993</v>
       </c>
       <c r="D7" s="25">
-        <v>211</v>
+        <v>286</v>
       </c>
       <c r="F7" t="str">
         <v>entre 100 et 250</v>
@@ -12324,13 +13333,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="25" t="str">
-        <v>Joachim</v>
+        <v>Samuel</v>
       </c>
       <c r="C8" s="25" t="str">
-        <v>5.890</v>
+        <v>5.910</v>
       </c>
       <c r="D8" s="25">
-        <v>109</v>
+        <v>211</v>
       </c>
       <c r="F8" t="str">
         <v>entre 250 et 500</v>
@@ -12348,13 +13357,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="25" t="str">
-        <v>Mehdi</v>
+        <v>Joachim</v>
       </c>
       <c r="C9" s="25" t="str">
-        <v>5.770</v>
+        <v>5.890</v>
       </c>
       <c r="D9" s="25">
-        <v>421</v>
+        <v>109</v>
       </c>
       <c r="F9" t="str">
         <v>entre 500 et 1000</v>
@@ -12372,13 +13381,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="25" t="str">
-        <v>Jules</v>
+        <v>Mehdi</v>
       </c>
       <c r="C10" s="25" t="str">
-        <v>5.596</v>
+        <v>5.702</v>
       </c>
       <c r="D10" s="25">
-        <v>235</v>
+        <v>426</v>
       </c>
       <c r="F10" t="str">
         <v>plus de 1000</v>
@@ -12396,13 +13405,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="25" t="str">
-        <v>Damien</v>
+        <v>Jules</v>
       </c>
       <c r="C11" s="25" t="str">
-        <v>5.448</v>
+        <v>5.596</v>
       </c>
       <c r="D11" s="25">
-        <v>725</v>
+        <v>235</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
@@ -12410,13 +13419,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="25" t="str">
-        <v>Achille</v>
+        <v>Damien</v>
       </c>
       <c r="C12" s="25" t="str">
-        <v>5.407</v>
+        <v>5.431</v>
       </c>
       <c r="D12" s="25">
-        <v>829</v>
+        <v>733</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
@@ -12424,13 +13433,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="25" t="str">
-        <v>Lou</v>
+        <v>Achille</v>
       </c>
       <c r="C13" s="25" t="str">
-        <v>4.950</v>
+        <v>5.407</v>
       </c>
       <c r="D13" s="25">
-        <v>120</v>
+        <v>829</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
@@ -12438,13 +13447,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="25" t="str">
-        <v>Paul</v>
+        <v>Lou</v>
       </c>
       <c r="C14" s="25" t="str">
-        <v>4.813</v>
+        <v>4.950</v>
       </c>
       <c r="D14" s="25">
-        <v>32</v>
+        <v>120</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
@@ -12452,13 +13461,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="25" t="str">
-        <v>Joey</v>
+        <v>Paul</v>
       </c>
       <c r="C15" s="25" t="str">
-        <v>4.500</v>
+        <v>4.813</v>
       </c>
       <c r="D15" s="25">
-        <v>86</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
@@ -12466,13 +13475,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="25" t="str">
-        <v>Stanislas</v>
+        <v>Marie</v>
       </c>
       <c r="C16" s="25" t="str">
-        <v>4.481</v>
+        <v>4.617</v>
       </c>
       <c r="D16" s="25">
-        <v>27</v>
+        <v>294</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
@@ -12480,13 +13489,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="25" t="str">
-        <v>Marie</v>
+        <v>Joey</v>
       </c>
       <c r="C17" s="25" t="str">
-        <v>4.470</v>
+        <v>4.500</v>
       </c>
       <c r="D17" s="25">
-        <v>265</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
@@ -12494,13 +13503,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="25" t="str">
-        <v>Quentin</v>
+        <v>Stanislas</v>
       </c>
       <c r="C18" s="25" t="str">
-        <v>4.097</v>
+        <v>4.481</v>
       </c>
       <c r="D18" s="25">
-        <v>93</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
@@ -12508,13 +13517,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="25" t="str">
-        <v>Luca</v>
+        <v>Quentin</v>
       </c>
       <c r="C19" s="25" t="str">
-        <v>3.011</v>
+        <v>4.097</v>
       </c>
       <c r="D19" s="25">
-        <v>178</v>
+        <v>93</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
@@ -12522,13 +13531,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="25" t="str">
-        <v>Fantinne</v>
+        <v>Luca</v>
       </c>
       <c r="C20" s="25" t="str">
-        <v>2.961</v>
+        <v>3.129</v>
       </c>
       <c r="D20" s="25">
-        <v>51</v>
+        <v>186</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
@@ -12536,12 +13545,26 @@
         <v>20</v>
       </c>
       <c r="B21" s="25" t="str">
+        <v>Fantinne</v>
+      </c>
+      <c r="C21" s="25" t="str">
+        <v>2.961</v>
+      </c>
+      <c r="D21" s="25">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="str">
         <v>Loulou</v>
       </c>
-      <c r="C21" s="25" t="str">
+      <c r="C22" t="str">
         <v>2.427</v>
       </c>
-      <c r="D21" s="25">
+      <c r="D22">
         <v>75</v>
       </c>
     </row>

--- a/classement_whist_2023_2025.xlsx
+++ b/classement_whist_2023_2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a20b8382962b136a/Bureau/loisir/whist/projet_application_streamlit/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="253" documentId="14_{167F2DC3-291A-4B33-AB7D-1A6E034E4A5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{18689D16-4447-4657-8BB5-A1B6AFD6B2E8}"/>
+  <xr:revisionPtr revIDLastSave="257" documentId="14_{167F2DC3-291A-4B33-AB7D-1A6E034E4A5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F673405D-00B3-4C67-846E-184F764341FD}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="All stat" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="103">
   <si>
     <t>global</t>
   </si>
@@ -362,6 +362,9 @@
   </si>
   <si>
     <t>Samuel Fraire</t>
+  </si>
+  <si>
+    <t>moyenne des moyennes</t>
   </si>
 </sst>
 </file>
@@ -8892,8 +8895,8 @@
         <v>1</v>
       </c>
       <c r="CH120" s="1">
-        <f>AVERAGE(C1:BF1)</f>
-        <v>5.1444090837219676</v>
+        <f>AVERAGE(C1:CD1)</f>
+        <v>5.140630780075802</v>
       </c>
       <c r="CJ120" s="1">
         <v>13</v>
@@ -14302,7 +14305,7 @@
     <col min="3" max="3" width="13" style="1" customWidth="1"/>
     <col min="4" max="4" width="15.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20.109375" customWidth="1"/>
-    <col min="6" max="6" width="18.88671875" customWidth="1"/>
+    <col min="6" max="6" width="21.77734375" customWidth="1"/>
     <col min="7" max="7" width="18" customWidth="1"/>
     <col min="9" max="9" width="15.109375" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
@@ -14578,6 +14581,13 @@
       <c r="D13" s="1">
         <v>743</v>
       </c>
+      <c r="F13" t="s">
+        <v>102</v>
+      </c>
+      <c r="G13">
+        <f>AVERAGE('All stat'!C1:CD1)</f>
+        <v>5.140630780075802</v>
+      </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="1">

--- a/classement_whist_2023_2025.xlsx
+++ b/classement_whist_2023_2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a20b8382962b136a/Bureau/loisir/whist/projet_application_streamlit/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="257" documentId="14_{167F2DC3-291A-4B33-AB7D-1A6E034E4A5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F673405D-00B3-4C67-846E-184F764341FD}"/>
+  <xr:revisionPtr revIDLastSave="275" documentId="14_{167F2DC3-291A-4B33-AB7D-1A6E034E4A5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{419363F9-9091-4346-A444-A69D9C20EAED}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="All stat" sheetId="1" r:id="rId1"/>
@@ -634,71 +634,7 @@
     <cellStyle name="cf7" xfId="7" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="150">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF00B0F0"/>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF00B0F0"/>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC000"/>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF92D050"/>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB5E6A2"/>
-          <bgColor rgb="FFB5E6A2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF00B050"/>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="25">
     <dxf>
       <fill>
         <patternFill>
@@ -814,54 +750,6 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFF9900"/>
-          <bgColor rgb="FFFF9900"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF00B0F0"/>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF00B0F0"/>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC000"/>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
           <fgColor rgb="FFB5E6A2"/>
           <bgColor rgb="FFB5E6A2"/>
         </patternFill>
@@ -872,126 +760,6 @@
         <patternFill patternType="solid">
           <fgColor rgb="FF92D050"/>
           <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF00B050"/>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF5050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF5050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1013,697 +781,9 @@
     </dxf>
     <dxf>
       <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF5050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF5050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF92D050"/>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB5E6A2"/>
-          <bgColor rgb="FFB5E6A2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFFF0000"/>
           <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF9900"/>
-          <bgColor rgb="FFFF9900"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC000"/>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF00B0F0"/>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF00B0F0"/>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF5050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF5050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF00B050"/>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF92D050"/>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB5E6A2"/>
-          <bgColor rgb="FFB5E6A2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF9900"/>
-          <bgColor rgb="FFFF9900"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC000"/>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF00B0F0"/>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF00B0F0"/>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF5050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF5050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF00B050"/>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF92D050"/>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB5E6A2"/>
-          <bgColor rgb="FFB5E6A2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF9900"/>
-          <bgColor rgb="FFFF9900"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC000"/>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF00B0F0"/>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF00B0F0"/>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF5050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF5050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF00B050"/>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF92D050"/>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB5E6A2"/>
-          <bgColor rgb="FFB5E6A2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF9900"/>
-          <bgColor rgb="FFFF9900"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2122,7 +1202,7 @@
       </c>
       <c r="G1" s="1">
         <f t="shared" ref="G1" si="2">IF(H2&gt;19,G2/H2,"/")</f>
-        <v>7.173858921161826</v>
+        <v>7.2048440065681447</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>2</v>
@@ -2143,28 +1223,28 @@
       </c>
       <c r="M1" s="1">
         <f t="shared" ref="M1" si="5">IF(N2&gt;19,M2/N2,"/")</f>
-        <v>5.4266487213997312</v>
+        <v>5.3861517976031958</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="O1" s="1">
         <f t="shared" ref="O1" si="6">IF(P2&gt;19,O2/P2,"/")</f>
-        <v>7.2531645569620249</v>
+        <v>7.0804597701149428</v>
       </c>
       <c r="P1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="Q1" s="1">
         <f t="shared" ref="Q1" si="7">IF(R2&gt;19,Q2/R2,"/")</f>
-        <v>6.3369272237196768</v>
+        <v>6.3909574468085104</v>
       </c>
       <c r="R1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="S1" s="1">
         <f t="shared" ref="S1" si="8">IF(T2&gt;19,S2/T2,"/")</f>
-        <v>5.943708609271523</v>
+        <v>5.9387096774193546</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>2</v>
@@ -2199,7 +1279,7 @@
       </c>
       <c r="AC1" s="1">
         <f>IF(AD2&gt;19,AC2/AD2,"/")</f>
-        <v>5.5593869731800769</v>
+        <v>5.7555555555555555</v>
       </c>
       <c r="AD1" s="1" t="s">
         <v>2</v>
@@ -2304,7 +1384,7 @@
       </c>
       <c r="BG1" s="1">
         <f t="shared" ref="BG1" si="27">IF(BH2&gt;19,BG2/BH2,"/")</f>
-        <v>5.4333333333333336</v>
+        <v>5.6571428571428575</v>
       </c>
       <c r="BH1" s="1" t="s">
         <v>2</v>
@@ -2409,11 +1489,11 @@
       </c>
       <c r="G2" s="1">
         <f t="shared" si="39"/>
-        <v>8644.5</v>
+        <v>8775.5</v>
       </c>
       <c r="H2" s="1">
         <f t="shared" si="39"/>
-        <v>1205</v>
+        <v>1218</v>
       </c>
       <c r="I2" s="1">
         <f t="shared" si="39"/>
@@ -2433,35 +1513,35 @@
       </c>
       <c r="M2" s="1">
         <f t="shared" si="40"/>
-        <v>4032</v>
+        <v>4045</v>
       </c>
       <c r="N2" s="1">
         <f t="shared" si="40"/>
-        <v>743</v>
+        <v>751</v>
       </c>
       <c r="O2" s="1">
         <f t="shared" si="40"/>
-        <v>573</v>
+        <v>616</v>
       </c>
       <c r="P2" s="1">
         <f t="shared" si="40"/>
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="Q2" s="1">
         <f t="shared" si="40"/>
-        <v>2351</v>
+        <v>2403</v>
       </c>
       <c r="R2" s="1">
         <f t="shared" si="40"/>
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="S2" s="1">
         <f t="shared" si="40"/>
-        <v>1795</v>
+        <v>1841</v>
       </c>
       <c r="T2" s="1">
         <f t="shared" si="40"/>
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="U2" s="1">
         <f t="shared" si="40"/>
@@ -2497,11 +1577,11 @@
       </c>
       <c r="AC2" s="1">
         <f t="shared" si="40"/>
-        <v>1451</v>
+        <v>1554</v>
       </c>
       <c r="AD2" s="1">
         <f t="shared" si="40"/>
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="AE2" s="1">
         <f t="shared" si="40"/>
@@ -2617,11 +1697,11 @@
       </c>
       <c r="BG2" s="1">
         <f t="shared" ref="BG2:BL2" si="43">BG4+BG6+BG8</f>
-        <v>163</v>
+        <v>198</v>
       </c>
       <c r="BH2" s="1">
         <f t="shared" si="43"/>
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="BI2" s="1">
         <f t="shared" si="43"/>
@@ -3979,7 +3059,7 @@
       </c>
       <c r="G7" s="15">
         <f t="shared" ref="G7" si="139">G8/H8</f>
-        <v>7.3404411764705886</v>
+        <v>7.391774891774892</v>
       </c>
       <c r="H7" s="15" t="s">
         <v>2</v>
@@ -4000,28 +3080,28 @@
       </c>
       <c r="M7" s="15">
         <f t="shared" ref="M7" si="142">M8/N8</f>
-        <v>5.7945945945945949</v>
+        <v>5.7353463587921851</v>
       </c>
       <c r="N7" s="15" t="s">
         <v>2</v>
       </c>
       <c r="O7" s="15">
         <f t="shared" ref="O7" si="143">O8/P8</f>
-        <v>7.7894736842105265</v>
+        <v>7.4923076923076923</v>
       </c>
       <c r="P7" s="15" t="s">
         <v>2</v>
       </c>
       <c r="Q7" s="15">
         <f t="shared" ref="Q7" si="144">Q8/R8</f>
-        <v>6.4695945945945947</v>
+        <v>6.5348837209302326</v>
       </c>
       <c r="R7" s="15" t="s">
         <v>2</v>
       </c>
       <c r="S7" s="15">
         <f t="shared" ref="S7" si="145">S8/T8</f>
-        <v>5.3163265306122449</v>
+        <v>5.333333333333333</v>
       </c>
       <c r="T7" s="15" t="s">
         <v>2</v>
@@ -4056,7 +3136,7 @@
       </c>
       <c r="AC7" s="15">
         <f t="shared" ref="AC7" si="150">AC8/AD8</f>
-        <v>5.7171314741035859</v>
+        <v>5.9153846153846157</v>
       </c>
       <c r="AD7" s="15" t="s">
         <v>2</v>
@@ -4161,7 +3241,7 @@
       </c>
       <c r="BG7" s="15">
         <f t="shared" ref="BG7" si="165">BG8/BH8</f>
-        <v>5.4333333333333336</v>
+        <v>5.6571428571428575</v>
       </c>
       <c r="BH7" s="15" t="s">
         <v>2</v>
@@ -4267,11 +3347,11 @@
       </c>
       <c r="G8" s="15">
         <f t="shared" si="177"/>
-        <v>4991.5</v>
+        <v>5122.5</v>
       </c>
       <c r="H8" s="15">
         <f t="shared" si="177"/>
-        <v>680</v>
+        <v>693</v>
       </c>
       <c r="I8" s="15">
         <f t="shared" si="177"/>
@@ -4291,35 +3371,35 @@
       </c>
       <c r="M8" s="15">
         <f t="shared" si="178"/>
-        <v>3216</v>
+        <v>3229</v>
       </c>
       <c r="N8" s="15">
         <f t="shared" si="178"/>
-        <v>555</v>
+        <v>563</v>
       </c>
       <c r="O8" s="15">
         <f t="shared" si="178"/>
-        <v>444</v>
+        <v>487</v>
       </c>
       <c r="P8" s="15">
         <f t="shared" si="178"/>
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="Q8" s="15">
         <f t="shared" si="178"/>
-        <v>1915</v>
+        <v>1967</v>
       </c>
       <c r="R8" s="15">
         <f t="shared" si="178"/>
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="S8" s="15">
         <f t="shared" si="178"/>
-        <v>1042</v>
+        <v>1088</v>
       </c>
       <c r="T8" s="15">
         <f t="shared" si="178"/>
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="U8" s="15">
         <f t="shared" si="178"/>
@@ -4355,11 +3435,11 @@
       </c>
       <c r="AC8" s="15">
         <f t="shared" si="178"/>
-        <v>1435</v>
+        <v>1538</v>
       </c>
       <c r="AD8" s="15">
         <f t="shared" si="178"/>
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="AE8" s="15">
         <f t="shared" si="178"/>
@@ -4475,11 +3555,11 @@
       </c>
       <c r="BG8" s="15">
         <f t="shared" ref="BG8:BL8" si="181">SUM(BG10:BG130)</f>
-        <v>163</v>
+        <v>198</v>
       </c>
       <c r="BH8" s="15">
         <f t="shared" si="181"/>
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="BI8" s="15">
         <f t="shared" si="181"/>
@@ -4776,10 +3856,64 @@
       <c r="B18" s="1">
         <v>168</v>
       </c>
+      <c r="G18" s="1">
+        <v>59</v>
+      </c>
+      <c r="H18" s="1">
+        <v>8</v>
+      </c>
+      <c r="M18" s="1">
+        <v>36</v>
+      </c>
+      <c r="N18" s="1">
+        <v>3</v>
+      </c>
+      <c r="O18" s="1">
+        <v>43</v>
+      </c>
+      <c r="P18" s="1">
+        <v>8</v>
+      </c>
+      <c r="S18" s="1">
+        <v>46</v>
+      </c>
+      <c r="T18" s="1">
+        <v>8</v>
+      </c>
+      <c r="AC18" s="1">
+        <v>103</v>
+      </c>
+      <c r="AD18" s="1">
+        <v>9</v>
+      </c>
     </row>
     <row r="19" spans="1:78" x14ac:dyDescent="0.3">
       <c r="B19" s="1">
         <v>167</v>
+      </c>
+      <c r="G19" s="1">
+        <v>72</v>
+      </c>
+      <c r="H19" s="1">
+        <v>5</v>
+      </c>
+      <c r="M19" s="1">
+        <v>-23</v>
+      </c>
+      <c r="N19" s="1">
+        <v>5</v>
+      </c>
+      <c r="Q19" s="1">
+        <v>52</v>
+      </c>
+      <c r="R19" s="1">
+        <v>5</v>
+      </c>
+      <c r="BG19" s="1">
+        <v>35</v>
+      </c>
+      <c r="BH19" s="1">
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:78" x14ac:dyDescent="0.3">
@@ -7947,13 +7081,13 @@
         <v>1</v>
       </c>
       <c r="CK108" s="1" t="str">
-        <v>Gauthier</v>
+        <v>Boris</v>
       </c>
       <c r="CL108" s="1" t="str">
-        <v>7.253</v>
+        <v>7.205</v>
       </c>
       <c r="CM108" s="1">
-        <v>79</v>
+        <v>1218</v>
       </c>
       <c r="CO108" s="1" cm="1">
         <f t="array" ref="CO108:CR114">_xlfn.LET(
@@ -7987,10 +7121,10 @@
       </c>
       <c r="CT108" s="1" t="str" cm="1">
         <f t="array" ref="CT108:CU135">_xlfn.LET(  _xlpm.noms, TRANSPOSE(INDEX(C9:BF9,_xlfn.SEQUENCE(1,COLUMNS(C9:BF9)/2,1,2))),_xlpm.moy,  TRANSPOSE(INDEX(C1:BF1,,_xlfn.SEQUENCE(1,COLUMNS(C1:BF1)/2,1,2))),_xlfn.SORTBY(CHOOSE({1,2}, _xlpm.noms, _xlpm.moy), IF(ISNUMBER(_xlpm.moy), _xlpm.moy, -1E+99), -1))</f>
-        <v>Gauthier</v>
+        <v>Boris</v>
       </c>
       <c r="CU108" s="1">
-        <v>7.2531645569620249</v>
+        <v>7.2048440065681447</v>
       </c>
     </row>
     <row r="109" spans="1:99" x14ac:dyDescent="0.3">
@@ -8032,13 +7166,13 @@
         <v>2</v>
       </c>
       <c r="CK109" s="1" t="str">
-        <v>Boris</v>
+        <v>Gauthier</v>
       </c>
       <c r="CL109" s="1" t="str">
-        <v>7.174</v>
+        <v>7.080</v>
       </c>
       <c r="CM109" s="1">
-        <v>1205</v>
+        <v>87</v>
       </c>
       <c r="CO109" s="1">
         <v>2</v>
@@ -8053,10 +7187,10 @@
         <v>4</v>
       </c>
       <c r="CT109" s="1" t="str">
-        <v>Boris</v>
+        <v>Gauthier</v>
       </c>
       <c r="CU109" s="1">
-        <v>7.173858921161826</v>
+        <v>7.0804597701149428</v>
       </c>
     </row>
     <row r="110" spans="1:99" x14ac:dyDescent="0.3">
@@ -8122,7 +7256,7 @@
         <v>Célian</v>
       </c>
       <c r="CU110" s="1">
-        <v>6.3369272237196768</v>
+        <v>6.3909574468085104</v>
       </c>
     </row>
     <row r="111" spans="1:99" x14ac:dyDescent="0.3">
@@ -8163,10 +7297,10 @@
         <v>Célian</v>
       </c>
       <c r="CL111" s="1" t="str">
-        <v>6.337</v>
+        <v>6.391</v>
       </c>
       <c r="CM111" s="1">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="CO111" s="1">
         <v>4</v>
@@ -8250,7 +7384,7 @@
         <v>Tom</v>
       </c>
       <c r="CU112" s="1">
-        <v>5.943708609271523</v>
+        <v>5.9387096774193546</v>
       </c>
     </row>
     <row r="113" spans="1:99" x14ac:dyDescent="0.3">
@@ -8295,10 +7429,10 @@
         <v>Tom</v>
       </c>
       <c r="CL113" s="1" t="str">
-        <v>5.944</v>
+        <v>5.939</v>
       </c>
       <c r="CM113" s="1">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="CO113" s="1">
         <v>6</v>
@@ -8429,10 +7563,10 @@
         <v>109</v>
       </c>
       <c r="CT115" s="1" t="str">
-        <v>Mehdi</v>
+        <v>Jules</v>
       </c>
       <c r="CU115" s="1">
-        <v>5.7018779342723001</v>
+        <v>5.7555555555555555</v>
       </c>
     </row>
     <row r="116" spans="1:99" x14ac:dyDescent="0.3">
@@ -8519,19 +7653,19 @@
         <v>9</v>
       </c>
       <c r="CK116" s="1" t="str">
+        <v>Jules</v>
+      </c>
+      <c r="CL116" s="1" t="str">
+        <v>5.756</v>
+      </c>
+      <c r="CM116" s="1">
+        <v>270</v>
+      </c>
+      <c r="CT116" s="1" t="str">
         <v>Mehdi</v>
       </c>
-      <c r="CL116" s="1" t="str">
-        <v>5.702</v>
-      </c>
-      <c r="CM116" s="1">
-        <v>426</v>
-      </c>
-      <c r="CT116" s="1" t="str">
-        <v>Jules</v>
-      </c>
       <c r="CU116" s="1">
-        <v>5.5593869731800769</v>
+        <v>5.7018779342723001</v>
       </c>
     </row>
     <row r="117" spans="1:99" x14ac:dyDescent="0.3">
@@ -8614,19 +7748,19 @@
         <v>10</v>
       </c>
       <c r="CK117" s="1" t="str">
-        <v>Jules</v>
+        <v>Mehdi</v>
       </c>
       <c r="CL117" s="1" t="str">
-        <v>5.559</v>
+        <v>5.702</v>
       </c>
       <c r="CM117" s="1">
-        <v>261</v>
+        <v>426</v>
       </c>
       <c r="CT117" s="1" t="str">
-        <v>Damien</v>
+        <v>Achille</v>
       </c>
       <c r="CU117" s="1">
-        <v>5.4266487213997312</v>
+        <v>5.4065138721351023</v>
       </c>
     </row>
     <row r="118" spans="1:99" x14ac:dyDescent="0.3">
@@ -8712,16 +7846,16 @@
         <v>Hugo</v>
       </c>
       <c r="CL118" s="1" t="str">
-        <v>5.433</v>
+        <v>5.657</v>
       </c>
       <c r="CM118" s="1">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="CT118" s="1" t="str">
-        <v>Achille</v>
+        <v>Damien</v>
       </c>
       <c r="CU118" s="1">
-        <v>5.4065138721351023</v>
+        <v>5.3861517976031958</v>
       </c>
     </row>
     <row r="119" spans="1:99" x14ac:dyDescent="0.3">
@@ -8800,13 +7934,13 @@
         <v>12</v>
       </c>
       <c r="CK119" s="1" t="str">
-        <v>Damien</v>
+        <v>Achille</v>
       </c>
       <c r="CL119" s="1" t="str">
-        <v>5.427</v>
+        <v>5.407</v>
       </c>
       <c r="CM119" s="1">
-        <v>743</v>
+        <v>829</v>
       </c>
       <c r="CT119" s="1" t="str">
         <v>Joey</v>
@@ -8896,19 +8030,19 @@
       </c>
       <c r="CH120" s="1">
         <f>AVERAGE(C1:CD1)</f>
-        <v>5.140630780075802</v>
+        <v>5.151661271313662</v>
       </c>
       <c r="CJ120" s="1">
         <v>13</v>
       </c>
       <c r="CK120" s="1" t="str">
-        <v>Achille</v>
+        <v>Bruno</v>
       </c>
       <c r="CL120" s="1" t="str">
-        <v>5.407</v>
+        <v>5.400</v>
       </c>
       <c r="CM120" s="1">
-        <v>829</v>
+        <v>20</v>
       </c>
       <c r="CT120" s="1" t="str">
         <v>Lou</v>
@@ -8993,13 +8127,13 @@
         <v>14</v>
       </c>
       <c r="CK121" s="1" t="str">
-        <v>Bruno</v>
+        <v>Damien</v>
       </c>
       <c r="CL121" s="1" t="str">
-        <v>5.400</v>
+        <v>5.386</v>
       </c>
       <c r="CM121" s="1">
-        <v>20</v>
+        <v>751</v>
       </c>
       <c r="CT121" s="1" t="str">
         <v>Paul</v>
@@ -10678,13 +9812,13 @@
         <v>1</v>
       </c>
       <c r="CU140" s="1" t="str">
-        <v>Gauthier</v>
+        <v>Boris</v>
       </c>
       <c r="CV140" s="1">
-        <v>7.2530000000000001</v>
+        <v>7.2050000000000001</v>
       </c>
       <c r="CW140" s="1">
-        <v>79</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="141" spans="1:101" x14ac:dyDescent="0.3">
@@ -10767,13 +9901,13 @@
         <v>2</v>
       </c>
       <c r="CU141" s="1" t="str">
-        <v>Boris</v>
+        <v>Gauthier</v>
       </c>
       <c r="CV141" s="1">
-        <v>7.1740000000000004</v>
+        <v>7.08</v>
       </c>
       <c r="CW141" s="1">
-        <v>1205</v>
+        <v>87</v>
       </c>
     </row>
     <row r="142" spans="1:101" x14ac:dyDescent="0.3">
@@ -10859,10 +9993,10 @@
         <v>Célian</v>
       </c>
       <c r="CV142" s="1">
-        <v>6.3369999999999997</v>
+        <v>6.391</v>
       </c>
       <c r="CW142" s="1">
-        <v>371</v>
+        <v>376</v>
       </c>
     </row>
     <row r="143" spans="1:101" x14ac:dyDescent="0.3">
@@ -11029,10 +10163,10 @@
         <v>Tom</v>
       </c>
       <c r="CV144" s="1">
-        <v>5.944</v>
+        <v>5.9390000000000001</v>
       </c>
       <c r="CW144" s="1">
-        <v>302</v>
+        <v>310</v>
       </c>
     </row>
     <row r="145" spans="1:101" x14ac:dyDescent="0.3">
@@ -11286,13 +10420,13 @@
         <v>8</v>
       </c>
       <c r="CU147" s="1" t="str">
-        <v>Mehdi</v>
+        <v>Jules</v>
       </c>
       <c r="CV147" s="1">
-        <v>5.702</v>
+        <v>5.7560000000000002</v>
       </c>
       <c r="CW147" s="1">
-        <v>426</v>
+        <v>270</v>
       </c>
     </row>
     <row r="148" spans="1:101" x14ac:dyDescent="0.3">
@@ -11375,13 +10509,13 @@
         <v>9</v>
       </c>
       <c r="CU148" s="1" t="str">
-        <v>Jules</v>
+        <v>Mehdi</v>
       </c>
       <c r="CV148" s="1">
-        <v>5.5590000000000002</v>
+        <v>5.702</v>
       </c>
       <c r="CW148" s="1">
-        <v>261</v>
+        <v>426</v>
       </c>
     </row>
     <row r="149" spans="1:101" x14ac:dyDescent="0.3">
@@ -11464,13 +10598,13 @@
         <v>10</v>
       </c>
       <c r="CU149" s="1" t="str">
-        <v>Damien</v>
+        <v>Achille</v>
       </c>
       <c r="CV149" s="1">
-        <v>5.4269999999999996</v>
+        <v>5.407</v>
       </c>
       <c r="CW149" s="1">
-        <v>743</v>
+        <v>829</v>
       </c>
     </row>
     <row r="150" spans="1:101" x14ac:dyDescent="0.3">
@@ -11549,13 +10683,13 @@
         <v>11</v>
       </c>
       <c r="CU150" s="1" t="str">
-        <v>Achille</v>
+        <v>Damien</v>
       </c>
       <c r="CV150" s="1">
-        <v>5.407</v>
+        <v>5.3860000000000001</v>
       </c>
       <c r="CW150" s="1">
-        <v>829</v>
+        <v>751</v>
       </c>
     </row>
     <row r="151" spans="1:101" x14ac:dyDescent="0.3">
@@ -12870,20 +12004,20 @@
   _xlpm.ok, ISNUMBER(_xlpm.moy),
   _xlfn._xlws.SORT(CHOOSE({1,2,3}, _xlfn._xlws.FILTER(_xlpm.noms,_xlpm.ok), _xlfn._xlws.FILTER(_xlpm.moy,_xlpm.ok), _xlfn._xlws.FILTER(_xlpm.parties,_xlpm.ok)), 2, -1)
 )</f>
-        <v>Gauthier</v>
+        <v>Boris</v>
       </c>
       <c r="CU166" s="1">
-        <v>7.2531645569620249</v>
+        <v>7.2048440065681447</v>
       </c>
       <c r="CV166" s="1">
-        <v>79</v>
+        <v>1218</v>
       </c>
       <c r="CY166" s="1" t="str" cm="1">
         <f t="array" ref="CY166:CZ186">_xlfn.LET(  _xlpm.noms, TRANSPOSE(INDEX(C9:BF9,_xlfn.SEQUENCE(1,COLUMNS(C9:BF9)/2,1,2))),_xlpm.moy,  TRANSPOSE(INDEX(C1:BF1,,_xlfn.SEQUENCE(1,COLUMNS(C1:BF1)/2,1,2))),_xlpm.ok, ISNUMBER(_xlpm.moy),_xlfn._xlws.SORT(CHOOSE({1,2}, _xlfn._xlws.FILTER(_xlpm.noms, _xlpm.ok), _xlfn._xlws.FILTER(_xlpm.moy, _xlpm.ok)), 2, -1))</f>
-        <v>Gauthier</v>
+        <v>Boris</v>
       </c>
       <c r="CZ166" s="1">
-        <v>7.2531645569620249</v>
+        <v>7.2048440065681447</v>
       </c>
     </row>
     <row r="167" spans="1:104" x14ac:dyDescent="0.3">
@@ -12959,19 +12093,19 @@
       <c r="AX167" s="15"/>
       <c r="AY167" s="15"/>
       <c r="CT167" s="1" t="str">
-        <v>Boris</v>
+        <v>Gauthier</v>
       </c>
       <c r="CU167" s="1">
-        <v>7.173858921161826</v>
+        <v>7.0804597701149428</v>
       </c>
       <c r="CV167" s="1">
-        <v>1205</v>
+        <v>87</v>
       </c>
       <c r="CY167" s="1" t="str">
-        <v>Boris</v>
+        <v>Gauthier</v>
       </c>
       <c r="CZ167" s="1">
-        <v>7.173858921161826</v>
+        <v>7.0804597701149428</v>
       </c>
     </row>
     <row r="168" spans="1:104" x14ac:dyDescent="0.3">
@@ -13050,16 +12184,16 @@
         <v>Célian</v>
       </c>
       <c r="CU168" s="1">
-        <v>6.3369272237196768</v>
+        <v>6.3909574468085104</v>
       </c>
       <c r="CV168" s="1">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="CY168" s="1" t="str">
         <v>Célian</v>
       </c>
       <c r="CZ168" s="1">
-        <v>6.3369272237196768</v>
+        <v>6.3909574468085104</v>
       </c>
     </row>
     <row r="169" spans="1:104" x14ac:dyDescent="0.3">
@@ -13226,16 +12360,16 @@
         <v>Tom</v>
       </c>
       <c r="CU170" s="1">
-        <v>5.943708609271523</v>
+        <v>5.9387096774193546</v>
       </c>
       <c r="CV170" s="1">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="CY170" s="1" t="str">
         <v>Tom</v>
       </c>
       <c r="CZ170" s="1">
-        <v>5.943708609271523</v>
+        <v>5.9387096774193546</v>
       </c>
     </row>
     <row r="171" spans="1:104" x14ac:dyDescent="0.3">
@@ -13491,19 +12625,19 @@
       <c r="AX173" s="15"/>
       <c r="AY173" s="15"/>
       <c r="CT173" s="1" t="str">
-        <v>Mehdi</v>
+        <v>Jules</v>
       </c>
       <c r="CU173" s="1">
-        <v>5.7018779342723001</v>
+        <v>5.7555555555555555</v>
       </c>
       <c r="CV173" s="1">
-        <v>426</v>
+        <v>270</v>
       </c>
       <c r="CY173" s="1" t="str">
-        <v>Mehdi</v>
+        <v>Jules</v>
       </c>
       <c r="CZ173" s="1">
-        <v>5.7018779342723001</v>
+        <v>5.7555555555555555</v>
       </c>
     </row>
     <row r="174" spans="1:104" x14ac:dyDescent="0.3">
@@ -13579,19 +12713,19 @@
       <c r="AX174" s="15"/>
       <c r="AY174" s="15"/>
       <c r="CT174" s="1" t="str">
-        <v>Jules</v>
+        <v>Mehdi</v>
       </c>
       <c r="CU174" s="1">
-        <v>5.5593869731800769</v>
+        <v>5.7018779342723001</v>
       </c>
       <c r="CV174" s="1">
-        <v>261</v>
+        <v>426</v>
       </c>
       <c r="CY174" s="1" t="str">
-        <v>Jules</v>
+        <v>Mehdi</v>
       </c>
       <c r="CZ174" s="1">
-        <v>5.5593869731800769</v>
+        <v>5.7018779342723001</v>
       </c>
     </row>
     <row r="175" spans="1:104" x14ac:dyDescent="0.3">
@@ -13602,19 +12736,19 @@
         <v>26</v>
       </c>
       <c r="CT175" s="1" t="str">
-        <v>Damien</v>
+        <v>Achille</v>
       </c>
       <c r="CU175" s="1">
-        <v>5.4266487213997312</v>
+        <v>5.4065138721351023</v>
       </c>
       <c r="CV175" s="1">
-        <v>743</v>
+        <v>829</v>
       </c>
       <c r="CY175" s="1" t="str">
-        <v>Damien</v>
+        <v>Achille</v>
       </c>
       <c r="CZ175" s="1">
-        <v>5.4266487213997312</v>
+        <v>5.4065138721351023</v>
       </c>
     </row>
     <row r="176" spans="1:104" x14ac:dyDescent="0.3">
@@ -13649,19 +12783,19 @@
         <v>11</v>
       </c>
       <c r="CT176" s="1" t="str">
-        <v>Achille</v>
+        <v>Damien</v>
       </c>
       <c r="CU176" s="1">
-        <v>5.4065138721351023</v>
+        <v>5.3861517976031958</v>
       </c>
       <c r="CV176" s="1">
-        <v>829</v>
+        <v>751</v>
       </c>
       <c r="CY176" s="1" t="str">
-        <v>Achille</v>
+        <v>Damien</v>
       </c>
       <c r="CZ176" s="1">
-        <v>5.4065138721351023</v>
+        <v>5.3861517976031958</v>
       </c>
     </row>
     <row r="177" spans="1:104" x14ac:dyDescent="0.3">
@@ -14153,13 +13287,18 @@
     <sortCondition descending="1" ref="B176:B187"/>
   </sortState>
   <mergeCells count="40">
-    <mergeCell ref="BW9:BX9"/>
-    <mergeCell ref="BY9:BZ9"/>
-    <mergeCell ref="CA9:CB9"/>
-    <mergeCell ref="CC9:CD9"/>
-    <mergeCell ref="BG9:BH9"/>
-    <mergeCell ref="BI9:BJ9"/>
-    <mergeCell ref="BK9:BL9"/>
+    <mergeCell ref="AY9:AZ9"/>
+    <mergeCell ref="AA9:AB9"/>
+    <mergeCell ref="AC9:AD9"/>
+    <mergeCell ref="AE9:AF9"/>
+    <mergeCell ref="AK9:AL9"/>
+    <mergeCell ref="AI9:AJ9"/>
+    <mergeCell ref="AG9:AH9"/>
+    <mergeCell ref="AM9:AN9"/>
+    <mergeCell ref="AO9:AP9"/>
+    <mergeCell ref="AQ9:AR9"/>
+    <mergeCell ref="AS9:AT9"/>
+    <mergeCell ref="AU9:AV9"/>
     <mergeCell ref="BA9:BB9"/>
     <mergeCell ref="BC9:BD9"/>
     <mergeCell ref="BE9:BF9"/>
@@ -14176,118 +13315,115 @@
     <mergeCell ref="U9:V9"/>
     <mergeCell ref="W9:X9"/>
     <mergeCell ref="AW9:AX9"/>
-    <mergeCell ref="AY9:AZ9"/>
-    <mergeCell ref="AA9:AB9"/>
-    <mergeCell ref="AC9:AD9"/>
-    <mergeCell ref="AE9:AF9"/>
-    <mergeCell ref="AK9:AL9"/>
-    <mergeCell ref="AI9:AJ9"/>
-    <mergeCell ref="AG9:AH9"/>
-    <mergeCell ref="AM9:AN9"/>
-    <mergeCell ref="AO9:AP9"/>
-    <mergeCell ref="AQ9:AR9"/>
-    <mergeCell ref="AS9:AT9"/>
-    <mergeCell ref="AU9:AV9"/>
+    <mergeCell ref="BW9:BX9"/>
+    <mergeCell ref="BY9:BZ9"/>
+    <mergeCell ref="CA9:CB9"/>
+    <mergeCell ref="CC9:CD9"/>
+    <mergeCell ref="BG9:BH9"/>
+    <mergeCell ref="BI9:BJ9"/>
+    <mergeCell ref="BK9:BL9"/>
     <mergeCell ref="BM9:BN9"/>
     <mergeCell ref="BO9:BP9"/>
     <mergeCell ref="BQ9:BR9"/>
     <mergeCell ref="BS9:BT9"/>
     <mergeCell ref="BU9:BV9"/>
   </mergeCells>
-  <conditionalFormatting sqref="C1 E1 G1 I1 K1 M1 O1 Q1 S1 U1 W1 Y1 AA1 AC1 AE1 AG1 AI1 AK1 AM1 AO1 AQ1 AS1 AU1 AW1 AY1 BA1 BC1 BE1 BG1 BI1 BK1 BM1 BO1 BQ1 BS1 BU1 C9:AM9 AO9 AQ9 AS9 AU9 AW9 AY9 BA9 BC9 BE9 BG9 BI9 BK9 BM9 BO9 BQ9 BS9 BU9 BW1 BY1 CA1 CC1 BW9">
-    <cfRule type="expression" dxfId="24" priority="83" stopIfTrue="1">
+  <conditionalFormatting sqref="C1 E1 G1 I1 K1 M1 O1 Q1 S1 U1 W1 Y1 AA1 AC1 AE1 AG1 AI1 AK1 AM1 AO1 AQ1 AS1 AU1 AW1 AY1 BA1 BC1 BE1 BG1 BI1 BK1 BM1 BO1 BQ1 BS1 BU1 BW1 BY1 CA1 CC1 C9:AM9 AO9 AQ9 AS9 AU9 AW9 AY9 BA9 BC9 BE9 BG9 BI9 BK9 BM9 BO9 BQ9 BS9 BU9 BW9 BY9 CA9 CC9">
+    <cfRule type="expression" dxfId="24" priority="41" stopIfTrue="1">
+      <formula>NOT(OR("/"=C$1,AVERAGE($C$1:$CD$1)&lt;C$1,SMALL($C$1:$CD$1,1)=C$1,SMALL($C$1:$CD$1,2)=C$1,SMALL($C$1:$CD$1,3)=C$1,LARGE($C$1:$CD$1,1)=C$1,LARGE($C$1:$CD$1,2)=C$1,LARGE($C$1:$CD$1,3)=C$1))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="23" priority="43" stopIfTrue="1">
+      <formula>("/"=C$1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="22" priority="44" stopIfTrue="1">
+      <formula>NOT(OR("/"=C$1,AVERAGE($C$1:$CD$1)&gt;C$1,SMALL($C$1:$CD$1,1)=C$1,SMALL($C$1:$CD$1,2)=C$1,SMALL($C$1:$CD$1,3)=C$1,LARGE($C$1:$CD$1,1)=C$1,LARGE($C$1:$CD$1,2)=C$1,LARGE($C$1:$CD$1,3)=C$1))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="21" priority="82" stopIfTrue="1">
+      <formula>SMALL($C$1:$CD$1,3)=C$1</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="20" priority="84" stopIfTrue="1">
+      <formula>SMALL($C$1:$CD$1,1)=C$1</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="19" priority="87" stopIfTrue="1">
+      <formula>MAX($C$1:$CD$1)=C$1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C1 E1 G1 I1 K1 M1 O1 Q1 S1 U1 W1 Y1 AA1 AC1 AE1 AG1 AI1 AK1 AM1 AO1 AQ1 AS1 AU1 AW1 AY1 BA1 BC1 BE1 BG1 BI1 BK1 BM1 BO1 BQ1 BS1 BU1 BW1 BY1 CA1 CC1 C9:AM9 AO9 AQ9 AS9 AU9 AW9 AY9 BA9 BC9 BE9 BG9 BI9 BK9 BM9 BO9 BQ9 BS9 BU9 BW9">
+    <cfRule type="expression" dxfId="18" priority="83" stopIfTrue="1">
       <formula>SMALL($C$1:$CD$1,2)=C$1</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="C1 E1 G1 I1 K1 M1 O1 Q1 S1 U1 W1 Y1 AA1 AC1 AE1 AG1 AI1 AK1 AM1 AO1 AQ1 AS1 AU1 AW1 AY1 BA1 BC1 BE1 BG1 BI1 BK1 BM1 BO1 BQ1 BS1 BU1 BW1 BY1 CA1 CC1 C9:AM9 AO9 AQ9 AS9 AU9 AW9 AY9 BA9 BC9 BE9 BG9 BI9 BK9 BM9 BO9 BQ9 BS9 BU9 BY9 CA9 CC9 BW9">
+    <cfRule type="expression" dxfId="17" priority="86" stopIfTrue="1">
+      <formula>LARGE($C$1:$CD$1,2)=C$1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C1 E1 G1 I1 K1 M1 O1 Q1 S1 U1 W1 Y1 AA1 AC1 AE1 AG1 AI1 AK1 AM1 AO1 AQ1 AS1 AU1 AW1 AY1 BA1 BC1 BE1 BG1 BI1 BK1 BM1 BO1 BQ1 BS1 BU1 BW1 BY1 CA1 CC1 C9:AM9 AO9 AQ9 AS9 AU9 AW9 AY9 BA9 BC9 BE9 BG9 BI9 BK9 BM9 BO9 BQ9 BS9 BU9 BY9 CA9 CC9">
+    <cfRule type="expression" dxfId="16" priority="85" stopIfTrue="1">
+      <formula>LARGE($C$1:$CD$1,3)=C$1</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="G10:G94 I10:I94 K10:K94 M10:M94 C10:C187 E10:E187 O10:O187 Q10:Q187 S10:S187 U10:U187 W10:W187 Y10:Y187 AA10:AA187 AC10:AC187 AE10:AE187 AG10:AG187 AI10:AI187 AK10:AK187 AM10:AM187 AO10:AO187 AQ10:AQ187 AS10:AS187 AU10:AU187 AW10:AW187 AY10:AY187 BA10:BA187 BC10:BC187 BE10:BE187 G96:G187 I96:I187 K96:K187 M96:M187">
-    <cfRule type="expression" dxfId="23" priority="26" stopIfTrue="1">
+    <cfRule type="expression" dxfId="15" priority="26" stopIfTrue="1">
       <formula>(C10/D10)&gt;12</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="28" stopIfTrue="1">
+    <cfRule type="expression" dxfId="14" priority="28" stopIfTrue="1">
       <formula>(C10/D10)&lt;-2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="30" stopIfTrue="1">
+    <cfRule type="expression" dxfId="13" priority="30" stopIfTrue="1">
       <formula>(C10/D10)&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="32" stopIfTrue="1">
+    <cfRule type="expression" dxfId="12" priority="32" stopIfTrue="1">
       <formula>(C10/D10)&gt;10</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H10:H94 J10:J94 L10:L94 N10:N94 D10:D187 F10:F187 P10:P187 R10:R187 T10:T187 V10:V187 X10:X187 Z10:Z187 AB10:AB187 AD10:AD187 AF10:AF187 AH10:AH187 AJ10:AJ187 AL10:AL187 AN10:AN187 AP10:AP187 AR10:AR187 AT10:AT187 AV10:AV187 AX10:AX187 AZ10:AZ187 BB10:BB187 BD10:BD187 BF10:BF187 H96:H187 J96:J187 L96:L187 N96:N187">
-    <cfRule type="expression" dxfId="19" priority="25" stopIfTrue="1">
+    <cfRule type="expression" dxfId="11" priority="25" stopIfTrue="1">
       <formula>(C10/D10)&gt;12</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="27" stopIfTrue="1">
+    <cfRule type="expression" dxfId="10" priority="27" stopIfTrue="1">
       <formula>(C10/D10)&lt;-2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="29" stopIfTrue="1">
+    <cfRule type="expression" dxfId="9" priority="29" stopIfTrue="1">
       <formula>(C10/D10)&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="31" stopIfTrue="1">
+    <cfRule type="expression" dxfId="8" priority="31" stopIfTrue="1">
       <formula>(C10/D10)&gt;10</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="CM108:CM136">
-    <cfRule type="cellIs" dxfId="15" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="7" priority="3" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="4" operator="between">
+    <cfRule type="cellIs" dxfId="6" priority="4" operator="between">
       <formula>20</formula>
       <formula>50</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="5" operator="between">
+    <cfRule type="cellIs" dxfId="5" priority="5" operator="between">
       <formula>50</formula>
       <formula>100</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="6" operator="between">
+    <cfRule type="cellIs" dxfId="4" priority="6" operator="between">
       <formula>100</formula>
       <formula>250</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="11" priority="7" operator="between">
+    <cfRule type="cellIs" dxfId="3" priority="7" operator="between">
       <formula>250</formula>
       <formula>500</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="8" operator="between">
+    <cfRule type="cellIs" dxfId="2" priority="8" operator="between">
       <formula>500</formula>
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="CR108:CR129">
-    <cfRule type="cellIs" dxfId="9" priority="1" operator="between">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="between">
       <formula>1</formula>
       <formula>10</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="2" operator="between">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="between">
       <formula>10</formula>
       <formula>20</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1 E1 G1 I1 K1 M1 O1 Q1 S1 U1 W1 Y1 AA1 AC1 AE1 AG1 AI1 AK1 AM1 AO1 AQ1 AS1 AU1 AW1 AY1 BA1 BC1 BE1 BG1 BI1 BK1 BM1 BO1 BQ1 BS1 BU1 C9:AM9 AO9 AQ9 AS9 AU9 AW9 AY9 BA9 BC9 BE9 BG9 BI9 BK9 BM9 BO9 BQ9 BS9 BU9 BW1 BY1 CA1 CC1 BY9 CA9 CC9 BW9">
-    <cfRule type="expression" dxfId="7" priority="87" stopIfTrue="1">
-      <formula>MAX($C$1:$CD$1)=C$1</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="5" priority="86" stopIfTrue="1">
-      <formula>LARGE($C$1:$CD$1,2)=C$1</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="84" stopIfTrue="1">
-      <formula>SMALL($C$1:$CD$1,1)=C$1</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="3" priority="82" stopIfTrue="1">
-      <formula>SMALL($C$1:$CD$1,3)=C$1</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="2" priority="44" stopIfTrue="1">
-      <formula>NOT(OR("/"=C$1,AVERAGE($C$1:$CD$1)&gt;C$1,SMALL($C$1:$CD$1,1)=C$1,SMALL($C$1:$CD$1,2)=C$1,SMALL($C$1:$CD$1,3)=C$1,LARGE($C$1:$CD$1,1)=C$1,LARGE($C$1:$CD$1,2)=C$1,LARGE($C$1:$CD$1,3)=C$1))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="43" stopIfTrue="1">
-      <formula>("/"=C$1)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="0" priority="41" stopIfTrue="1">
-      <formula>NOT(OR("/"=C$1,AVERAGE($C$1:$CD$1)&lt;C$1,SMALL($C$1:$CD$1,1)=C$1,SMALL($C$1:$CD$1,2)=C$1,SMALL($C$1:$CD$1,3)=C$1,LARGE($C$1:$CD$1,1)=C$1,LARGE($C$1:$CD$1,2)=C$1,LARGE($C$1:$CD$1,3)=C$1))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1 E1 G1 I1 K1 M1 O1 Q1 S1 U1 W1 Y1 AA1 AC1 AE1 AG1 AI1 AK1 AM1 AO1 AQ1 AS1 AU1 AW1 AY1 BA1 BC1 BE1 BG1 BI1 BK1 BM1 BO1 BQ1 BS1 BU1 C9:AM9 AO9 AQ9 AS9 AU9 AW9 AY9 BA9 BC9 BE9 BG9 BI9 BK9 BM9 BO9 BQ9 BS9 BU9 BW1 BY1 CA1 CC1 BY9 CA9 CC9">
-    <cfRule type="expression" dxfId="6" priority="85" stopIfTrue="1">
-      <formula>LARGE($C$1:$CD$1,3)=C$1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.70000000000000007" right="0.70000000000000007" top="0.75" bottom="0.75" header="0.30000000000000004" footer="0.30000000000000004"/>
@@ -14335,13 +13471,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="str">
-        <v>Gauthier</v>
+        <v>Boris</v>
       </c>
       <c r="C2" s="1" t="str">
-        <v>7.253</v>
+        <v>7.205</v>
       </c>
       <c r="D2" s="1">
-        <v>79</v>
+        <v>1218</v>
       </c>
       <c r="F2" t="str">
         <v>nombre de parties</v>
@@ -14352,13 +13488,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="str">
-        <v>Boris</v>
+        <v>Gauthier</v>
       </c>
       <c r="C3" s="1" t="str">
-        <v>7.174</v>
+        <v>7.080</v>
       </c>
       <c r="D3" s="1">
-        <v>1205</v>
+        <v>87</v>
       </c>
       <c r="F3" t="str">
         <v>entre 1 et 10</v>
@@ -14404,10 +13540,10 @@
         <v>Célian</v>
       </c>
       <c r="C5" s="1" t="str">
-        <v>6.337</v>
+        <v>6.391</v>
       </c>
       <c r="D5" s="1">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="F5" t="str">
         <v>entre 20 et 50</v>
@@ -14452,10 +13588,10 @@
         <v>Tom</v>
       </c>
       <c r="C7" s="1" t="str">
-        <v>5.944</v>
+        <v>5.939</v>
       </c>
       <c r="D7" s="1">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="F7" t="str">
         <v>entre 100 et 250</v>
@@ -14521,13 +13657,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="str">
-        <v>Mehdi</v>
+        <v>Jules</v>
       </c>
       <c r="C10" s="1" t="str">
-        <v>5.702</v>
+        <v>5.756</v>
       </c>
       <c r="D10" s="1">
-        <v>426</v>
+        <v>270</v>
       </c>
       <c r="F10" t="str">
         <v>plus de 1000</v>
@@ -14545,13 +13681,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="str">
-        <v>Jules</v>
+        <v>Mehdi</v>
       </c>
       <c r="C11" s="1" t="str">
-        <v>5.559</v>
+        <v>5.702</v>
       </c>
       <c r="D11" s="1">
-        <v>261</v>
+        <v>426</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
@@ -14562,10 +13698,10 @@
         <v>Hugo</v>
       </c>
       <c r="C12" s="1" t="str">
-        <v>5.433</v>
+        <v>5.657</v>
       </c>
       <c r="D12" s="1">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
@@ -14573,20 +13709,20 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="str">
-        <v>Damien</v>
+        <v>Achille</v>
       </c>
       <c r="C13" s="1" t="str">
-        <v>5.427</v>
+        <v>5.407</v>
       </c>
       <c r="D13" s="1">
-        <v>743</v>
+        <v>829</v>
       </c>
       <c r="F13" t="s">
         <v>102</v>
       </c>
       <c r="G13">
         <f>AVERAGE('All stat'!C1:CD1)</f>
-        <v>5.140630780075802</v>
+        <v>5.151661271313662</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
@@ -14594,13 +13730,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="str">
-        <v>Achille</v>
+        <v>Bruno</v>
       </c>
       <c r="C14" s="1" t="str">
-        <v>5.407</v>
+        <v>5.400</v>
       </c>
       <c r="D14" s="1">
-        <v>829</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
@@ -14608,13 +13744,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="str">
-        <v>Bruno</v>
+        <v>Damien</v>
       </c>
       <c r="C15" s="1" t="str">
-        <v>5.400</v>
+        <v>5.386</v>
       </c>
       <c r="D15" s="1">
-        <v>20</v>
+        <v>751</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">

--- a/classement_whist_2023_2025.xlsx
+++ b/classement_whist_2023_2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a20b8382962b136a/Bureau/loisir/whist/projet_application_streamlit/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="275" documentId="14_{167F2DC3-291A-4B33-AB7D-1A6E034E4A5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{419363F9-9091-4346-A444-A69D9C20EAED}"/>
+  <xr:revisionPtr revIDLastSave="343" documentId="14_{167F2DC3-291A-4B33-AB7D-1A6E034E4A5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7AB4943E-9C2D-42E6-ACA4-A2B2BD7669C5}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="103">
   <si>
     <t>global</t>
   </si>
@@ -618,10 +618,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="8">
@@ -634,7 +634,35 @@
     <cellStyle name="cf7" xfId="7" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="25">
+  <dxfs count="29">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF5050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1202,7 +1230,7 @@
       </c>
       <c r="G1" s="1">
         <f t="shared" ref="G1" si="2">IF(H2&gt;19,G2/H2,"/")</f>
-        <v>7.2048440065681447</v>
+        <v>7.2051597051597049</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>2</v>
@@ -1223,7 +1251,7 @@
       </c>
       <c r="M1" s="1">
         <f t="shared" ref="M1" si="5">IF(N2&gt;19,M2/N2,"/")</f>
-        <v>5.3861517976031958</v>
+        <v>5.4432855280312911</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>2</v>
@@ -1237,14 +1265,14 @@
       </c>
       <c r="Q1" s="1">
         <f t="shared" ref="Q1" si="7">IF(R2&gt;19,Q2/R2,"/")</f>
-        <v>6.3909574468085104</v>
+        <v>6.3045685279187813</v>
       </c>
       <c r="R1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="S1" s="1">
         <f t="shared" ref="S1" si="8">IF(T2&gt;19,S2/T2,"/")</f>
-        <v>5.9387096774193546</v>
+        <v>5.8761329305135952</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>2</v>
@@ -1272,14 +1300,14 @@
       </c>
       <c r="AA1" s="1">
         <f t="shared" ref="AA1" si="12">IF(AB2&gt;19,AA2/AB2,"/")</f>
-        <v>4.7625368731563418</v>
+        <v>4.8478260869565215</v>
       </c>
       <c r="AB1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="AC1" s="1">
         <f>IF(AD2&gt;19,AC2/AD2,"/")</f>
-        <v>5.7555555555555555</v>
+        <v>5.7119205298013247</v>
       </c>
       <c r="AD1" s="1" t="s">
         <v>2</v>
@@ -1300,7 +1328,7 @@
       </c>
       <c r="AI1" s="1">
         <f t="shared" ref="AI1" si="15">IF(AJ2&gt;19,AI2/AJ2,"/")</f>
-        <v>2.9607843137254903</v>
+        <v>3.6440677966101696</v>
       </c>
       <c r="AJ1" s="1" t="s">
         <v>2</v>
@@ -1377,28 +1405,28 @@
       </c>
       <c r="BE1" s="1">
         <f t="shared" ref="BE1" si="26">IF(BF2&gt;19,BE2/BF2,"/")</f>
-        <v>4.8974358974358978</v>
+        <v>4.7732558139534884</v>
       </c>
       <c r="BF1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="BG1" s="1">
         <f t="shared" ref="BG1" si="27">IF(BH2&gt;19,BG2/BH2,"/")</f>
-        <v>5.6571428571428575</v>
+        <v>5.2249999999999996</v>
       </c>
       <c r="BH1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="BI1" s="1">
         <f t="shared" ref="BI1" si="28">IF(BJ2&gt;19,BI2/BJ2,"/")</f>
-        <v>4.6833333333333336</v>
+        <v>5.3421052631578947</v>
       </c>
       <c r="BJ1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="BK1" s="1" t="str">
+      <c r="BK1" s="1">
         <f t="shared" ref="BK1" si="29">IF(BL2&gt;19,BK2/BL2,"/")</f>
-        <v>/</v>
+        <v>5.5</v>
       </c>
       <c r="BL1" s="1" t="s">
         <v>2</v>
@@ -1489,11 +1517,11 @@
       </c>
       <c r="G2" s="1">
         <f t="shared" si="39"/>
-        <v>8775.5</v>
+        <v>8797.5</v>
       </c>
       <c r="H2" s="1">
         <f t="shared" si="39"/>
-        <v>1218</v>
+        <v>1221</v>
       </c>
       <c r="I2" s="1">
         <f t="shared" si="39"/>
@@ -1513,11 +1541,11 @@
       </c>
       <c r="M2" s="1">
         <f t="shared" si="40"/>
-        <v>4045</v>
+        <v>4175</v>
       </c>
       <c r="N2" s="1">
         <f t="shared" si="40"/>
-        <v>751</v>
+        <v>767</v>
       </c>
       <c r="O2" s="1">
         <f t="shared" si="40"/>
@@ -1529,19 +1557,19 @@
       </c>
       <c r="Q2" s="1">
         <f t="shared" si="40"/>
-        <v>2403</v>
+        <v>2484</v>
       </c>
       <c r="R2" s="1">
         <f t="shared" si="40"/>
-        <v>376</v>
+        <v>394</v>
       </c>
       <c r="S2" s="1">
         <f t="shared" si="40"/>
-        <v>1841</v>
+        <v>1945</v>
       </c>
       <c r="T2" s="1">
         <f t="shared" si="40"/>
-        <v>310</v>
+        <v>331</v>
       </c>
       <c r="U2" s="1">
         <f t="shared" si="40"/>
@@ -1569,19 +1597,19 @@
       </c>
       <c r="AA2" s="1">
         <f t="shared" si="40"/>
-        <v>1614.5</v>
+        <v>1672.5</v>
       </c>
       <c r="AB2" s="1">
         <f t="shared" si="40"/>
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="AC2" s="1">
         <f t="shared" si="40"/>
-        <v>1554</v>
+        <v>1725</v>
       </c>
       <c r="AD2" s="1">
         <f t="shared" si="40"/>
-        <v>270</v>
+        <v>302</v>
       </c>
       <c r="AE2" s="1">
         <f t="shared" si="40"/>
@@ -1601,11 +1629,11 @@
       </c>
       <c r="AI2" s="1">
         <f t="shared" si="40"/>
-        <v>151</v>
+        <v>215</v>
       </c>
       <c r="AJ2" s="1">
         <f t="shared" si="40"/>
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="AK2" s="1">
         <f t="shared" si="40"/>
@@ -1689,35 +1717,35 @@
       </c>
       <c r="BE2" s="1">
         <f t="shared" ref="BE2:BF2" si="42">BE4+BE6+BE8</f>
-        <v>764</v>
+        <v>821</v>
       </c>
       <c r="BF2" s="1">
         <f t="shared" si="42"/>
-        <v>156</v>
+        <v>172</v>
       </c>
       <c r="BG2" s="1">
         <f t="shared" ref="BG2:BL2" si="43">BG4+BG6+BG8</f>
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="BH2" s="1">
         <f t="shared" si="43"/>
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="BI2" s="1">
         <f t="shared" si="43"/>
-        <v>281</v>
+        <v>406</v>
       </c>
       <c r="BJ2" s="1">
         <f t="shared" si="43"/>
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="BK2" s="1">
         <f t="shared" si="43"/>
-        <v>47</v>
+        <v>121</v>
       </c>
       <c r="BL2" s="1">
         <f t="shared" si="43"/>
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="BM2" s="1">
         <f t="shared" ref="BM2:BV2" si="44">BM4+BM6+BM8</f>
@@ -3059,7 +3087,7 @@
       </c>
       <c r="G7" s="15">
         <f t="shared" ref="G7" si="139">G8/H8</f>
-        <v>7.391774891774892</v>
+        <v>7.3915229885057467</v>
       </c>
       <c r="H7" s="15" t="s">
         <v>2</v>
@@ -3080,7 +3108,7 @@
       </c>
       <c r="M7" s="15">
         <f t="shared" ref="M7" si="142">M8/N8</f>
-        <v>5.7353463587921851</v>
+        <v>5.8013816925734023</v>
       </c>
       <c r="N7" s="15" t="s">
         <v>2</v>
@@ -3094,14 +3122,14 @@
       </c>
       <c r="Q7" s="15">
         <f t="shared" ref="Q7" si="144">Q8/R8</f>
-        <v>6.5348837209302326</v>
+        <v>6.4200626959247646</v>
       </c>
       <c r="R7" s="15" t="s">
         <v>2</v>
       </c>
       <c r="S7" s="15">
         <f t="shared" ref="S7" si="145">S8/T8</f>
-        <v>5.333333333333333</v>
+        <v>5.2977777777777781</v>
       </c>
       <c r="T7" s="15" t="s">
         <v>2</v>
@@ -3129,14 +3157,14 @@
       </c>
       <c r="AA7" s="15">
         <f t="shared" ref="AA7" si="149">AA8/AB8</f>
-        <v>5.1960431654676258</v>
+        <v>5.290492957746479</v>
       </c>
       <c r="AB7" s="15" t="s">
         <v>2</v>
       </c>
       <c r="AC7" s="15">
         <f t="shared" ref="AC7" si="150">AC8/AD8</f>
-        <v>5.9153846153846157</v>
+        <v>5.852739726027397</v>
       </c>
       <c r="AD7" s="15" t="s">
         <v>2</v>
@@ -3157,7 +3185,7 @@
       </c>
       <c r="AI7" s="15">
         <f t="shared" ref="AI7" si="153">AI8/AJ8</f>
-        <v>2.9607843137254903</v>
+        <v>3.6440677966101696</v>
       </c>
       <c r="AJ7" s="15" t="s">
         <v>2</v>
@@ -3234,28 +3262,28 @@
       </c>
       <c r="BE7" s="15">
         <f t="shared" ref="BE7" si="164">BE8/BF8</f>
-        <v>4.8974358974358978</v>
+        <v>4.7732558139534884</v>
       </c>
       <c r="BF7" s="15" t="s">
         <v>2</v>
       </c>
       <c r="BG7" s="15">
         <f t="shared" ref="BG7" si="165">BG8/BH8</f>
-        <v>5.6571428571428575</v>
+        <v>5.2249999999999996</v>
       </c>
       <c r="BH7" s="15" t="s">
         <v>2</v>
       </c>
       <c r="BI7" s="15">
         <f t="shared" ref="BI7" si="166">BI8/BJ8</f>
-        <v>4.6833333333333336</v>
+        <v>5.3421052631578947</v>
       </c>
       <c r="BJ7" s="15" t="s">
         <v>2</v>
       </c>
       <c r="BK7" s="15">
         <f t="shared" ref="BK7" si="167">BK8/BL8</f>
-        <v>4.2727272727272725</v>
+        <v>5.5</v>
       </c>
       <c r="BL7" s="15" t="s">
         <v>2</v>
@@ -3347,11 +3375,11 @@
       </c>
       <c r="G8" s="15">
         <f t="shared" si="177"/>
-        <v>5122.5</v>
+        <v>5144.5</v>
       </c>
       <c r="H8" s="15">
         <f t="shared" si="177"/>
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="I8" s="15">
         <f t="shared" si="177"/>
@@ -3371,11 +3399,11 @@
       </c>
       <c r="M8" s="15">
         <f t="shared" si="178"/>
-        <v>3229</v>
+        <v>3359</v>
       </c>
       <c r="N8" s="15">
         <f t="shared" si="178"/>
-        <v>563</v>
+        <v>579</v>
       </c>
       <c r="O8" s="15">
         <f t="shared" si="178"/>
@@ -3387,19 +3415,19 @@
       </c>
       <c r="Q8" s="15">
         <f t="shared" si="178"/>
-        <v>1967</v>
+        <v>2048</v>
       </c>
       <c r="R8" s="15">
         <f t="shared" si="178"/>
-        <v>301</v>
+        <v>319</v>
       </c>
       <c r="S8" s="15">
         <f t="shared" si="178"/>
-        <v>1088</v>
+        <v>1192</v>
       </c>
       <c r="T8" s="15">
         <f t="shared" si="178"/>
-        <v>204</v>
+        <v>225</v>
       </c>
       <c r="U8" s="15">
         <f t="shared" si="178"/>
@@ -3427,19 +3455,19 @@
       </c>
       <c r="AA8" s="15">
         <f t="shared" si="178"/>
-        <v>1444.5</v>
+        <v>1502.5</v>
       </c>
       <c r="AB8" s="15">
         <f t="shared" si="178"/>
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="AC8" s="15">
         <f t="shared" si="178"/>
-        <v>1538</v>
+        <v>1709</v>
       </c>
       <c r="AD8" s="15">
         <f t="shared" si="178"/>
-        <v>260</v>
+        <v>292</v>
       </c>
       <c r="AE8" s="15">
         <f t="shared" si="178"/>
@@ -3459,11 +3487,11 @@
       </c>
       <c r="AI8" s="15">
         <f t="shared" si="178"/>
-        <v>151</v>
+        <v>215</v>
       </c>
       <c r="AJ8" s="15">
         <f t="shared" si="178"/>
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="AK8" s="15">
         <f t="shared" si="178"/>
@@ -3547,35 +3575,35 @@
       </c>
       <c r="BE8" s="15">
         <f t="shared" ref="BE8:BF8" si="180">SUM(BE10:BE130)</f>
-        <v>764</v>
+        <v>821</v>
       </c>
       <c r="BF8" s="15">
         <f t="shared" si="180"/>
-        <v>156</v>
+        <v>172</v>
       </c>
       <c r="BG8" s="15">
         <f t="shared" ref="BG8:BL8" si="181">SUM(BG10:BG130)</f>
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="BH8" s="15">
         <f t="shared" si="181"/>
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="BI8" s="15">
         <f t="shared" si="181"/>
-        <v>281</v>
+        <v>406</v>
       </c>
       <c r="BJ8" s="15">
         <f t="shared" si="181"/>
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="BK8" s="15">
         <f t="shared" si="181"/>
-        <v>47</v>
+        <v>121</v>
       </c>
       <c r="BL8" s="15">
         <f t="shared" si="181"/>
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="BM8" s="15">
         <f t="shared" ref="BM8:BV8" si="182">SUM(BM10:BM130)</f>
@@ -3651,166 +3679,166 @@
       </c>
     </row>
     <row r="9" spans="1:87" x14ac:dyDescent="0.3">
-      <c r="C9" s="25" t="s">
+      <c r="C9" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="D9" s="25"/>
-      <c r="E9" s="25" t="s">
+      <c r="D9" s="26"/>
+      <c r="E9" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="F9" s="25"/>
-      <c r="G9" s="25" t="s">
+      <c r="F9" s="26"/>
+      <c r="G9" s="26" t="s">
         <v>72</v>
       </c>
-      <c r="H9" s="25"/>
-      <c r="I9" s="25" t="s">
+      <c r="H9" s="26"/>
+      <c r="I9" s="26" t="s">
         <v>73</v>
       </c>
-      <c r="J9" s="25"/>
-      <c r="K9" s="25" t="s">
+      <c r="J9" s="26"/>
+      <c r="K9" s="26" t="s">
         <v>74</v>
       </c>
-      <c r="L9" s="25"/>
-      <c r="M9" s="25" t="s">
+      <c r="L9" s="26"/>
+      <c r="M9" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="N9" s="25"/>
-      <c r="O9" s="25" t="s">
+      <c r="N9" s="26"/>
+      <c r="O9" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="P9" s="25"/>
-      <c r="Q9" s="25" t="s">
+      <c r="P9" s="26"/>
+      <c r="Q9" s="26" t="s">
         <v>77</v>
       </c>
-      <c r="R9" s="25"/>
-      <c r="S9" s="25" t="s">
+      <c r="R9" s="26"/>
+      <c r="S9" s="26" t="s">
         <v>78</v>
       </c>
-      <c r="T9" s="25"/>
-      <c r="U9" s="25" t="s">
+      <c r="T9" s="26"/>
+      <c r="U9" s="26" t="s">
         <v>79</v>
       </c>
-      <c r="V9" s="25"/>
-      <c r="W9" s="25" t="s">
+      <c r="V9" s="26"/>
+      <c r="W9" s="26" t="s">
         <v>80</v>
       </c>
-      <c r="X9" s="25"/>
-      <c r="Y9" s="25" t="s">
+      <c r="X9" s="26"/>
+      <c r="Y9" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="Z9" s="25"/>
-      <c r="AA9" s="25" t="s">
+      <c r="Z9" s="26"/>
+      <c r="AA9" s="26" t="s">
         <v>82</v>
       </c>
-      <c r="AB9" s="25"/>
-      <c r="AC9" s="25" t="s">
+      <c r="AB9" s="26"/>
+      <c r="AC9" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="AD9" s="25"/>
-      <c r="AE9" s="25" t="s">
+      <c r="AD9" s="26"/>
+      <c r="AE9" s="26" t="s">
         <v>83</v>
       </c>
-      <c r="AF9" s="25"/>
-      <c r="AG9" s="25" t="s">
+      <c r="AF9" s="26"/>
+      <c r="AG9" s="26" t="s">
         <v>84</v>
       </c>
-      <c r="AH9" s="25"/>
-      <c r="AI9" s="25" t="s">
+      <c r="AH9" s="26"/>
+      <c r="AI9" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="AJ9" s="25"/>
-      <c r="AK9" s="25" t="s">
+      <c r="AJ9" s="26"/>
+      <c r="AK9" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="AL9" s="25"/>
-      <c r="AM9" s="26" t="s">
+      <c r="AL9" s="26"/>
+      <c r="AM9" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="AN9" s="26"/>
-      <c r="AO9" s="26" t="s">
+      <c r="AN9" s="25"/>
+      <c r="AO9" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="AP9" s="26"/>
-      <c r="AQ9" s="26" t="s">
+      <c r="AP9" s="25"/>
+      <c r="AQ9" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="AR9" s="26"/>
-      <c r="AS9" s="26" t="s">
+      <c r="AR9" s="25"/>
+      <c r="AS9" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="AT9" s="26"/>
-      <c r="AU9" s="26" t="s">
+      <c r="AT9" s="25"/>
+      <c r="AU9" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="AV9" s="26"/>
-      <c r="AW9" s="26" t="s">
+      <c r="AV9" s="25"/>
+      <c r="AW9" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="AX9" s="26"/>
-      <c r="AY9" s="26" t="s">
+      <c r="AX9" s="25"/>
+      <c r="AY9" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="AZ9" s="26"/>
-      <c r="BA9" s="25" t="s">
+      <c r="AZ9" s="25"/>
+      <c r="BA9" s="26" t="s">
         <v>90</v>
       </c>
-      <c r="BB9" s="25"/>
-      <c r="BC9" s="25" t="s">
+      <c r="BB9" s="26"/>
+      <c r="BC9" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="BD9" s="25"/>
-      <c r="BE9" s="25" t="s">
+      <c r="BD9" s="26"/>
+      <c r="BE9" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="BF9" s="25"/>
-      <c r="BG9" s="26" t="s">
+      <c r="BF9" s="26"/>
+      <c r="BG9" s="25" t="s">
         <v>91</v>
       </c>
-      <c r="BH9" s="26"/>
-      <c r="BI9" s="25" t="s">
+      <c r="BH9" s="25"/>
+      <c r="BI9" s="26" t="s">
         <v>92</v>
       </c>
-      <c r="BJ9" s="25"/>
-      <c r="BK9" s="25" t="s">
+      <c r="BJ9" s="26"/>
+      <c r="BK9" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="BL9" s="25"/>
-      <c r="BM9" s="25" t="s">
+      <c r="BL9" s="26"/>
+      <c r="BM9" s="26" t="s">
         <v>95</v>
       </c>
-      <c r="BN9" s="25"/>
-      <c r="BO9" s="25" t="s">
+      <c r="BN9" s="26"/>
+      <c r="BO9" s="26" t="s">
         <v>96</v>
       </c>
-      <c r="BP9" s="25"/>
-      <c r="BQ9" s="25" t="s">
+      <c r="BP9" s="26"/>
+      <c r="BQ9" s="26" t="s">
         <v>97</v>
       </c>
-      <c r="BR9" s="25"/>
-      <c r="BS9" s="25" t="s">
+      <c r="BR9" s="26"/>
+      <c r="BS9" s="26" t="s">
         <v>99</v>
       </c>
-      <c r="BT9" s="25"/>
-      <c r="BU9" s="25" t="s">
+      <c r="BT9" s="26"/>
+      <c r="BU9" s="26" t="s">
         <v>98</v>
       </c>
-      <c r="BV9" s="25"/>
-      <c r="BW9" s="25" t="s">
+      <c r="BV9" s="26"/>
+      <c r="BW9" s="26" t="s">
         <v>100</v>
       </c>
-      <c r="BX9" s="25"/>
-      <c r="BY9" s="25" t="s">
+      <c r="BX9" s="26"/>
+      <c r="BY9" s="26" t="s">
         <v>101</v>
       </c>
-      <c r="BZ9" s="25"/>
-      <c r="CA9" s="25" t="s">
+      <c r="BZ9" s="26"/>
+      <c r="CA9" s="26" t="s">
         <v>94</v>
       </c>
-      <c r="CB9" s="25"/>
-      <c r="CC9" s="25" t="s">
+      <c r="CB9" s="26"/>
+      <c r="CC9" s="26" t="s">
         <v>94</v>
       </c>
-      <c r="CD9" s="25"/>
+      <c r="CD9" s="26"/>
     </row>
     <row r="10" spans="1:87" x14ac:dyDescent="0.3">
       <c r="B10" s="1">
@@ -3831,28 +3859,157 @@
       <c r="B13" s="1">
         <v>173</v>
       </c>
+      <c r="S13" s="1">
+        <v>41</v>
+      </c>
+      <c r="T13" s="1">
+        <v>5</v>
+      </c>
+      <c r="AC13" s="1">
+        <v>43</v>
+      </c>
+      <c r="AD13" s="1">
+        <v>5</v>
+      </c>
+      <c r="BG13" s="1">
+        <v>11</v>
+      </c>
+      <c r="BH13" s="1">
+        <v>5</v>
+      </c>
+      <c r="BK13" s="1">
+        <v>47</v>
+      </c>
+      <c r="BL13" s="1">
+        <v>5</v>
+      </c>
     </row>
     <row r="14" spans="1:87" x14ac:dyDescent="0.3">
       <c r="B14" s="1">
         <v>172</v>
       </c>
+      <c r="Q14" s="1">
+        <v>70</v>
+      </c>
+      <c r="R14" s="1">
+        <v>16</v>
+      </c>
+      <c r="AC14" s="1">
+        <v>103</v>
+      </c>
+      <c r="AD14" s="1">
+        <v>16</v>
+      </c>
+      <c r="BE14" s="1">
+        <v>57</v>
+      </c>
+      <c r="BF14" s="1">
+        <v>16</v>
+      </c>
+      <c r="BI14" s="1">
+        <v>125</v>
+      </c>
+      <c r="BJ14" s="1">
+        <v>16</v>
+      </c>
     </row>
     <row r="15" spans="1:87" x14ac:dyDescent="0.3">
       <c r="B15" s="1">
         <v>171</v>
       </c>
+      <c r="M15" s="1">
+        <v>65</v>
+      </c>
+      <c r="N15" s="1">
+        <v>8</v>
+      </c>
+      <c r="S15" s="1">
+        <v>52</v>
+      </c>
+      <c r="T15" s="1">
+        <v>8</v>
+      </c>
+      <c r="AC15" s="1">
+        <v>25</v>
+      </c>
+      <c r="AD15" s="1">
+        <v>8</v>
+      </c>
+      <c r="AI15" s="1">
+        <v>64</v>
+      </c>
+      <c r="AJ15" s="1">
+        <v>8</v>
+      </c>
     </row>
     <row r="16" spans="1:87" x14ac:dyDescent="0.3">
       <c r="B16" s="1">
         <v>170</v>
       </c>
+      <c r="M16" s="1">
+        <v>42</v>
+      </c>
+      <c r="N16" s="1">
+        <v>6</v>
+      </c>
+      <c r="S16" s="1">
+        <v>11</v>
+      </c>
+      <c r="T16" s="1">
+        <v>6</v>
+      </c>
+      <c r="AA16" s="1">
+        <v>58</v>
+      </c>
+      <c r="AB16" s="1">
+        <v>6</v>
+      </c>
+      <c r="BK16" s="1">
+        <v>27</v>
+      </c>
+      <c r="BL16" s="1">
+        <v>6</v>
+      </c>
     </row>
     <row r="17" spans="1:78" x14ac:dyDescent="0.3">
       <c r="B17" s="1">
         <v>169</v>
       </c>
+      <c r="G17" s="1">
+        <v>22</v>
+      </c>
+      <c r="H17" s="1">
+        <v>3</v>
+      </c>
+      <c r="M17" s="1">
+        <v>23</v>
+      </c>
+      <c r="N17" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q17" s="1">
+        <v>11</v>
+      </c>
+      <c r="R17" s="1">
+        <v>2</v>
+      </c>
+      <c r="S17" s="1">
+        <v>0</v>
+      </c>
+      <c r="T17" s="1">
+        <v>2</v>
+      </c>
+      <c r="AC17" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD17" s="1">
+        <v>3</v>
+      </c>
     </row>
     <row r="18" spans="1:78" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="B18" s="1">
         <v>168</v>
       </c>
@@ -3888,6 +4045,9 @@
       </c>
     </row>
     <row r="19" spans="1:78" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="B19" s="1">
         <v>167</v>
       </c>
@@ -4217,6 +4377,9 @@
       </c>
     </row>
     <row r="29" spans="1:78" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="B29" s="1">
         <v>157</v>
       </c>
@@ -4246,6 +4409,9 @@
       </c>
     </row>
     <row r="30" spans="1:78" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="B30" s="1">
         <v>156</v>
       </c>
@@ -7061,7 +7227,7 @@
         <v>30</v>
       </c>
       <c r="CJ108" s="1" cm="1">
-        <f t="array" ref="CJ108:CM133">_xlfn.LET(
+        <f t="array" ref="CJ108:CM134">_xlfn.LET(
   _xlpm.cols_impairs, _xlfn.SEQUENCE(1,COLUMNS(C1:BV1)/2,1,2),
   _xlpm.cols_pairs,   _xlfn.SEQUENCE(1,COLUMNS(C2:BV2)/2,2,2),
   _xlpm.noms,     TRANSPOSE(INDEX(C9:BV9,,_xlpm.cols_impairs)),
@@ -7087,7 +7253,7 @@
         <v>7.205</v>
       </c>
       <c r="CM108" s="1">
-        <v>1218</v>
+        <v>1221</v>
       </c>
       <c r="CO108" s="1" cm="1">
         <f t="array" ref="CO108:CR114">_xlfn.LET(
@@ -7124,7 +7290,7 @@
         <v>Boris</v>
       </c>
       <c r="CU108" s="1">
-        <v>7.2048440065681447</v>
+        <v>7.2051597051597049</v>
       </c>
     </row>
     <row r="109" spans="1:99" x14ac:dyDescent="0.3">
@@ -7256,7 +7422,7 @@
         <v>Célian</v>
       </c>
       <c r="CU110" s="1">
-        <v>6.3909574468085104</v>
+        <v>6.3045685279187813</v>
       </c>
     </row>
     <row r="111" spans="1:99" x14ac:dyDescent="0.3">
@@ -7297,10 +7463,10 @@
         <v>Célian</v>
       </c>
       <c r="CL111" s="1" t="str">
-        <v>6.391</v>
+        <v>6.305</v>
       </c>
       <c r="CM111" s="1">
-        <v>376</v>
+        <v>394</v>
       </c>
       <c r="CO111" s="1">
         <v>4</v>
@@ -7381,10 +7547,10 @@
         <v>5</v>
       </c>
       <c r="CT112" s="1" t="str">
-        <v>Tom</v>
+        <v>Samuel</v>
       </c>
       <c r="CU112" s="1">
-        <v>5.9387096774193546</v>
+        <v>5.9099526066350707</v>
       </c>
     </row>
     <row r="113" spans="1:99" x14ac:dyDescent="0.3">
@@ -7426,13 +7592,13 @@
         <v>6</v>
       </c>
       <c r="CK113" s="1" t="str">
-        <v>Tom</v>
+        <v>Samuel</v>
       </c>
       <c r="CL113" s="1" t="str">
-        <v>5.939</v>
+        <v>5.910</v>
       </c>
       <c r="CM113" s="1">
-        <v>310</v>
+        <v>211</v>
       </c>
       <c r="CO113" s="1">
         <v>6</v>
@@ -7447,10 +7613,10 @@
         <v>11</v>
       </c>
       <c r="CT113" s="1" t="str">
-        <v>Samuel</v>
+        <v>Joachim</v>
       </c>
       <c r="CU113" s="1">
-        <v>5.9099526066350707</v>
+        <v>5.8899082568807337</v>
       </c>
     </row>
     <row r="114" spans="1:99" x14ac:dyDescent="0.3">
@@ -7492,13 +7658,13 @@
         <v>7</v>
       </c>
       <c r="CK114" s="1" t="str">
-        <v>Samuel</v>
+        <v>Joachim</v>
       </c>
       <c r="CL114" s="1" t="str">
-        <v>5.910</v>
+        <v>5.890</v>
       </c>
       <c r="CM114" s="1">
-        <v>211</v>
+        <v>109</v>
       </c>
       <c r="CO114" s="1">
         <v>7</v>
@@ -7513,10 +7679,10 @@
         <v>12</v>
       </c>
       <c r="CT114" s="1" t="str">
-        <v>Joachim</v>
+        <v>Tom</v>
       </c>
       <c r="CU114" s="1">
-        <v>5.8899082568807337</v>
+        <v>5.8761329305135952</v>
       </c>
     </row>
     <row r="115" spans="1:99" x14ac:dyDescent="0.3">
@@ -7554,19 +7720,19 @@
         <v>8</v>
       </c>
       <c r="CK115" s="1" t="str">
-        <v>Joachim</v>
+        <v>Tom</v>
       </c>
       <c r="CL115" s="1" t="str">
-        <v>5.890</v>
+        <v>5.876</v>
       </c>
       <c r="CM115" s="1">
-        <v>109</v>
+        <v>331</v>
       </c>
       <c r="CT115" s="1" t="str">
         <v>Jules</v>
       </c>
       <c r="CU115" s="1">
-        <v>5.7555555555555555</v>
+        <v>5.7119205298013247</v>
       </c>
     </row>
     <row r="116" spans="1:99" x14ac:dyDescent="0.3">
@@ -7656,10 +7822,10 @@
         <v>Jules</v>
       </c>
       <c r="CL116" s="1" t="str">
-        <v>5.756</v>
+        <v>5.712</v>
       </c>
       <c r="CM116" s="1">
-        <v>270</v>
+        <v>302</v>
       </c>
       <c r="CT116" s="1" t="str">
         <v>Mehdi</v>
@@ -7757,10 +7923,10 @@
         <v>426</v>
       </c>
       <c r="CT117" s="1" t="str">
-        <v>Achille</v>
+        <v>Damien</v>
       </c>
       <c r="CU117" s="1">
-        <v>5.4065138721351023</v>
+        <v>5.4432855280312911</v>
       </c>
     </row>
     <row r="118" spans="1:99" x14ac:dyDescent="0.3">
@@ -7843,19 +8009,19 @@
         <v>11</v>
       </c>
       <c r="CK118" s="1" t="str">
-        <v>Hugo</v>
+        <v>ethan</v>
       </c>
       <c r="CL118" s="1" t="str">
-        <v>5.657</v>
+        <v>5.500</v>
       </c>
       <c r="CM118" s="1">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="CT118" s="1" t="str">
-        <v>Damien</v>
+        <v>Achille</v>
       </c>
       <c r="CU118" s="1">
-        <v>5.3861517976031958</v>
+        <v>5.4065138721351023</v>
       </c>
     </row>
     <row r="119" spans="1:99" x14ac:dyDescent="0.3">
@@ -7934,13 +8100,13 @@
         <v>12</v>
       </c>
       <c r="CK119" s="1" t="str">
-        <v>Achille</v>
+        <v>Damien</v>
       </c>
       <c r="CL119" s="1" t="str">
-        <v>5.407</v>
+        <v>5.443</v>
       </c>
       <c r="CM119" s="1">
-        <v>829</v>
+        <v>767</v>
       </c>
       <c r="CT119" s="1" t="str">
         <v>Joey</v>
@@ -8030,25 +8196,25 @@
       </c>
       <c r="CH120" s="1">
         <f>AVERAGE(C1:CD1)</f>
-        <v>5.151661271313662</v>
+        <v>5.1918171658336769</v>
       </c>
       <c r="CJ120" s="1">
         <v>13</v>
       </c>
       <c r="CK120" s="1" t="str">
-        <v>Bruno</v>
+        <v>Achille</v>
       </c>
       <c r="CL120" s="1" t="str">
-        <v>5.400</v>
+        <v>5.407</v>
       </c>
       <c r="CM120" s="1">
-        <v>20</v>
+        <v>829</v>
       </c>
       <c r="CT120" s="1" t="str">
-        <v>Lou</v>
+        <v>Marie</v>
       </c>
       <c r="CU120" s="1">
-        <v>4.8974358974358978</v>
+        <v>4.8478260869565215</v>
       </c>
     </row>
     <row r="121" spans="1:99" x14ac:dyDescent="0.3">
@@ -8127,13 +8293,13 @@
         <v>14</v>
       </c>
       <c r="CK121" s="1" t="str">
-        <v>Damien</v>
+        <v>Bruno</v>
       </c>
       <c r="CL121" s="1" t="str">
-        <v>5.386</v>
+        <v>5.400</v>
       </c>
       <c r="CM121" s="1">
-        <v>751</v>
+        <v>20</v>
       </c>
       <c r="CT121" s="1" t="str">
         <v>Paul</v>
@@ -8222,19 +8388,19 @@
         <v>15</v>
       </c>
       <c r="CK122" s="1" t="str">
-        <v>Joey</v>
+        <v>gaspard</v>
       </c>
       <c r="CL122" s="1" t="str">
-        <v>5.192</v>
+        <v>5.342</v>
       </c>
       <c r="CM122" s="1">
-        <v>99</v>
+        <v>76</v>
       </c>
       <c r="CT122" s="1" t="str">
-        <v>Marie</v>
+        <v>Lou</v>
       </c>
       <c r="CU122" s="1">
-        <v>4.7625368731563418</v>
+        <v>4.7732558139534884</v>
       </c>
     </row>
     <row r="123" spans="1:99" x14ac:dyDescent="0.3">
@@ -8316,13 +8482,13 @@
         <v>16</v>
       </c>
       <c r="CK123" s="1" t="str">
-        <v>Lou</v>
+        <v>Hugo</v>
       </c>
       <c r="CL123" s="1" t="str">
-        <v>4.897</v>
+        <v>5.225</v>
       </c>
       <c r="CM123" s="1">
-        <v>156</v>
+        <v>40</v>
       </c>
       <c r="CT123" s="1" t="str">
         <v>Émile</v>
@@ -8419,13 +8585,13 @@
         <v>17</v>
       </c>
       <c r="CK124" s="1" t="str">
-        <v>Paul</v>
+        <v>Joey</v>
       </c>
       <c r="CL124" s="1" t="str">
-        <v>4.813</v>
+        <v>5.192</v>
       </c>
       <c r="CM124" s="1">
-        <v>32</v>
+        <v>99</v>
       </c>
       <c r="CT124" s="1" t="str">
         <v>Stanislas</v>
@@ -8517,10 +8683,10 @@
         <v>Marie</v>
       </c>
       <c r="CL125" s="1" t="str">
-        <v>4.763</v>
+        <v>4.848</v>
       </c>
       <c r="CM125" s="1">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="CT125" s="1" t="str">
         <v>Quentin</v>
@@ -8613,19 +8779,19 @@
         <v>19</v>
       </c>
       <c r="CK126" s="1" t="str">
-        <v>gaspard</v>
+        <v>Paul</v>
       </c>
       <c r="CL126" s="1" t="str">
-        <v>4.683</v>
+        <v>4.813</v>
       </c>
       <c r="CM126" s="1">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="CT126" s="1" t="str">
-        <v>Luca</v>
+        <v>Fantinne</v>
       </c>
       <c r="CU126" s="1">
-        <v>3.2315789473684209</v>
+        <v>3.6440677966101696</v>
       </c>
     </row>
     <row r="127" spans="1:99" x14ac:dyDescent="0.3">
@@ -8708,19 +8874,19 @@
         <v>20</v>
       </c>
       <c r="CK127" s="1" t="str">
-        <v>Émile</v>
+        <v>Lou</v>
       </c>
       <c r="CL127" s="1" t="str">
-        <v>4.500</v>
+        <v>4.773</v>
       </c>
       <c r="CM127" s="1">
-        <v>28</v>
+        <v>172</v>
       </c>
       <c r="CT127" s="1" t="str">
-        <v>Fantinne</v>
+        <v>Luca</v>
       </c>
       <c r="CU127" s="1">
-        <v>2.9607843137254903</v>
+        <v>3.2315789473684209</v>
       </c>
     </row>
     <row r="128" spans="1:99" x14ac:dyDescent="0.3">
@@ -8799,13 +8965,13 @@
         <v>21</v>
       </c>
       <c r="CK128" s="1" t="str">
-        <v>Stanislas</v>
+        <v>Émile</v>
       </c>
       <c r="CL128" s="1" t="str">
-        <v>4.481</v>
+        <v>4.500</v>
       </c>
       <c r="CM128" s="1">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="CT128" s="1" t="str">
         <v>Loulou</v>
@@ -8894,13 +9060,13 @@
         <v>22</v>
       </c>
       <c r="CK129" s="1" t="str">
-        <v>Quentin</v>
+        <v>Stanislas</v>
       </c>
       <c r="CL129" s="1" t="str">
-        <v>4.097</v>
+        <v>4.481</v>
       </c>
       <c r="CM129" s="1">
-        <v>93</v>
+        <v>27</v>
       </c>
       <c r="CT129" s="1" t="str">
         <v>Harrison</v>
@@ -8989,13 +9155,13 @@
         <v>23</v>
       </c>
       <c r="CK130" s="1" t="str">
-        <v>Thomas</v>
+        <v>Quentin</v>
       </c>
       <c r="CL130" s="1" t="str">
-        <v>3.357</v>
+        <v>4.097</v>
       </c>
       <c r="CM130" s="1">
-        <v>28</v>
+        <v>93</v>
       </c>
       <c r="CT130" s="1" t="str">
         <v>Pascale</v>
@@ -9064,13 +9230,13 @@
         <v>24</v>
       </c>
       <c r="CK131" s="1" t="str">
-        <v>Luca</v>
+        <v>Fantinne</v>
       </c>
       <c r="CL131" s="1" t="str">
-        <v>3.232</v>
+        <v>3.644</v>
       </c>
       <c r="CM131" s="1">
-        <v>190</v>
+        <v>59</v>
       </c>
       <c r="CT131" s="1" t="str">
         <v>Robin</v>
@@ -9155,13 +9321,13 @@
         <v>25</v>
       </c>
       <c r="CK132" s="1" t="str">
-        <v>Fantinne</v>
+        <v>Thomas</v>
       </c>
       <c r="CL132" s="1" t="str">
-        <v>2.961</v>
+        <v>3.357</v>
       </c>
       <c r="CM132" s="1">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="CT132" s="1" t="str">
         <v>Maxime_Go</v>
@@ -9250,13 +9416,13 @@
         <v>26</v>
       </c>
       <c r="CK133" s="1" t="str">
-        <v>Loulou</v>
+        <v>Luca</v>
       </c>
       <c r="CL133" s="1" t="str">
-        <v>2.427</v>
+        <v>3.232</v>
       </c>
       <c r="CM133" s="1">
-        <v>75</v>
+        <v>190</v>
       </c>
       <c r="CT133" s="1" t="str">
         <v>Maxime_Ca</v>
@@ -9337,6 +9503,18 @@
       <c r="AW134" s="15"/>
       <c r="AX134" s="15"/>
       <c r="AY134" s="15"/>
+      <c r="CJ134" s="1">
+        <v>27</v>
+      </c>
+      <c r="CK134" s="1" t="str">
+        <v>Loulou</v>
+      </c>
+      <c r="CL134" s="1" t="str">
+        <v>2.427</v>
+      </c>
+      <c r="CM134" s="1">
+        <v>75</v>
+      </c>
       <c r="CT134" s="1" t="str">
         <v>Aurélien</v>
       </c>
@@ -9818,7 +9996,7 @@
         <v>7.2050000000000001</v>
       </c>
       <c r="CW140" s="1">
-        <v>1218</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="141" spans="1:101" x14ac:dyDescent="0.3">
@@ -9993,10 +10171,10 @@
         <v>Célian</v>
       </c>
       <c r="CV142" s="1">
-        <v>6.391</v>
+        <v>6.3049999999999997</v>
       </c>
       <c r="CW142" s="1">
-        <v>376</v>
+        <v>394</v>
       </c>
     </row>
     <row r="143" spans="1:101" x14ac:dyDescent="0.3">
@@ -10160,13 +10338,13 @@
         <v>5</v>
       </c>
       <c r="CU144" s="1" t="str">
-        <v>Tom</v>
+        <v>Samuel</v>
       </c>
       <c r="CV144" s="1">
-        <v>5.9390000000000001</v>
+        <v>5.91</v>
       </c>
       <c r="CW144" s="1">
-        <v>310</v>
+        <v>211</v>
       </c>
     </row>
     <row r="145" spans="1:101" x14ac:dyDescent="0.3">
@@ -10245,13 +10423,13 @@
         <v>6</v>
       </c>
       <c r="CU145" s="1" t="str">
-        <v>Samuel</v>
+        <v>Joachim</v>
       </c>
       <c r="CV145" s="1">
-        <v>5.91</v>
+        <v>5.89</v>
       </c>
       <c r="CW145" s="1">
-        <v>211</v>
+        <v>109</v>
       </c>
     </row>
     <row r="146" spans="1:101" x14ac:dyDescent="0.3">
@@ -10330,13 +10508,13 @@
         <v>7</v>
       </c>
       <c r="CU146" s="1" t="str">
-        <v>Joachim</v>
+        <v>Tom</v>
       </c>
       <c r="CV146" s="1">
-        <v>5.89</v>
+        <v>5.8760000000000003</v>
       </c>
       <c r="CW146" s="1">
-        <v>109</v>
+        <v>331</v>
       </c>
     </row>
     <row r="147" spans="1:101" x14ac:dyDescent="0.3">
@@ -10423,10 +10601,10 @@
         <v>Jules</v>
       </c>
       <c r="CV147" s="1">
-        <v>5.7560000000000002</v>
+        <v>5.7119999999999997</v>
       </c>
       <c r="CW147" s="1">
-        <v>270</v>
+        <v>302</v>
       </c>
     </row>
     <row r="148" spans="1:101" x14ac:dyDescent="0.3">
@@ -10598,13 +10776,13 @@
         <v>10</v>
       </c>
       <c r="CU149" s="1" t="str">
-        <v>Achille</v>
+        <v>Damien</v>
       </c>
       <c r="CV149" s="1">
-        <v>5.407</v>
+        <v>5.4429999999999996</v>
       </c>
       <c r="CW149" s="1">
-        <v>829</v>
+        <v>767</v>
       </c>
     </row>
     <row r="150" spans="1:101" x14ac:dyDescent="0.3">
@@ -10683,13 +10861,13 @@
         <v>11</v>
       </c>
       <c r="CU150" s="1" t="str">
-        <v>Damien</v>
+        <v>Achille</v>
       </c>
       <c r="CV150" s="1">
-        <v>5.3860000000000001</v>
+        <v>5.407</v>
       </c>
       <c r="CW150" s="1">
-        <v>751</v>
+        <v>829</v>
       </c>
     </row>
     <row r="151" spans="1:101" x14ac:dyDescent="0.3">
@@ -10849,13 +11027,13 @@
         <v>13</v>
       </c>
       <c r="CU152" s="1" t="str">
-        <v>Lou</v>
+        <v>Marie</v>
       </c>
       <c r="CV152" s="1">
-        <v>4.8970000000000002</v>
+        <v>4.8479999999999999</v>
       </c>
       <c r="CW152" s="1">
-        <v>156</v>
+        <v>345</v>
       </c>
     </row>
     <row r="153" spans="1:101" x14ac:dyDescent="0.3">
@@ -11023,13 +11201,13 @@
         <v>15</v>
       </c>
       <c r="CU154" s="1" t="str">
-        <v>Marie</v>
+        <v>Lou</v>
       </c>
       <c r="CV154" s="1">
-        <v>4.7629999999999999</v>
+        <v>4.7729999999999997</v>
       </c>
       <c r="CW154" s="1">
-        <v>339</v>
+        <v>172</v>
       </c>
     </row>
     <row r="155" spans="1:101" x14ac:dyDescent="0.3">
@@ -11371,13 +11549,13 @@
         <v>19</v>
       </c>
       <c r="CU158" s="1" t="str">
-        <v>Luca</v>
+        <v>Fantinne</v>
       </c>
       <c r="CV158" s="1">
-        <v>3.2320000000000002</v>
+        <v>3.6440000000000001</v>
       </c>
       <c r="CW158" s="1">
-        <v>190</v>
+        <v>59</v>
       </c>
     </row>
     <row r="159" spans="1:101" x14ac:dyDescent="0.3">
@@ -11460,13 +11638,13 @@
         <v>20</v>
       </c>
       <c r="CU159" s="1" t="str">
-        <v>Fantinne</v>
+        <v>Luca</v>
       </c>
       <c r="CV159" s="1">
-        <v>2.9609999999999999</v>
+        <v>3.2320000000000002</v>
       </c>
       <c r="CW159" s="1">
-        <v>51</v>
+        <v>190</v>
       </c>
     </row>
     <row r="160" spans="1:101" x14ac:dyDescent="0.3">
@@ -12007,17 +12185,17 @@
         <v>Boris</v>
       </c>
       <c r="CU166" s="1">
-        <v>7.2048440065681447</v>
+        <v>7.2051597051597049</v>
       </c>
       <c r="CV166" s="1">
-        <v>1218</v>
+        <v>1221</v>
       </c>
       <c r="CY166" s="1" t="str" cm="1">
         <f t="array" ref="CY166:CZ186">_xlfn.LET(  _xlpm.noms, TRANSPOSE(INDEX(C9:BF9,_xlfn.SEQUENCE(1,COLUMNS(C9:BF9)/2,1,2))),_xlpm.moy,  TRANSPOSE(INDEX(C1:BF1,,_xlfn.SEQUENCE(1,COLUMNS(C1:BF1)/2,1,2))),_xlpm.ok, ISNUMBER(_xlpm.moy),_xlfn._xlws.SORT(CHOOSE({1,2}, _xlfn._xlws.FILTER(_xlpm.noms, _xlpm.ok), _xlfn._xlws.FILTER(_xlpm.moy, _xlpm.ok)), 2, -1))</f>
         <v>Boris</v>
       </c>
       <c r="CZ166" s="1">
-        <v>7.2048440065681447</v>
+        <v>7.2051597051597049</v>
       </c>
     </row>
     <row r="167" spans="1:104" x14ac:dyDescent="0.3">
@@ -12184,16 +12362,16 @@
         <v>Célian</v>
       </c>
       <c r="CU168" s="1">
-        <v>6.3909574468085104</v>
+        <v>6.3045685279187813</v>
       </c>
       <c r="CV168" s="1">
-        <v>376</v>
+        <v>394</v>
       </c>
       <c r="CY168" s="1" t="str">
         <v>Célian</v>
       </c>
       <c r="CZ168" s="1">
-        <v>6.3909574468085104</v>
+        <v>6.3045685279187813</v>
       </c>
     </row>
     <row r="169" spans="1:104" x14ac:dyDescent="0.3">
@@ -12357,19 +12535,19 @@
       <c r="AX170" s="15"/>
       <c r="AY170" s="15"/>
       <c r="CT170" s="1" t="str">
-        <v>Tom</v>
+        <v>Samuel</v>
       </c>
       <c r="CU170" s="1">
-        <v>5.9387096774193546</v>
+        <v>5.9099526066350707</v>
       </c>
       <c r="CV170" s="1">
-        <v>310</v>
+        <v>211</v>
       </c>
       <c r="CY170" s="1" t="str">
-        <v>Tom</v>
+        <v>Samuel</v>
       </c>
       <c r="CZ170" s="1">
-        <v>5.9387096774193546</v>
+        <v>5.9099526066350707</v>
       </c>
     </row>
     <row r="171" spans="1:104" x14ac:dyDescent="0.3">
@@ -12445,19 +12623,19 @@
       <c r="AX171" s="15"/>
       <c r="AY171" s="15"/>
       <c r="CT171" s="1" t="str">
-        <v>Samuel</v>
+        <v>Joachim</v>
       </c>
       <c r="CU171" s="1">
-        <v>5.9099526066350707</v>
+        <v>5.8899082568807337</v>
       </c>
       <c r="CV171" s="1">
-        <v>211</v>
+        <v>109</v>
       </c>
       <c r="CY171" s="1" t="str">
-        <v>Samuel</v>
+        <v>Joachim</v>
       </c>
       <c r="CZ171" s="1">
-        <v>5.9099526066350707</v>
+        <v>5.8899082568807337</v>
       </c>
     </row>
     <row r="172" spans="1:104" x14ac:dyDescent="0.3">
@@ -12533,19 +12711,19 @@
       <c r="AX172" s="15"/>
       <c r="AY172" s="15"/>
       <c r="CT172" s="1" t="str">
-        <v>Joachim</v>
+        <v>Tom</v>
       </c>
       <c r="CU172" s="1">
-        <v>5.8899082568807337</v>
+        <v>5.8761329305135952</v>
       </c>
       <c r="CV172" s="1">
-        <v>109</v>
+        <v>331</v>
       </c>
       <c r="CY172" s="1" t="str">
-        <v>Joachim</v>
+        <v>Tom</v>
       </c>
       <c r="CZ172" s="1">
-        <v>5.8899082568807337</v>
+        <v>5.8761329305135952</v>
       </c>
     </row>
     <row r="173" spans="1:104" x14ac:dyDescent="0.3">
@@ -12628,16 +12806,16 @@
         <v>Jules</v>
       </c>
       <c r="CU173" s="1">
-        <v>5.7555555555555555</v>
+        <v>5.7119205298013247</v>
       </c>
       <c r="CV173" s="1">
-        <v>270</v>
+        <v>302</v>
       </c>
       <c r="CY173" s="1" t="str">
         <v>Jules</v>
       </c>
       <c r="CZ173" s="1">
-        <v>5.7555555555555555</v>
+        <v>5.7119205298013247</v>
       </c>
     </row>
     <row r="174" spans="1:104" x14ac:dyDescent="0.3">
@@ -12736,19 +12914,19 @@
         <v>26</v>
       </c>
       <c r="CT175" s="1" t="str">
-        <v>Achille</v>
+        <v>Damien</v>
       </c>
       <c r="CU175" s="1">
-        <v>5.4065138721351023</v>
+        <v>5.4432855280312911</v>
       </c>
       <c r="CV175" s="1">
-        <v>829</v>
+        <v>767</v>
       </c>
       <c r="CY175" s="1" t="str">
-        <v>Achille</v>
+        <v>Damien</v>
       </c>
       <c r="CZ175" s="1">
-        <v>5.4065138721351023</v>
+        <v>5.4432855280312911</v>
       </c>
     </row>
     <row r="176" spans="1:104" x14ac:dyDescent="0.3">
@@ -12783,19 +12961,19 @@
         <v>11</v>
       </c>
       <c r="CT176" s="1" t="str">
-        <v>Damien</v>
+        <v>Achille</v>
       </c>
       <c r="CU176" s="1">
-        <v>5.3861517976031958</v>
+        <v>5.4065138721351023</v>
       </c>
       <c r="CV176" s="1">
-        <v>751</v>
+        <v>829</v>
       </c>
       <c r="CY176" s="1" t="str">
-        <v>Damien</v>
+        <v>Achille</v>
       </c>
       <c r="CZ176" s="1">
-        <v>5.3861517976031958</v>
+        <v>5.4065138721351023</v>
       </c>
     </row>
     <row r="177" spans="1:104" x14ac:dyDescent="0.3">
@@ -12877,19 +13055,19 @@
         <v>8</v>
       </c>
       <c r="CT178" s="1" t="str">
-        <v>Paul</v>
+        <v>Marie</v>
       </c>
       <c r="CU178" s="1">
-        <v>4.8125</v>
+        <v>4.8478260869565215</v>
       </c>
       <c r="CV178" s="1">
-        <v>32</v>
+        <v>345</v>
       </c>
       <c r="CY178" s="1" t="str">
-        <v>Lou</v>
+        <v>Marie</v>
       </c>
       <c r="CZ178" s="1">
-        <v>4.8974358974358978</v>
+        <v>4.8478260869565215</v>
       </c>
     </row>
     <row r="179" spans="1:104" x14ac:dyDescent="0.3">
@@ -12924,13 +13102,13 @@
         <v>9</v>
       </c>
       <c r="CT179" s="1" t="str">
-        <v>Marie</v>
+        <v>Paul</v>
       </c>
       <c r="CU179" s="1">
-        <v>4.7625368731563418</v>
+        <v>4.8125</v>
       </c>
       <c r="CV179" s="1">
-        <v>339</v>
+        <v>32</v>
       </c>
       <c r="CY179" s="1" t="str">
         <v>Paul</v>
@@ -12980,10 +13158,10 @@
         <v>28</v>
       </c>
       <c r="CY180" s="1" t="str">
-        <v>Marie</v>
+        <v>Lou</v>
       </c>
       <c r="CZ180" s="1">
-        <v>4.7625368731563418</v>
+        <v>4.7732558139534884</v>
       </c>
     </row>
     <row r="181" spans="1:104" x14ac:dyDescent="0.3">
@@ -13065,13 +13243,13 @@
         <v>13</v>
       </c>
       <c r="CT182" s="1" t="str">
-        <v>Luca</v>
+        <v>Fantinne</v>
       </c>
       <c r="CU182" s="1">
-        <v>3.2315789473684209</v>
+        <v>3.6440677966101696</v>
       </c>
       <c r="CV182" s="1">
-        <v>190</v>
+        <v>59</v>
       </c>
       <c r="CY182" s="1" t="str">
         <v>Stanislas</v>
@@ -13112,13 +13290,13 @@
         <v>9</v>
       </c>
       <c r="CT183" s="1" t="str">
-        <v>Fantinne</v>
+        <v>Luca</v>
       </c>
       <c r="CU183" s="1">
-        <v>2.9607843137254903</v>
+        <v>3.2315789473684209</v>
       </c>
       <c r="CV183" s="1">
-        <v>51</v>
+        <v>190</v>
       </c>
       <c r="CY183" s="1" t="str">
         <v>Quentin</v>
@@ -13168,10 +13346,10 @@
         <v>75</v>
       </c>
       <c r="CY184" s="1" t="str">
-        <v>Luca</v>
+        <v>Fantinne</v>
       </c>
       <c r="CZ184" s="1">
-        <v>3.2315789473684209</v>
+        <v>3.6440677966101696</v>
       </c>
     </row>
     <row r="185" spans="1:104" x14ac:dyDescent="0.3">
@@ -13206,10 +13384,10 @@
         <v>13</v>
       </c>
       <c r="CY185" s="1" t="str">
-        <v>Fantinne</v>
+        <v>Luca</v>
       </c>
       <c r="CZ185" s="1">
-        <v>2.9607843137254903</v>
+        <v>3.2315789473684209</v>
       </c>
     </row>
     <row r="186" spans="1:104" x14ac:dyDescent="0.3">
@@ -13287,18 +13465,18 @@
     <sortCondition descending="1" ref="B176:B187"/>
   </sortState>
   <mergeCells count="40">
-    <mergeCell ref="AY9:AZ9"/>
-    <mergeCell ref="AA9:AB9"/>
-    <mergeCell ref="AC9:AD9"/>
-    <mergeCell ref="AE9:AF9"/>
-    <mergeCell ref="AK9:AL9"/>
-    <mergeCell ref="AI9:AJ9"/>
-    <mergeCell ref="AG9:AH9"/>
-    <mergeCell ref="AM9:AN9"/>
-    <mergeCell ref="AO9:AP9"/>
-    <mergeCell ref="AQ9:AR9"/>
-    <mergeCell ref="AS9:AT9"/>
-    <mergeCell ref="AU9:AV9"/>
+    <mergeCell ref="BW9:BX9"/>
+    <mergeCell ref="BY9:BZ9"/>
+    <mergeCell ref="CA9:CB9"/>
+    <mergeCell ref="CC9:CD9"/>
+    <mergeCell ref="BG9:BH9"/>
+    <mergeCell ref="BI9:BJ9"/>
+    <mergeCell ref="BK9:BL9"/>
+    <mergeCell ref="BM9:BN9"/>
+    <mergeCell ref="BO9:BP9"/>
+    <mergeCell ref="BQ9:BR9"/>
+    <mergeCell ref="BS9:BT9"/>
+    <mergeCell ref="BU9:BV9"/>
     <mergeCell ref="BA9:BB9"/>
     <mergeCell ref="BC9:BD9"/>
     <mergeCell ref="BE9:BF9"/>
@@ -13315,115 +13493,129 @@
     <mergeCell ref="U9:V9"/>
     <mergeCell ref="W9:X9"/>
     <mergeCell ref="AW9:AX9"/>
-    <mergeCell ref="BW9:BX9"/>
-    <mergeCell ref="BY9:BZ9"/>
-    <mergeCell ref="CA9:CB9"/>
-    <mergeCell ref="CC9:CD9"/>
-    <mergeCell ref="BG9:BH9"/>
-    <mergeCell ref="BI9:BJ9"/>
-    <mergeCell ref="BK9:BL9"/>
-    <mergeCell ref="BM9:BN9"/>
-    <mergeCell ref="BO9:BP9"/>
-    <mergeCell ref="BQ9:BR9"/>
-    <mergeCell ref="BS9:BT9"/>
-    <mergeCell ref="BU9:BV9"/>
+    <mergeCell ref="AY9:AZ9"/>
+    <mergeCell ref="AA9:AB9"/>
+    <mergeCell ref="AC9:AD9"/>
+    <mergeCell ref="AE9:AF9"/>
+    <mergeCell ref="AK9:AL9"/>
+    <mergeCell ref="AI9:AJ9"/>
+    <mergeCell ref="AG9:AH9"/>
+    <mergeCell ref="AM9:AN9"/>
+    <mergeCell ref="AO9:AP9"/>
+    <mergeCell ref="AQ9:AR9"/>
+    <mergeCell ref="AS9:AT9"/>
+    <mergeCell ref="AU9:AV9"/>
   </mergeCells>
   <conditionalFormatting sqref="C1 E1 G1 I1 K1 M1 O1 Q1 S1 U1 W1 Y1 AA1 AC1 AE1 AG1 AI1 AK1 AM1 AO1 AQ1 AS1 AU1 AW1 AY1 BA1 BC1 BE1 BG1 BI1 BK1 BM1 BO1 BQ1 BS1 BU1 BW1 BY1 CA1 CC1 C9:AM9 AO9 AQ9 AS9 AU9 AW9 AY9 BA9 BC9 BE9 BG9 BI9 BK9 BM9 BO9 BQ9 BS9 BU9 BW9 BY9 CA9 CC9">
-    <cfRule type="expression" dxfId="24" priority="41" stopIfTrue="1">
+    <cfRule type="expression" dxfId="28" priority="41" stopIfTrue="1">
       <formula>NOT(OR("/"=C$1,AVERAGE($C$1:$CD$1)&lt;C$1,SMALL($C$1:$CD$1,1)=C$1,SMALL($C$1:$CD$1,2)=C$1,SMALL($C$1:$CD$1,3)=C$1,LARGE($C$1:$CD$1,1)=C$1,LARGE($C$1:$CD$1,2)=C$1,LARGE($C$1:$CD$1,3)=C$1))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="23" priority="43" stopIfTrue="1">
+    <cfRule type="expression" dxfId="27" priority="43" stopIfTrue="1">
       <formula>("/"=C$1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="44" stopIfTrue="1">
+    <cfRule type="expression" dxfId="26" priority="44" stopIfTrue="1">
       <formula>NOT(OR("/"=C$1,AVERAGE($C$1:$CD$1)&gt;C$1,SMALL($C$1:$CD$1,1)=C$1,SMALL($C$1:$CD$1,2)=C$1,SMALL($C$1:$CD$1,3)=C$1,LARGE($C$1:$CD$1,1)=C$1,LARGE($C$1:$CD$1,2)=C$1,LARGE($C$1:$CD$1,3)=C$1))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="82" stopIfTrue="1">
+    <cfRule type="expression" dxfId="25" priority="82" stopIfTrue="1">
       <formula>SMALL($C$1:$CD$1,3)=C$1</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="84" stopIfTrue="1">
+    <cfRule type="expression" dxfId="24" priority="84" stopIfTrue="1">
       <formula>SMALL($C$1:$CD$1,1)=C$1</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="19" priority="87" stopIfTrue="1">
+    <cfRule type="expression" dxfId="23" priority="87" stopIfTrue="1">
       <formula>MAX($C$1:$CD$1)=C$1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1 E1 G1 I1 K1 M1 O1 Q1 S1 U1 W1 Y1 AA1 AC1 AE1 AG1 AI1 AK1 AM1 AO1 AQ1 AS1 AU1 AW1 AY1 BA1 BC1 BE1 BG1 BI1 BK1 BM1 BO1 BQ1 BS1 BU1 BW1 BY1 CA1 CC1 C9:AM9 AO9 AQ9 AS9 AU9 AW9 AY9 BA9 BC9 BE9 BG9 BI9 BK9 BM9 BO9 BQ9 BS9 BU9 BW9">
-    <cfRule type="expression" dxfId="18" priority="83" stopIfTrue="1">
+    <cfRule type="expression" dxfId="22" priority="83" stopIfTrue="1">
       <formula>SMALL($C$1:$CD$1,2)=C$1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1 E1 G1 I1 K1 M1 O1 Q1 S1 U1 W1 Y1 AA1 AC1 AE1 AG1 AI1 AK1 AM1 AO1 AQ1 AS1 AU1 AW1 AY1 BA1 BC1 BE1 BG1 BI1 BK1 BM1 BO1 BQ1 BS1 BU1 BW1 BY1 CA1 CC1 C9:AM9 AO9 AQ9 AS9 AU9 AW9 AY9 BA9 BC9 BE9 BG9 BI9 BK9 BM9 BO9 BQ9 BS9 BU9 BY9 CA9 CC9 BW9">
-    <cfRule type="expression" dxfId="17" priority="86" stopIfTrue="1">
+    <cfRule type="expression" dxfId="21" priority="86" stopIfTrue="1">
       <formula>LARGE($C$1:$CD$1,2)=C$1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1 E1 G1 I1 K1 M1 O1 Q1 S1 U1 W1 Y1 AA1 AC1 AE1 AG1 AI1 AK1 AM1 AO1 AQ1 AS1 AU1 AW1 AY1 BA1 BC1 BE1 BG1 BI1 BK1 BM1 BO1 BQ1 BS1 BU1 BW1 BY1 CA1 CC1 C9:AM9 AO9 AQ9 AS9 AU9 AW9 AY9 BA9 BC9 BE9 BG9 BI9 BK9 BM9 BO9 BQ9 BS9 BU9 BY9 CA9 CC9">
-    <cfRule type="expression" dxfId="16" priority="85" stopIfTrue="1">
+    <cfRule type="expression" dxfId="20" priority="85" stopIfTrue="1">
       <formula>LARGE($C$1:$CD$1,3)=C$1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G10:G94 I10:I94 K10:K94 M10:M94 C10:C187 E10:E187 O10:O187 Q10:Q187 S10:S187 U10:U187 W10:W187 Y10:Y187 AA10:AA187 AC10:AC187 AE10:AE187 AG10:AG187 AI10:AI187 AK10:AK187 AM10:AM187 AO10:AO187 AQ10:AQ187 AS10:AS187 AU10:AU187 AW10:AW187 AY10:AY187 BA10:BA187 BC10:BC187 BE10:BE187 G96:G187 I96:I187 K96:K187 M96:M187">
-    <cfRule type="expression" dxfId="15" priority="26" stopIfTrue="1">
+  <conditionalFormatting sqref="G10:G94 I10:I94 K10:K94 M10:M94 C10:C187 E10:E187 O10:O187 Q10:Q187 U10:U187 W10:W187 Y10:Y187 AA10:AA187 AC10:AC187 AE10:AE187 AG10:AG187 AI10:AI187 AK10:AK187 AM10:AM187 AO10:AO187 AQ10:AQ187 AS10:AS187 AU10:AU187 AW10:AW187 AY10:AY187 BA10:BA187 BC10:BC187 BE10:BE187 G96:G187 I96:I187 K96:K187 M96:M187 S10:S14 S17:S187">
+    <cfRule type="expression" dxfId="19" priority="26" stopIfTrue="1">
       <formula>(C10/D10)&gt;12</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="28" stopIfTrue="1">
+    <cfRule type="expression" dxfId="18" priority="28" stopIfTrue="1">
       <formula>(C10/D10)&lt;-2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="30" stopIfTrue="1">
+    <cfRule type="expression" dxfId="17" priority="30" stopIfTrue="1">
       <formula>(C10/D10)&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="32" stopIfTrue="1">
+    <cfRule type="expression" dxfId="16" priority="32" stopIfTrue="1">
       <formula>(C10/D10)&gt;10</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H10:H94 J10:J94 L10:L94 N10:N94 D10:D187 F10:F187 P10:P187 R10:R187 T10:T187 V10:V187 X10:X187 Z10:Z187 AB10:AB187 AD10:AD187 AF10:AF187 AH10:AH187 AJ10:AJ187 AL10:AL187 AN10:AN187 AP10:AP187 AR10:AR187 AT10:AT187 AV10:AV187 AX10:AX187 AZ10:AZ187 BB10:BB187 BD10:BD187 BF10:BF187 H96:H187 J96:J187 L96:L187 N96:N187">
-    <cfRule type="expression" dxfId="11" priority="25" stopIfTrue="1">
+  <conditionalFormatting sqref="H10:H94 J10:J94 L10:L94 N10:N94 D10:D187 F10:F187 P10:P187 R10:R187 V10:V187 X10:X187 Z10:Z187 AB10:AB187 AD10:AD187 AF10:AF187 AH10:AH187 AJ10:AJ187 AL10:AL187 AN10:AN187 AP10:AP187 AR10:AR187 AT10:AT187 AV10:AV187 AX10:AX187 AZ10:AZ187 BB10:BB187 BD10:BD187 BF10:BF187 H96:H187 J96:J187 L96:L187 N96:N187 T10:T187">
+    <cfRule type="expression" dxfId="15" priority="25" stopIfTrue="1">
       <formula>(C10/D10)&gt;12</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="27" stopIfTrue="1">
+    <cfRule type="expression" dxfId="14" priority="27" stopIfTrue="1">
       <formula>(C10/D10)&lt;-2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="29" stopIfTrue="1">
+    <cfRule type="expression" dxfId="13" priority="29" stopIfTrue="1">
       <formula>(C10/D10)&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="31" stopIfTrue="1">
+    <cfRule type="expression" dxfId="12" priority="31" stopIfTrue="1">
       <formula>(C10/D10)&gt;10</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="CM108:CM136">
-    <cfRule type="cellIs" dxfId="7" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="11" priority="3" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="4" operator="between">
+    <cfRule type="cellIs" dxfId="10" priority="4" operator="between">
       <formula>20</formula>
       <formula>50</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="5" operator="between">
+    <cfRule type="cellIs" dxfId="9" priority="5" operator="between">
       <formula>50</formula>
       <formula>100</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="6" operator="between">
+    <cfRule type="cellIs" dxfId="8" priority="6" operator="between">
       <formula>100</formula>
       <formula>250</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="7" operator="between">
+    <cfRule type="cellIs" dxfId="7" priority="7" operator="between">
       <formula>250</formula>
       <formula>500</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="8" operator="between">
+    <cfRule type="cellIs" dxfId="6" priority="8" operator="between">
       <formula>500</formula>
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="CR108:CR129">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="between">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="between">
       <formula>1</formula>
       <formula>10</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="between">
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="between">
       <formula>10</formula>
       <formula>20</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S16">
+    <cfRule type="expression" dxfId="3" priority="92" stopIfTrue="1">
+      <formula>(S16/T15)&gt;12</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="93" stopIfTrue="1">
+      <formula>(S16/T15)&lt;-2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="94" stopIfTrue="1">
+      <formula>(S16/T15)&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="95" stopIfTrue="1">
+      <formula>(S16/T15)&gt;10</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.70000000000000007" right="0.70000000000000007" top="0.75" bottom="0.75" header="0.30000000000000004" footer="0.30000000000000004"/>
@@ -13433,7 +13625,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22D977F6-AD3F-47F0-926D-61192148887D}">
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.5546875" style="1"/>
@@ -13467,7 +13659,7 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="1" cm="1">
-        <f t="array" ref="A2:D27">_xlfn.ANCHORARRAY('All stat'!CJ108)</f>
+        <f t="array" ref="A2:D28">_xlfn.ANCHORARRAY('All stat'!CJ108)</f>
         <v>1</v>
       </c>
       <c r="B2" s="1" t="str">
@@ -13477,7 +13669,7 @@
         <v>7.205</v>
       </c>
       <c r="D2" s="1">
-        <v>1218</v>
+        <v>1221</v>
       </c>
       <c r="F2" t="str">
         <v>nombre de parties</v>
@@ -13540,10 +13732,10 @@
         <v>Célian</v>
       </c>
       <c r="C5" s="1" t="str">
-        <v>6.391</v>
+        <v>6.305</v>
       </c>
       <c r="D5" s="1">
-        <v>376</v>
+        <v>394</v>
       </c>
       <c r="F5" t="str">
         <v>entre 20 et 50</v>
@@ -13585,13 +13777,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="str">
-        <v>Tom</v>
+        <v>Samuel</v>
       </c>
       <c r="C7" s="1" t="str">
-        <v>5.939</v>
+        <v>5.910</v>
       </c>
       <c r="D7" s="1">
-        <v>310</v>
+        <v>211</v>
       </c>
       <c r="F7" t="str">
         <v>entre 100 et 250</v>
@@ -13609,13 +13801,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="str">
-        <v>Samuel</v>
+        <v>Joachim</v>
       </c>
       <c r="C8" s="1" t="str">
-        <v>5.910</v>
+        <v>5.890</v>
       </c>
       <c r="D8" s="1">
-        <v>211</v>
+        <v>109</v>
       </c>
       <c r="F8" t="str">
         <v>entre 250 et 500</v>
@@ -13633,13 +13825,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="str">
-        <v>Joachim</v>
+        <v>Tom</v>
       </c>
       <c r="C9" s="1" t="str">
-        <v>5.890</v>
+        <v>5.876</v>
       </c>
       <c r="D9" s="1">
-        <v>109</v>
+        <v>331</v>
       </c>
       <c r="F9" t="str">
         <v>entre 500 et 1000</v>
@@ -13660,10 +13852,10 @@
         <v>Jules</v>
       </c>
       <c r="C10" s="1" t="str">
-        <v>5.756</v>
+        <v>5.712</v>
       </c>
       <c r="D10" s="1">
-        <v>270</v>
+        <v>302</v>
       </c>
       <c r="F10" t="str">
         <v>plus de 1000</v>
@@ -13695,13 +13887,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="str">
-        <v>Hugo</v>
+        <v>ethan</v>
       </c>
       <c r="C12" s="1" t="str">
-        <v>5.657</v>
+        <v>5.500</v>
       </c>
       <c r="D12" s="1">
-        <v>35</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
@@ -13709,20 +13901,20 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="str">
-        <v>Achille</v>
+        <v>Damien</v>
       </c>
       <c r="C13" s="1" t="str">
-        <v>5.407</v>
+        <v>5.443</v>
       </c>
       <c r="D13" s="1">
-        <v>829</v>
+        <v>767</v>
       </c>
       <c r="F13" t="s">
         <v>102</v>
       </c>
       <c r="G13">
         <f>AVERAGE('All stat'!C1:CD1)</f>
-        <v>5.151661271313662</v>
+        <v>5.1918171658336769</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
@@ -13730,13 +13922,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="str">
-        <v>Bruno</v>
+        <v>Achille</v>
       </c>
       <c r="C14" s="1" t="str">
-        <v>5.400</v>
+        <v>5.407</v>
       </c>
       <c r="D14" s="1">
-        <v>20</v>
+        <v>829</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
@@ -13744,13 +13936,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="str">
-        <v>Damien</v>
+        <v>Bruno</v>
       </c>
       <c r="C15" s="1" t="str">
-        <v>5.386</v>
+        <v>5.400</v>
       </c>
       <c r="D15" s="1">
-        <v>751</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
@@ -13758,13 +13950,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="str">
-        <v>Joey</v>
+        <v>gaspard</v>
       </c>
       <c r="C16" s="1" t="str">
-        <v>5.192</v>
+        <v>5.342</v>
       </c>
       <c r="D16" s="1">
-        <v>99</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
@@ -13772,13 +13964,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="str">
-        <v>Lou</v>
+        <v>Hugo</v>
       </c>
       <c r="C17" s="1" t="str">
-        <v>4.897</v>
+        <v>5.225</v>
       </c>
       <c r="D17" s="1">
-        <v>156</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
@@ -13786,13 +13978,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="str">
-        <v>Paul</v>
+        <v>Joey</v>
       </c>
       <c r="C18" s="1" t="str">
-        <v>4.813</v>
+        <v>5.192</v>
       </c>
       <c r="D18" s="1">
-        <v>32</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
@@ -13803,10 +13995,10 @@
         <v>Marie</v>
       </c>
       <c r="C19" s="1" t="str">
-        <v>4.763</v>
+        <v>4.848</v>
       </c>
       <c r="D19" s="1">
-        <v>339</v>
+        <v>345</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
@@ -13814,13 +14006,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="str">
-        <v>gaspard</v>
+        <v>Paul</v>
       </c>
       <c r="C20" s="1" t="str">
-        <v>4.683</v>
+        <v>4.813</v>
       </c>
       <c r="D20" s="1">
-        <v>60</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
@@ -13828,13 +14020,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="str">
-        <v>Émile</v>
+        <v>Lou</v>
       </c>
       <c r="C21" s="1" t="str">
-        <v>4.500</v>
+        <v>4.773</v>
       </c>
       <c r="D21" s="1">
-        <v>28</v>
+        <v>172</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
@@ -13842,13 +14034,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="str">
-        <v>Stanislas</v>
+        <v>Émile</v>
       </c>
       <c r="C22" s="1" t="str">
-        <v>4.481</v>
+        <v>4.500</v>
       </c>
       <c r="D22" s="1">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
@@ -13856,13 +14048,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="str">
-        <v>Quentin</v>
+        <v>Stanislas</v>
       </c>
       <c r="C23" s="1" t="str">
-        <v>4.097</v>
+        <v>4.481</v>
       </c>
       <c r="D23" s="1">
-        <v>93</v>
+        <v>27</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
@@ -13870,13 +14062,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="str">
-        <v>Thomas</v>
+        <v>Quentin</v>
       </c>
       <c r="C24" s="1" t="str">
-        <v>3.357</v>
+        <v>4.097</v>
       </c>
       <c r="D24" s="1">
-        <v>28</v>
+        <v>93</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
@@ -13884,13 +14076,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="str">
-        <v>Luca</v>
+        <v>Fantinne</v>
       </c>
       <c r="C25" s="1" t="str">
-        <v>3.232</v>
+        <v>3.644</v>
       </c>
       <c r="D25" s="1">
-        <v>190</v>
+        <v>59</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
@@ -13898,13 +14090,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="str">
-        <v>Fantinne</v>
+        <v>Thomas</v>
       </c>
       <c r="C26" s="1" t="str">
-        <v>2.961</v>
+        <v>3.357</v>
       </c>
       <c r="D26" s="1">
-        <v>51</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
@@ -13912,12 +14104,26 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="str">
+        <v>Luca</v>
+      </c>
+      <c r="C27" s="1" t="str">
+        <v>3.232</v>
+      </c>
+      <c r="D27" s="1">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" s="1">
+        <v>27</v>
+      </c>
+      <c r="B28" s="1" t="str">
         <v>Loulou</v>
       </c>
-      <c r="C27" s="1" t="str">
+      <c r="C28" s="1" t="str">
         <v>2.427</v>
       </c>
-      <c r="D27" s="1">
+      <c r="D28" s="1">
         <v>75</v>
       </c>
     </row>
